--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -2922,8 +2922,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. The unassigned shift starts at the shop's business-hours start (there is no technician whose hours could apply).
-2. If the shop had no business hours, it would start at the 7:00 AM default.</t>
+          <t>1. The unassigned shift starts at the shop's business-hours start (there is no technician whose hours could apply).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -5519,7 +5518,7 @@
       <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
-2. At least two conflicts of different types exist (set up via/02).
+2. At least two conflicts of different types exist (for example one double-booked overlap and one Saturday shift - create them first).
 3. You are on the Schedule page.</t>
         </is>
       </c>
@@ -5862,7 +5861,8 @@
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A multi-line shift exists covering 5 lines, with some time logged.
-3. You are on the Schedule page in week view.</t>
+3. The VIN toggle in 'Filter and Display' is ON (the tooltip shows the VIN only when this toggle is on).
+4. You are on the Schedule page in week view.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
         <is>
           <t>1. Edit cannot be granted without View (the admin UI enforces or auto-selects the dependency).
 2. Delete cannot be granted without Edit.
-3. The three tiers can be enabled in dependency order, giving View ⊂ Edit ⊂ Delete.</t>
+3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4710,7 +4710,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>The modal shows a scope summary and the scheduled line(s) with labor/total figures</t>
+          <t>The modal shows a scope summary and the scheduled line(s) with number, title, hours, and status only</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4743,9 +4743,10 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1. The scope summary states what the shift covers.
-2. Exactly the 2 scheduled lines are listed (not all 4), each with its labor/total figures.
-3. This is where whole-order vs subset scope is spelled out (the grid block only says 'N Lines').</t>
+          <t>1. The 'Work Order Lines' section shows the line count and a scope summary of what the shift covers.
+2. Exactly the 2 scheduled lines are listed (not all 4), each showing its line number, title, hours, and a status pill only.
+3. No labor figures and no total dollar amount appear anywhere in the modal.
+4. This is where whole-order vs subset scope is spelled out (the grid block only says 'N Lines').</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4909,7 +4910,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>The modal offers Delete (series-aware) and Reassign actions</t>
+          <t>The modal offers a Delete (series-aware) action only - there is no Reassign action</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4936,14 +4937,14 @@
       <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Look at the modal's actions.
-2. Click Reassign and read what it offers (cancel without changing).
+2. Confirm there is no 'Reassign' action anywhere in the modal.
 3. Click Delete on a series shift and read what it asks (cancel without deleting).</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1. The modal offers a Delete action and a 'Reassign' (to another technician) action.
-2. Reassign offers choosing another technician (the full reassignment behavior has its own case).
+          <t>1. The modal offers a Delete action (a trash icon in the header) and a close (x) icon - and no other actions.
+2. There is no 'Reassign' action in the modal; reassignment is done by dragging a shift to another technician row (covered by its own case).
 3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).</t>
         </is>
       </c>
@@ -5302,39 +5303,89 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>An event does not count toward a technician's capacity bar and does not raise a conflict</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. Capacity Bars and Events are ON in View Options.
+3. A technician has a shift and, on the same day/time, an event (create both, ZZAUTOTEST).</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1. Note the day's capacity bar fill with only the shift present.
+2. Add an all-day (or long) event on the same technician and day.
+3. Look at the capacity bar again and check for any conflict on the block and in the toolbar conflict pill.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1. Adding the event does NOT change the capacity bar fill - events are not counted toward booked/available hours.
+2. The event does NOT create a double-booked or overlap conflict with the shift, and the toolbar conflict count does not increase because of it.
+3. Only shifts drive capacity and conflicts.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md §4.10 (Events), §4.11, §4.12</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
           <t>Double-booked: two work orders overlapping on the same technician at the same time are flagged</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Two different work orders have schedulable lines.
 3. You are on the Schedule page; note the toolbar conflict pill's current count.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Schedule work order 1 on a technician for a given time.
 2. Schedule work order 2 on the SAME technician overlapping the same time.
 3. Look at the two blocks and the toolbar conflict pill.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. The overlap is detected as a Double-booked conflict.
 2. A warning icon appears on the affected block(s).
@@ -5342,57 +5393,9 @@
 4. The conflict is listed in the pill's dropdown.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.11 (Double-booked)</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Weekend shift: a shift on Saturday or Sunday is flagged as a conflict</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Conflict Detection</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in on a desktop browser with Schedule: Edit.
-2. Saturday/Sunday columns are visible (View Options - Saturday and Sunday on).
-3. A schedulable work order line exists.</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>1. Drop the line onto a technician's SATURDAY cell.
-2. Look at the block and the conflict pill.</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>1. The shift is created but flagged as a Weekend shift conflict (outside working days).
-2. The warning icon appears on the block and the conflict is listed in the toolbar dropdown.</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §4.11 (Weekend shift)</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -5401,7 +5404,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Before hours: a shift starting before the working-day start is flagged</t>
+          <t>Working-day conflict: a shift on a day outside the technician's configured working days is flagged</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5420,116 +5423,167 @@
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. A technician's configured working days are known (for example Monday to Friday); Saturday/Sunday columns are visible (View Options - Saturday and Sunday on).
+3. A schedulable work order line exists.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>1. Drop the line onto that technician's cell on a day OUTSIDE their working days (for example a Saturday when the technician works Monday to Friday).
+2. Look at the block and the conflict pill.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1. The shift is created but flagged as a conflict because the day is outside the technician's configured working days (the design's reason sentence reads in the spirit of 'Scheduled on a weekend (outside Mon-Fri)').
+2. If the technician's working days DO include that day (for example Saturday hours are configured), a shift on that day is NOT flagged.
+3. The warning icon appears on the block and the conflict is listed in the toolbar dropdown.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md §4.11 (Weekend shift)</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Before hours: a shift starting before the technician's configured working-day start is flagged</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Conflict Detection</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A technician has a known working-day start (for example 8:00 AM).
 3. A shift exists for that technician.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. In day view, drag the shift so it starts BEFORE the technician's working-day start (for example 6:00 AM).
 2. Look at the block and the conflict pill.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>1. The shift is flagged as a Before hours conflict.
-2. Warning icon on the block; the conflict appears in the toolbar dropdown.</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1. The shift is flagged as a before-hours conflict (the design's reason sentence reads in the spirit of 'Starts before working hours (8:00 AM)'), measured against the technician's configured working-day start.
+2. The working-day start follows the hierarchy technician hours, then business hours, then the default.
+3. Warning icon on the block; the conflict appears in the toolbar dropdown.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.11 (Before hours)</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>After hours: a shift extending past the working-day end is flagged</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>After hours: a shift extending past the technician's configured working-day end is flagged</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A technician has a known working-day end (for example 5:00 PM).
 3. A shift exists for that technician ending before 5:00 PM.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. In day view, drag the shift's right edge so it extends PAST the working-day end (for example to 7:00 PM).
 2. Look at the block and the conflict pill.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>1. The shift is flagged as an After hours conflict.
-2. Warning icon on the block; the conflict appears in the toolbar dropdown.</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1. The shift is flagged as an after-hours conflict (the design's reason sentence reads in the spirit of 'Extends past working hours (5:00 PM)'), measured against the technician's configured working-day end.
+2. The working-day end follows the hierarchy technician hours, then business hours, then the default.
+3. Warning icon on the block; the conflict appears in the toolbar dropdown.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.11 (After hours)</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>The toolbar conflict pill shows the issue count and opens a dropdown listing the conflicts</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. At least two conflicts of different types exist (for example one double-booked overlap and one Saturday shift - create them first).
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Read the conflict pill in the grid toolbar.
 2. Click it.
 3. Read the dropdown.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The pill shows the current number of scheduling issues.
 2. Clicking opens a dropdown listing each conflict.
@@ -5537,132 +5591,132 @@
 4. Resolving a conflict (for example moving the shift) reduces the count - detection is continuous.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.11, §6 (Conflict pill)</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Clicking a conflict in the dropdown navigates to the relevant technician and day</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A conflict exists on a technician/day that is NOT currently in view (navigate the grid away first).
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Open the conflict pill's dropdown.
 2. Click the conflict entry.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. The grid navigates to the relevant technician and day.
 2. The conflicted shift is brought into view.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.11 (Clicking a conflict navigates)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Red/alarming styling is reserved for conflicts and genuine errors - never used for overtime</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. One technician is booked into OVERTIME on a day WITHOUT any conflict (more hours than their day, sequential non-overlapping shifts within working hours - use the technician's working window carefully, or observe the OT tag day).
 3. Capacity Bars are on.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Look at the overtime signals for that day ('OT' tag, amber highlights).
 2. Look at a conflicted shift for comparison.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. Overtime is signaled with the 'OT' text tag and amber tones - NOT red or alarming styling.
 2. Red/alarming styling appears only for conflicts and genuine errors.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.11 (styling rule), §4.12</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Day-column headers show a capacity bar - blue fill = aggregate booked vs total available, clamped at 100%, equal track widths</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Capacity Bars</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Capacity Bars are ON in View Options (default).
@@ -5670,346 +5724,345 @@
 4. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Look at each day column's header bar.
 2. Compare a lightly-booked day with a heavily-booked day.
 3. Compare the bars' track widths across days.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. Each day header shows a capacity bar; the blue fill represents total technician-hours booked divided by total available (sum of all techs' working hours).
 2. A more heavily booked day shows a longer blue fill; the fill never exceeds the track (clamped at 100%).
 3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.12 (Blue fill)</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>When aggregate hours exceed capacity, an amber spill extends past the track's right edge with a tick at the 100% line</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Capacity Bars</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Capacity Bars are ON.
 3. One day is booked BEYOND the team's total available hours (seed extra shifts).</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Look at that day's capacity bar.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. An amber segment extends past the right edge of the track, showing the excess.
 2. A tick marks the 100% line where the track ends.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.12 (Amber spill)</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>The 'OT' text tag appears whenever any single technician exceeds their own daily hours - even when the day's aggregate is under capacity</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Capacity Bars</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Capacity Bars are ON.
 3. On one day, a single technician is booked beyond THEIR daily hours while the team's aggregate for that day remains UNDER total capacity (other techs lightly booked).</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Look at that day's capacity bar and header.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. An 'OT' tag appears for the day even though the aggregate bar is under 100%.
 2. The tag is text, not a color-only signal.
 3. Overtime (per-technician) and capacity (aggregate) are independent signals.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.12 (OT tag), §11 (not color-only)</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Hovering a capacity bar shows a per-technician breakdown, with overtime technicians highlighted in amber</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Capacity Bars</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Capacity Bars are ON; a day exists where one technician is in overtime and others are not.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Hover over that day's capacity bar.
 2. Read the tooltip.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. A tooltip shows a per-technician breakdown: assigned hours vs that technician's capacity.
 2. The overtime technician's entry is highlighted in amber.
 3. The numbers agree with the shifts actually on the grid.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.12 (Hover tooltip)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Shift hover tooltip shows customer, unit/vehicle/VIN, date and time, technician, scope, up to 3 line names, and a progress bar</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Hover Tooltips</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
-2. A multi-line shift exists covering 5 lines, with some time logged.
-3. The VIN toggle in 'Filter and Display' is ON (the tooltip shows the VIN only when this toggle is on).
-4. You are on the Schedule page in week view.</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
+2. A multi-line shift exists covering 5 lines, with some time logged, for a unit that has a VIN.
+3. You are on the Schedule page in week view.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Hover over the shift block and wait briefly for the tooltip.
 2. Read the tooltip from top to bottom.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>1. The tooltip shows: the customer name; unit, vehicle, and VIN; the date and time range; the technician; and a scope summary ('N lines · Xh' style).
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>1. The tooltip shows: the customer name; unit, vehicle, and VIN (the tooltip shows the VIN whenever the unit has one, regardless of the 'VIN Number' toggle); the date and time range; the technician; and a scope summary ('N lines · Xh' style).
 2. The individual line names appear as a short list capped at 3, with a '+N more lines' row for the rest (here '+2 more lines'); line statuses are NOT shown.
 3. A time-logged progress bar shows logged vs estimated hours ('X / Yh' style).</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.13 (Shift tooltip)</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>A conflicted shift's tooltip shows the conflict icon and the conflict reason in amber</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Hover Tooltips</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A conflicted shift exists (for example double-booked).
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Hover the conflicted shift and read the tooltip.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. The customer name line includes the conflict icon.
 2. The conflict reason is shown in amber.</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.13 (Shift tooltip - conflict)</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Event hover tooltip shows the event name with its grey category dot, date and time range, and technician</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Hover Tooltips</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. An event exists on a technician's day.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Hover the event card and read the tooltip.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. The tooltip shows the event name with its category dot (grey for a default event).
 2. The date and time range are shown.
 3. The technician is shown.</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.13 (Event tooltip)</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Tooltips open after a short hover delay, dismiss on mouse-leave, and are read-only - clicking still opens the modal</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Hover Tooltips</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A shift exists on the grid.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Move the mouse quickly across the block without stopping - watch for tooltips.
 2. Rest the pointer on the block and wait briefly.
@@ -6017,7 +6070,7 @@
 4. Click the block.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. A quick pass does not flash tooltips - the tooltip opens only after a short hover delay (spec: roughly 300 to 500ms).
 2. It dismisses when the mouse leaves the block.
@@ -6025,145 +6078,145 @@
 4. Clicking the block opens the full detail modal as normal.</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.13 (Behavior)</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>The tooltip flips above the block or shifts horizontally to stay within the viewport - it is never clipped</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Hover Tooltips</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A multi-line shift (tall tooltip) exists near the BOTTOM edge of the viewport, and another near a horizontal edge (scroll to arrange).
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Hover the shift near the bottom edge and look at where its tooltip opens.
 2. Hover the shift near the side edge.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. When there is not enough room below, the tooltip opens ABOVE the block instead.
 2. Near a side edge, the tooltip shifts horizontally to stay fully within the viewport.
 3. No part of the tooltip is clipped off-screen.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.13 (flip/shift to stay in viewport)</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>'Today' button jumps the grid to the current date</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Grid Toolbar</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page, navigated several weeks away from today.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Click the 'Today' button in the grid toolbar.
 2. Look at the grid and the date label.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. The grid jumps to the range containing the current date (today's day, this week, or this month depending on the active view).
 2. The date label updates accordingly.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>requirements.md §6 (Today button)</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Left/right arrows navigate by day, week, or month depending on the active range, and the date label shows the current range</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Grid Toolbar</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. In week view, click the right arrow and read the date label.
 2. Switch to day view and click the right arrow.
 3. Switch to month view and click the left arrow.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>1. Week view: each arrow click moves one whole week; the label shows the week range (spec's example format: 'Jul 14 to 20, 2026').
 2. Day view: each click moves one day; the label shows that day.
@@ -6171,50 +6224,50 @@
 4. The label always matches what the grid displays.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>requirements.md §6 (Left/right arrows, Date label)</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Toolbar search fades non-matching blocks and highlights matching ones (customer, WO number, unit, technician, line name)</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Grid Toolbar</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Several shifts exist on the visible range for different customers/orders/technicians.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Type a customer name into the toolbar search; look at the grid.
 2. Clear, then search a work order number, a unit number, a technician name, and a line name in turn.
 3. Clear the search.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. Blocks that match the search are highlighted; blocks that do not match fade.
 2. All five fields match: customer name, work order number, unit number, technician name, and line name.
@@ -6222,540 +6275,541 @@
 4. Clearing the search restores all blocks to normal.</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>requirements.md §6 (Search)</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>'Filter and Display' is a checkbox-style dropdown combining department toggles, My Shifts, and VIN</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. Open the 'Filter and Display' dropdown in the grid toolbar.
 2. Read its contents and default states.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown is checkbox style and contains: a toggle per department, 'My Shifts', and 'VIN'.
 2. Defaults: all department toggles ON, 'My Shifts' OFF, 'VIN' OFF.
 3. There is no separate departments-only control - this dropdown replaces it.</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>requirements.md §6, §9 (Filter and Display dropdown)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Department toggles show or hide individual department groups in the grid</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. At least two department groups are visible in the grid.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. In 'Filter and Display', turn OFF one department's toggle.
 2. Look at the grid.
 3. Turn it back ON.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>1. The turned-off department's group (header and technician rows) disappears from the grid.
 2. Other departments are unaffected.
 3. Turning it back on restores the group.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>requirements.md §9 (Department toggles)</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>'My Shifts' filters the grid to only the current user's shifts, hiding all other technician rows</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser as a user who appears as a technician row and has at least one shift.
 2. Other technicians also have shifts on the visible range.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. In 'Filter and Display', turn ON 'My Shifts'.
 2. Look at the grid.
 3. Turn it OFF again.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>1. Only shifts assigned to you remain visible; all other technician rows and their shifts are hidden.
 2. Turning it off restores the full grid.
 3. This is a personal convenience filter only - it does not change what you are permitted to see (default is OFF, everyone's shifts visible).</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>requirements.md §9 (My Shifts), §14.3</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>The VIN toggle adds the VIN to shift blocks (day/week) and hover tooltips; the detail modal shows VIN regardless</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>The 'VIN Number' toggle adds the VIN to shift blocks (day/week) only; the hover tooltip and the detail modal always show the VIN</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A shift exists for a unit with a VIN; the VIN toggle is OFF.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>1. With VIN off: read the block, hover for the tooltip, then open the detail modal.
-2. Turn VIN ON in 'Filter and Display' and repeat.</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>1. VIN off: no VIN on the block or tooltip - but the detail modal still shows the VIN.
-2. VIN on: the VIN appears as an additional line on blocks in day and week views and in the hover tooltip.
-3. Month view blocks never show the VIN.</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>1. With 'VIN Number' off: read the block, hover for the tooltip, then open the detail modal.
+2. Turn 'VIN Number' ON in 'Filter and Display' and repeat.</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>1. 'VIN Number' off: no VIN line on the block - but the hover tooltip still shows the VIN, and the detail modal still shows the VIN.
+2. 'VIN Number' on: the VIN appears as an additional line on blocks in day and week views (and the day-view lane grows taller to fit it).
+3. The 'VIN Number' toggle affects the block only - the tooltip and the modal always show the VIN when the unit has one.
+4. Month view blocks never show the VIN.</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>requirements.md §9 (VIN), §4.4</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>'View Options' popover offers Business Hours, Capacity Bars, Events, Tech Hours, Saturday, Sunday with the spec defaults</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page with no view options changed yet (fresh state).</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. Open 'View Options' in the grid toolbar.
 2. Read each toggle and its state.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. Six toggles are offered: Business Hours, Capacity Bars, Events, Tech Hours, Saturday, Sunday.
 2. Defaults: Business Hours OFF, Capacity Bars ON, Events ON, Tech Hours OFF, Saturday ON, Sunday ON.</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>requirements.md §6, §9 (View Options popover)</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Business Hours toggle shades non-working hours in day view</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. The shop has working hours set.
 3. You are on the Schedule page in DAY view with Business Hours OFF.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. Note the timeline background outside working hours.
 2. Turn ON Business Hours in 'View Options'.
 3. Look at the timeline again.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle on, the hours OUTSIDE the working day are shaded with a grey overlay.
 2. Working hours remain unshaded.
 3. Turning it off removes the shading.</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>requirements.md §9 (Business Hours), §4.8 (Business-hours shading)</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Capacity Bars toggle shows and hides the per-day capacity bars</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Shifts exist so capacity bars have fill.
 3. You are on the Schedule page in week view with Capacity Bars ON (default).</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the bars are visible in the day column headers.
 2. Turn OFF Capacity Bars in 'View Options'.
 3. Turn it back ON.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. Off: the capacity bars disappear from the column headers.
 2. On: they reappear with the same values.</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>requirements.md §9 (Capacity Bars), §4.12</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Events toggle shows and hides event blocks on the grid</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. At least one event and one shift exist on the visible range.
 3. You are on the Schedule page with Events ON (default).</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Turn OFF Events in 'View Options'.
 2. Look at the grid.
 3. Turn it back ON.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>1. Off: event blocks disappear from the grid; shifts remain.
 2. On: the events reappear unchanged.</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>requirements.md §9 (Events)</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Tech Hours toggle displays each technician's working hours next to their name</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Technicians have configured working hours.
 3. You are on the Schedule page with Tech Hours OFF (default).</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Turn ON Tech Hours in 'View Options'.
 2. Look at the technician rows.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>1. Each technician's working hours are displayed next to their name in the row header.
 2. The hours match the technicians' configured hours.
 3. Turning it off hides the hours again.</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>requirements.md §9 (Tech Hours)</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Saturday and Sunday toggles include or exclude the weekend columns</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in WEEK view with Saturday and Sunday ON (default) - 7 columns visible.</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. Turn OFF Saturday in 'View Options'; look at the grid.
 2. Turn OFF Sunday too; look again.
 3. Turn both back ON.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>1. Saturday off: the Saturday column is removed (6 columns remain).
 2. Sunday off too: 5 weekday columns remain (Monday to Friday).
 3. Both back on: the full Monday-to-Sunday 7-column week returns.</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>requirements.md §9 (Saturday, Sunday), §3.2 (Week view)</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Dragging a shift to another technician row reassigns it - target tech added to the line's roster, source removed, with a confirmation modal</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists on technician A; note the affected line's roster.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Drag the shift block from technician A's row to technician B's row.
 2. Confirm the move in the confirmation modal.
 3. Check the line's roster on the work order.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. A confirmation modal appears for the cross-technician move.
 2. After confirming, the shift sits on technician B's row.
@@ -6763,291 +6817,291 @@
 4. A toast with Undo appears.</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Shift reassignment), §12</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>'Reassign' in the shift detail modal moves the shift to another technician</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists on technician A; its detail modal is open.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Click the 'Reassign' action.
 2. Choose technician B and confirm.
 3. Check the grid and the line's roster.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. The shift moves to technician B's row.
 2. The roster updates the same way as a drag reassignment (B added, A removed).
 3. A toast with Undo appears.</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.9 (Reassign action), §7</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Right-click on any grid cell opens a context menu with New Shift, New Event, and View Day</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. Right-click a technician's grid cell.
 2. Read the menu items.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>1. A context menu opens at the cell.
 2. It contains: 'New Shift', 'New Event', and 'View Day'.
 3. The browser's own right-click menu does not appear instead.</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Right-click context menu)</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>'View Day' in the context menu opens day view for that cell's date</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page in week or month view.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. Right-click a cell on a specific day.
 2. Choose 'View Day'.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>1. The grid switches to day view showing that cell's date.
 2. The toolbar date label and the Day/Week/Month control reflect the switch.</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Right-click context menu - View Day)</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>'New Shift' in the context menu starts shift creation for that technician and day</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Schedulable work order lines exist.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. Right-click a technician's cell and choose 'New Shift'.
 2. Complete the creation flow that opens.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. A shift-creation flow opens targeted at that technician and day.
 2. Completing it creates a shift in that cell, following the same scope/spread rules as drag-and-drop.</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Right-click context menu - New Shift), §14.1 (creation via context menu)</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Deleting a middle shift of a series asks for scope with all three options, each stating the hours returned</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists for one technician.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Delete a MIDDLE shift of the series (via the detail modal's Delete).
 2. Read the scope options offered (do not confirm yet).</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. A scope prompt appears with three options: this shift only, this and everything after, and the whole series.
 2. Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').
 3. The prompt uses routine, lightweight styling - not alarming destructive styling.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Series-aware deletion)</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>'This shift only' removes that day, the series keeps the gap, and the hours return to the estimate's remaining</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists; note the total scheduled hours.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Delete a middle shift with the 'this shift only' scope.
 2. Look at the series on the grid.
 3. Check the scheduled hours.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. Only that day's shift is removed.
 2. The series keeps the gap - the remaining shifts do NOT shuffle to close it.
@@ -7055,148 +7109,148 @@
 4. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (This shift only)</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>'This and everything after' removes from the clicked shift onward, keeping earlier shifts</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 4 shifts exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Delete the series' THIRD shift with the 'this and everything after' scope.
 2. Look at the series on the grid.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. The third shift and every later shift of the series are removed.
 2. The first two shifts remain untouched.
 3. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (This and everything after)</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>'The whole series' removes all of the series' shifts for that technician</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. The SAME work order has a series on technician A and an independent series on technician B.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Delete one of technician A's series shifts with the 'whole series' scope.
 2. Look at both technicians' rows.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. All of technician A's series shifts are removed.
 2. Technician B's independent series is untouched (the scope is per technician's series).
 3. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (The whole series - 'for that technician')</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Scope options adapt to position: first and last shifts of a series each show only two options</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Start deleting the FIRST shift of the series; read the options, then cancel.
 2. Start deleting the LAST shift; read the options, then cancel.
 3. Start deleting a MIDDLE shift; read the options, then cancel.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. First shift: two options ('this and after' would equal 'whole series', so only two are shown).
 2. Last shift: two options ('this and after' would equal 'this only').
@@ -7204,91 +7258,91 @@
 4. Cancelling leaves the series unchanged in every case.</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (options adapt to position)</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Deleting a standalone (non-series) shift does not ask for a series scope</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A single standalone shift (not part of any series) exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Watch what is asked.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
 2. The shift is deleted and an undo toast appears.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (derived - scope prompt is for series shifts)</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Every create, delete, move, and reassign action produces a toast with an Undo option</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. Schedulable lines and an existing shift are available.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Create a shift - watch for a toast.
 2. Move a shift to another day - watch for a toast.
@@ -7296,98 +7350,98 @@
 4. Delete a shift - watch for a toast.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. Each of the four actions produces a toast notification.
 2. Every toast offers an Undo option.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Toast notifications), §11 (Undo)</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>The toast persists 4 to 7 seconds, stays while the cursor is over it, and dismisses on mouse-leave</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Perform an action that shows a toast (for example move a shift) and let the toast sit untouched - time how long it stays.
 2. Trigger another toast and hold the cursor OVER it well past its normal lifetime.
 3. Move the cursor off the toast.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. Untouched, the toast persists for roughly 4 to 7 seconds before dismissing.
 2. While the cursor is over it, the toast stays (does not auto-dismiss).
 3. After the cursor leaves, it dismisses.</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Toast notifications), §11 (Undo)</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Undo restores the state before the action - for delete, move, and reassign</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A shift exists; note its technician, day, and time.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Delete the shift, then click Undo on the toast.
 2. Move the shift to another day, then click Undo.
@@ -7395,7 +7449,7 @@
 4. Check the line's roster after the reassign undo.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. Undo after delete: the shift is back exactly where it was.
 2. Undo after move: the shift returns to its original day/time.
@@ -7403,91 +7457,91 @@
 4. Every destructive action is undoable within the toast's lifetime.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>requirements.md §11 (Undo), §7</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Escape closes the topmost open modal or popover, following the stacking order</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. Open the shift detail modal, then open a popover on top of it (for example the color picker or a filter/search popover elsewhere).
 2. Press Escape once.
 3. Press Escape again.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. The FIRST Escape closes only the topmost layer (the popover), leaving the layer beneath open.
 2. The SECOND Escape closes the next layer down.
 3. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Keyboard support - Escape)</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Within the shift modal, Escape first dismisses an open sub-picker before closing the modal itself</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Open the color picker inside the modal, press Escape, and watch.
 2. Open the time picker, press Escape.
@@ -7495,50 +7549,50 @@
 4. With nothing open inside the modal, press Escape.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. Escape with the color picker open closes only the color picker - the modal stays open.
 2. Same for the time picker and the note edit.
 3. Escape with no open sub-picker closes the modal itself.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Escape within the shift modal)</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Enter confirms the active confirmable dialog (delete scope, reassign, spread, event create/edit)</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. Shifts/series and events exist to exercise the dialogs.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step for a large job, press Enter.
 2. Open the reassign dialog for a shift, choose a technician, press Enter.
@@ -7546,241 +7600,241 @@
 4. Open a series delete-scope prompt, select a scope, press Enter.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. In each confirmable dialog, Enter confirms it - equivalent to clicking its confirm action.
 2. The confirmed action takes effect (spread created / reassigned / event saved / delete applied).</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Keyboard support - Enter)</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Enter does not fire inside textareas - multiline note editing works normally</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open with the note editor active.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Type a line of note text and press Enter.
 2. Type a second line.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. Enter inserts a new line in the note - it does NOT confirm/close the dialog.
 2. The multiline note can be completed and saved normally.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Enter does not fire inside textareas)</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Modals trap focus and all interactive elements are keyboard-reachable</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Press Tab repeatedly and watch where focus goes.
 2. Continue tabbing past the last control in the modal.
 3. Close the modal and Tab through the schedule page's toolbar and sidebar controls.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. Focus moves through the modal's interactive elements with visible focus rings.
 2. Focus stays trapped inside the modal (wraps back to its first control) until the modal closes.
 3. On the page, toolbar and sidebar controls are reachable by keyboard.</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>requirements.md §11 (Accessibility)</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Blue is the default color for all shifts, including long and multi-week jobs</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Create a normal single-day shift without touching any color option.
 2. Create a multi-week series without touching any color option.
 3. Look at both on the grid.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Both the single shift and the multi-week series render in the default blue.
 2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>requirements.md §10</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Choosing a color from the shift modal's picker recolors the shift with matching background, text, and accent tones</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists; its detail modal is open.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Open the color picker in the modal.
 2. Choose a non-default color.
 3. Look at the block on the grid.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. The shift's block re-renders in the chosen color.
 2. The color provides three consistent tones: background fill, text color, and accent (left border).
 3. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>requirements.md §10, §4.9 (Color picker)</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Color labels are editable per shop</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's or event's color picker is open.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Find the editable label of one color in the picker.
 2. Rename it (for example to 'ZZAUTOTEST Rush').
@@ -7788,50 +7842,50 @@
 4. Restore the original label.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. Each color's label can be edited.
 2. The renamed label shows for the whole shop - the same picker opened elsewhere shows 'ZZAUTOTEST Rush'.
 3. Shifts and events share the same custom palette with the same labels.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>requirements.md §10 (Color labels are editable per shop), §4.10 (shared picker)</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Schedule: View grants the full read experience - page, all three views, mini calendar, search, filter, tooltips, read-only modals</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit (assign a suitable system role or a purpose-made custom role; restore after).
 2. Shifts and events exist on the grid, created by an Edit-capable user.
 3. You are signed in AS that View-only user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Open the Schedule page.
 2. Switch between Day, Week, and Month.
@@ -7839,7 +7893,7 @@
 4. Hover a shift for its tooltip, then click it to open the detail modal.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule page opens and all three views work.
 2. The mini calendar, search, and filters all work.
@@ -7847,43 +7901,43 @@
 4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.1 (Schedule: View), §14.3</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>View-only: every editing affordance is hidden or disabled</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit.
 2. Shifts, a series, and events exist on the grid.
 3. You are signed in AS that View-only user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Look for drag handles on sidebar lines and try to drag a work order card onto the grid.
 2. Try dragging an existing shift block (move/reassign) and look for resize handles in day view.
@@ -7891,7 +7945,7 @@
 4. Open a shift's detail modal and inspect its fields and actions.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. No drag handles are offered and nothing can be dragged from the sidebar onto the grid.
 2. Shift blocks cannot be moved or resized - no drop targets or resize handles appear.
@@ -7899,89 +7953,89 @@
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.1 (Schedule: View - editing affordances hidden or disabled)</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>With Schedule: View OFF, the Schedule top-level nav item is hidden entirely</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View OFF (no Schedule permission).
 2. You are signed in AS that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Look at the app's main navigation.
 2. Search the nav for any Schedule entry.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule top-level nav item is not shown at all.
 2. The rest of the app works normally for the role.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.1 (When Schedule: View is OFF)</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Schedule: Edit unlocks all creation and modification interactions</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit (and View) but NOT Delete.
 2. Work orders with approved lines exist; you are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Drag a work order from the sidebar onto a technician cell and complete the scope picker (and spread modal for a large job).
 2. Right-click a cell and create an event via 'New Event'; in day view, click empty space to create.
@@ -7990,7 +8044,7 @@
 5. Edit fields in the shift and event detail modals.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. Drag-and-drop from the sidebar, the scope picker, and the spread modal all work.
 2. Shift and event creation works, including via the right-click context menu and day-view click-to-create.
@@ -7999,100 +8053,100 @@
 5. Modal fields are editable and save.</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.1 (Schedule: Edit)</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Edit without Delete: the user can create and modify but cannot remove - delete action and trash icon hidden</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit but NOT Delete.
 2. A shift, a series, and an event exist (some created by this user).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Open a shift's detail modal and look for the delete action / trash icon.
 2. Open an event's modal and look for a delete action.
 3. Try to find ANY way to remove a shift or event.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. The delete action and the trash icon are hidden in the shift modal.
 2. Events likewise offer no delete.
 3. No path exists to remove shifts or events - while creating and modifying still work.</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.1 (Schedule: Delete - without it)</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Schedule: Delete unlocks deleting shifts and events, including the three series-aware scopes</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Delete.
 2. A standalone shift, a series, and an event exist.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Delete a series shift and read the scope options.
 3. Delete the event.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. The delete action is available and works for shifts.
 2. Series deletion offers its scopes (this shift / this and after / whole series).
@@ -8100,339 +8154,389 @@
 4. Undo toasts appear (restore the items via Undo to clean up).</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.1 (Schedule: Delete)</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>The permission tiers depend on each other: Delete requires Edit, and Edit requires View</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as an admin who can edit custom roles.
 2. A ZZAUTOTEST custom role exists (create one; delete after).</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. In the role's Schedule permissions, try to enable Edit while View is off.
 2. Try to enable Delete while Edit is off.
 3. Enable View, then Edit, then Delete in order.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. Edit cannot be granted without View (the admin UI enforces or auto-selects the dependency).
 2. Delete cannot be granted without Edit.
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14 (Delete requires Edit and Edit requires View)</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Schedule access without Work Orders: View - sidebar hides the WO list and drill-down; mini calendar stays; grid shifts remain usable</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF.
 2. Shifts already exist on the grid.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Look at the left sidebar.
 2. Interact with the shifts already on the grid (hover, open modal, and - if the role has Edit - move one).
 3. Try to find any way to drag a new work order onto the grid.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. The sidebar hides the work order list and the line drill-down; the mini calendar remains available.
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
 3. New work orders cannot be dragged on - the WO list is simply not visible.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.2</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>No own-only restriction: every Schedule: View user sees ALL technicians' shifts and events</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. Shifts and events exist for SEVERAL different technicians.
 2. A test user with a low-tier View-only role exists (and is themselves one of the technicians).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Read the grid across all departments and technicians.
 2. Check 'My Shifts' in 'Filter and Display' is OFF (default).</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.3</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Grid rows are department-based: any staff member in a visible department appears as a row, regardless of role</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. A staff member with a NON-technician role (for example Office) is assigned to a department that is visible on the schedule (set up; restore after).
 2. Another staff member has NO department assignment.
 3. You are signed in on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Look for the department-assigned Office staff member among the grid rows.
 2. Look for the staff member with no department.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
 2. The staff member without a department does not appear as a row.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.4</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Clocking into work order line tasks is gated by the staff record's 'Time Clock' setting, not the permission model</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. Two staff members exist: one with the 'Time Clock' setting ON on their staff record, one with it OFF (set up; restore after).
 2. Both appear as schedule rows and have shifts on work order lines.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. As (or with) the Time-Clock-ON staff member, attempt to clock into their work order line task.
 2. As (or with) the Time-Clock-OFF staff member, attempt the same.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. The Time-Clock-ON staff member can clock in.
 2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.4 (Time Clock setting)</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>With Work Orders: View OFF, work-order-derived details on shifts (customer, lines, money fields) are hidden or masked</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>1. A test user's role has Schedule access but Work Orders: View OFF (assign a suitable role; restore after).
+2. Shifts already exist on the grid, created by a fully-permissioned user, for units that have customers, scheduled lines, and a VIN.
+3. You are signed in AS that user on a desktop browser, on the Schedule page.</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at a shift block on the grid and read its text lines.
+2. Hover the shift for its tooltip.
+3. Open the shift's detail modal and read the work-order-derived fields.</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>1. Work-order-derived details (customer, the scheduled line list, and any money-bearing fields) are hidden or masked wherever they would normally appear - on the block, in the tooltip, and in the modal.
+2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
+3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md §14.2 (Work Orders: View dependency)</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Planned hours across technicians may exceed the estimate - accepted without error</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A work order line with a 40h estimate exists.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. Spread the full estimate onto technician A.
 2. Spread the full estimate of the SAME work order onto technician B.
 3. Look for any warning or error about exceeding the estimate.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. Both series are created - 80 planned hours against a 40h estimate is accepted.
 2. No error or blocking warning appears - this is expected behavior because progress is driven by clocked-in time, and scheduled hours, the estimate, and actual hours are three separate quantities that are not forced to reconcile.</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>requirements.md §12, §4.5</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Below 960px the grid scrolls horizontally, and the sidebar collapses on narrow viewports</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in week view with shifts visible.</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. Resize the browser window to just under 960px wide.
 2. Try to reach the right-hand days of the grid.
 3. Narrow the window further and watch the sidebar.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. Below the 960px minimum supported width, the grid scrolls horizontally rather than breaking.
 2. All days remain reachable by horizontal scroll.
@@ -8440,210 +8544,210 @@
 4. No content becomes permanently unreachable and nothing errors.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>requirements.md §11 (Responsiveness)</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>The sidebar work order list and line drill-down stay smooth with 50+ items</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. 50 or more open work orders exist (seed ZZAUTOTEST orders if the environment lacks them), including one order with many approved lines.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the full work order list top to bottom quickly.
 2. Open the many-line order's drill-down and scroll it.
 3. Type in the search while the long list is shown.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
 3. Search stays responsive on the long list.</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>requirements.md §11 (Performance - virtualization)</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>The grid renders smoothly at full load - 15 technicians × 7 days with several shifts per cell</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. The schedule is loaded to roughly the spec's stated scale: around 15 technician rows across a week with several shifts per cell (seed ZZAUTOTEST shifts as needed).
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the grid vertically and horizontally.
 2. Switch between Day, Week, and Month.
 3. Hover several blocks and open/close a modal.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>1. The grid renders and scrolls smoothly at this scale.
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>requirements.md §11 (Performance)</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Shop closures block the spread step from placing shifts on those days</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shop closure (holiday/inventory day) is defined at the shop level on a working weekday inside the planned spread window (set it up; remove after).
 3. A large job (multi-day scope) is ready to spread.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step across the window containing the closure.
 2. Expand the preview and find the closure day.
 3. Confirm the spread and check the grid.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>1. The preview shows the closure day struck through with its reason.
 2. No shift is placed on the closure day - the series flows around it.
 3. The series' end date extends accordingly (the skipped day's hours land on later working days).</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>requirements.md §12 (Shop closures), §4.5</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Scheduled hours, the estimate, and actual (clocked) hours are three separate quantities that are not forced to reconcile</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A line has estimate 10h; a technician has 6h scheduled against it and some different amount of time actually clocked (seed what is possible).</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. Open the shift's detail modal.
 2. Compare the scheduled hours, the estimate, and the logged/actual time.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>1. All three quantities are shown/derivable and may differ from one another.
 2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>requirements.md §4.5 (three separate quantities), §12</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6828,7 +6828,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>'Reassign' in the shift detail modal moves the shift to another technician</t>
+          <t>Right-click on any grid cell opens a context menu with New Shift, New Event, and View Day</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6847,76 +6847,74 @@
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in on a desktop browser with Schedule: Edit.
-2. A shift exists on technician A; its detail modal is open.</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>1. Click the 'Reassign' action.
-2. Choose technician B and confirm.
-3. Check the grid and the line's roster.</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>1. The shift moves to technician B's row.
-2. The roster updates the same way as a drag reassignment (B added, A removed).
-3. A toast with Undo appears.</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §4.9 (Reassign action), §7</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Right-click on any grid cell opens a context menu with New Shift, New Event, and View Day</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Reassignment and Context Menu</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Right-click a technician's grid cell.
 2. Read the menu items.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. A context menu opens at the cell.
 2. It contains: 'New Shift', 'New Event', and 'View Day'.
 3. The browser's own right-click menu does not appear instead.</t>
         </is>
       </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md §7 (Right-click context menu)</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>'View Day' in the context menu opens day view for that cell's date</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Reassignment and Context Menu</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. You are on the Schedule page in week or month view.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>1. Right-click a cell on a specific day.
+2. Choose 'View Day'.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>1. The grid switches to day view showing that cell's date.
+2. The toolbar date label and the Day/Week/Month control reflect the switch.</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §7 (Right-click context menu)</t>
+          <t>requirements.md §7 (Right-click context menu - View Day)</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -6925,7 +6923,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>'View Day' in the context menu opens day view for that cell's date</t>
+          <t>'New Shift' in the context menu starts shift creation for that technician and day</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6944,164 +6942,117 @@
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in on a desktop browser with Schedule: Edit.
-2. You are on the Schedule page in week or month view.</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>1. Right-click a cell on a specific day.
-2. Choose 'View Day'.</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>1. The grid switches to day view showing that cell's date.
-2. The toolbar date label and the Day/Week/Month control reflect the switch.</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (Right-click context menu - View Day)</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>'New Shift' in the context menu starts shift creation for that technician and day</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Reassignment and Context Menu</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Schedulable work order lines exist.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. Right-click a technician's cell and choose 'New Shift'.
 2. Complete the creation flow that opens.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>1. A shift-creation flow opens targeted at that technician and day.
 2. Completing it creates a shift in that cell, following the same scope/spread rules as drag-and-drop.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Right-click context menu - New Shift), §14.1 (creation via context menu)</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Deleting a middle shift of a series asks for scope with all three options, each stating the hours returned</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists for one technician.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. Delete a MIDDLE shift of the series (via the detail modal's Delete).
 2. Read the scope options offered (do not confirm yet).</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. A scope prompt appears with three options: this shift only, this and everything after, and the whole series.
 2. Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').
 3. The prompt uses routine, lightweight styling - not alarming destructive styling.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Series-aware deletion)</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>'This shift only' removes that day, the series keeps the gap, and the hours return to the estimate's remaining</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists; note the total scheduled hours.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Delete a middle shift with the 'this shift only' scope.
 2. Look at the series on the grid.
 3. Check the scheduled hours.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. Only that day's shift is removed.
 2. The series keeps the gap - the remaining shifts do NOT shuffle to close it.
@@ -7109,148 +7060,148 @@
 4. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (This shift only)</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>'This and everything after' removes from the clicked shift onward, keeping earlier shifts</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 4 shifts exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Delete the series' THIRD shift with the 'this and everything after' scope.
 2. Look at the series on the grid.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. The third shift and every later shift of the series are removed.
 2. The first two shifts remain untouched.
 3. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (This and everything after)</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>'The whole series' removes all of the series' shifts for that technician</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. The SAME work order has a series on technician A and an independent series on technician B.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Delete one of technician A's series shifts with the 'whole series' scope.
 2. Look at both technicians' rows.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. All of technician A's series shifts are removed.
 2. Technician B's independent series is untouched (the scope is per technician's series).
 3. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (The whole series - 'for that technician')</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Scope options adapt to position: first and last shifts of a series each show only two options</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Start deleting the FIRST shift of the series; read the options, then cancel.
 2. Start deleting the LAST shift; read the options, then cancel.
 3. Start deleting a MIDDLE shift; read the options, then cancel.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. First shift: two options ('this and after' would equal 'whole series', so only two are shown).
 2. Last shift: two options ('this and after' would equal 'this only').
@@ -7258,91 +7209,91 @@
 4. Cancelling leaves the series unchanged in every case.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (options adapt to position)</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Deleting a standalone (non-series) shift does not ask for a series scope</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A single standalone shift (not part of any series) exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Watch what is asked.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
 2. The shift is deleted and an undo toast appears.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (derived - scope prompt is for series shifts)</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Every create, delete, move, and reassign action produces a toast with an Undo option</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. Schedulable lines and an existing shift are available.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Create a shift - watch for a toast.
 2. Move a shift to another day - watch for a toast.
@@ -7350,98 +7301,98 @@
 4. Delete a shift - watch for a toast.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. Each of the four actions produces a toast notification.
 2. Every toast offers an Undo option.</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Toast notifications), §11 (Undo)</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>The toast persists 4 to 7 seconds, stays while the cursor is over it, and dismisses on mouse-leave</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Perform an action that shows a toast (for example move a shift) and let the toast sit untouched - time how long it stays.
 2. Trigger another toast and hold the cursor OVER it well past its normal lifetime.
 3. Move the cursor off the toast.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. Untouched, the toast persists for roughly 4 to 7 seconds before dismissing.
 2. While the cursor is over it, the toast stays (does not auto-dismiss).
 3. After the cursor leaves, it dismisses.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Toast notifications), §11 (Undo)</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Undo restores the state before the action - for delete, move, and reassign</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A shift exists; note its technician, day, and time.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Delete the shift, then click Undo on the toast.
 2. Move the shift to another day, then click Undo.
@@ -7449,7 +7400,7 @@
 4. Check the line's roster after the reassign undo.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. Undo after delete: the shift is back exactly where it was.
 2. Undo after move: the shift returns to its original day/time.
@@ -7457,91 +7408,91 @@
 4. Every destructive action is undoable within the toast's lifetime.</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>requirements.md §11 (Undo), §7</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Escape closes the topmost open modal or popover, following the stacking order</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Open the shift detail modal, then open a popover on top of it (for example the color picker or a filter/search popover elsewhere).
 2. Press Escape once.
 3. Press Escape again.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. The FIRST Escape closes only the topmost layer (the popover), leaving the layer beneath open.
 2. The SECOND Escape closes the next layer down.
 3. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Keyboard support - Escape)</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Within the shift modal, Escape first dismisses an open sub-picker before closing the modal itself</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. Open the color picker inside the modal, press Escape, and watch.
 2. Open the time picker, press Escape.
@@ -7549,50 +7500,50 @@
 4. With nothing open inside the modal, press Escape.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. Escape with the color picker open closes only the color picker - the modal stays open.
 2. Same for the time picker and the note edit.
 3. Escape with no open sub-picker closes the modal itself.</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>requirements.md §7 (Escape within the shift modal)</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Enter confirms the active confirmable dialog (delete scope, reassign, spread, event create/edit)</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. Shifts/series and events exist to exercise the dialogs.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step for a large job, press Enter.
 2. Open the reassign dialog for a shift, choose a technician, press Enter.
@@ -7600,15 +7551,62 @@
 4. Open a series delete-scope prompt, select a scope, press Enter.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. In each confirmable dialog, Enter confirms it - equivalent to clicking its confirm action.
 2. The confirmed action takes effect (spread created / reassigned / event saved / delete applied).</t>
         </is>
       </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md §7 (Keyboard support - Enter)</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Enter does not fire inside textareas - multiline note editing works normally</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Keyboard Interactions</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. A shift's detail modal is open with the note editor active.</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a line of note text and press Enter.
+2. Type a second line.</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter inserts a new line in the note - it does NOT confirm/close the dialog.
+2. The multiline note can be completed and saved normally.</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §7 (Keyboard support - Enter)</t>
+          <t>requirements.md §7 (Enter does not fire inside textareas)</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -7617,7 +7615,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Enter does not fire inside textareas - multiline note editing works normally</t>
+          <t>Modals trap focus and all interactive elements are keyboard-reachable</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7627,7 +7625,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -7636,205 +7634,158 @@
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in on a desktop browser with Schedule: Edit.
-2. A shift's detail modal is open with the note editor active.</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>1. Type a line of note text and press Enter.
-2. Type a second line.</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter inserts a new line in the note - it does NOT confirm/close the dialog.
-2. The multiline note can be completed and saved normally.</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (Enter does not fire inside textareas)</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Modals trap focus and all interactive elements are keyboard-reachable</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>Keyboard Interactions</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Press Tab repeatedly and watch where focus goes.
 2. Continue tabbing past the last control in the modal.
 3. Close the modal and Tab through the schedule page's toolbar and sidebar controls.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. Focus moves through the modal's interactive elements with visible focus rings.
 2. Focus stays trapped inside the modal (wraps back to its first control) until the modal closes.
 3. On the page, toolbar and sidebar controls are reachable by keyboard.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>requirements.md §11 (Accessibility)</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Blue is the default color for all shifts, including long and multi-week jobs</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Create a normal single-day shift without touching any color option.
 2. Create a multi-week series without touching any color option.
 3. Look at both on the grid.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. Both the single shift and the multi-week series render in the default blue.
 2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>requirements.md §10</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Choosing a color from the shift modal's picker recolors the shift with matching background, text, and accent tones</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists; its detail modal is open.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Open the color picker in the modal.
 2. Choose a non-default color.
 3. Look at the block on the grid.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. The shift's block re-renders in the chosen color.
 2. The color provides three consistent tones: background fill, text color, and accent (left border).
 3. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>requirements.md §10, §4.9 (Color picker)</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Color labels are editable per shop</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's or event's color picker is open.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Find the editable label of one color in the picker.
 2. Rename it (for example to 'ZZAUTOTEST Rush').
@@ -7842,50 +7793,50 @@
 4. Restore the original label.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. Each color's label can be edited.
 2. The renamed label shows for the whole shop - the same picker opened elsewhere shows 'ZZAUTOTEST Rush'.
 3. Shifts and events share the same custom palette with the same labels.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>requirements.md §10 (Color labels are editable per shop), §4.10 (shared picker)</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Schedule: View grants the full read experience - page, all three views, mini calendar, search, filter, tooltips, read-only modals</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit (assign a suitable system role or a purpose-made custom role; restore after).
 2. Shifts and events exist on the grid, created by an Edit-capable user.
 3. You are signed in AS that View-only user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Open the Schedule page.
 2. Switch between Day, Week, and Month.
@@ -7893,7 +7844,7 @@
 4. Hover a shift for its tooltip, then click it to open the detail modal.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule page opens and all three views work.
 2. The mini calendar, search, and filters all work.
@@ -7901,43 +7852,43 @@
 4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.1 (Schedule: View), §14.3</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>View-only: every editing affordance is hidden or disabled</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit.
 2. Shifts, a series, and events exist on the grid.
 3. You are signed in AS that View-only user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Look for drag handles on sidebar lines and try to drag a work order card onto the grid.
 2. Try dragging an existing shift block (move/reassign) and look for resize handles in day view.
@@ -7945,7 +7896,7 @@
 4. Open a shift's detail modal and inspect its fields and actions.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. No drag handles are offered and nothing can be dragged from the sidebar onto the grid.
 2. Shift blocks cannot be moved or resized - no drop targets or resize handles appear.
@@ -7953,9 +7904,56 @@
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.</t>
         </is>
       </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md §14.1 (Schedule: View - editing affordances hidden or disabled)</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>With Schedule: View OFF, the Schedule top-level nav item is hidden entirely</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>1. A test user's role has Schedule: View OFF (no Schedule permission).
+2. You are signed in AS that user on a desktop browser.</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at the app's main navigation.
+2. Search the nav for any Schedule entry.</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>1. The Schedule top-level nav item is not shown at all.
+2. The rest of the app works normally for the role.</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §14.1 (Schedule: View - editing affordances hidden or disabled)</t>
+          <t>requirements.md §14.1 (When Schedule: View is OFF)</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
@@ -7964,7 +7962,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>With Schedule: View OFF, the Schedule top-level nav item is hidden entirely</t>
+          <t>Schedule: Edit unlocks all creation and modification interactions</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -7974,7 +7972,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -7983,59 +7981,12 @@
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>1. A test user's role has Schedule: View OFF (no Schedule permission).
-2. You are signed in AS that user on a desktop browser.</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>1. Look at the app's main navigation.
-2. Search the nav for any Schedule entry.</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>1. The Schedule top-level nav item is not shown at all.
-2. The rest of the app works normally for the role.</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.1 (When Schedule: View is OFF)</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>Schedule: Edit unlocks all creation and modification interactions</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit (and View) but NOT Delete.
 2. Work orders with approved lines exist; you are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Drag a work order from the sidebar onto a technician cell and complete the scope picker (and spread modal for a large job).
 2. Right-click a cell and create an event via 'New Event'; in day view, click empty space to create.
@@ -8044,7 +7995,7 @@
 5. Edit fields in the shift and event detail modals.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. Drag-and-drop from the sidebar, the scope picker, and the spread modal all work.
 2. Shift and event creation works, including via the right-click context menu and day-view click-to-create.
@@ -8053,100 +8004,100 @@
 5. Modal fields are editable and save.</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.1 (Schedule: Edit)</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Edit without Delete: the user can create and modify but cannot remove - delete action and trash icon hidden</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit but NOT Delete.
 2. A shift, a series, and an event exist (some created by this user).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Open a shift's detail modal and look for the delete action / trash icon.
 2. Open an event's modal and look for a delete action.
 3. Try to find ANY way to remove a shift or event.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. The delete action and the trash icon are hidden in the shift modal.
 2. Events likewise offer no delete.
 3. No path exists to remove shifts or events - while creating and modifying still work.</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.1 (Schedule: Delete - without it)</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Schedule: Delete unlocks deleting shifts and events, including the three series-aware scopes</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Delete.
 2. A standalone shift, a series, and an event exist.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Delete a series shift and read the scope options.
 3. Delete the event.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. The delete action is available and works for shifts.
 2. Series deletion offers its scopes (this shift / this and after / whole series).
@@ -8154,204 +8105,251 @@
 4. Undo toasts appear (restore the items via Undo to clean up).</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.1 (Schedule: Delete)</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>The permission tiers depend on each other: Delete requires Edit, and Edit requires View</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as an admin who can edit custom roles.
 2. A ZZAUTOTEST custom role exists (create one; delete after).</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. In the role's Schedule permissions, try to enable Edit while View is off.
 2. Try to enable Delete while Edit is off.
 3. Enable View, then Edit, then Delete in order.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. Edit cannot be granted without View (the admin UI enforces or auto-selects the dependency).
 2. Delete cannot be granted without Edit.
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14 (Delete requires Edit and Edit requires View)</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Schedule access without Work Orders: View - sidebar hides the WO list and drill-down; mini calendar stays; grid shifts remain usable</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF.
 2. Shifts already exist on the grid.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Look at the left sidebar.
 2. Interact with the shifts already on the grid (hover, open modal, and - if the role has Edit - move one).
 3. Try to find any way to drag a new work order onto the grid.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. The sidebar hides the work order list and the line drill-down; the mini calendar remains available.
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
 3. New work orders cannot be dragged on - the WO list is simply not visible.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.2</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>No own-only restriction: every Schedule: View user sees ALL technicians' shifts and events</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. Shifts and events exist for SEVERAL different technicians.
 2. A test user with a low-tier View-only role exists (and is themselves one of the technicians).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Read the grid across all departments and technicians.
 2. Check 'My Shifts' in 'Filter and Display' is OFF (default).</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.3</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Grid rows are department-based: any staff member in a visible department appears as a row, regardless of role</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. A staff member with a NON-technician role (for example Office) is assigned to a department that is visible on the schedule (set up; restore after).
 2. Another staff member has NO department assignment.
 3. You are signed in on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Look for the department-assigned Office staff member among the grid rows.
 2. Look for the staff member with no department.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
 2. The staff member without a department does not appear as a row.</t>
         </is>
       </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md §14.4</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Clocking into work order line tasks is gated by the staff record's 'Time Clock' setting, not the permission model</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>1. Two staff members exist: one with the 'Time Clock' setting ON on their staff record, one with it OFF (set up; restore after).
+2. Both appear as schedule rows and have shifts on work order lines.</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>1. As (or with) the Time-Clock-ON staff member, attempt to clock into their work order line task.
+2. As (or with) the Time-Clock-OFF staff member, attempt the same.</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>1. The Time-Clock-ON staff member can clock in.
+2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.</t>
+        </is>
+      </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §14.4</t>
+          <t>requirements.md §14.4 (Time Clock setting)</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
@@ -8360,7 +8358,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Clocking into work order line tasks is gated by the staff record's 'Time Clock' setting, not the permission model</t>
+          <t>With Work Orders: View OFF, work-order-derived details on shifts (customer, lines, money fields) are hidden or masked</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8370,173 +8368,126 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>1. Two staff members exist: one with the 'Time Clock' setting ON on their staff record, one with it OFF (set up; restore after).
-2. Both appear as schedule rows and have shifts on work order lines.</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>1. As (or with) the Time-Clock-ON staff member, attempt to clock into their work order line task.
-2. As (or with) the Time-Clock-OFF staff member, attempt the same.</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>1. The Time-Clock-ON staff member can clock in.
-2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.4 (Time Clock setting)</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>With Work Orders: View OFF, work-order-derived details on shifts (customer, lines, money fields) are hidden or masked</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF (assign a suitable role; restore after).
 2. Shifts already exist on the grid, created by a fully-permissioned user, for units that have customers, scheduled lines, and a VIN.
 3. You are signed in AS that user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Look at a shift block on the grid and read its text lines.
 2. Hover the shift for its tooltip.
 3. Open the shift's detail modal and read the work-order-derived fields.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. Work-order-derived details (customer, the scheduled line list, and any money-bearing fields) are hidden or masked wherever they would normally appear - on the block, in the tooltip, and in the modal.
 2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
 3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>requirements.md §14.2 (Work Orders: View dependency)</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Planned hours across technicians may exceed the estimate - accepted without error</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A work order line with a 40h estimate exists.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. Spread the full estimate onto technician A.
 2. Spread the full estimate of the SAME work order onto technician B.
 3. Look for any warning or error about exceeding the estimate.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. Both series are created - 80 planned hours against a 40h estimate is accepted.
 2. No error or blocking warning appears - this is expected behavior because progress is driven by clocked-in time, and scheduled hours, the estimate, and actual hours are three separate quantities that are not forced to reconcile.</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>requirements.md §12, §4.5</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Below 960px the grid scrolls horizontally, and the sidebar collapses on narrow viewports</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in week view with shifts visible.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. Resize the browser window to just under 960px wide.
 2. Try to reach the right-hand days of the grid.
 3. Narrow the window further and watch the sidebar.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. Below the 960px minimum supported width, the grid scrolls horizontally rather than breaking.
 2. All days remain reachable by horizontal scroll.
@@ -8544,210 +8495,210 @@
 4. No content becomes permanently unreachable and nothing errors.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>requirements.md §11 (Responsiveness)</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>The sidebar work order list and line drill-down stay smooth with 50+ items</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. 50 or more open work orders exist (seed ZZAUTOTEST orders if the environment lacks them), including one order with many approved lines.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the full work order list top to bottom quickly.
 2. Open the many-line order's drill-down and scroll it.
 3. Type in the search while the long list is shown.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
 3. Search stays responsive on the long list.</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>requirements.md §11 (Performance - virtualization)</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>The grid renders smoothly at full load - 15 technicians × 7 days with several shifts per cell</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. The schedule is loaded to roughly the spec's stated scale: around 15 technician rows across a week with several shifts per cell (seed ZZAUTOTEST shifts as needed).
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the grid vertically and horizontally.
 2. Switch between Day, Week, and Month.
 3. Hover several blocks and open/close a modal.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. The grid renders and scrolls smoothly at this scale.
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>requirements.md §11 (Performance)</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Shop closures block the spread step from placing shifts on those days</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shop closure (holiday/inventory day) is defined at the shop level on a working weekday inside the planned spread window (set it up; remove after).
 3. A large job (multi-day scope) is ready to spread.</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step across the window containing the closure.
 2. Expand the preview and find the closure day.
 3. Confirm the spread and check the grid.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>1. The preview shows the closure day struck through with its reason.
 2. No shift is placed on the closure day - the series flows around it.
 3. The series' end date extends accordingly (the skipped day's hours land on later working days).</t>
         </is>
       </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md §12 (Shop closures), §4.5</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled hours, the estimate, and actual (clocked) hours are three separate quantities that are not forced to reconcile</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Edge Cases and Responsiveness</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. A line has estimate 10h; a technician has 6h scheduled against it and some different amount of time actually clocked (seed what is possible).</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the shift's detail modal.
+2. Compare the scheduled hours, the estimate, and the logged/actual time.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>1. All three quantities are shown/derivable and may differ from one another.
+2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).</t>
+        </is>
+      </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §12 (Shop closures), §4.5</t>
+          <t>requirements.md §4.5 (three separate quantities), §12</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled hours, the estimate, and actual (clocked) hours are three separate quantities that are not forced to reconcile</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>Edge Cases and Responsiveness</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in on a desktop browser with Schedule: Edit.
-2. A line has estimate 10h; a technician has 6h scheduled against it and some different amount of time actually clocked (seed what is possible).</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the shift's detail modal.
-2. Compare the scheduled hours, the estimate, and the logged/actual time.</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>1. All three quantities are shown/derivable and may differ from one another.
-2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §4.5 (three separate quantities), §12</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3</t>
+          <t>SV-8686 (§3)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -575,7 +575,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3, §3.1, §3.2</t>
+          <t>SV-8686 (§3, §3.1, §3.2)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -626,7 +626,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.2, §6</t>
+          <t>SV-8686 (§3.2, §6)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.2, §14.4</t>
+          <t>SV-8686 (§3.2, §14.4)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.2</t>
+          <t>SV-8686 (§3.2)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.2</t>
+          <t>SV-8686 (§3.2)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -818,7 +818,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.2, §4.2</t>
+          <t>SV-8686 (§3.2, §4.2)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1, §5.2</t>
+          <t>SV-8687 (§3.1, §5.2)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §5.2</t>
+          <t>SV-8687 (§5.2)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1, §5.2</t>
+          <t>SV-8687 (§3.1, §5.2)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §5.2</t>
+          <t>SV-8687 (§5.2)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1, §5.1</t>
+          <t>SV-8687 (§3.1, §5.1)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (Work order card anatomy)</t>
+          <t>SV-8687 (§3.1 (Work order card anatomy))</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (Sidebar search)</t>
+          <t>SV-8687 (§3.1 (Sidebar search))</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (Sidebar search, Work order card anatomy)</t>
+          <t>SV-8687 (§3.1 (Sidebar search, Work order card anatomy))</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (Sidebar search)</t>
+          <t>SV-8687 (§3.1 (Sidebar search))</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (derived - search behavior with no matches)</t>
+          <t>SV-8687 (§3.1 (derived - search behavior with no matches))</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>The 'Filter' button opens Assignment / Status / Priority filter groups and shows an active-count badge</t>
+          <t>The 'Filters' button opens Assignment / Status / Priority filter groups</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1345,21 +1345,21 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Click the 'Filter' button on the sidebar.
+          <t>1. Click the 'Filters' button on the sidebar.
 2. Read the filter groups offered.
-3. Apply one filter option and look at the 'Filter' button.</t>
+3. Apply one filter option and look at the 'Filters' button.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. The filter panel offers three groups: Assignment (Assigned, Unassigned), Status (the work order statuses supported in the app), and Priority (High, Medium, Low).
 2. Applying a filter narrows the flat card list.
-3. The 'Filter' button shows a badge with the number of active filters.</t>
+3. The 'Filters' button shows a badge with the number of active filters.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §5.1</t>
+          <t>SV-8687 (§5.1)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §5.1, §3.1</t>
+          <t>SV-8687 (§5.1, §3.1)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §5.1</t>
+          <t>SV-8687 (§5.1)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §5.1</t>
+          <t>SV-8687 (§5.1)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §5.1</t>
+          <t>SV-8687 (§5.1)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §5.1</t>
+          <t>SV-8687 (§5.1)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (Line drill-down)</t>
+          <t>SV-8687 (§3.1 (Line drill-down))</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (Line drill-down)</t>
+          <t>SV-8687 (§3.1 (Line drill-down))</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (Line drill-down - approved-only)</t>
+          <t>SV-8687 (§3.1 (Line drill-down - approved-only))</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (Line drill-down), §8.1 (Line labor roster - no cap)</t>
+          <t>SV-8687 (§3.1 (Line drill-down), §8.1 (Line labor roster - no cap))</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (Line drill-down - Needs techs badge)</t>
+          <t>SV-8687 (§3.1 (Line drill-down - Needs techs badge))</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1 (Line search)</t>
+          <t>SV-8687 (§3.1 (Line search))</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.1, §5.1 (drill-down filters)</t>
+          <t>SV-8687 (§3.1, §5.1 (drill-down filters))</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.1 (Single-line work order), §1.2 (roster sync), §7 (toast)</t>
+          <t>SV-8688 (§4.1 (Single-line work order), §1.2 (roster sync), §7 (toast))</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.1 (Multi-line work order), §4.3</t>
+          <t>SV-8688 (§4.1 (Multi-line work order), §4.3)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.1 (Specific line drag)</t>
+          <t>SV-8688 (§4.1 (Specific line drag))</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.1 (Large job), §4.5</t>
+          <t>SV-8688 (§4.1 (Large job), §4.5)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.1 (spread step is conditional)</t>
+          <t>SV-8688 (§4.1 (spread step is conditional))</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §7 (Drag feedback)</t>
+          <t>SV-8688 (§7 (Drag feedback))</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §1.2 (Goals - roster sync), §4.3 (roster add), §7</t>
+          <t>SV-8688 (§1.2 (Goals - roster sync), §4.3 (roster add), §7)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §7 (Keyboard support - click-to-arm), §11 (Accessibility)</t>
+          <t>SV-8688 (§7 (Keyboard support - click-to-arm), §11 (Accessibility))</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.3</t>
+          <t>SV-8689 (§4.3)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.3, §4.4</t>
+          <t>SV-8689 (§4.3, §4.4)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.3 (Individual line rows - fast path)</t>
+          <t>SV-8689 (§4.3 (Individual line rows - fast path))</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.3</t>
+          <t>SV-8689 (§4.3)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.3 (Select multiple)</t>
+          <t>SV-8689 (§4.3 (Select multiple))</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.3 (Select all shortcut, Cancel)</t>
+          <t>SV-8689 (§4.3 (Select all shortcut, Cancel))</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.2</t>
+          <t>SV-8688 (§4.2)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.2</t>
+          <t>SV-8688 (§4.2)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.2</t>
+          <t>SV-8688 (§4.2)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.2 (day view drop position)</t>
+          <t>SV-8688 (§4.2 (day view drop position))</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.2 (Unassigned shifts), §3.2</t>
+          <t>SV-8688 (§4.2 (Unassigned shifts), §3.2)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.2</t>
+          <t>SV-8688 (§4.2)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §3.2 (Unassigned placeholder), §4.2</t>
+          <t>SV-8688 (§3.2 (Unassigned placeholder), §4.2)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.2, §12</t>
+          <t>SV-8688 (§4.2, §12)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.5</t>
+          <t>SV-8691 (§4.5)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.5</t>
+          <t>SV-8691 (§4.5)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.5 (How much to schedule)</t>
+          <t>SV-8691 (§4.5 (How much to schedule))</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.5 (progressive disclosure)</t>
+          <t>SV-8691 (§4.5 (progressive disclosure))</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.5 (progressive disclosure)</t>
+          <t>SV-8691 (§4.5 (progressive disclosure))</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.5 (Start date)</t>
+          <t>SV-8691 (§4.5 (Start date))</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3325,7 +3325,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Spread uses the technician's own working hours and skips weekends and shop closures - the end date is emergent</t>
+          <t>Spread uses the tech's working hours; skips weekends only when hours not set</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3360,13 +3360,14 @@
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. Daily shifts are sized to the technician's own working hours (8h each in the example).
-2. No shifts are placed on Saturday, Sunday, or the shop closure day.
-3. The end date is a result of the daily distribution (for 40h at 8h/day starting Monday with one closure, the series extends one extra working day).</t>
+2. Weekends are skipped ONLY when the technician has no business hours set for them; if the tech has hours on a weekend day (e.g. Saturday hours) that day is NOT skipped.
+3. Shop closures and public holidays are NOT skipped in V1 - shifts can be placed on those days.
+4. The end date is a result of the daily distribution (for 40h at 8h/day starting Monday, the series ends on the fifth working day).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.5, §12 (shop closures)</t>
+          <t>SV-8691 (§4.5, §12 (shop closures))</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3415,7 +3416,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.5 (Preview)</t>
+          <t>SV-8691 (§4.5 (Preview))</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3465,7 +3466,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.5 (Confirming), §4.6, §8.2</t>
+          <t>SV-8691 (§4.5 (Confirming), §4.6, §8.2)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3514,7 +3515,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.5 (independent per-tech spread), §12</t>
+          <t>SV-8691 (§4.5 (independent per-tech spread), §12)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3565,7 +3566,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.6 (Month view)</t>
+          <t>SV-8692 (§4.6 (Month view))</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3616,7 +3617,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.6 (Week view)</t>
+          <t>SV-8692 (§4.6 (Week view))</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3664,7 +3665,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.6 (Day view)</t>
+          <t>SV-8692 (§4.6 (Day view))</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3714,7 +3715,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.6, §8.2</t>
+          <t>SV-8692 (§4.6, §8.2)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3763,7 +3764,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.4</t>
+          <t>SV-8690 (§4.4)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3813,7 +3814,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.4, §12</t>
+          <t>SV-8690 (§4.4, §12)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3863,7 +3864,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.4, §9 (VIN option)</t>
+          <t>SV-8690 (§4.4, §9 (VIN option))</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3872,7 +3873,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Block color is tied to the work order - blocks from the same order share a color</t>
+          <t>Shift blocks default to blue; a custom colour can be set per shift</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3899,20 +3900,21 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1. Compare the colors of the two blocks from the same work order.
-2. Compare them with the other order's block.</t>
+          <t>1. Look at a newly created shift block's colour.
+2. Open the shift detail modal and set a custom colour via the colour picker.
+3. Compare that shift with another shift from the same work order.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. The two blocks from the same work order share the same color.
-2. Blocks from different work orders can have different colors.
-3. By default blocks are blue (the default shift color) unless a custom color was chosen.</t>
+          <t>1. By default every shift block is blue (the default shift colour).
+2. A custom colour can be assigned per shift via the colour picker in the detail modal.
+3. Colour is per shift - it is NOT tied to the work order, so two shifts from the same order do not automatically share a colour.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.4, §10</t>
+          <t>SV-8690 (§4.4, §10)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3961,7 +3963,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.4</t>
+          <t>SV-8690 (§4.4)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -4009,7 +4011,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.7</t>
+          <t>SV-8693 (§4.7)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4057,7 +4059,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.7, §4.11</t>
+          <t>SV-8693 (§4.7, §4.11)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4107,7 +4109,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.7</t>
+          <t>SV-8693 (§4.7)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4157,7 +4159,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.7</t>
+          <t>SV-8693 (§4.7)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4205,7 +4207,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §12 (edge case), §4.7</t>
+          <t>SV-8693 (§12 (edge case), §4.7)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4254,7 +4256,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.8 (Auto-scroll to business hours)</t>
+          <t>SV-8694 (§4.8 (Auto-scroll to business hours))</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4303,7 +4305,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.8</t>
+          <t>SV-8694 (§4.8)</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4352,7 +4354,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.8 (Sticky header bar)</t>
+          <t>SV-8694 (§4.8 (Sticky header bar))</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4403,7 +4405,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.8 (Horizontal drag), §7 (toast)</t>
+          <t>SV-8694 (§4.8 (Horizontal drag), §7 (toast))</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4454,7 +4456,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.8 (Edge resize)</t>
+          <t>SV-8694 (§4.8 (Edge resize))</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4503,7 +4505,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.8 (Now line)</t>
+          <t>SV-8694 (§4.8 (Now line))</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4552,7 +4554,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.8 (Lane height with VIN)</t>
+          <t>SV-8694 (§4.8 (Lane height with VIN))</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4601,7 +4603,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.9, §9 (VIN always in modal)</t>
+          <t>SV-8695 (§4.9, §9 (VIN always in modal))</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4652,7 +4654,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.9</t>
+          <t>SV-8695 (§4.9)</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4701,7 +4703,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.9</t>
+          <t>SV-8695 (§4.9)</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4751,7 +4753,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.9, §4.4</t>
+          <t>SV-8695 (§4.9, §4.4)</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4800,7 +4802,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.9 (Estimated hours with inline edit)</t>
+          <t>SV-8695 (§4.9 (Estimated hours with inline edit))</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4850,7 +4852,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.9 (Notes: add, edit, and delete per work order)</t>
+          <t>SV-8695 (§4.9 (Notes: add, edit, and delete per work order))</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4901,7 +4903,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.9 (conflict banner + Adjust)</t>
+          <t>SV-8695 (§4.9 (conflict banner + Adjust))</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4950,7 +4952,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.9 (Actions), §7</t>
+          <t>SV-8695 (§4.9 (Actions), §7)</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4959,7 +4961,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Create an event via right-click 'New Event' on a grid cell</t>
+          <t>Create an event via right-click 'Create Event' on a grid cell</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4986,13 +4988,13 @@
       <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Right-click a technician's cell on a working day.
-2. Choose 'New Event' from the context menu.
+2. Choose 'Create Event' from the context menu.
 3. Fill in a name (for example 'ZZAUTOTEST stand-up'), keep the date/times offered, and save.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1. The right-click context menu contains 'New Event'.
+          <t>1. The right-click context menu contains 'Create Event'.
 2. The event modal opens with the clicked cell's technician and date pre-set.
 3. Saving creates an event block on that technician's day.
 4. A toast with Undo appears.</t>
@@ -5000,7 +5002,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.10, §7 (right-click menu)</t>
+          <t>SV-8696 (§4.10, §7 (right-click menu))</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -5049,7 +5051,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.10 (day-view click-to-create, live preview)</t>
+          <t>SV-8696 (§4.10 (day-view click-to-create, live preview))</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -5098,7 +5100,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.10 (Event modal)</t>
+          <t>SV-8696 (§4.10 (Event modal))</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -5146,7 +5148,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.10, §8.1 (Event allDay field)</t>
+          <t>SV-8696 (§4.10, §8.1 (Event allDay field))</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -5196,7 +5198,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.10 (Drag-and-drop to reassign/move), §7 (toast)</t>
+          <t>SV-8696 (§4.10 (Drag-and-drop to reassign/move), §7 (toast))</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -5244,7 +5246,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.10 (Event card anatomy)</t>
+          <t>SV-8696 (§4.10 (Event card anatomy))</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -5294,7 +5296,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.10 (Event color), §10</t>
+          <t>SV-8696 (§4.10 (Event color), §10)</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
@@ -5344,7 +5346,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.10 (Events), §4.11, §4.12</t>
+          <t>SV-8696 (§4.10 (Events), §4.11, §4.12)</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -5395,7 +5397,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.11 (Double-booked)</t>
+          <t>SV-8697 (§4.11 (Double-booked))</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -5444,7 +5446,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.11 (Weekend shift)</t>
+          <t>SV-8697 (§4.11 (Weekend shift))</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -5493,7 +5495,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.11 (Before hours)</t>
+          <t>SV-8697 (§4.11 (Before hours))</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -5542,7 +5544,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.11 (After hours)</t>
+          <t>SV-8697 (§4.11 (After hours))</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -5593,7 +5595,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.11, §6 (Conflict pill)</t>
+          <t>SV-8697 (§4.11, §6 (Conflict pill))</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -5641,7 +5643,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.11 (Clicking a conflict navigates)</t>
+          <t>SV-8697 (§4.11 (Clicking a conflict navigates))</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -5689,7 +5691,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.11 (styling rule), §4.12</t>
+          <t>SV-8697 (§4.11 (styling rule), §4.12)</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5740,7 +5742,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.12 (Blue fill)</t>
+          <t>SV-8698 (§4.12 (Blue fill))</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5787,7 +5789,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.12 (Amber spill)</t>
+          <t>SV-8698 (§4.12 (Amber spill))</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5835,7 +5837,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.12 (OT tag), §11 (not color-only)</t>
+          <t>SV-8698 (§4.12 (OT tag), §11 (not color-only))</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5884,7 +5886,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.12 (Hover tooltip)</t>
+          <t>SV-8698 (§4.12 (Hover tooltip))</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
@@ -5933,7 +5935,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.13 (Shift tooltip)</t>
+          <t>SV-8695 (§4.13 (Shift tooltip))</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
@@ -5980,7 +5982,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.13 (Shift tooltip - conflict)</t>
+          <t>SV-8695 (§4.13 (Shift tooltip - conflict))</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
@@ -6028,7 +6030,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.13 (Event tooltip)</t>
+          <t>SV-8695 (§4.13 (Event tooltip))</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
@@ -6080,7 +6082,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.13 (Behavior)</t>
+          <t>SV-8695 (§4.13 (Behavior))</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
@@ -6129,7 +6131,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §4.13 (flip/shift to stay in viewport)</t>
+          <t>SV-8695 (§4.13 (flip/shift to stay in viewport))</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -6176,7 +6178,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §6 (Today button)</t>
+          <t>SV-8686 (§6 (Today button))</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -6226,7 +6228,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §6 (Left/right arrows, Date label)</t>
+          <t>SV-8686 (§6 (Left/right arrows, Date label))</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -6277,7 +6279,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §6 (Search)</t>
+          <t>SV-8686 (§6 (Search))</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
@@ -6286,7 +6288,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>'Filter and Display' is a checkbox-style dropdown combining department toggles, My Shifts, and VIN</t>
+          <t>'Filter &amp; Display' dropdown combines department toggles, My Shifts, and VIN</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6312,7 +6314,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>1. Open the 'Filter and Display' dropdown in the grid toolbar.
+          <t>1. Open the 'Filter &amp; Display' dropdown in the grid toolbar.
 2. Read its contents and default states.</t>
         </is>
       </c>
@@ -6325,7 +6327,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §6, §9 (Filter and Display dropdown)</t>
+          <t>SV-8700 (§6, §9 (Filter and Display dropdown))</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
@@ -6375,7 +6377,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §9 (Department toggles)</t>
+          <t>SV-8700 (§9 (Department toggles))</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
@@ -6425,7 +6427,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §9 (My Shifts), §14.3</t>
+          <t>SV-8700 (§9 (My Shifts), §14.3)</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -6475,7 +6477,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §9 (VIN), §4.4</t>
+          <t>SV-8700 (§9 (VIN), §4.4)</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -6522,7 +6524,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §6, §9 (View Options popover)</t>
+          <t>SV-8700 (§6, §9 (View Options popover))</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
@@ -6572,7 +6574,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §9 (Business Hours), §4.8 (Business-hours shading)</t>
+          <t>SV-8700 (§9 (Business Hours), §4.8 (Business-hours shading))</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -6621,7 +6623,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §9 (Capacity Bars), §4.12</t>
+          <t>SV-8700 (§9 (Capacity Bars), §4.12)</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -6670,7 +6672,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §9 (Events)</t>
+          <t>SV-8700 (§9 (Events))</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -6719,7 +6721,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §9 (Tech Hours)</t>
+          <t>SV-8700 (§9 (Tech Hours))</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -6768,7 +6770,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §9 (Saturday, Sunday), §3.2 (Week view)</t>
+          <t>SV-8700 (§9 (Saturday, Sunday), §3.2 (Week view))</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -6819,7 +6821,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §7 (Shift reassignment), §12</t>
+          <t>SV-8695 (§7 (Shift reassignment), §12)</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -6828,7 +6830,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Right-click on any grid cell opens a context menu with New Shift, New Event, and View Day</t>
+          <t>Right-click a grid cell opens a menu with Create Event and New Work Order</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6861,13 +6863,13 @@
       <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. A context menu opens at the cell.
-2. It contains: 'New Shift', 'New Event', and 'View Day'.
+2. It contains: 'Create Event' and 'New Work Order'.
 3. The browser's own right-click menu does not appear instead.</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §7 (Right-click context menu)</t>
+          <t>SV-8700 (§7 (Right-click context menu))</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
@@ -6876,7 +6878,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>'View Day' in the context menu opens day view for that cell's date</t>
+          <t>'View Day' is no longer offered in the grid cell context menu</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6902,19 +6904,19 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>1. Right-click a cell on a specific day.
-2. Choose 'View Day'.</t>
+          <t>1. Right-click a technician's grid cell.
+2. Read the menu items.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>1. The grid switches to day view showing that cell's date.
-2. The toolbar date label and the Day/Week/Month control reflect the switch.</t>
+          <t>1. The context menu shows only 'Create Event' and 'New Work Order'.
+2. There is no 'View Day' item - it was removed from the menu.</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §7 (Right-click context menu - View Day)</t>
+          <t>SV-8700 (§7 (Right-click context menu - View Day))</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -6923,7 +6925,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>'New Shift' in the context menu starts shift creation for that technician and day</t>
+          <t>'New Shift' is no longer offered in the grid cell context menu</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6950,19 +6952,19 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>1. Right-click a technician's cell and choose 'New Shift'.
-2. Complete the creation flow that opens.</t>
+          <t>1. Right-click a technician's grid cell.
+2. Read the menu items.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>1. A shift-creation flow opens targeted at that technician and day.
-2. Completing it creates a shift in that cell, following the same scope/spread rules as drag-and-drop.</t>
+          <t>1. The context menu shows only 'Create Event' and 'New Work Order'.
+2. There is no 'New Shift' item - it was removed from the menu.</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §7 (Right-click context menu - New Shift), §14.1 (creation via context menu)</t>
+          <t>SV-8700 (§7 (Right-click context menu - New Shift), §14.1 (creation via context menu))</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -6971,88 +6973,136 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>'New Work Order' in the cell menu points the user to the Work Orders tab</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Reassignment and Context Menu</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Schedule grid.
+2. The cell context menu shows 'Create Event' and 'New Work Order' ().</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>1. Right-click an empty grid cell.
+2. Choose 'New Work Order' from the menu.</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>1. The menu offers a 'New Work Order' item.
+2. Choosing it directs the user to create a work order (a toast / prompt pointing to the Work Orders tab).
+3. The exact target flow (toast or navigation) is confirmed during live testing.</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§7 / §4.10 New Work Order cell-menu shortcut)</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
           <t>Deleting a middle shift of a series asks for scope with all three options, each stating the hours returned</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists for one technician.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Delete a MIDDLE shift of the series (via the detail modal's Delete).
 2. Read the scope options offered (do not confirm yet).</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. A scope prompt appears with three options: this shift only, this and everything after, and the whole series.
 2. Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').
 3. The prompt uses routine, lightweight styling - not alarming destructive styling.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (Series-aware deletion)</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>SV-8692 (§7 (Series-aware deletion))</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>'This shift only' removes that day, the series keeps the gap, and the hours return to the estimate's remaining</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists; note the total scheduled hours.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Delete a middle shift with the 'this shift only' scope.
 2. Look at the series on the grid.
 3. Check the scheduled hours.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. Only that day's shift is removed.
 2. The series keeps the gap - the remaining shifts do NOT shuffle to close it.
@@ -7060,148 +7110,148 @@
 4. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (This shift only)</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>SV-8692 (§7 (This shift only))</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>'This and everything after' removes from the clicked shift onward, keeping earlier shifts</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 4 shifts exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Delete the series' THIRD shift with the 'this and everything after' scope.
 2. Look at the series on the grid.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. The third shift and every later shift of the series are removed.
 2. The first two shifts remain untouched.
 3. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (This and everything after)</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>SV-8692 (§7 (This and everything after))</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>'The whole series' removes all of the series' shifts for that technician</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. The SAME work order has a series on technician A and an independent series on technician B.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Delete one of technician A's series shifts with the 'whole series' scope.
 2. Look at both technicians' rows.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. All of technician A's series shifts are removed.
 2. Technician B's independent series is untouched (the scope is per technician's series).
 3. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (The whole series - 'for that technician')</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>SV-8692 (§7 (The whole series - 'for that technician'))</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Scope options adapt to position: first and last shifts of a series each show only two options</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Start deleting the FIRST shift of the series; read the options, then cancel.
 2. Start deleting the LAST shift; read the options, then cancel.
 3. Start deleting a MIDDLE shift; read the options, then cancel.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. First shift: two options ('this and after' would equal 'whole series', so only two are shown).
 2. Last shift: two options ('this and after' would equal 'this only').
@@ -7209,91 +7259,91 @@
 4. Cancelling leaves the series unchanged in every case.</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (options adapt to position)</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>SV-8692 (§7 (options adapt to position))</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Deleting a standalone (non-series) shift does not ask for a series scope</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A single standalone shift (not part of any series) exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Watch what is asked.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
 2. The shift is deleted and an undo toast appears.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (derived - scope prompt is for series shifts)</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>SV-8692 (§7 (derived - scope prompt is for series shifts))</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Every create, delete, move, and reassign action produces a toast with an Undo option</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. Schedulable lines and an existing shift are available.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Create a shift - watch for a toast.
 2. Move a shift to another day - watch for a toast.
@@ -7301,98 +7351,98 @@
 4. Delete a shift - watch for a toast.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. Each of the four actions produces a toast notification.
 2. Every toast offers an Undo option.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (Toast notifications), §11 (Undo)</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>The toast persists 4 to 7 seconds, stays while the cursor is over it, and dismisses on mouse-leave</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>SV-8688 (§7 (Toast notifications), §11 (Undo))</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Toast lasts ~7s with Undo (about 4s without); stays on hover, goes on leave</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Perform an action that shows a toast (for example move a shift) and let the toast sit untouched - time how long it stays.
 2. Trigger another toast and hold the cursor OVER it well past its normal lifetime.
 3. Move the cursor off the toast.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>1. Untouched, the toast persists for roughly 4 to 7 seconds before dismissing.
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>1. Untouched, a toast that has an Undo action persists about 7 seconds; a toast without Undo persists about 4 seconds, before dismissing.
 2. While the cursor is over it, the toast stays (does not auto-dismiss).
 3. After the cursor leaves, it dismisses.</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (Toast notifications), §11 (Undo)</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>SV-8688 (§7 (Toast notifications), §11 (Undo))</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Undo restores the state before the action - for delete, move, and reassign</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A shift exists; note its technician, day, and time.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Delete the shift, then click Undo on the toast.
 2. Move the shift to another day, then click Undo.
@@ -7400,7 +7450,7 @@
 4. Check the line's roster after the reassign undo.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. Undo after delete: the shift is back exactly where it was.
 2. Undo after move: the shift returns to its original day/time.
@@ -7408,91 +7458,91 @@
 4. Every destructive action is undoable within the toast's lifetime.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §11 (Undo), §7</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>SV-8688 (§11 (Undo), §7)</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Escape closes the topmost open modal or popover, following the stacking order</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. Open the shift detail modal, then open a popover on top of it (for example the color picker or a filter/search popover elsewhere).
 2. Press Escape once.
 3. Press Escape again.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. The FIRST Escape closes only the topmost layer (the popover), leaving the layer beneath open.
 2. The SECOND Escape closes the next layer down.
 3. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (Keyboard support - Escape)</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§7 (Keyboard support - Escape))</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Within the shift modal, Escape first dismisses an open sub-picker before closing the modal itself</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Open the color picker inside the modal, press Escape, and watch.
 2. Open the time picker, press Escape.
@@ -7500,50 +7550,50 @@
 4. With nothing open inside the modal, press Escape.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. Escape with the color picker open closes only the color picker - the modal stays open.
 2. Same for the time picker and the note edit.
 3. Escape with no open sub-picker closes the modal itself.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (Escape within the shift modal)</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§7 (Escape within the shift modal))</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Enter confirms the active confirmable dialog (delete scope, reassign, spread, event create/edit)</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. Shifts/series and events exist to exercise the dialogs.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step for a large job, press Enter.
 2. Open the reassign dialog for a shift, choose a technician, press Enter.
@@ -7551,241 +7601,241 @@
 4. Open a series delete-scope prompt, select a scope, press Enter.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. In each confirmable dialog, Enter confirms it - equivalent to clicking its confirm action.
 2. The confirmed action takes effect (spread created / reassigned / event saved / delete applied).</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (Keyboard support - Enter)</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§7 (Keyboard support - Enter))</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Enter does not fire inside textareas - multiline note editing works normally</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open with the note editor active.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Type a line of note text and press Enter.
 2. Type a second line.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. Enter inserts a new line in the note - it does NOT confirm/close the dialog.
 2. The multiline note can be completed and saved normally.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §7 (Enter does not fire inside textareas)</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§7 (Enter does not fire inside textareas))</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Modals trap focus and all interactive elements are keyboard-reachable</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Press Tab repeatedly and watch where focus goes.
 2. Continue tabbing past the last control in the modal.
 3. Close the modal and Tab through the schedule page's toolbar and sidebar controls.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. Focus moves through the modal's interactive elements with visible focus rings.
 2. Focus stays trapped inside the modal (wraps back to its first control) until the modal closes.
 3. On the page, toolbar and sidebar controls are reachable by keyboard.</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §11 (Accessibility)</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§11 (Accessibility))</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Blue is the default color for all shifts, including long and multi-week jobs</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Create a normal single-day shift without touching any color option.
 2. Create a multi-week series without touching any color option.
 3. Look at both on the grid.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Both the single shift and the multi-week series render in the default blue.
 2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §10</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§10)</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Choosing a color from the shift modal's picker recolors the shift with matching background, text, and accent tones</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists; its detail modal is open.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Open the color picker in the modal.
 2. Choose a non-default color.
 3. Look at the block on the grid.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. The shift's block re-renders in the chosen color.
 2. The color provides three consistent tones: background fill, text color, and accent (left border).
 3. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §10, §4.9 (Color picker)</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§10, §4.9 (Color picker))</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Color labels are editable per shop</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's or event's color picker is open.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Find the editable label of one color in the picker.
 2. Rename it (for example to 'ZZAUTOTEST Rush').
@@ -7793,50 +7843,479 @@
 4. Restore the original label.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. Each color's label can be edited.
 2. The renamed label shows for the whole shop - the same picker opened elsewhere shows 'ZZAUTOTEST Rush'.
 3. Shifts and events share the same custom palette with the same labels.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §10 (Color labels are editable per shop), §4.10 (shared picker)</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§10 (Color labels are editable per shop), §4.10 (shared picker))</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Edit Location has a 'Set business hours for this shop' toggle, off by default</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Working Hours Settings</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App with access to location settings.
+2. You open the Edit Location screen for a shop.</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Edit Location screen.
+2. Find the business hours setting and read its default state.
+3. Turn the 'Set business hours for this shop' toggle ON.</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>1. Edit Location shows a toggle labelled 'Set business hours for this shop'.
+2. The toggle is OFF by default (no business hours set).
+3. Turning it ON reveals a per-day working-hours editor for the shop.</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>SV-8699 (§4.2 Working Hours - business hours toggle)</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Edit Location shows a per-day (Mon-Sun) From-To business-hours editor</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Working Hours Settings</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Edit Location screen.
+2. The 'Set business hours for this shop' toggle is ON.</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the per-day rows shown when business hours are ON.
+2. Set a From time and a To time for one day (for example Monday).
+3. Save the location settings.</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>1. There is one row per day of the week, Monday through Sunday.
+2. Each day has a From time and a To time you can set.
+3. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>SV-8699 (§4.2 Working Hours - per-day From/To editor)</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Edit Staff has a 'Set custom hours for this technician' toggle, off by default</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Working Hours Settings</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in with access to staff settings.
+2. You open the Edit Staff Member screen for a technician.</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Edit Staff Member screen for a technician.
+2. Find the custom-hours setting and read its default state.
+3. Turn the 'Set custom hours for this technician' toggle ON.</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>1. Edit Staff Member shows a toggle labelled 'Set custom hours for this technician'.
+2. The toggle is OFF by default (no custom hours set).
+3. Turning it ON reveals a per-day working-hours editor for that technician.</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>SV-8699 (§4.2 Working Hours - technician custom-hours toggle)</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>A technician with no custom hours inherits the shop business hours</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Working Hours Settings</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>1. The shop has business hours set (/02).
+2. A technician has the 'Set custom hours for this technician' toggle OFF.</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>1. Confirm the technician has no custom hours set.
+2. Schedule a shift for that technician and check start-time defaults / before-after-hours conflicts against the shop business hours.</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>1. With no custom hours, the technician's working hours fall back to the shop business hours.
+2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>SV-8699 (§4.2 Working Hours - inherit shop hours when no custom hours)</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>'Add hours' appends a removable second range for split shifts, starting empty</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Working Hours Settings</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>1. You are in the per-day working-hours editor (location or technician) with a day's first range set.</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>1. On one day, click 'Add hours'.
+2. Read the new range that appears.
+3. Set the second range, then remove it.</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>1. 'Add hours' appends an additional From-To range to that day (to support split shifts).
+2. The added range starts empty (no From/To pre-filled).
+3. Each added range can be removed individually.</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>SV-8699 (§4.2 Working Hours - Add hours split shifts)</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Overlapping hour ranges flag red with a message and disable Save</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Working Hours Settings</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>1. You are in the per-day working-hours editor with at least two ranges on one day.</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>1. Set two ranges on the same day so their times overlap.
+2. Look at the offending range and the Save button.</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>1. The offending (overlapping) range is flagged in red.
+2. An inline message reads 'These hours overlap. Adjust the times so they don't conflict.'
+3. Save is disabled while the overlap exists.</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>SV-8699 (§4.2 Working Hours - overlap validation)</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete hour rows (empty From or To) are ignored by the overlap check</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Working Hours Settings</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>1. You are in the per-day working-hours editor with one complete range and one empty added range.</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>1. On one day, add a range but leave its From and/or To empty.
+2. Look at the validation state and the Save button.</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>1. The incomplete row (empty From/To) is ignored by the overlap check - it does not raise the overlap error.
+2. Save is not blocked by an incomplete row on its own (only genuine overlaps disable Save).</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>SV-8699 (§4.2 Working Hours - incomplete rows ignored by overlap check)</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Week Export opens a printable Department-by-Technician week grid</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Week Export and Printing</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Schedule screen in Week view with some shifts scheduled.
+2. Your role has Schedule: View.</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Week Export / Print action for the current week.
+2. Read the exported / printable layout.</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>1. A printable week view opens laid out as a Department-by-Technician grid for the week.
+2. It is formatted for printing (a clean page layout, without the interactive grid controls).</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (design Week Export - V1 scope pending Branko)</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Exported week view lists each department with its technicians and shifts</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Week Export and Printing</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>1. You have opened the Week Export / Print view for a week that has shifts.</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the exported week view.
+2. Check the department grouping, the technician rows, and the shifts shown per day.</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>1. The exported view groups technicians by department, with department headers.
+2. Each technician's shifts for the week appear in the correct day columns.
+3. The week's date range is shown.</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (design Week Export - V1 scope pending Branko)</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Schedule: View grants the full read experience - page, all three views, mini calendar, search, filter, tooltips, read-only modals</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit (assign a suitable system role or a purpose-made custom role; restore after).
 2. Shifts and events exist on the grid, created by an Edit-capable user.
 3. You are signed in AS that View-only user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Open the Schedule page.
 2. Switch between Day, Week, and Month.
@@ -7844,7 +8323,7 @@
 4. Hover a shift for its tooltip, then click it to open the detail modal.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule page opens and all three views work.
 2. The mini calendar, search, and filters all work.
@@ -7852,43 +8331,43 @@
 4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.1 (Schedule: View), §14.3</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14.1 (Schedule: View), §14.3)</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>View-only: every editing affordance is hidden or disabled</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit.
 2. Shifts, a series, and events exist on the grid.
 3. You are signed in AS that View-only user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Look for drag handles on sidebar lines and try to drag a work order card onto the grid.
 2. Try dragging an existing shift block (move/reassign) and look for resize handles in day view.
@@ -7896,7 +8375,7 @@
 4. Open a shift's detail modal and inspect its fields and actions.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. No drag handles are offered and nothing can be dragged from the sidebar onto the grid.
 2. Shift blocks cannot be moved or resized - no drop targets or resize handles appear.
@@ -7904,89 +8383,89 @@
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.1 (Schedule: View - editing affordances hidden or disabled)</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14.1 (Schedule: View - editing affordances hidden or disabled))</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>With Schedule: View OFF, the Schedule top-level nav item is hidden entirely</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View OFF (no Schedule permission).
 2. You are signed in AS that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. Look at the app's main navigation.
 2. Search the nav for any Schedule entry.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule top-level nav item is not shown at all.
 2. The rest of the app works normally for the role.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.1 (When Schedule: View is OFF)</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14.1 (When Schedule: View is OFF))</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Schedule: Edit unlocks all creation and modification interactions</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit (and View) but NOT Delete.
 2. Work orders with approved lines exist; you are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. Drag a work order from the sidebar onto a technician cell and complete the scope picker (and spread modal for a large job).
 2. Right-click a cell and create an event via 'New Event'; in day view, click empty space to create.
@@ -7995,7 +8474,7 @@
 5. Edit fields in the shift and event detail modals.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. Drag-and-drop from the sidebar, the scope picker, and the spread modal all work.
 2. Shift and event creation works, including via the right-click context menu and day-view click-to-create.
@@ -8004,100 +8483,100 @@
 5. Modal fields are editable and save.</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.1 (Schedule: Edit)</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14.1 (Schedule: Edit))</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Edit without Delete: the user can create and modify but cannot remove - delete action and trash icon hidden</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit but NOT Delete.
 2. A shift, a series, and an event exist (some created by this user).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. Open a shift's detail modal and look for the delete action / trash icon.
 2. Open an event's modal and look for a delete action.
 3. Try to find ANY way to remove a shift or event.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. The delete action and the trash icon are hidden in the shift modal.
 2. Events likewise offer no delete.
 3. No path exists to remove shifts or events - while creating and modifying still work.</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.1 (Schedule: Delete - without it)</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14.1 (Schedule: Delete - without it))</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>Schedule: Delete unlocks deleting shifts and events, including the three series-aware scopes</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Delete.
 2. A standalone shift, a series, and an event exist.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Delete a series shift and read the scope options.
 3. Delete the event.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. The delete action is available and works for shifts.
 2. Series deletion offers its scopes (this shift / this and after / whole series).
@@ -8105,389 +8584,389 @@
 4. Undo toasts appear (restore the items via Undo to clean up).</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.1 (Schedule: Delete)</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14.1 (Schedule: Delete))</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>The permission tiers depend on each other: Delete requires Edit, and Edit requires View</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as an admin who can edit custom roles.
 2. A ZZAUTOTEST custom role exists (create one; delete after).</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. In the role's Schedule permissions, try to enable Edit while View is off.
 2. Try to enable Delete while Edit is off.
 3. Enable View, then Edit, then Delete in order.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>1. Edit cannot be granted without View (the admin UI enforces or auto-selects the dependency).
 2. Delete cannot be granted without Edit.
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14 (Delete requires Edit and Edit requires View)</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14 (Delete requires Edit and Edit requires View))</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Schedule access without Work Orders: View - sidebar hides the WO list and drill-down; mini calendar stays; grid shifts remain usable</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF.
 2. Shifts already exist on the grid.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. Look at the left sidebar.
 2. Interact with the shifts already on the grid (hover, open modal, and - if the role has Edit - move one).
 3. Try to find any way to drag a new work order onto the grid.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>1. The sidebar hides the work order list and the line drill-down; the mini calendar remains available.
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
 3. New work orders cannot be dragged on - the WO list is simply not visible.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.2</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>SV-8687 (§14.2)</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>No own-only restriction: every Schedule: View user sees ALL technicians' shifts and events</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. Shifts and events exist for SEVERAL different technicians.
 2. A test user with a low-tier View-only role exists (and is themselves one of the technicians).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. Read the grid across all departments and technicians.
 2. Check 'My Shifts' in 'Filter and Display' is OFF (default).</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.3</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14.3)</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Grid rows are department-based: any staff member in a visible department appears as a row, regardless of role</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. A staff member with a NON-technician role (for example Office) is assigned to a department that is visible on the schedule (set up; restore after).
 2. Another staff member has NO department assignment.
 3. You are signed in on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>1. Look for the department-assigned Office staff member among the grid rows.
 2. Look for the staff member with no department.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
 2. The staff member without a department does not appear as a row.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.4</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§14.4)</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>Clocking into work order line tasks is gated by the staff record's 'Time Clock' setting, not the permission model</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. Two staff members exist: one with the 'Time Clock' setting ON on their staff record, one with it OFF (set up; restore after).
 2. Both appear as schedule rows and have shifts on work order lines.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. As (or with) the Time-Clock-ON staff member, attempt to clock into their work order line task.
 2. As (or with) the Time-Clock-OFF staff member, attempt the same.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>1. The Time-Clock-ON staff member can clock in.
 2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.4 (Time Clock setting)</t>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§14.4 (Time Clock setting))</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>With Work Orders: View OFF, work-order-derived details on shifts (customer, lines, money fields) are hidden or masked</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF (assign a suitable role; restore after).
 2. Shifts already exist on the grid, created by a fully-permissioned user, for units that have customers, scheduled lines, and a VIN.
 3. You are signed in AS that user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. Look at a shift block on the grid and read its text lines.
 2. Hover the shift for its tooltip.
 3. Open the shift's detail modal and read the work-order-derived fields.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>1. Work-order-derived details (customer, the scheduled line list, and any money-bearing fields) are hidden or masked wherever they would normally appear - on the block, in the tooltip, and in the modal.
 2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
 3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §14.2 (Work Orders: View dependency)</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>SV-8687 (§14.2 (Work Orders: View dependency))</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Planned hours across technicians may exceed the estimate - accepted without error</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A work order line with a 40h estimate exists.</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>1. Spread the full estimate onto technician A.
 2. Spread the full estimate of the SAME work order onto technician B.
 3. Look for any warning or error about exceeding the estimate.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>1. Both series are created - 80 planned hours against a 40h estimate is accepted.
 2. No error or blocking warning appears - this is expected behavior because progress is driven by clocked-in time, and scheduled hours, the estimate, and actual hours are three separate quantities that are not forced to reconcile.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §12, §4.5</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>SV-8691 (§12, §4.5)</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>Below 960px the grid scrolls horizontally, and the sidebar collapses on narrow viewports</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in week view with shifts visible.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>1. Resize the browser window to just under 960px wide.
 2. Try to reach the right-hand days of the grid.
 3. Narrow the window further and watch the sidebar.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>1. Below the 960px minimum supported width, the grid scrolls horizontally rather than breaking.
 2. All days remain reachable by horizontal scroll.
@@ -8495,210 +8974,210 @@
 4. No content becomes permanently unreachable and nothing errors.</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §11 (Responsiveness)</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§11 (Responsiveness))</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>The sidebar work order list and line drill-down stay smooth with 50+ items</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. 50 or more open work orders exist (seed ZZAUTOTEST orders if the environment lacks them), including one order with many approved lines.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the full work order list top to bottom quickly.
 2. Open the many-line order's drill-down and scroll it.
 3. Type in the search while the long list is shown.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
 3. Search stays responsive on the long list.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §11 (Performance - virtualization)</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§11 (Performance - virtualization))</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>The grid renders smoothly at full load - 15 technicians × 7 days with several shifts per cell</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. The schedule is loaded to roughly the spec's stated scale: around 15 technician rows across a week with several shifts per cell (seed ZZAUTOTEST shifts as needed).
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the grid vertically and horizontally.
 2. Switch between Day, Week, and Month.
 3. Hover several blocks and open/close a modal.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>1. The grid renders and scrolls smoothly at this scale.
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §11 (Performance)</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Shop closures block the spread step from placing shifts on those days</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§11 (Performance))</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Shop closures do NOT block spread in V1 - shifts can land on closure days</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shop closure (holiday/inventory day) is defined at the shop level on a working weekday inside the planned spread window (set it up; remove after).
 3. A large job (multi-day scope) is ready to spread.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the spread step across the window containing the closure.
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the spread step across a window that contains a shop closure day.
 2. Expand the preview and find the closure day.
 3. Confirm the spread and check the grid.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>1. The preview shows the closure day struck through with its reason.
-2. No shift is placed on the closure day - the series flows around it.
-3. The series' end date extends accordingly (the skipped day's hours land on later working days).</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §12 (Shop closures), §4.5</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>1. The closure day is NOT struck through or skipped by the spread in V1.
+2. A shift CAN be placed on the shop closure day (only weekend days with no business hours are skipped).
+3. The end date follows the normal daily distribution - no extra day is added for the closure.</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>SV-8691 (§12 (Shop closures), §4.5)</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Scheduled hours, the estimate, and actual (clocked) hours are three separate quantities that are not forced to reconcile</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A line has estimate 10h; a technician has 6h scheduled against it and some different amount of time actually clocked (seed what is possible).</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>1. Open the shift's detail modal.
 2. Compare the scheduled hours, the estimate, and the logged/actual time.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>1. All three quantities are shown/derivable and may differ from one another.
 2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md §4.5 (three separate quantities), §12</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>SV-8691 (§4.5 (three separate quantities), §12)</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Schedule V1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule V1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J178"/>
+  <dimension ref="A1:J191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1255,7 +1255,8 @@
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. The list narrows live with each keystroke - no Enter press or apply button is needed.
-2. Deleting characters widens the results again.</t>
+2. Deleting characters widens the results again.
+3. With very many work orders, the list may load further results in pages as you scroll - that is expected, not a fault.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -3524,39 +3525,91 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>Spread past 8 weeks asks to confirm; a series can never exceed 120 shifts</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Multi-Day Spread Scheduling</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. A work order line with a very large hours estimate exists (enough to fill more than 8 weeks of daily shifts - seed one if needed).
+3. You are on the Schedule page.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Drag the large job onto a technician and reach the spread step.
+2. Choose a spread that runs longer than 8 weeks (about 2 months) and try to confirm.
+3. Read the message that appears, then confirm/acknowledge it and continue.
+4. Now try an extreme spread that would create more than 120 daily shifts in one go (raise the hours or extend the finish-by date) and try to confirm.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1. Going past 8 weeks does not silently succeed: a warning about the very long series appears and asks you to confirm before the shifts are created.
+2. After you confirm the warning, the long series is created normally.
+3. A single spread that would create more than 120 daily shifts is refused outright - no confirmation can override it, and no shifts are created for that attempt.
+4. No half-created series is left behind after a refused attempt.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>SV-8691 (§4.5 + tech-plan D8 series caps)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
           <t>Month view renders a series as a continuous banner wrapping across week rows, labeled once, with a faded 'continues' label on later weeks</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Linked Series and Banners</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A multi-week series exists for one technician (spread a 40h+ job first).
 3. You are on the Schedule page in MONTH view showing the series' month.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Find the series on the month grid.
 2. Read the banner across the week rows.
 3. Look at the weekend columns and any skipped or booked days inside the series.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The series renders as one continuous bar wrapping across the week rows.
 2. It is labeled once at the start (including the technician); later weeks show a faded 'continues'-style label instead of repeating the full label.
@@ -3564,50 +3617,50 @@
 4. Visible breaks appear around skipped days and days the technician is otherwise booked.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§4.6 (Month view))</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Week view renders a series as one banner spanning the week's working days, with edge chevrons and a 'week N of M' cue</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Linked Series and Banners</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A multi-week series exists for one technician; on one of its days the technician also has an unrelated booking.
 3. You are on the Schedule page in WEEK view on a middle week of the series.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Find the series banner in the technician's row.
 2. Look at the banner's left and right edges.
 3. Look for the week-position cue and at the day with the other booking.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. One banner spans the working days of that week in the technician's row.
 2. Chevrons at the banner's edges indicate the series continues beyond the visible week (both sides, on a middle week).
@@ -3615,146 +3668,146 @@
 4. The banner breaks around the day the technician is otherwise booked.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§4.6 (Week view))</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Day view shows the series day as a single time-positioned block with a 'part of an M-week job' cue</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Linked Series and Banners</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A multi-week series exists for one technician.
 3. You are on the Schedule page in DAY view on one of the series' days.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Find the series' block on the technician's timeline.
 2. Read its cue text.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The day shows a single time-positioned block (no spanning bar - only one day is visible).
 2. The block carries a cue in the spirit of 'part of an M-week job' indicating it belongs to a longer series.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§4.6 (Day view))</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>A series is a grouping of ordinary daily shifts - capacity, overtime, and conflicts operate on the individual shifts</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Linked Series and Banners</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A series exists for a technician; on one series day the technician also has a second, overlapping shift (set up with Edit permission).
 3. Capacity Bars are on in View Options.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Look at the capacity bar of a day inside the series.
 2. Look at the day with the overlapping second shift.
 3. Open one series shift's detail.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. Each series day contributes its own daily hours to that day's capacity bar (the series is not counted as one lump).
 2. The overlapping day is flagged as a Double-booked conflict, exactly as it would be for standalone shifts.
 3. The detail modal shows that single day's shift (its own day and hours) while indicating it belongs to the series.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§4.6, §8.2)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>A single-line shift block shows three text lines: customer name, unit number, and the line name</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Shift Block Anatomy</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A single-line shift exists on the grid (VIN toggle off).
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Read the shift block's text lines from top to bottom.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. Line 1: the customer name.
 2. Line 2: the unit number.
@@ -3762,344 +3815,344 @@
 4. No work order number appears on the block.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8690 (§4.4)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Whole-order and multi-line-subset shifts both read 'N Lines' on the block - the detail modal spells out the exact scope</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Shift Block Anatomy</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Two shifts exist for a 4-line work order: one whole-order shift (4 lines) and one 2-line subset shift.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Read the last text line of the whole-order shift's block.
 2. Read the last text line of the subset shift's block.
 3. Open each shift's detail modal.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The whole-order block reads '4 Lines'.
 2. The subset block reads '2 Lines' - the block does not distinguish whole-order from subset beyond the count.
 3. Each detail modal lists exactly which lines the shift covers.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8690 (§4.4, §12)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>VIN appears as an extra block line only when the VIN toggle is on, in day and week views only (month omits it)</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Shift Block Anatomy</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A shift exists for a unit that has a VIN.
 3. You are on the Schedule page; the VIN toggle in 'Filter and Display' is OFF.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. In week view, read the shift block (VIN off).
 2. Turn the VIN toggle ON in 'Filter and Display'.
 3. Read the block again in week view, then in day view, then in month view.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. VIN off: the block shows three lines, no VIN.
 2. VIN on: a VIN line is added to the block in week view and day view.
 3. Month view still omits the VIN line even with the toggle on (space constraints).</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8690 (§4.4, §9 (VIN option))</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Shift blocks default to blue; a custom colour can be set per shift</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Shift Block Anatomy</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Two shifts from the SAME work order exist (for example on different technicians), plus one shift from a different work order whose color has been changed.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Look at a newly created shift block's colour.
 2. Open the shift detail modal and set a custom colour via the colour picker.
 3. Compare that shift with another shift from the same work order.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. By default every shift block is blue (the default shift colour).
 2. A custom colour can be assigned per shift via the colour picker in the detail modal.
 3. Colour is per shift - it is NOT tied to the work order, so two shifts from the same order do not automatically share a colour.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8690 (§4.4, §10)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>The conflict icon is the only icon on a shift block - no work order number and no scope icons</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Shift Block Anatomy</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. One normal (unconflicted) shift and one conflicted shift exist (create an overlapping second shift to force a conflict).
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the unconflicted block for icons and a work order number.
 2. Inspect the conflicted block.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The unconflicted block shows NO icons and NO work order number - only its text lines.
 2. The conflicted block shows the conflict (warning) icon on its first line - and that is the only icon that ever appears on a block.
 3. No scope icons distinguish whole-order from subset shifts.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8690 (§4.4)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Shifts whose times do not overlap share a single lane - the row keeps its normal height</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Overlap and Lane Stacking</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. One technician has two shifts on the same day whose time ranges do NOT intersect (for example 8:00-10:00 and 10:00-12:00 back-to-back).
 3. You are on the Schedule page in day view.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Look at the technician's row on that day.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. Both shifts sit in the same single lane, one after the other.
 2. The row stays at its normal height.
 3. No conflict is flagged for back-to-back (non-intersecting) shifts.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8693 (§4.7)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Shifts whose times intersect split into stacked lanes and the row grows to fit</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Overlap and Lane Stacking</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. One technician has two shifts on the same day whose time ranges DO intersect (for example 9:00-12:00 and 10:00-13:00).
 3. You are on the Schedule page in day view.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Look at the technician's row on that day.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The two overlapping shifts render in separate stacked lanes - they never visually collide.
 2. The row grows in height to fit the lanes.
 3. The overlap is also flagged as a Double-booked conflict (stacking reads as 'resolve me').</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8693 (§4.7, §4.11)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Visible lanes cap at 3 - additional overlapping shifts collapse into a '+N more' affordance that opens a popover</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Overlap and Lane Stacking</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. One technician has FIVE mutually overlapping shifts at the same time on the same day (seed ZZAUTOTEST work orders as needed).
 3. You are on the Schedule page in day view.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Count the visible lanes in the technician's row.
 2. Find and click the '+N more' affordance.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. At most 3 lanes are visible.
 2. The remaining overlapping shifts collapse into a '+N more' affordance (here '+2 more').
@@ -4107,295 +4160,295 @@
 4. The hidden shifts can be opened from that popover.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8693 (§4.7)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Lane stacking and the '+N more' overflow apply in day, week, and month views</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Overlap and Lane Stacking</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. One technician has several overlapping shifts on the same day.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. View the day in day view and note the stacking/overflow.
 2. Switch to week view and look at the same day's cell.
 3. Switch to month view and look at the same day.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. All three views handle the overlap without blocks visually colliding.
 2. Week and month views reach the '+N more' overflow sooner than day view (their cells are narrower), but the same cap-and-overflow model applies.
 3. The overflow affordance opens the hidden-shifts popover in each view.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8693 (§4.7)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>A technician can hold multiple shifts on the same day from different work orders</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Overlap and Lane Stacking</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Two different work orders have schedulable lines.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Schedule a shift from work order 1 onto a technician for a given day.
 2. Schedule a shift from work order 2 onto the SAME technician for the SAME day at a non-overlapping time.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. Both shifts are created and shown on the same day for the same technician - multiple same-day shifts are allowed.
 2. With non-overlapping times, no conflict is raised and both share one lane.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8693 (§12 (edge case), §4.7)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Day view auto-scrolls on load and day navigation so the working-day start sits at the left edge (with a small buffer)</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Day View Timeline</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Technicians have configured start times; note the EARLIEST one (or the business-hours start / 7:00 AM if none).
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Switch to day view and look at where the timeline is scrolled to.
 2. Navigate to the next day with the toolbar arrow and look again.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. On load and on each day navigation, the timeline is auto-scrolled so the working-day start sits at the left edge of the visible area, with a small buffer (roughly 30 to 60 minutes) before it.
 2. The start used is the earliest technician's configured start; if no tech hours are set, business hours; otherwise 7:00 AM - so no shifts sit off-screen to the left.
 3. The timeline is not stuck there - it remains a full 24-hour scrollable timeline.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8694 (§4.8 (Auto-scroll to business hours))</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Manual scrolling is not overridden - auto-scroll fires only on load or day navigation</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Day View Timeline</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in day view (already auto-scrolled).</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Manually scroll the timeline to a late-night hour (for example 11:00 PM).
 2. Wait a few seconds and interact with the page without changing the day (hover blocks, open/close a tooltip).
 3. Then navigate to the next day.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Your manual scroll position stays put - nothing jumps you back to the morning while you remain on the same day.
 2. Scrolling works across the entire 24-hour timeline (midnight to midnight).
 3. Only navigating to another day re-triggers the auto-scroll.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8694 (§4.8)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Date and time headers stick to the top of the viewport during vertical scroll (day and week views)</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Day View Timeline</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Enough technician rows exist that the grid scrolls vertically.
 3. You are on the Schedule page in day view.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the grid down so lower technician rows come into view.
 2. Look at the top of the viewport.
 3. Repeat in week view.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. In day view, the date/time header bar stays stuck to the top while the rows scroll beneath it - you always know which time column you are looking at.
 2. The same sticky-header behavior applies in week view.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8694 (§4.8 (Sticky header bar))</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Dragging a shift horizontally moves its start time, snapping to 15-minute intervals</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Day View Timeline</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists on a technician's day-view timeline.
 3. You are on the Schedule page in day view.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Drag the shift block horizontally along the timeline and release at a position between clean quarter-hours.
 2. Open the shift and read its new start time.
 3. Undo via the toast if needed and restore the original time.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The shift moves along the timeline as you drag.
 2. The released start time snaps to a 15-minute interval (for example 9:15, 9:30 - never 9:22).
@@ -4403,50 +4456,50 @@
 4. A toast with Undo appears for the move.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8694 (§4.8 (Horizontal drag), §7 (toast))</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Dragging a shift's left or right edge resizes its duration</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Day View Timeline</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists on a technician's day-view timeline (note its start/end).
 3. You are on the Schedule page in day view.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Drag the shift's RIGHT edge further right and release.
 2. Drag the shift's LEFT edge and release.
 3. Open the shift and read its times.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. Dragging the right edge extends/shortens the end time (start unchanged).
 2. Dragging the left edge adjusts the start time (end unchanged).
@@ -4454,189 +4507,189 @@
 4. The shift's duration on the grid matches the modal's start/end.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8694 (§4.8 (Edge resize))</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>A now line marks the current time on today's day view, with a label on hover</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Day View Timeline</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in day view, on TODAY (click 'Today' if needed).</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the timeline to the current time.
 2. Find the vertical current-time indicator.
 3. Hover over it.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. A vertical line marks the current time on the timeline.
 2. Its position matches the actual clock time.
 3. Hovering it shows a label (the current time).</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8694 (§4.8 (Now line))</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>With the VIN toggle on, day-view lane heights grow so block text is not clipped</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Day View Timeline</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A shift exists for a unit with a VIN.
 3. You are on the Schedule page in day view with the VIN toggle OFF.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Note the height of the shift's lane and that its text fits.
 2. Turn the VIN toggle ON in 'Filter and Display'.
 3. Look at the same lane.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. With VIN on, the lane height grows to accommodate the additional VIN line.
 2. No block text is clipped or cut off.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8694 (§4.8 (Lane height with VIN))</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Clicking a shift opens its detail modal showing customer, unit, VIN (always visible), and the work order id</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Shift Detail Modal</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A shift exists for a unit that has a VIN; the VIN toggle in 'Filter and Display' is OFF.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Click the shift block.
 2. Read the modal's identity section.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. A detail panel opens for the shift.
 2. It shows the customer name, unit number, the VIN (below unit and asset), and the work order id.
 3. The VIN is visible here even though the grid's VIN toggle is off - the modal always shows it.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.9, §9 (VIN always in modal))</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Scheduled date and start/end time pickers work in 15-minute increments</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Shift Detail Modal</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists; its detail modal is open.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Open the start-time picker and read the available options.
 2. Change the start and end times.
@@ -4644,7 +4697,7 @@
 4. Check the block on the grid.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. The time pickers offer 15-minute increments (for example 8:00, 8:15, 8:30, 8:45).
 2. Saving/applying the change updates the shift's times.
@@ -4652,98 +4705,98 @@
 4. The grid block reflects the new date/times.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.9)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>The modal shows the technician and time logged vs estimate progress</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Shift Detail Modal</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A shift exists whose line has some clocked-in time logged against an estimate (seed by clocking a technician in/out if possible).
 3. The shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Read the technician shown.
 2. Read the time-logged vs estimate progress.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. The assigned technician is shown.
 2. A progress indication compares time logged against the estimate (logged hours vs estimated hours).
 3. The numbers are consistent with the line's actual logged time and estimate.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.9)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>The modal shows a scope summary and the scheduled line(s) with number, title, hours, and status only</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Shift Detail Modal</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A multi-line (subset) shift exists covering 2 of a work order's 4 lines.
 3. The shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Read the scope summary.
 2. Read the list of scheduled lines and their figures.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The 'Work Order Lines' section shows the line count and a scope summary of what the shift covers.
 2. Exactly the 2 scheduled lines are listed (not all 4), each showing its line number, title, hours, and a status pill only.
@@ -4751,98 +4804,98 @@
 4. This is where whole-order vs subset scope is spelled out (the grid block only says 'N Lines').</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.9, §4.4)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Estimated hours can be edited inline in the modal</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Shift Detail Modal</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists; its detail modal is open; note the current estimated hours.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Edit the estimated hours inline (change the value).
 2. Confirm/apply the edit.
 3. Re-open the modal and read the estimate.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The estimated hours field is editable directly in the modal.
 2. The new value persists after closing and re-opening.
 3. Dependent displays (progress vs estimate) reflect the new value.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.9 (Estimated hours with inline edit))</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Notes can be added, edited, and deleted per work order from the modal</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Shift Detail Modal</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists; its detail modal is open.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Add a note (text 'ZZAUTOTEST note').
 2. Edit the note's text.
 3. Delete the note.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. The note is added and shown in the modal.
 2. The edit is saved and displayed.
@@ -4850,50 +4903,50 @@
 4. Notes are kept per work order (the same note is visible from another shift of the same work order).</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.9 (Notes: add, edit, and delete per work order))</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>A conflicted shift's modal shows a conflict banner with an 'Adjust' action</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Shift Detail Modal</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A conflicted shift exists (for example double-booked - create an overlap).
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Open the conflicted shift's detail modal.
 2. Read the banner.
 3. Click 'Adjust'.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. A conflict banner is shown in the modal describing the conflict.
 2. It offers an 'Adjust' action.
@@ -4901,98 +4954,98 @@
 4. An unconflicted shift's modal shows no such banner.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.9 (conflict banner + Adjust))</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>The modal offers a Delete (series-aware) action only - there is no Reassign action</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Shift Detail Modal</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete (which includes Edit and View).
 2. A shift exists; its detail modal is open.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Look at the modal's actions.
 2. Confirm there is no 'Reassign' action anywhere in the modal.
 3. Click Delete on a series shift and read what it asks (cancel without deleting).</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. The modal offers a Delete action (a trash icon in the header) and a close (x) icon - and no other actions.
 2. There is no 'Reassign' action in the modal; reassignment is done by dragging a shift to another technician row (covered by its own case).
 3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.9 (Actions), §7)</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Create an event via right-click 'Create Event' on a grid cell</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Right-click a technician's cell on a working day.
 2. Choose 'Create Event' from the context menu.
 3. Fill in a name (for example 'ZZAUTOTEST stand-up'), keep the date/times offered, and save.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. The right-click context menu contains 'Create Event'.
 2. The event modal opens with the clicked cell's technician and date pre-set.
@@ -5000,394 +5053,394 @@
 4. A toast with Undo appears.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>SV-8696 (§4.10, §7 (right-click menu))</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Create an event by clicking empty grid space in day view, with a live preview block and drag-to-resize</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page in DAY view.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Click (or click-drag) an empty spot on a technician's timeline.
 2. While creating, watch the block and try dragging to size it.
 3. Complete the event creation.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. Clicking empty day-view space starts event creation at that time.
 2. A live preview block is shown while creating, and dragging resizes it.
 3. Completing creates the event at the previewed time/duration.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>SV-8696 (§4.10 (day-view click-to-create, live preview))</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Event modal offers name, date, start/end time, an all-day toggle, and a color category</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page with the event modal open (via right-click 'New Event').</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Read the fields the modal offers.
 2. Fill each: name, date, start and end time, and pick a color category.
 3. Save.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. The modal contains: name, date, start/end time, an all-day toggle, and a color category.
 2. The event saves with the entered values.
 3. Re-opening the event shows the saved values.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>SV-8696 (§4.10 (Event modal))</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>The all-day toggle creates an all-day event</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page with the event modal open.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Turn the all-day toggle ON.
 2. Save the event.
 3. Look at how it renders in day and week views.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. With all-day on, specific start/end times are not required (the time fields are disabled or hidden).
 2. The event is created as an all-day block for that technician and day.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>SV-8696 (§4.10, §8.1 (Event allDay field))</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Events can be dragged to another technician or another day</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. An event exists on a technician's day.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Drag the event block to a different technician's row.
 2. Drag it to a different day.
 3. Undo/move back to restore.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. Dropping on another technician reassigns the event to them.
 2. Dropping on another day moves it to that day.
 3. Each move produces a toast with Undo.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>SV-8696 (§4.10 (Drag-and-drop to reassign/move), §7 (toast))</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Event cards are structurally distinct from shift cards - white outlined card with a grey icon chip, no colored left rail</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. An event and a shift sit near each other on the grid.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Compare the event card with the shift block side by side.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The event card is a white/neutral card with a thin, even border on all four sides and NO colored left rail (the left rail is the shift's cue).
 2. It has a small grey-filled rounded chip on the left containing a calendar icon, and two lines of text beside it: the event name, then the time range in secondary text.
 3. The shift reads as a tinted color-filled block with a colored left rail - the two types are separable at a glance, not by color alone.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>SV-8696 (§4.10 (Event card anatomy))</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Events default to neutral/grey; choosing a color tints the card and its icon chip</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A newly created event exists with no color chosen.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Look at the new event's default color.
 2. Open the event and choose a color from the color picker.
 3. Look at the card again.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. The default event color is neutral/grey.
 2. The color picker offers the same custom color palette as shifts (shared picker with editable labels).
 3. Choosing a color tints the card and the icon chip in matching tones, the same way a colored shift is tinted.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>SV-8696 (§4.10 (Event color), §10)</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>An event does not count toward a technician's capacity bar and does not raise a conflict</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Capacity Bars and Events are ON in View Options.
 3. A technician has a shift and, on the same day/time, an event (create both, ZZAUTOTEST).</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Note the day's capacity bar fill with only the shift present.
 2. Add an all-day (or long) event on the same technician and day.
 3. Look at the capacity bar again and check for any conflict on the block and in the toolbar conflict pill.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. Adding the event does NOT change the capacity bar fill - events are not counted toward booked/available hours.
 2. The event does NOT create a double-booked or overlap conflict with the shift, and the toolbar conflict count does not increase because of it.
 3. Only shifts drive capacity and conflicts.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>SV-8696 (§4.10 (Events), §4.11, §4.12)</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Double-booked: two work orders overlapping on the same technician at the same time are flagged</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Two different work orders have schedulable lines.
 3. You are on the Schedule page; note the toolbar conflict pill's current count.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Schedule work order 1 on a technician for a given time.
 2. Schedule work order 2 on the SAME technician overlapping the same time.
 3. Look at the two blocks and the toolbar conflict pill.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. The overlap is detected as a Double-booked conflict.
 2. A warning icon appears on the affected block(s).
@@ -5395,197 +5448,197 @@
 4. The conflict is listed in the pill's dropdown.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>SV-8697 (§4.11 (Double-booked))</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Working-day conflict: a shift on a day outside the technician's configured working days is flagged</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A technician's configured working days are known (for example Monday to Friday); Saturday/Sunday columns are visible (View Options - Saturday and Sunday on).
 3. A schedulable work order line exists.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Drop the line onto that technician's cell on a day OUTSIDE their working days (for example a Saturday when the technician works Monday to Friday).
 2. Look at the block and the conflict pill.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. The shift is created but flagged as a conflict because the day is outside the technician's configured working days (the design's reason sentence reads in the spirit of 'Scheduled on a weekend (outside Mon-Fri)').
 2. If the technician's working days DO include that day (for example Saturday hours are configured), a shift on that day is NOT flagged.
 3. The warning icon appears on the block and the conflict is listed in the toolbar dropdown.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>SV-8697 (§4.11 (Weekend shift))</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Before hours: a shift starting before the technician's configured working-day start is flagged</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A technician has a known working-day start (for example 8:00 AM).
 3. A shift exists for that technician.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. In day view, drag the shift so it starts BEFORE the technician's working-day start (for example 6:00 AM).
 2. Look at the block and the conflict pill.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The shift is flagged as a before-hours conflict (the design's reason sentence reads in the spirit of 'Starts before working hours (8:00 AM)'), measured against the technician's configured working-day start.
 2. The working-day start follows the hierarchy technician hours, then business hours, then the default.
 3. Warning icon on the block; the conflict appears in the toolbar dropdown.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>SV-8697 (§4.11 (Before hours))</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>After hours: a shift extending past the technician's configured working-day end is flagged</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A technician has a known working-day end (for example 5:00 PM).
 3. A shift exists for that technician ending before 5:00 PM.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. In day view, drag the shift's right edge so it extends PAST the working-day end (for example to 7:00 PM).
 2. Look at the block and the conflict pill.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The shift is flagged as an after-hours conflict (the design's reason sentence reads in the spirit of 'Extends past working hours (5:00 PM)'), measured against the technician's configured working-day end.
 2. The working-day end follows the hierarchy technician hours, then business hours, then the default.
 3. Warning icon on the block; the conflict appears in the toolbar dropdown.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>SV-8697 (§4.11 (After hours))</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>The toolbar conflict pill shows the issue count and opens a dropdown listing the conflicts</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. At least two conflicts of different types exist (for example one double-booked overlap and one Saturday shift - create them first).
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Read the conflict pill in the grid toolbar.
 2. Click it.
 3. Read the dropdown.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. The pill shows the current number of scheduling issues.
 2. Clicking opens a dropdown listing each conflict.
@@ -5593,132 +5646,132 @@
 4. Resolving a conflict (for example moving the shift) reduces the count - detection is continuous.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>SV-8697 (§4.11, §6 (Conflict pill))</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Clicking a conflict in the dropdown navigates to the relevant technician and day</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A conflict exists on a technician/day that is NOT currently in view (navigate the grid away first).
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Open the conflict pill's dropdown.
 2. Click the conflict entry.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. The grid navigates to the relevant technician and day.
 2. The conflicted shift is brought into view.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>SV-8697 (§4.11 (Clicking a conflict navigates))</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Red/alarming styling is reserved for conflicts and genuine errors - never used for overtime</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Conflict Detection</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. One technician is booked into OVERTIME on a day WITHOUT any conflict (more hours than their day, sequential non-overlapping shifts within working hours - use the technician's working window carefully, or observe the OT tag day).
 3. Capacity Bars are on.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Look at the overtime signals for that day ('OT' tag, amber highlights).
 2. Look at a conflicted shift for comparison.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. Overtime is signaled with the 'OT' text tag and amber tones - NOT red or alarming styling.
 2. Red/alarming styling appears only for conflicts and genuine errors.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>SV-8697 (§4.11 (styling rule), §4.12)</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Day-column headers show a capacity bar - blue fill = aggregate booked vs total available, clamped at 100%, equal track widths</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Capacity Bars</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Capacity Bars are ON in View Options (default).
@@ -5726,345 +5779,345 @@
 4. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Look at each day column's header bar.
 2. Compare a lightly-booked day with a heavily-booked day.
 3. Compare the bars' track widths across days.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. Each day header shows a capacity bar; the blue fill represents total technician-hours booked divided by total available (sum of all techs' working hours).
 2. A more heavily booked day shows a longer blue fill; the fill never exceeds the track (clamped at 100%).
 3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>SV-8698 (§4.12 (Blue fill))</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>When aggregate hours exceed capacity, an amber spill extends past the track's right edge with a tick at the 100% line</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Capacity Bars</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Capacity Bars are ON.
 3. One day is booked BEYOND the team's total available hours (seed extra shifts).</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Look at that day's capacity bar.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. An amber segment extends past the right edge of the track, showing the excess.
 2. A tick marks the 100% line where the track ends.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>SV-8698 (§4.12 (Amber spill))</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>The 'OT' text tag appears whenever any single technician exceeds their own daily hours - even when the day's aggregate is under capacity</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Capacity Bars</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Capacity Bars are ON.
 3. On one day, a single technician is booked beyond THEIR daily hours while the team's aggregate for that day remains UNDER total capacity (other techs lightly booked).</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Look at that day's capacity bar and header.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. An 'OT' tag appears for the day even though the aggregate bar is under 100%.
 2. The tag is text, not a color-only signal.
 3. Overtime (per-technician) and capacity (aggregate) are independent signals.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>SV-8698 (§4.12 (OT tag), §11 (not color-only))</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Hovering a capacity bar shows a per-technician breakdown, with overtime technicians highlighted in amber</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Capacity Bars</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Capacity Bars are ON; a day exists where one technician is in overtime and others are not.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Hover over that day's capacity bar.
 2. Read the tooltip.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>1. A tooltip shows a per-technician breakdown: assigned hours vs that technician's capacity.
 2. The overtime technician's entry is highlighted in amber.
 3. The numbers agree with the shifts actually on the grid.</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>SV-8698 (§4.12 (Hover tooltip))</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Shift hover tooltip shows customer, unit/vehicle/VIN, date and time, technician, scope, up to 3 line names, and a progress bar</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Hover Tooltips</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A multi-line shift exists covering 5 lines, with some time logged, for a unit that has a VIN.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Hover over the shift block and wait briefly for the tooltip.
 2. Read the tooltip from top to bottom.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. The tooltip shows: the customer name; unit, vehicle, and VIN (the tooltip shows the VIN whenever the unit has one, regardless of the 'VIN Number' toggle); the date and time range; the technician; and a scope summary ('N lines · Xh' style).
 2. The individual line names appear as a short list capped at 3, with a '+N more lines' row for the rest (here '+2 more lines'); line statuses are NOT shown.
 3. A time-logged progress bar shows logged vs estimated hours ('X / Yh' style).</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.13 (Shift tooltip))</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>A conflicted shift's tooltip shows the conflict icon and the conflict reason in amber</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Hover Tooltips</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A conflicted shift exists (for example double-booked).
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Hover the conflicted shift and read the tooltip.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. The customer name line includes the conflict icon.
 2. The conflict reason is shown in amber.</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.13 (Shift tooltip - conflict))</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Event hover tooltip shows the event name with its grey category dot, date and time range, and technician</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Hover Tooltips</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. An event exists on a technician's day.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Hover the event card and read the tooltip.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. The tooltip shows the event name with its category dot (grey for a default event).
 2. The date and time range are shown.
 3. The technician is shown.</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.13 (Event tooltip))</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Tooltips open after a short hover delay, dismiss on mouse-leave, and are read-only - clicking still opens the modal</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Hover Tooltips</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A shift exists on the grid.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Move the mouse quickly across the block without stopping - watch for tooltips.
 2. Rest the pointer on the block and wait briefly.
@@ -6072,7 +6125,7 @@
 4. Click the block.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. A quick pass does not flash tooltips - the tooltip opens only after a short hover delay (spec: roughly 300 to 500ms).
 2. It dismisses when the mouse leaves the block.
@@ -6080,145 +6133,145 @@
 4. Clicking the block opens the full detail modal as normal.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.13 (Behavior))</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>The tooltip flips above the block or shifts horizontally to stay within the viewport - it is never clipped</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Hover Tooltips</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A multi-line shift (tall tooltip) exists near the BOTTOM edge of the viewport, and another near a horizontal edge (scroll to arrange).
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Hover the shift near the bottom edge and look at where its tooltip opens.
 2. Hover the shift near the side edge.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. When there is not enough room below, the tooltip opens ABOVE the block instead.
 2. Near a side edge, the tooltip shifts horizontally to stay fully within the viewport.
 3. No part of the tooltip is clipped off-screen.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§4.13 (flip/shift to stay in viewport))</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>'Today' button jumps the grid to the current date</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Grid Toolbar</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page, navigated several weeks away from today.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. Click the 'Today' button in the grid toolbar.
 2. Look at the grid and the date label.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>1. The grid jumps to the range containing the current date (today's day, this week, or this month depending on the active view).
 2. The date label updates accordingly.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§6 (Today button))</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Left/right arrows navigate by day, week, or month depending on the active range, and the date label shows the current range</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Grid Toolbar</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. In week view, click the right arrow and read the date label.
 2. Switch to day view and click the right arrow.
 3. Switch to month view and click the left arrow.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. Week view: each arrow click moves one whole week; the label shows the week range (spec's example format: 'Jul 14 to 20, 2026').
 2. Day view: each click moves one day; the label shows that day.
@@ -6226,50 +6279,50 @@
 4. The label always matches what the grid displays.</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§6 (Left/right arrows, Date label))</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Toolbar search fades non-matching blocks and highlights matching ones (customer, WO number, unit, technician, line name)</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Grid Toolbar</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Several shifts exist on the visible range for different customers/orders/technicians.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. Type a customer name into the toolbar search; look at the grid.
 2. Clear, then search a work order number, a unit number, a technician name, and a line name in turn.
 3. Clear the search.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>1. Blocks that match the search are highlighted; blocks that do not match fade.
 2. All five fields match: customer name, work order number, unit number, technician name, and line name.
@@ -6277,197 +6330,198 @@
 4. Clearing the search restores all blocks to normal.</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§6 (Search))</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>'Filter &amp; Display' dropdown combines department toggles, My Shifts, and VIN</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Open the 'Filter &amp; Display' dropdown in the grid toolbar.
 2. Read its contents and default states.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown is checkbox style and contains: a toggle per department, 'My Shifts', and 'VIN'.
 2. Defaults: all department toggles ON, 'My Shifts' OFF, 'VIN' OFF.
 3. There is no separate departments-only control - this dropdown replaces it.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§6, §9 (Filter and Display dropdown))</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Department toggles show or hide individual department groups in the grid</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. At least two department groups are visible in the grid.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. In 'Filter and Display', turn OFF one department's toggle.
 2. Look at the grid.
 3. Turn it back ON.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>1. The turned-off department's group (header and technician rows) disappears from the grid.
 2. Other departments are unaffected.
 3. Turning it back on restores the group.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (Department toggles))</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>'My Shifts' filters the grid to only the current user's shifts, hiding all other technician rows</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser as a user who appears as a technician row and has at least one shift.
 2. Other technicians also have shifts on the visible range.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. In 'Filter and Display', turn ON 'My Shifts'.
 2. Look at the grid.
 3. Turn it OFF again.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. Only shifts assigned to you remain visible; all other technician rows and their shifts are hidden.
 2. Turning it off restores the full grid.
-3. This is a personal convenience filter only - it does not change what you are permitted to see (default is OFF, everyone's shifts visible).</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
+3. This is a personal convenience filter only - it does not change what you are permitted to see (default is OFF, everyone's shifts visible).
+4. For a user who has no technician/staff record of their own, the 'My Shifts' option is not shown at all.</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (My Shifts), §14.3)</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>The 'VIN Number' toggle adds the VIN to shift blocks (day/week) only; the hover tooltip and the detail modal always show the VIN</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A shift exists for a unit with a VIN; the VIN toggle is OFF.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. With 'VIN Number' off: read the block, hover for the tooltip, then open the detail modal.
 2. Turn 'VIN Number' ON in 'Filter and Display' and repeat.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. 'VIN Number' off: no VIN line on the block - but the hover tooltip still shows the VIN, and the detail modal still shows the VIN.
 2. 'VIN Number' on: the VIN appears as an additional line on blocks in day and week views (and the day-view lane grows taller to fit it).
@@ -6475,343 +6529,343 @@
 4. Month view blocks never show the VIN.</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (VIN), §4.4)</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>'View Options' popover offers Business Hours, Capacity Bars, Events, Tech Hours, Saturday, Sunday with the spec defaults</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page with no view options changed yet (fresh state).</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. Open 'View Options' in the grid toolbar.
 2. Read each toggle and its state.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>1. Six toggles are offered: Business Hours, Capacity Bars, Events, Tech Hours, Saturday, Sunday.
 2. Defaults: Business Hours OFF, Capacity Bars ON, Events ON, Tech Hours OFF, Saturday ON, Sunday ON.</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§6, §9 (View Options popover))</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Business Hours toggle shades non-working hours in day view</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. The shop has working hours set.
 3. You are on the Schedule page in DAY view with Business Hours OFF.</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Note the timeline background outside working hours.
 2. Turn ON Business Hours in 'View Options'.
 3. Look at the timeline again.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle on, the hours OUTSIDE the working day are shaded with a grey overlay.
 2. Working hours remain unshaded.
 3. Turning it off removes the shading.</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (Business Hours), §4.8 (Business-hours shading))</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Capacity Bars toggle shows and hides the per-day capacity bars</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Shifts exist so capacity bars have fill.
 3. You are on the Schedule page in week view with Capacity Bars ON (default).</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the bars are visible in the day column headers.
 2. Turn OFF Capacity Bars in 'View Options'.
 3. Turn it back ON.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>1. Off: the capacity bars disappear from the column headers.
 2. On: they reappear with the same values.</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (Capacity Bars), §4.12)</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Events toggle shows and hides event blocks on the grid</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. At least one event and one shift exist on the visible range.
 3. You are on the Schedule page with Events ON (default).</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Turn OFF Events in 'View Options'.
 2. Look at the grid.
 3. Turn it back ON.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>1. Off: event blocks disappear from the grid; shifts remain.
 2. On: the events reappear unchanged.</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (Events))</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Tech Hours toggle displays each technician's working hours next to their name</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Technicians have configured working hours.
 3. You are on the Schedule page with Tech Hours OFF (default).</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. Turn ON Tech Hours in 'View Options'.
 2. Look at the technician rows.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>1. Each technician's working hours are displayed next to their name in the row header.
 2. The hours match the technicians' configured hours.
 3. Turning it off hides the hours again.</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (Tech Hours))</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Saturday and Sunday toggles include or exclude the weekend columns</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in WEEK view with Saturday and Sunday ON (default) - 7 columns visible.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Turn OFF Saturday in 'View Options'; look at the grid.
 2. Turn OFF Sunday too; look again.
 3. Turn both back ON.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. Saturday off: the Saturday column is removed (6 columns remain).
 2. Sunday off too: 5 weekday columns remain (Monday to Friday).
 3. Both back on: the full Monday-to-Sunday 7-column week returns.</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (Saturday, Sunday), §3.2 (Week view))</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Dragging a shift to another technician row reassigns it - target tech added to the line's roster, source removed, with a confirmation modal</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists on technician A; note the affected line's roster.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Drag the shift block from technician A's row to technician B's row.
 2. Confirm the move in the confirmation modal.
 3. Check the line's roster on the work order.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. A confirmation modal appears for the cross-technician move.
 2. After confirming, the shift sits on technician B's row.
@@ -6819,290 +6873,290 @@
 4. A toast with Undo appears.</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§7 (Shift reassignment), §12)</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Right-click a grid cell opens a menu with Create Event and New Work Order</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. Right-click a technician's grid cell.
 2. Read the menu items.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>1. A context menu opens at the cell.
 2. It contains: 'Create Event' and 'New Work Order'.
 3. The browser's own right-click menu does not appear instead.</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 (Right-click context menu))</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>'View Day' is no longer offered in the grid cell context menu</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page in week or month view.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. Right-click a technician's grid cell.
 2. Read the menu items.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>1. The context menu shows only 'Create Event' and 'New Work Order'.
 2. There is no 'View Day' item - it was removed from the menu.</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 (Right-click context menu - View Day))</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>'New Shift' is no longer offered in the grid cell context menu</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Schedulable work order lines exist.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. Right-click a technician's grid cell.
 2. Read the menu items.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. The context menu shows only 'Create Event' and 'New Work Order'.
 2. There is no 'New Shift' item - it was removed from the menu.</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 (Right-click context menu - New Shift), §14.1 (creation via context menu))</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>'New Work Order' in the cell menu points the user to the Work Orders tab</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Schedule grid.
 2. The cell context menu shows 'Create Event' and 'New Work Order' ().</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Right-click an empty grid cell.
 2. Choose 'New Work Order' from the menu.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. The menu offers a 'New Work Order' item.
 2. Choosing it directs the user to create a work order (a toast / prompt pointing to the Work Orders tab).
 3. The exact target flow (toast or navigation) is confirmed during live testing.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 / §4.10 New Work Order cell-menu shortcut)</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Deleting a middle shift of a series asks for scope with all three options, each stating the hours returned</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists for one technician.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Delete a MIDDLE shift of the series (via the detail modal's Delete).
 2. Read the scope options offered (do not confirm yet).</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. A scope prompt appears with three options: this shift only, this and everything after, and the whole series.
 2. Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').
 3. The prompt uses routine, lightweight styling - not alarming destructive styling.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (Series-aware deletion))</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>'This shift only' removes that day, the series keeps the gap, and the hours return to the estimate's remaining</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists; note the total scheduled hours.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Delete a middle shift with the 'this shift only' scope.
 2. Look at the series on the grid.
 3. Check the scheduled hours.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. Only that day's shift is removed.
 2. The series keeps the gap - the remaining shifts do NOT shuffle to close it.
@@ -7110,148 +7164,148 @@
 4. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (This shift only))</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>'This and everything after' removes from the clicked shift onward, keeping earlier shifts</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 4 shifts exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Delete the series' THIRD shift with the 'this and everything after' scope.
 2. Look at the series on the grid.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. The third shift and every later shift of the series are removed.
 2. The first two shifts remain untouched.
 3. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (This and everything after))</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>'The whole series' removes all of the series' shifts for that technician</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. The SAME work order has a series on technician A and an independent series on technician B.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Delete one of technician A's series shifts with the 'whole series' scope.
 2. Look at both technicians' rows.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. All of technician A's series shifts are removed.
 2. Technician B's independent series is untouched (the scope is per technician's series).
 3. An undo toast appears.</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (The whole series - 'for that technician'))</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Scope options adapt to position: first and last shifts of a series each show only two options</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Start deleting the FIRST shift of the series; read the options, then cancel.
 2. Start deleting the LAST shift; read the options, then cancel.
 3. Start deleting a MIDDLE shift; read the options, then cancel.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. First shift: two options ('this and after' would equal 'whole series', so only two are shown).
 2. Last shift: two options ('this and after' would equal 'this only').
@@ -7259,91 +7313,91 @@
 4. Cancelling leaves the series unchanged in every case.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (options adapt to position))</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Deleting a standalone (non-series) shift does not ask for a series scope</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A single standalone shift (not part of any series) exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Watch what is asked.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
 2. The shift is deleted and an undo toast appears.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (derived - scope prompt is for series shifts))</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Every create, delete, move, and reassign action produces a toast with an Undo option</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. Schedulable lines and an existing shift are available.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Create a shift - watch for a toast.
 2. Move a shift to another day - watch for a toast.
@@ -7351,98 +7405,98 @@
 4. Delete a shift - watch for a toast.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. Each of the four actions produces a toast notification.
 2. Every toast offers an Undo option.</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>SV-8688 (§7 (Toast notifications), §11 (Undo))</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Toast lasts ~7s with Undo (about 4s without); stays on hover, goes on leave</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Perform an action that shows a toast (for example move a shift) and let the toast sit untouched - time how long it stays.
 2. Trigger another toast and hold the cursor OVER it well past its normal lifetime.
 3. Move the cursor off the toast.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. Untouched, a toast that has an Undo action persists about 7 seconds; a toast without Undo persists about 4 seconds, before dismissing.
 2. While the cursor is over it, the toast stays (does not auto-dismiss).
 3. After the cursor leaves, it dismisses.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>SV-8688 (§7 (Toast notifications), §11 (Undo))</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Undo restores the state before the action - for delete, move, and reassign</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A shift exists; note its technician, day, and time.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. Delete the shift, then click Undo on the toast.
 2. Move the shift to another day, then click Undo.
@@ -7450,7 +7504,7 @@
 4. Check the line's roster after the reassign undo.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. Undo after delete: the shift is back exactly where it was.
 2. Undo after move: the shift returns to its original day/time.
@@ -7458,91 +7512,143 @@
 4. Every destructive action is undoable within the toast's lifetime.</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>SV-8688 (§11 (Undo), §7)</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Schedule actions save immediately - Undo reverses them, closing does not cancel</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Deletion, Series Scopes and Undo</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser with Schedule: Delete.
+2. A shift exists on the grid; note its technician, day, and time.
+3. You are on the Schedule page.</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>1. Delete the shift. While the Undo toast is still showing, refresh the page WITHOUT clicking Undo.
+2. Check the grid for the shift.
+3. Recreate a shift, move it to another day, and again refresh while the toast shows, without clicking Undo.
+4. Finally do one more delete and this time click Undo before the toast disappears.</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>1. The delete took effect immediately: after the refresh the shift is gone even though Undo was never clicked - closing or refreshing does not cancel the action.
+2. The move also stuck after the refresh - the shift is on the new day.
+3. Clicking Undo within the toast's lifetime reverses the action (the deleted shift comes back).
+4. Note for the tester: Undo works by performing a reversing action, not by holding the change back - a change surviving a refresh before Undo is expected, not a bug.</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>SV-8688 (§7 toast/undo + tech-plan D10)</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Escape closes the topmost open modal or popover, following the stacking order</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Open the shift detail modal, then open a popover on top of it (for example the color picker or a filter/search popover elsewhere).
 2. Press Escape once.
 3. Press Escape again.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. The FIRST Escape closes only the topmost layer (the popover), leaving the layer beneath open.
 2. The SECOND Escape closes the next layer down.
 3. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 (Keyboard support - Escape))</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Within the shift modal, Escape first dismisses an open sub-picker before closing the modal itself</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Open the color picker inside the modal, press Escape, and watch.
 2. Open the time picker, press Escape.
@@ -7550,50 +7656,50 @@
 4. With nothing open inside the modal, press Escape.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. Escape with the color picker open closes only the color picker - the modal stays open.
 2. Same for the time picker and the note edit.
 3. Escape with no open sub-picker closes the modal itself.</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 (Escape within the shift modal))</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Enter confirms the active confirmable dialog (delete scope, reassign, spread, event create/edit)</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. Shifts/series and events exist to exercise the dialogs.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step for a large job, press Enter.
 2. Open the reassign dialog for a shift, choose a technician, press Enter.
@@ -7601,241 +7707,241 @@
 4. Open a series delete-scope prompt, select a scope, press Enter.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. In each confirmable dialog, Enter confirms it - equivalent to clicking its confirm action.
 2. The confirmed action takes effect (spread created / reassigned / event saved / delete applied).</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 (Keyboard support - Enter))</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Enter does not fire inside textareas - multiline note editing works normally</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open with the note editor active.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Type a line of note text and press Enter.
 2. Type a second line.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Enter inserts a new line in the note - it does NOT confirm/close the dialog.
 2. The multiline note can be completed and saved normally.</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 (Enter does not fire inside textareas))</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Modals trap focus and all interactive elements are keyboard-reachable</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Press Tab repeatedly and watch where focus goes.
 2. Continue tabbing past the last control in the modal.
 3. Close the modal and Tab through the schedule page's toolbar and sidebar controls.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. Focus moves through the modal's interactive elements with visible focus rings.
 2. Focus stays trapped inside the modal (wraps back to its first control) until the modal closes.
 3. On the page, toolbar and sidebar controls are reachable by keyboard.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§11 (Accessibility))</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Blue is the default color for all shifts, including long and multi-week jobs</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Create a normal single-day shift without touching any color option.
 2. Create a multi-week series without touching any color option.
 3. Look at both on the grid.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. Both the single shift and the multi-week series render in the default blue.
 2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§10)</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Choosing a color from the shift modal's picker recolors the shift with matching background, text, and accent tones</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists; its detail modal is open.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Open the color picker in the modal.
 2. Choose a non-default color.
 3. Look at the block on the grid.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. The shift's block re-renders in the chosen color.
 2. The color provides three consistent tones: background fill, text color, and accent (left border).
 3. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§10, §4.9 (Color picker))</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Color labels are editable per shop</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's or event's color picker is open.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Find the editable label of one color in the picker.
 2. Rename it (for example to 'ZZAUTOTEST Rush').
@@ -7843,479 +7949,479 @@
 4. Restore the original label.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. Each color's label can be edited.
 2. The renamed label shows for the whole shop - the same picker opened elsewhere shows 'ZZAUTOTEST Rush'.
 3. Shifts and events share the same custom palette with the same labels.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§10 (Color labels are editable per shop), §4.10 (shared picker))</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Edit Location has a 'Set business hours for this shop' toggle, off by default</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App with access to location settings.
 2. You open the Edit Location screen for a shop.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Open the Edit Location screen.
 2. Find the business hours setting and read its default state.
 3. Turn the 'Set business hours for this shop' toggle ON.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. Edit Location shows a toggle labelled 'Set business hours for this shop'.
 2. The toggle is OFF by default (no business hours set).
 3. Turning it ON reveals a per-day working-hours editor for the shop.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - business hours toggle)</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Edit Location shows a per-day (Mon-Sun) From-To business-hours editor</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Edit Location screen.
 2. The 'Set business hours for this shop' toggle is ON.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Read the per-day rows shown when business hours are ON.
 2. Set a From time and a To time for one day (for example Monday).
 3. Save the location settings.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. There is one row per day of the week, Monday through Sunday.
 2. Each day has a From time and a To time you can set.
 3. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - per-day From/To editor)</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Edit Staff has a 'Set custom hours for this technician' toggle, off by default</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with access to staff settings.
 2. You open the Edit Staff Member screen for a technician.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Open the Edit Staff Member screen for a technician.
 2. Find the custom-hours setting and read its default state.
 3. Turn the 'Set custom hours for this technician' toggle ON.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. Edit Staff Member shows a toggle labelled 'Set custom hours for this technician'.
 2. The toggle is OFF by default (no custom hours set).
 3. Turning it ON reveals a per-day working-hours editor for that technician.</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - technician custom-hours toggle)</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>A technician with no custom hours inherits the shop business hours</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. The shop has business hours set (/02).
 2. A technician has the 'Set custom hours for this technician' toggle OFF.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the technician has no custom hours set.
 2. Schedule a shift for that technician and check start-time defaults / before-after-hours conflicts against the shop business hours.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. With no custom hours, the technician's working hours fall back to the shop business hours.
 2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - inherit shop hours when no custom hours)</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>'Add hours' appends a removable second range for split shifts, starting empty</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. You are in the per-day working-hours editor (location or technician) with a day's first range set.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. On one day, click 'Add hours'.
 2. Read the new range that appears.
 3. Set the second range, then remove it.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. 'Add hours' appends an additional From-To range to that day (to support split shifts).
 2. The added range starts empty (no From/To pre-filled).
 3. Each added range can be removed individually.</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - Add hours split shifts)</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Overlapping hour ranges flag red with a message and disable Save</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. You are in the per-day working-hours editor with at least two ranges on one day.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Set two ranges on the same day so their times overlap.
 2. Look at the offending range and the Save button.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. The offending (overlapping) range is flagged in red.
 2. An inline message reads 'These hours overlap. Adjust the times so they don't conflict.'
 3. Save is disabled while the overlap exists.</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - overlap validation)</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Incomplete hour rows (empty From or To) are ignored by the overlap check</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. You are in the per-day working-hours editor with one complete range and one empty added range.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. On one day, add a range but leave its From and/or To empty.
 2. Look at the validation state and the Save button.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The incomplete row (empty From/To) is ignored by the overlap check - it does not raise the overlap error.
 2. Save is not blocked by an incomplete row on its own (only genuine overlaps disable Save).</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - incomplete rows ignored by overlap check)</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Week Export opens a printable Department-by-Technician week grid</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Week Export and Printing</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Schedule screen in Week view with some shifts scheduled.
 2. Your role has Schedule: View.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Open the Week Export / Print action for the current week.
 2. Read the exported / printable layout.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. A printable week view opens laid out as a Department-by-Technician grid for the week.
 2. It is formatted for printing (a clean page layout, without the interactive grid controls).</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (design Week Export - V1 scope pending Branko)</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Exported week view lists each department with its technicians and shifts</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Week Export and Printing</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. You have opened the Week Export / Print view for a week that has shifts.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Read the exported week view.
 2. Check the department grouping, the technician rows, and the shifts shown per day.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. The exported view groups technicians by department, with department headers.
 2. Each technician's shifts for the week appear in the correct day columns.
 3. The week's date range is shown.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (design Week Export - V1 scope pending Branko)</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Schedule: View grants the full read experience - page, all three views, mini calendar, search, filter, tooltips, read-only modals</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit (assign a suitable system role or a purpose-made custom role; restore after).
 2. Shifts and events exist on the grid, created by an Edit-capable user.
 3. You are signed in AS that View-only user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. Open the Schedule page.
 2. Switch between Day, Week, and Month.
@@ -8323,7 +8429,7 @@
 4. Hover a shift for its tooltip, then click it to open the detail modal.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule page opens and all three views work.
 2. The mini calendar, search, and filters all work.
@@ -8331,43 +8437,43 @@
 4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.1 (Schedule: View), §14.3)</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>View-only: every editing affordance is hidden or disabled</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit.
 2. Shifts, a series, and events exist on the grid.
 3. You are signed in AS that View-only user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. Look for drag handles on sidebar lines and try to drag a work order card onto the grid.
 2. Try dragging an existing shift block (move/reassign) and look for resize handles in day view.
@@ -8375,7 +8481,7 @@
 4. Open a shift's detail modal and inspect its fields and actions.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. No drag handles are offered and nothing can be dragged from the sidebar onto the grid.
 2. Shift blocks cannot be moved or resized - no drop targets or resize handles appear.
@@ -8383,89 +8489,89 @@
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.1 (Schedule: View - editing affordances hidden or disabled))</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>With Schedule: View OFF, the Schedule top-level nav item is hidden entirely</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View OFF (no Schedule permission).
 2. You are signed in AS that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. Look at the app's main navigation.
 2. Search the nav for any Schedule entry.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule top-level nav item is not shown at all.
 2. The rest of the app works normally for the role.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.1 (When Schedule: View is OFF))</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>Schedule: Edit unlocks all creation and modification interactions</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit (and View) but NOT Delete.
 2. Work orders with approved lines exist; you are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. Drag a work order from the sidebar onto a technician cell and complete the scope picker (and spread modal for a large job).
 2. Right-click a cell and create an event via 'New Event'; in day view, click empty space to create.
@@ -8474,7 +8580,7 @@
 5. Edit fields in the shift and event detail modals.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. Drag-and-drop from the sidebar, the scope picker, and the spread modal all work.
 2. Shift and event creation works, including via the right-click context menu and day-view click-to-create.
@@ -8483,100 +8589,100 @@
 5. Modal fields are editable and save.</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.1 (Schedule: Edit))</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Edit without Delete: the user can create and modify but cannot remove - delete action and trash icon hidden</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit but NOT Delete.
 2. A shift, a series, and an event exist (some created by this user).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. Open a shift's detail modal and look for the delete action / trash icon.
 2. Open an event's modal and look for a delete action.
 3. Try to find ANY way to remove a shift or event.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>1. The delete action and the trash icon are hidden in the shift modal.
 2. Events likewise offer no delete.
 3. No path exists to remove shifts or events - while creating and modifying still work.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.1 (Schedule: Delete - without it))</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Schedule: Delete unlocks deleting shifts and events, including the three series-aware scopes</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Delete.
 2. A standalone shift, a series, and an event exist.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Delete a series shift and read the scope options.
 3. Delete the event.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>1. The delete action is available and works for shifts.
 2. Series deletion offers its scopes (this shift / this and after / whole series).
@@ -8584,389 +8690,389 @@
 4. Undo toasts appear (restore the items via Undo to clean up).</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.1 (Schedule: Delete))</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>The permission tiers depend on each other: Delete requires Edit, and Edit requires View</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as an admin who can edit custom roles.
 2. A ZZAUTOTEST custom role exists (create one; delete after).</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. In the role's Schedule permissions, try to enable Edit while View is off.
 2. Try to enable Delete while Edit is off.
 3. Enable View, then Edit, then Delete in order.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>1. Edit cannot be granted without View (the admin UI enforces or auto-selects the dependency).
 2. Delete cannot be granted without Edit.
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14 (Delete requires Edit and Edit requires View))</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Schedule access without Work Orders: View - sidebar hides the WO list and drill-down; mini calendar stays; grid shifts remain usable</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF.
 2. Shifts already exist on the grid.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>1. Look at the left sidebar.
 2. Interact with the shifts already on the grid (hover, open modal, and - if the role has Edit - move one).
 3. Try to find any way to drag a new work order onto the grid.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>1. The sidebar hides the work order list and the line drill-down; the mini calendar remains available.
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
 3. New work orders cannot be dragged on - the WO list is simply not visible.</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§14.2)</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>No own-only restriction: every Schedule: View user sees ALL technicians' shifts and events</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. Shifts and events exist for SEVERAL different technicians.
 2. A test user with a low-tier View-only role exists (and is themselves one of the technicians).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. Read the grid across all departments and technicians.
 2. Check 'My Shifts' in 'Filter and Display' is OFF (default).</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.3)</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Grid rows are department-based: any staff member in a visible department appears as a row, regardless of role</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>1. A staff member with a NON-technician role (for example Office) is assigned to a department that is visible on the schedule (set up; restore after).
 2. Another staff member has NO department assignment.
 3. You are signed in on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. Look for the department-assigned Office staff member among the grid rows.
 2. Look for the staff member with no department.</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
 2. The staff member without a department does not appear as a row.</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§14.4)</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Clocking into work order line tasks is gated by the staff record's 'Time Clock' setting, not the permission model</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. Two staff members exist: one with the 'Time Clock' setting ON on their staff record, one with it OFF (set up; restore after).
 2. Both appear as schedule rows and have shifts on work order lines.</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>1. As (or with) the Time-Clock-ON staff member, attempt to clock into their work order line task.
 2. As (or with) the Time-Clock-OFF staff member, attempt the same.</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>1. The Time-Clock-ON staff member can clock in.
 2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§14.4 (Time Clock setting))</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>With Work Orders: View OFF, work-order-derived details on shifts (customer, lines, money fields) are hidden or masked</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF (assign a suitable role; restore after).
 2. Shifts already exist on the grid, created by a fully-permissioned user, for units that have customers, scheduled lines, and a VIN.
 3. You are signed in AS that user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>1. Look at a shift block on the grid and read its text lines.
 2. Hover the shift for its tooltip.
 3. Open the shift's detail modal and read the work-order-derived fields.</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>1. Work-order-derived details (customer, the scheduled line list, and any money-bearing fields) are hidden or masked wherever they would normally appear - on the block, in the tooltip, and in the modal.
 2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
 3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§14.2 (Work Orders: View dependency))</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>Planned hours across technicians may exceed the estimate - accepted without error</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A work order line with a 40h estimate exists.</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>1. Spread the full estimate onto technician A.
 2. Spread the full estimate of the SAME work order onto technician B.
 3. Look for any warning or error about exceeding the estimate.</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>1. Both series are created - 80 planned hours against a 40h estimate is accepted.
 2. No error or blocking warning appears - this is expected behavior because progress is driven by clocked-in time, and scheduled hours, the estimate, and actual hours are three separate quantities that are not forced to reconcile.</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§12, §4.5)</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>Below 960px the grid scrolls horizontally, and the sidebar collapses on narrow viewports</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in week view with shifts visible.</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>1. Resize the browser window to just under 960px wide.
 2. Try to reach the right-hand days of the grid.
 3. Narrow the window further and watch the sidebar.</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>1. Below the 960px minimum supported width, the grid scrolls horizontally rather than breaking.
 2. All days remain reachable by horizontal scroll.
@@ -8974,210 +9080,758 @@
 4. No content becomes permanently unreachable and nothing errors.</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§11 (Responsiveness))</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>The sidebar work order list and line drill-down stay smooth with 50+ items</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. 50 or more open work orders exist (seed ZZAUTOTEST orders if the environment lacks them), including one order with many approved lines.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the full work order list top to bottom quickly.
 2. Open the many-line order's drill-down and scroll it.
 3. Type in the search while the long list is shown.</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
 3. Search stays responsive on the long list.</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§11 (Performance - virtualization))</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>The grid renders smoothly at full load - 15 technicians × 7 days with several shifts per cell</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. The schedule is loaded to roughly the spec's stated scale: around 15 technician rows across a week with several shifts per cell (seed ZZAUTOTEST shifts as needed).
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the grid vertically and horizontally.
 2. Switch between Day, Week, and Month.
 3. Hover several blocks and open/close a modal.</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>1. The grid renders and scrolls smoothly at this scale.
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§11 (Performance))</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>Shop closures do NOT block spread in V1 - shifts can land on closure days</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shop closure (holiday/inventory day) is defined at the shop level on a working weekday inside the planned spread window (set it up; remove after).
 3. A large job (multi-day scope) is ready to spread.</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step across a window that contains a shop closure day.
 2. Expand the preview and find the closure day.
 3. Confirm the spread and check the grid.</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>1. The closure day is NOT struck through or skipped by the spread in V1.
 2. A shift CAN be placed on the shop closure day (only weekend days with no business hours are skipped).
 3. The end date follows the normal daily distribution - no extra day is added for the closure.</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§12 (Shop closures), §4.5)</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Scheduled hours, the estimate, and actual (clocked) hours are three separate quantities that are not forced to reconcile</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A line has estimate 10h; a technician has 6h scheduled against it and some different amount of time actually clocked (seed what is possible).</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>1. Open the shift's detail modal.
 2. Compare the scheduled hours, the estimate, and the logged/actual time.</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>1. All three quantities are shown/derivable and may differ from one another.
 2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§4.5 (three separate quantities), §12)</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>A multi-week series keeps the same local start time across the clock change</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Edge Cases and Responsiveness</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. The shop's location observes daylight saving (clocks change); the next clock-change date is known (e.g. the November change).
+3. A job large enough to spread across the clock-change date exists.</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>1. Spread the job across a window that includes the clock-change date (shifts before and after it).
+2. Open shifts from before the change and from after the change and read their start times.</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>1. Every shift in the series starts at the SAME local wall-clock time (e.g. 8:00 AM) on both sides of the clock change.
+2. No shift in the series silently moves an hour earlier or later after the change date.</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>SV-8691 (§4.5 + tech-plan D2 NFR-005 DST)</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Schedule and all its dialogs display correctly in dark mode</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Edge Cases and Responsiveness</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser; the app's dark mode / theme toggle is available.
+2. The Schedule page has shifts, an event, a conflict, and capacity bars visible.</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>1. Switch the app to dark mode.
+2. Look over the Schedule grid: shift blocks, event cards, capacity bars, conflict styling, tooltips.
+3. Open each dialog/popover you can reach (shift detail, event form, spread step, delete scope, filters, view options).
+4. Switch back to light mode and spot-check again.</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>1. In dark mode every part of the Schedule stays readable - no white-on-white or black-on-black text, no unreadable labels or invisible icons.
+2. Every dialog and popover opened from the Schedule follows the dark theme too.
+3. Conflict and overtime cues remain distinguishable (they never rely on colour alone - text/icon still present).
+4. Switching back to light mode restores the normal look with nothing stuck in dark colours.</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (tech-plan §6 checklist 13 dark mode)</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Shifts and events created before the Schedule rewrite still appear after it</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Module and Rewrite Regression</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>1. This case runs around the Schedule rewrite release: before the release, note (or create) a handful of scheduled shifts and calendar events - including at least one future-dated one - with their technician, day, and time.
+2. The release (which replaces the Schedule behind the scenes) has been deployed.</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>1. After the release, open the Schedule and navigate to the dates of the noted entries.
+2. Compare each noted shift and event against what the grid now shows.
+3. Open a couple of them to check their details.</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>1. Every shift and event that existed before the release is still there after it - same technician, same day, same time, same work order.
+2. Events are still events and shifts are still shifts (nothing changed kind or vanished).
+3. Their details open normally and are editable/deletable like any other entry.</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (tech-plan §3 FR-015 data migration)</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard shows one schedule row per work order even with many shifts</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Module and Rewrite Regression</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>1. The Schedule rewrite release is deployed.
+2. One work order has been spread across MANY days for a technician (e.g. a 2-week series - 10+ daily shifts).</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Dashboard and find its schedule/today sections.
+2. Look for the spread work order in those sections.
+3. Count how many rows that one work order produces.</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>1. The Dashboard shows that work order as ONE row (covering the whole scheduled span), not one row per daily shift.
+2. Note for the tester: before this release the Dashboard duplicated such a work order once per scheduled day - showing one combined row now is the intended fix, do not report it as a missing-rows bug.
+3. Work orders with a single shift are unaffected.</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (tech-plan §4 Dashboard FR-016)</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>A work order created with an appointment shows up on the Schedule board</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Module and Rewrite Regression</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>1. The Schedule rewrite release is deployed.
+2. You can create a work order and set its appointment/scheduling details during creation.</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>1. Create a new work order and give it an appointment (a scheduled date/time) as part of the creation flow.
+2. Open the Schedule and navigate to that date.
+3. Find the new work order on the board.</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>1. The appointment created with the work order appears on the Schedule board at the chosen date/time.
+2. It behaves like any other scheduled entry (opens, moves, deletes normally).
+3. It also appears in the Dashboard's schedule section for that day.</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (tech-plan §4 WO-create AppointmentScheduler)</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>A multi-location technician's shift appears only on the work order's location</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Module and Rewrite Regression</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>1. The Schedule rewrite release is deployed.
+2. A technician is enrolled at TWO locations (set this up if needed).
+3. A work order belonging to location A has a shift scheduled on that technician.</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Schedule while working in location A and find the technician's shift.
+2. Switch to location B and open its Schedule for the same date.
+3. Look for the same shift on location B's board.</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>1. The shift appears on location A's board (the location the work order belongs to).
+2. The shift does NOT appear on location B's board, even though the technician is enrolled there too.
+3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (tech-plan §3 WO-primary location resolution)</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Work order form offers a Priority (High/Medium/Low) that drives the sidebar</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Module and Rewrite Regression</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>1. The Schedule rewrite release (which adds the Priority field) is deployed.
+2. You can create/edit a work order.</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order create/edit form and find the Priority field.
+2. Read its default value on a brand-new work order.
+3. Set it to High and save.
+4. Open the Schedule sidebar, find that work order's card, and apply the Priority = High filter.</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>1. The work order form offers a Priority choice of High, Medium, Low.
+2. A new work order has NO priority pre-selected by default.
+3. After saving, the Schedule sidebar reflects the chosen priority and the Priority filter finds the work order under High.
+4. A work order with no priority set simply shows none (it is not treated as an error).</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>SV-8687 (§5.1 + tech-plan FR-P4 WO priority)</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>API - Schedule reads need View; writes need Edit; deletes need Delete (403)</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>API — Schedule</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>1. The Schedule rewrite build (new /api/schedule endpoints) is deployed.
+2. Three test users exist: one with NO Schedule permission, one with Schedule: View only, one with Schedule: View + Edit (but not Delete).
+3. A shift id from the current location is known.</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>1. As the user with NO Schedule permission, call GET /api/schedule/board?from=&amp;to= for the current week.
+2. As the View-only user, call the same GET, then try POST /api/schedule/shifts (a minimal single-shift body) and PATCH /api/schedule/shifts/{id}.
+3. As the View+Edit user, repeat the POST and PATCH, then try DELETE /api/schedule/shifts/{id}?scope=shift.</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>1. No Schedule permission: the board GET is refused with HTTP 403.
+2. View-only: the board GET returns HTTP 200 with the grid data; the POST and PATCH are refused with HTTP 403.
+3. View + Edit: the POST and PATCH succeed (HTTP 201/200); the DELETE is refused with HTTP 403 because the user lacks Schedule: Delete.
+4. Each refusal is a clean 403 response - never a server error.</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14 + tech-plan §4 NFR-003 permissions)</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>API - Series past 8 weeks returns 409 until acknowledged; over 120 shifts 422</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>API — Schedule</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>1. The Schedule rewrite build is deployed; an API session with Schedule: Edit exists.
+2. A schedulable work order line id and a technician staff id are known.</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/schedule/shifts with a spread whose window exceeds 8 weeks (56 calendar days), WITHOUT acknowledgeLongSeries.
+2. Repeat the same POST with acknowledgeLongSeries=true.
+3. POST a spread that would materialize MORE than 120 shifts in one request, with acknowledgeLongSeries=true.
+4. Check the board for leftovers after the refused calls.</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>1. The over-8-week create is refused with HTTP 409 (a 'series too long' error) - nothing is created.
+2. With acknowledgeLongSeries=true the same request succeeds (HTTP 201) and returns the full materialized series under one series id.
+3. The over-120-shift request is refused with HTTP 422 even WITH the acknowledgement - the hard cap cannot be overridden.
+4. Refused calls leave no partial series behind.</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>SV-8691 (§4.5 + tech-plan D8 error cases)</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>API - No pricing fields in Schedule responses; WO details need Work Orders View</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>API — Schedule</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>1. The Schedule rewrite build is deployed.
+2. A shift covering work order lines exists.
+3. Two API users: one with Schedule: View + Work Orders: View, one with Schedule: View but WITHOUT Work Orders: View.</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>1. As the full user, call GET /api/schedule/board, GET /api/schedule/shifts/{id}, and GET /api/schedule/work-orders and search the raw responses for money fields (price, cost, rate, total, $ amounts).
+2. As the user WITHOUT Work Orders: View, call GET /api/schedule/board and GET /api/schedule/shifts/{id} and read the work-order-derived fields (customer, unit, VIN, lines).</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>1. No Schedule response contains any pricing/money field for ANY caller - the schedule never returns labor, totals, or dollar amounts.
+2. For the caller without Work Orders: View, the work-order-derived details (customer, unit, VIN, line names) are absent/empty in the response itself - not just hidden on screen.
+3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14 + tech-plan D6/NFR-002 no pricing)</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>API - A shift from another location returns 404, not another shop's data</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>API — Schedule</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>1. The Schedule rewrite build is deployed.
+2. Two locations exist; a shift exists at location B; your API session is scoped to location A.
+3. The location-B shift's id is known (create it while switched to B, then switch back to A).</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>1. While scoped to location A, call GET /api/schedule/shifts/{id} with the location-B shift id.
+2. Also try PATCH /api/schedule/shifts/{id} on the same id.
+3. Call GET /api/schedule/board for location A's current week.</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>1. The foreign-location GET is refused as not found (HTTP 404) - the response reveals nothing about the other location's shift.
+2. The PATCH on the foreign id is refused the same way (404) - no cross-location edit is possible.
+3. Location A's board contains only location A's shifts - nothing from location B leaks in.</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (tech-plan NFR-001 location scoping)</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -3261,7 +3261,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Month view renders a series as a continuous banner wrapping across week rows, labeled once, with a faded 'continues' label on later weeks</t>
+          <t>Month view: series banner wraps across weeks, labeled once, then 'continues'</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3290,15 +3290,14 @@
         <is>
           <t>1. Find the series on the month grid.
 2. Read the banner across the week rows.
-3. Look at the weekend columns and any skipped or booked days inside the series.</t>
+3. Look at the weekend columns inside the series.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The series renders as one continuous bar wrapping across the week rows.
 2. It is labeled once at the start (including the technician); later weeks show a faded 'continues'-style label instead of repeating the full label.
-3. Weekend columns inside the series are empty (no bar).
-4. Visible breaks appear around skipped days and days the technician is otherwise booked.</t>
+3. Weekend columns inside the series are empty (no bar) when no business hours are set for those weekend days.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3312,7 +3311,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Week view renders a series as one banner spanning the week's working days, with edge chevrons and a 'week N of M' cue</t>
+          <t>Week view: series banner spans the week, with chevrons and 'week N of M'</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3348,8 +3347,7 @@
         <is>
           <t>1. One banner spans the working days of that week in the technician's row.
 2. Chevrons at the banner's edges indicate the series continues beyond the visible week (both sides, on a middle week).
-3. A 'week N of M' cue shows the position within the series.
-4. The banner breaks around the day the technician is otherwise booked.</t>
+3. A 'week N of M' cue shows the position within the series.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4047,7 +4045,7 @@
         <is>
           <t>1. A vertical line marks the current time on the timeline.
 2. Its position matches the actual clock time.
-3. Hovering it shows a label (the current time).</t>
+3. Hovering the now line while your pointer is over the grid shows a label (the current time).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4410,7 +4408,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>The modal offers a Delete (series-aware) action only - there is no Reassign action</t>
+          <t>Shift modal offers Delete only - there is no Reassign action</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4450,7 +4448,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>SV-8695 (§4.9 (Actions), §7)</t>
+          <t>SV-8695 (§4.9 (Actions - Delete only; Reassign removed in Confluence v23), §7)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4459,7 +4457,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Create an event via right-click 'Create Event' on a grid cell</t>
+          <t>Create an event via left-click 'Create Event' on empty grid space</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4485,14 +4483,14 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>1. Right-click a technician's cell on a working day.
-2. Choose 'Create Event' from the context menu.
+          <t>1. Left-click an empty spot in a technician's cell on a working day (not on an existing block).
+2. Choose 'Create Event' from the menu that opens.
 3. Fill in a name (for example 'ZZAUTOTEST stand-up'), keep the date/times offered, and save.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. The right-click context menu contains 'Create Event'.
+          <t>1. A menu opens at the spot you clicked and contains 'Create Event'.
 2. The event modal opens with the clicked cell's technician and date pre-set.
 3. Saving creates an event block on that technician's day.
 4. A toast with Undo appears.</t>
@@ -4500,7 +4498,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>SV-8696 (§4.10, §7 (right-click menu))</t>
+          <t>SV-8696 (§4.10 (left-click menu on empty grid space), §7)</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4509,7 +4507,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Create an event by clicking empty grid space in day view, with a live preview block and drag-to-resize</t>
+          <t>Day view event creation shows a live preview block you can drag to resize</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4535,21 +4533,21 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>1. Click (or click-drag) an empty spot on a technician's timeline.
+          <t>1. Left-click an empty spot on a technician's timeline and choose 'Create Event' from the menu that opens.
 2. While creating, watch the block and try dragging to size it.
 3. Complete the event creation.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1. Clicking empty day-view space starts event creation at that time.
+          <t>1. Left-clicking empty day-view space opens the cell menu; choosing 'Create Event' starts creation at the time you clicked.
 2. A live preview block is shown while creating, and dragging resizes it.
 3. Completing creates the event at the previewed time/duration.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>SV-8696 (§4.10 (day-view click-to-create, live preview))</t>
+          <t>SV-8696 (§4.10 (left-click menu entry; day-view live preview, drag-to-resize))</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4579,7 +4577,7 @@
       <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
-2. You are on the Schedule page with the event modal open (via right-click 'Create Event').</t>
+2. You are on the Schedule page with the event modal open (left-click empty grid space, then 'Create Event').</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4758,7 +4756,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>An event does not count toward a technician's capacity bar and does not raise a conflict</t>
+          <t>An event's hours count toward the capacity bar but raise no conflict</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4792,14 +4790,14 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1. Adding the event does NOT change the capacity bar fill - events are not counted toward booked/available hours.
+          <t>1. Adding the event DOES increase that day's capacity bar fill - the event's hours are counted alongside shift hours (a 2-hour meeting uses up 2 hours of the technician's available time).
 2. The event does NOT create a double-booked or overlap conflict with the shift, and the toolbar conflict count does not increase because of it.
-3. Only shifts drive capacity and conflicts.</t>
+3. The two behave differently on purpose: an event uses up capacity, but it is never flagged as a conflict.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>SV-8696 (§4.10 (Events), §4.11, §4.12)</t>
+          <t>SV-8696 (§4.10 (Events), §4.11 (events not conflict-checked), §4.12 (event time included in the utilization total))</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4943,15 +4941,15 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>1. The shift is flagged as a before-hours conflict (the design's reason sentence reads in the spirit of 'Starts before working hours (8:00 AM)'), measured against the technician's configured working-day start.
-2. The shift is flagged as an after-hours conflict (the design's reason sentence reads in the spirit of 'Extends past working hours (5:00 PM)'), measured against the technician's configured working-day end.
-3. Both the start and the end follow the hierarchy technician hours, then business hours, then the default.
+          <t>1. The shift is flagged as a before-hours conflict, with a reason sentence in the spirit of 'Starts before working hours', measured against that technician's own configured working-day START time (not a fixed hour).
+2. The shift is flagged as an after-hours conflict, with a reason sentence in the spirit of 'Extends past working hours', measured against that technician's own configured working-day END time (not a fixed hour).
+3. Both the start and the end follow the hierarchy technician hours, then shop business hours, then the general default working day of 7:00 AM to 7:00 PM.
 4. Warning icon on the block in each case; the conflict appears in the toolbar dropdown.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>SV-8697 (§4.11 (Before hours, After hours))</t>
+          <t>SV-8697 (§4.11 (Before hours, After hours), §4.2 (working-hours hierarchy; 7:00 AM to 7:00 PM default))</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -5107,7 +5105,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Day-column headers show a capacity bar - blue fill = aggregate booked vs total available, clamped at 100%, equal track widths</t>
+          <t>Capacity bar fill = booked (shifts + events) vs available, clamped, equal tracks</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5142,14 +5140,14 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1. Each day header shows a capacity bar; the blue fill represents total technician-hours booked divided by total available (sum of all techs' working hours).
+          <t>1. Each day header shows a capacity bar; the blue fill represents total technician-hours booked - shift hours PLUS event hours - divided by total available (sum of all techs' working hours).
 2. A more heavily booked day shows a longer blue fill; the fill never exceeds the track (clamped at 100%).
 3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>SV-8698 (§4.12 (Blue fill))</t>
+          <t>SV-8698 (§4.12 (Blue fill - aggregate booked = shifts plus events))</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -6148,7 +6146,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Right-click a grid cell opens a menu with Create Event and New Work Order</t>
+          <t>Left-click empty grid space opens a menu: Create Event and New Work Order</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -6175,22 +6173,22 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>1. Right-click a technician's grid cell.
+          <t>1. Left-click an empty spot in a technician's grid cell (not on an existing shift or event block).
 2. Read the menu items.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>1. A context menu opens at the cell.
+          <t>1. A dropdown menu opens at the spot you clicked.
 2. It contains ONLY two items: 'Create Event' and 'New Work Order'.
 3. There is no 'View Day' item - it was removed from the menu.
 4. There is no 'New Shift' item - it was removed from the menu.
-5. The browser's own right-click menu does not appear instead.</t>
+5. This menu is opened by a normal left-click - right-clicking the cell does not open it.</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>SV-8700 (§7 (Right-click context menu; View Day and New Shift removed), §14.1 (creation via context menu))</t>
+          <t>SV-8700 (§7 (left-click menu on empty grid space; View Day and New Shift removed), §14.1 (creation via the cell menu))</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -6220,12 +6218,12 @@
       <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Schedule grid.
-2. The cell context menu shows 'Create Event' and 'New Work Order' ().</t>
+2. The cell menu already shows 'Create Event' and 'New Work Order'.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>1. Right-click an empty grid cell.
+          <t>1. Left-click an empty spot in a grid cell.
 2. Choose 'New Work Order' from the menu.</t>
         </is>
       </c>
@@ -7382,7 +7380,7 @@
         <is>
           <t>1. Look for drag handles on sidebar lines and try to drag a work order card onto the grid.
 2. Try dragging an existing shift block (move/reassign) and look for resize handles in day view.
-3. Right-click a grid cell.
+3. Left-click an empty spot in a grid cell.
 4. Open a shift's detail modal and inspect its fields and actions.</t>
         </is>
       </c>
@@ -7390,7 +7388,7 @@
         <is>
           <t>1. No drag handles are offered and nothing can be dragged from the sidebar onto the grid.
 2. Shift blocks cannot be moved or resized - no drop targets or resize handles appear.
-3. The right-click context menu does not appear (no creation entries - no 'Create Event' and no 'New Work Order').
+3. No creation menu opens at all - there is no 'Create Event' and no 'New Work Order' offered.
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.</t>
         </is>
       </c>
@@ -7479,7 +7477,7 @@
       <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Drag a work order from the sidebar onto a technician cell and complete the scope picker (and spread modal for a large job).
-2. Right-click a cell and create an event via 'Create Event'; in day view, click empty space to create.
+2. Left-click an empty spot in a cell and create an event via 'Create Event'; do the same on the timeline in day view.
 3. Reassign a shift between technicians by dragging.
 4. In day view, edge-resize and horizontally drag a shift.
 5. Edit fields in the shift and event detail modals.</t>
@@ -7488,7 +7486,7 @@
       <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. Drag-and-drop from the sidebar, the scope picker, and the spread modal all work.
-2. Shift and event creation works, including via the right-click context menu and day-view click-to-create.
+2. Shift and event creation works, including via the menu opened by left-clicking empty grid space in both week and day view.
 3. Reassignment between technicians works.
 4. Edge-resize and horizontal drag work in day view.
 5. Modal fields are editable and save.</t>
@@ -8235,7 +8233,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (tech-plan §6 checklist 13 dark mode)</t>
+          <t>SV-8685 (§11 (Dark theme - user-selectable Light / Dark, persisted per user))</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr"/>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:J165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7248,12 +7248,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Week Export opens a printable Department-by-Technician week grid</t>
+          <t>Schedule: View grants the full read experience - page, all three views, mini calendar, search, filter, tooltips, read-only modals</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Week Export and Printing</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7263,68 +7263,17 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Schedule screen in Week view with some shifts scheduled.
-2. Your role has Schedule: View.</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Week Export / Print action for the current week.
-2. Read the exported / printable layout.
-3. Check the department grouping, the technician rows, and the shifts shown per day.</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>1. A printable week view opens laid out as a Department-by-Technician grid for the week.
-2. It is formatted for printing (a clean page layout, without the interactive grid controls).
-3. The exported view groups technicians by department, with department headers.
-4. Each technician's shifts for the week appear in the correct day columns.
-5. The week's date range is shown.</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>SV-8685 (design Week Export - V1 scope pending Branko)</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Schedule: View grants the full read experience - page, all three views, mini calendar, search, filter, tooltips, read-only modals</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit (assign a suitable system role or a purpose-made custom role; restore after).
 2. Shifts and events exist on the grid, created by an Edit-capable user.
 3. You are signed in AS that View-only user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Open the Schedule page.
 2. Switch between Day, Week, and Month.
@@ -7332,7 +7281,7 @@
 4. Hover a shift for its tooltip, then click it to open the detail modal.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule page opens and all three views work.
 2. The mini calendar, search, and filters all work.
@@ -7340,43 +7289,43 @@
 4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.1 (Schedule: View), §14.3)</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>View-only: every editing affordance is hidden or disabled</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit.
 2. Shifts, a series, and events exist on the grid.
 3. You are signed in AS that View-only user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Look for drag handles on sidebar lines and try to drag a work order card onto the grid.
 2. Try dragging an existing shift block (move/reassign) and look for resize handles in day view.
@@ -7384,7 +7333,7 @@
 4. Open a shift's detail modal and inspect its fields and actions.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. No drag handles are offered and nothing can be dragged from the sidebar onto the grid.
 2. Shift blocks cannot be moved or resized - no drop targets or resize handles appear.
@@ -7392,9 +7341,56 @@
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.</t>
         </is>
       </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 (§14.1 (Schedule: View - editing affordances hidden or disabled))</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>With Schedule: View OFF, the Schedule top-level nav item is hidden entirely</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>1. A test user's role has Schedule: View OFF (no Schedule permission).
+2. You are signed in AS that user on a desktop browser.</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at the app's main navigation.
+2. Search the nav for any Schedule entry.</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>1. The Schedule top-level nav item is not shown at all.
+2. The rest of the app works normally for the role.</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14.1 (Schedule: View - editing affordances hidden or disabled))</t>
+          <t>SV-8685 (§14.1 (When Schedule: View is OFF))</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
@@ -7403,7 +7399,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>With Schedule: View OFF, the Schedule top-level nav item is hidden entirely</t>
+          <t>Schedule: Edit unlocks all creation and modification interactions</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7413,7 +7409,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -7422,59 +7418,12 @@
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>1. A test user's role has Schedule: View OFF (no Schedule permission).
-2. You are signed in AS that user on a desktop browser.</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>1. Look at the app's main navigation.
-2. Search the nav for any Schedule entry.</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>1. The Schedule top-level nav item is not shown at all.
-2. The rest of the app works normally for the role.</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>SV-8685 (§14.1 (When Schedule: View is OFF))</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Schedule: Edit unlocks all creation and modification interactions</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit (and View) but NOT Delete.
 2. Work orders with approved lines exist; you are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Drag a work order from the sidebar onto a technician cell and complete the scope picker (and spread modal for a large job).
 2. Left-click an empty spot in a cell and create an event via 'Create Event'; do the same on the timeline in day view.
@@ -7483,7 +7432,7 @@
 5. Edit fields in the shift and event detail modals.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. Drag-and-drop from the sidebar, the scope picker, and the spread modal all work.
 2. Shift and event creation works, including via the menu opened by left-clicking empty grid space in both week and day view.
@@ -7492,100 +7441,100 @@
 5. Modal fields are editable and save.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.1 (Schedule: Edit))</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Edit without Delete: the user can create and modify but cannot remove - delete action and trash icon hidden</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit but NOT Delete.
 2. A shift, a series, and an event exist (some created by this user).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Open a shift's detail modal and look for the delete action / trash icon.
 2. Open an event's modal and look for a delete action.
 3. Try to find ANY way to remove a shift or event.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. The delete action and the trash icon are hidden in the shift modal.
 2. Events likewise offer no delete.
 3. No path exists to remove shifts or events - while creating and modifying still work.</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.1 (Schedule: Delete - without it))</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Schedule: Delete unlocks deleting shifts and events, including the three series-aware scopes</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Delete.
 2. A standalone shift, a series, and an event exist.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Delete a series shift and read the scope options.
 3. Delete the event.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. The delete action is available and works for shifts.
 2. Series deletion offers its scopes (this shift / this and after / whole series).
@@ -7593,204 +7542,251 @@
 4. Undo toasts appear (restore the items via Undo to clean up).</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.1 (Schedule: Delete))</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>The permission tiers depend on each other: Delete requires Edit, and Edit requires View</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as an admin who can edit custom roles.
 2. A ZZAUTOTEST custom role exists (create one; delete after).</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. In the role's Schedule permissions, try to enable Edit while View is off.
 2. Try to enable Delete while Edit is off.
 3. Enable View, then Edit, then Delete in order.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. Edit cannot be granted without View (the admin UI enforces or auto-selects the dependency).
 2. Delete cannot be granted without Edit.
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14 (Delete requires Edit and Edit requires View))</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Schedule access without Work Orders: View - sidebar hides the WO list and drill-down; mini calendar stays; grid shifts remain usable</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF.
 2. Shifts already exist on the grid.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Look at the left sidebar.
 2. Interact with the shifts already on the grid (hover, open modal, and - if the role has Edit - move one).
 3. Try to find any way to drag a new work order onto the grid.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. The sidebar hides the work order list and the line drill-down; the mini calendar remains available.
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
 3. New work orders cannot be dragged on - the WO list is simply not visible.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§14.2)</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>No own-only restriction: every Schedule: View user sees ALL technicians' shifts and events</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. Shifts and events exist for SEVERAL different technicians.
 2. A test user with a low-tier View-only role exists (and is themselves one of the technicians).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Read the grid across all departments and technicians.
 2. Check 'My Shifts' in 'Filter and Display' is OFF (default).</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14.3)</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Grid rows are department-based: any staff member in a visible department appears as a row, regardless of role</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. A staff member with a NON-technician role (for example Office) is assigned to a department that is visible on the schedule (set up; restore after).
 2. Another staff member has NO department assignment.
 3. You are signed in on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Look for the department-assigned Office staff member among the grid rows.
 2. Look for the staff member with no department.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
 2. The staff member without a department does not appear as a row.</t>
         </is>
       </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§14.4)</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Clocking into work order line tasks is gated by the staff record's 'Time Clock' setting, not the permission model</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>1. Two staff members exist: one with the 'Time Clock' setting ON on their staff record, one with it OFF (set up; restore after).
+2. Both appear as schedule rows and have shifts on work order lines.</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>1. As (or with) the Time-Clock-ON staff member, attempt to clock into their work order line task.
+2. As (or with) the Time-Clock-OFF staff member, attempt the same.</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>1. The Time-Clock-ON staff member can clock in.
+2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>SV-8686 (§14.4)</t>
+          <t>SV-8686 (§14.4 (Time Clock setting))</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
@@ -7799,7 +7795,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Clocking into work order line tasks is gated by the staff record's 'Time Clock' setting, not the permission model</t>
+          <t>With Work Orders: View OFF, work-order-derived details on shifts (customer, lines, money fields) are hidden or masked</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7809,125 +7805,78 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>1. Two staff members exist: one with the 'Time Clock' setting ON on their staff record, one with it OFF (set up; restore after).
-2. Both appear as schedule rows and have shifts on work order lines.</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>1. As (or with) the Time-Clock-ON staff member, attempt to clock into their work order line task.
-2. As (or with) the Time-Clock-OFF staff member, attempt the same.</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>1. The Time-Clock-ON staff member can clock in.
-2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>SV-8686 (§14.4 (Time Clock setting))</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>With Work Orders: View OFF, work-order-derived details on shifts (customer, lines, money fields) are hidden or masked</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF (assign a suitable role; restore after).
 2. Shifts already exist on the grid, created by a fully-permissioned user, for units that have customers, scheduled lines, and a VIN.
 3. You are signed in AS that user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Look at a shift block on the grid and read its text lines.
 2. Hover the shift for its tooltip.
 3. Open the shift's detail modal and read the work-order-derived fields.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Work-order-derived details (customer, the scheduled line list, and any money-bearing fields) are hidden or masked wherever they would normally appear - on the block, in the tooltip, and in the modal.
 2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
 3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§14.2 (Work Orders: View dependency))</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Below 960px the grid scrolls horizontally, and the sidebar collapses on narrow viewports</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in week view with shifts visible.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Resize the browser window to just under 960px wide.
 2. Try to reach the right-hand days of the grid.
 3. Narrow the window further and watch the sidebar.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. Below the 960px minimum supported width, the grid scrolls horizontally rather than breaking.
 2. All days remain reachable by horizontal scroll.
@@ -7935,159 +7884,206 @@
 4. No content becomes permanently unreachable and nothing errors.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§11 (Responsiveness))</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>The sidebar work order list and line drill-down stay smooth with 50+ items</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. 50 or more open work orders exist (seed ZZAUTOTEST orders if the environment lacks them), including one order with many approved lines.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the full work order list top to bottom quickly.
 2. Open the many-line order's drill-down and scroll it.
 3. Type in the search while the long list is shown.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
 3. Search stays responsive on the long list.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§11 (Performance - virtualization))</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>The grid renders smoothly at full load - 15 technicians × 7 days with several shifts per cell</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. The schedule is loaded to roughly the spec's stated scale: around 15 technician rows across a week with several shifts per cell (seed ZZAUTOTEST shifts as needed).
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the grid vertically and horizontally.
 2. Switch between Day, Week, and Month.
 3. Hover several blocks and open/close a modal.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. The grid renders and scrolls smoothly at this scale.
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§11 (Performance))</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Shop closures do NOT block spread in V1 - shifts can land on closure days</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shop closure (holiday/inventory day) is defined at the shop level on a working weekday inside the planned spread window (set it up; remove after).
 3. A large job (multi-day scope) is ready to spread.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step across a window that contains a shop closure day.
 2. Expand the preview and find the closure day.
 3. Confirm the spread and check the grid.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. The closure day is NOT struck through or skipped by the spread in V1.
 2. A shift CAN be placed on the shop closure day (only weekend days with no business hours are skipped).
 3. The end date follows the normal daily distribution - no extra day is added for the closure.</t>
         </is>
       </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>SV-8691 (§12 (Shop closures), §4.5)</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled hours, the estimate, and actual (clocked) hours are three separate quantities that are not forced to reconcile</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Edge Cases and Responsiveness</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. A line has estimate 10h; a technician has 6h scheduled against it and some different amount of time actually clocked (seed what is possible).</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the shift's detail modal.
+2. Compare the scheduled hours, the estimate, and the logged/actual time.</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>1. All three quantities are shown/derivable and may differ from one another.
+2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>SV-8691 (§12 (Shop closures), §4.5)</t>
+          <t>SV-8691 (§4.5 (three separate quantities), §12)</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
@@ -8096,7 +8092,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Scheduled hours, the estimate, and actual (clocked) hours are three separate quantities that are not forced to reconcile</t>
+          <t>A multi-week series keeps the same local start time across the clock change</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -8111,111 +8107,64 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in on a desktop browser with Schedule: Edit.
-2. A line has estimate 10h; a technician has 6h scheduled against it and some different amount of time actually clocked (seed what is possible).</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the shift's detail modal.
-2. Compare the scheduled hours, the estimate, and the logged/actual time.</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>1. All three quantities are shown/derivable and may differ from one another.
-2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>SV-8691 (§4.5 (three separate quantities), §12)</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>A multi-week series keeps the same local start time across the clock change</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>Edge Cases and Responsiveness</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. The shop's location observes daylight saving (clocks change); the next clock-change date is known (e.g. the November change).
 3. A job large enough to spread across the clock-change date exists.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Spread the job across a window that includes the clock-change date (shifts before and after it).
 2. Open shifts from before the change and from after the change and read their start times.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. Every shift in the series starts at the SAME local wall-clock time (e.g. 8:00 AM) on both sides of the clock change.
 2. No shift in the series silently moves an hour earlier or later after the change date.</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§4.5 + tech-plan D2 NFR-005 DST)</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Schedule and all its dialogs display correctly in dark mode</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser; the app's dark mode / theme toggle is available.
 2. The Schedule page has shifts, an event, a conflict, and capacity bars visible.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Switch the app to dark mode.
 2. Look over the Schedule grid: shift blocks, event cards, capacity bars, conflict styling, tooltips.
@@ -8223,7 +8172,7 @@
 4. Switch back to light mode and spot-check again.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every part of the Schedule stays readable - no white-on-white or black-on-black text, no unreadable labels or invisible icons.
 2. Every dialog and popover opened from the Schedule follows the dark theme too.
@@ -8231,239 +8180,239 @@
 4. Switching back to light mode restores the normal look with nothing stuck in dark colours.</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§11 (Dark theme - user-selectable Light / Dark, persisted per user))</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Shifts and events created before the Schedule rewrite still appear after it</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. This case runs around the Schedule rewrite release: before the release, note (or create) a handful of scheduled shifts and calendar events - including at least one future-dated one - with their technician, day, and time.
 2. The release (which replaces the Schedule behind the scenes) has been deployed.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. After the release, open the Schedule and navigate to the dates of the noted entries.
 2. Compare each noted shift and event against what the grid now shows.
 3. Open a couple of them to check their details.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. Every shift and event that existed before the release is still there after it - same technician, same day, same time, same work order.
 2. Events are still events and shifts are still shifts (nothing changed kind or vanished).
 3. Their details open normally and are editable/deletable like any other entry.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (tech-plan §3 FR-015 data migration)</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Dashboard shows one schedule row per work order even with many shifts</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. One work order has been spread across MANY days for a technician (e.g. a 2-week series - 10+ daily shifts).</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Open the Dashboard and find its schedule/today sections.
 2. Look for the spread work order in those sections.
 3. Count how many rows that one work order produces.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. The Dashboard shows that work order as ONE row (covering the whole scheduled span), not one row per daily shift.
 2. Note for the tester: before this release the Dashboard duplicated such a work order once per scheduled day - showing one combined row now is the intended fix, do not report it as a missing-rows bug.
 3. Work orders with a single shift are unaffected.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (tech-plan §4 Dashboard FR-016)</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>A work order created with an appointment shows up on the Schedule board</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. You can create a work order and set its appointment/scheduling details during creation.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order and give it an appointment (a scheduled date/time) as part of the creation flow.
 2. Open the Schedule and navigate to that date.
 3. Find the new work order on the board.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. The appointment created with the work order appears on the Schedule board at the chosen date/time.
 2. It behaves like any other scheduled entry (opens, moves, deletes normally).
 3. It also appears in the Dashboard's schedule section for that day.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (tech-plan §4 WO-create AppointmentScheduler)</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>A multi-location technician's shift appears only on the work order's location</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. A technician is enrolled at TWO locations (set this up if needed).
 3. A work order belonging to location A has a shift scheduled on that technician.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Open the Schedule while working in location A and find the technician's shift.
 2. Switch to location B and open its Schedule for the same date.
 3. Look for the same shift on location B's board.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The shift appears on location A's board (the location the work order belongs to).
 2. The shift does NOT appear on location B's board, even though the technician is enrolled there too.
 3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (tech-plan §3 WO-primary location resolution)</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Work order form offers a Priority (High/Medium/Low) that drives the sidebar</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release (which adds the Priority field) is deployed.
 2. You can create/edit a work order.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order create/edit form and find the Priority field.
 2. Read its default value on a brand-new work order.
@@ -8471,7 +8420,7 @@
 4. Open the Schedule sidebar, find that work order's card, and apply the Priority = High filter.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. The work order form offers a Priority choice of High, Medium, Low.
 2. A new work order has NO priority pre-selected by default.
@@ -8479,50 +8428,50 @@
 4. A work order with no priority set simply shows none (it is not treated as an error).</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§5.1 + tech-plan FR-P4 WO priority)</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>API - Schedule reads need View; writes need Edit; deletes need Delete (403)</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build (new /api/schedule endpoints) is deployed.
 2. Three test users exist: one with NO Schedule permission, one with Schedule: View only, one with Schedule: View + Edit (but not Delete).
 3. A shift id from the current location is known.</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. As the user with NO Schedule permission, call GET /api/schedule/board?from=&amp;to= for the current week.
 2. As the View-only user, call the same GET, then try POST /api/schedule/shifts (a minimal single-shift body) and PATCH /api/schedule/shifts/{id}.
 3. As the View+Edit user, repeat the POST and PATCH, then try DELETE /api/schedule/shifts/{id}?scope=shift.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. No Schedule permission: the board GET is refused with HTTP 403.
 2. View-only: the board GET returns HTTP 200 with the grid data; the POST and PATCH are refused with HTTP 403.
@@ -8530,42 +8479,42 @@
 4. Each refusal is a clean 403 response - never a server error.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14 + tech-plan §4 NFR-003 permissions)</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>API - Series past 8 weeks returns 409 until acknowledged; over 120 shifts 422</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed; an API session with Schedule: Edit exists.
 2. A schedulable work order line id and a technician staff id are known.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. POST /api/schedule/shifts with a spread whose window exceeds 8 weeks (56 calendar days), WITHOUT acknowledgeLongSeries.
 2. Repeat the same POST with acknowledgeLongSeries=true.
@@ -8573,7 +8522,7 @@
 4. Check the board for leftovers after the refused calls.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. The over-8-week create is refused with HTTP 409 (a 'series too long' error) - nothing is created.
 2. With acknowledgeLongSeries=true the same request succeeds (HTTP 201) and returns the full materialized series under one series id.
@@ -8581,112 +8530,112 @@
 4. Refused calls leave no partial series behind.</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§4.5 + tech-plan D8 error cases)</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>API - No pricing fields in Schedule responses; WO details need Work Orders View</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed.
 2. A shift covering work order lines exists.
 3. Two API users: one with Schedule: View + Work Orders: View, one with Schedule: View but WITHOUT Work Orders: View.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. As the full user, call GET /api/schedule/board, GET /api/schedule/shifts/{id}, and GET /api/schedule/work-orders and search the raw responses for money fields (price, cost, rate, total, $ amounts).
 2. As the user WITHOUT Work Orders: View, call GET /api/schedule/board and GET /api/schedule/shifts/{id} and read the work-order-derived fields (customer, unit, VIN, lines).</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. No Schedule response contains any pricing/money field for ANY caller - the schedule never returns labor, totals, or dollar amounts.
 2. For the caller without Work Orders: View, the work-order-derived details (customer, unit, VIN, line names) are absent/empty in the response itself - not just hidden on screen.
 3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§14 + tech-plan D6/NFR-002 no pricing)</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>API - A shift from another location returns 404, not another shop's data</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed.
 2. Two locations exist; a shift exists at location B; your API session is scoped to location A.
 3. The location-B shift's id is known (create it while switched to B, then switch back to A).</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. While scoped to location A, call GET /api/schedule/shifts/{id} with the location-B shift id.
 2. Also try PATCH /api/schedule/shifts/{id} on the same id.
 3. Call GET /api/schedule/board for location A's current week.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. The foreign-location GET is refused as not found (HTTP 404) - the response reveals nothing about the other location's shift.
 2. The PATCH on the foreign id is refused the same way (404) - no cross-location edit is possible.
 3. Location A's board contains only location A's shifts - nothing from location B leaks in.</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (tech-plan NFR-001 location scoping)</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Grid rows are grouped by department under group headers, with the department's technicians listed beneath</t>
+          <t>Grid rows are grouped by department under group headers</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Collapsing a department group header hides its technician rows; expanding restores them</t>
+          <t>Collapsing a department header hides its technician rows</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>There is no separate technician-only view or Tech/Dept toggle - department grouping is the only grid grouping</t>
+          <t>No Tech/Dept toggle - department grouping is the only grid grouping</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>An Unassigned row sits within the grid (not a separate tray) and holds shifts not yet tied to a technician</t>
+          <t>An Unassigned row sits inside the grid, not in a separate tray</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Mini calendar month/year picker offers a grid of month buttons and year navigation arrows</t>
+          <t>Mini calendar month/year picker has month buttons and year arrows</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Mini calendar highlights the selected date, indicates today, and highlights the week row on hover</t>
+          <t>Mini calendar highlights the selected date, today, and the hovered week</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>The sidebar shows a flat, scrollable list of work order cards with no Assigned/Unassigned tabs</t>
+          <t>The sidebar is a flat list of work order cards with no tabs</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Work order card shows WO number, line count plus hours, customer, unit, lead technician, and a status-colored left border</t>
+          <t>Work order card anatomy, incl. the status-colored left border</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Only approved work order lines appear in the drill-down - unapproved lines are not shown</t>
+          <t>Only approved work order lines appear in the drill-down</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Each line row shows its title, estimated hours, technician roster (avatar stack plus count, no cap), and a drag handle</t>
+          <t>Line row shows title, hours, the technician roster and a drag handle</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>'All / Unscheduled' filter chips with counts - Unscheduled shows only lines with no shifts yet</t>
+          <t>'All / Unscheduled' filter chips show counts and filter the line list</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Dropping a single-line work order on a technician cell creates a shift immediately, skipping the scope picker</t>
+          <t>Dropping a single-line work order creates a shift with no scope picker</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Dragging an individual line from the drill-down creates a single-line shift directly</t>
+          <t>Dragging a line from the drill-down creates a single-line shift</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>A job exceeding the technician's daily hours opens the spread step after the scope is chosen</t>
+          <t>A job over the technician's daily hours opens the spread step</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>A scope that fits within one working day skips the spread step and creates a single shift</t>
+          <t>A scope that fits one working day skips the spread step</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>While dragging, drop-target cells highlight and a ghost block shows the line name and hours</t>
+          <t>While dragging, target cells highlight and a ghost block follows</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Scheduling a technician onto a line adds them to that line's labor roster on the work order</t>
+          <t>Scheduling a technician onto a line adds them to its labor roster</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Choosing 'Schedule whole work order' assigns the technician to all lines and creates one whole-order shift</t>
+          <t>'Schedule whole work order' assigns all lines and creates one shift</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Tapping an individual line row immediately creates a single-line shift with no confirmation step</t>
+          <t>Tapping a line row creates a single-line shift with no confirm step</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>A shift's start time uses the technician's configured working hours when they are set</t>
+          <t>A shift's start time uses the technician's own working hours when set</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>With no technician hours set, the shift start time falls back to the shop's business hours</t>
+          <t>With no technician hours set, start time falls back to business hours</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2567,7 +2567,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>In day view, the start time comes from where the shift is dropped on the timeline</t>
+          <t>In day view the start time comes from the drop position</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Dropping a work order or line onto the Unassigned row creates an unassigned shift with no technician</t>
+          <t>Dropping onto the Unassigned row creates a shift with no technician</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Unassigned shift start time skips the technician-hours rule and uses business hours or the default</t>
+          <t>Unassigned shift start time uses business hours or the default</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Dragging an unassigned shift onto a technician row assigns it, and that technician's hours then apply</t>
+          <t>Dragging an unassigned shift onto a technician row assigns it</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>How-much selector defaults to Full estimate; Full estimate, 1 week, and 2 weeks apply immediately with no extra fields</t>
+          <t>How-much selector defaults to Full estimate; preset amounts apply at once</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Start date defaults to the earliest working day and can be adjusted to make a second technician sequential</t>
+          <t>Start date defaults to the earliest working day and can be changed</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Preview is collapsed to a one-line summary, expandable to a week-by-week breakdown with skipped days struck through and their reasons</t>
+          <t>Spread preview: one-line summary, expandable to a week-by-week breakdown</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Dropping the same work order on a second technician spreads the full estimate again, independently</t>
+          <t>The same work order on a second technician spreads the full estimate again</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Day view shows the series day as a single time-positioned block with a 'part of an M-week job' cue</t>
+          <t>Day view shows the series day as one block with a multi-week cue</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>A series is a grouping of ordinary daily shifts - capacity, overtime, and conflicts operate on the individual shifts</t>
+          <t>A series is just a grouping - capacity and conflicts use the daily shifts</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3459,7 +3459,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>A single-line shift block shows three text lines: customer name, unit number, and the line name</t>
+          <t>A single-line shift block shows customer, unit number and line name</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Whole-order and multi-line-subset shifts both read 'N Lines' on the block - the detail modal spells out the exact scope</t>
+          <t>Whole-order and multi-line shifts both read 'N Lines' on the block</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>The conflict icon is the only icon on a shift block - no work order number and no scope icons</t>
+          <t>The conflict icon is the only icon on a shift block</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Visible lanes cap at 3 - additional overlapping shifts collapse into a '+N more' affordance that opens a popover</t>
+          <t>Visible lanes cap at 3; extra overlapping shifts collapse into '+N more'</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Date and time headers stick to the top of the viewport during vertical scroll (day and week views)</t>
+          <t>Date and time headers stick to the top during vertical scroll</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Dragging a shift horizontally moves its start time, snapping to 15-minute intervals</t>
+          <t>Dragging a shift sideways moves its start time in 15-minute steps</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Clicking a shift opens its detail modal showing customer, unit, VIN (always visible), and the work order id</t>
+          <t>Clicking a shift opens its detail modal, with VIN always visible</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>The modal shows a scope summary and the scheduled line(s) with number, title, hours, and status only</t>
+          <t>The modal lists the scheduled line(s) with no money fields</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4658,7 +4658,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Event cards are structurally distinct from shift cards - white outlined card with a grey icon chip, no colored left rail</t>
+          <t>Event cards look structurally distinct from shift cards</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4706,7 +4706,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Events default to neutral/grey; choosing a color tints the card and its icon chip</t>
+          <t>Events default to grey; choosing a color tints the card and chip</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Double-booked: two work orders overlapping on the same technician at the same time are flagged</t>
+          <t>Double-booked: two overlapping work orders on one technician are flagged</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Working-day conflict: a shift on a day outside the technician's configured working days is flagged</t>
+          <t>Working-day conflict: a shift outside the tech's working days is flagged</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1. The shift is created but flagged as a conflict because the day is outside the technician's configured working days (the design's reason sentence reads in the spirit of 'Scheduled on a weekend (outside Mon-Fri)').
+          <t>1. The shift is created but flagged as a conflict because the day is outside the technician's configured working days (the reason sentence reads in the spirit of 'Scheduled on a weekend (outside working days)' - it names the technician's own working days, not a fixed Monday-to-Friday window).
 2. If the technician's working days DO include that day (for example Saturday hours are configured), a shift on that day is NOT flagged.
 3. The warning icon appears on the block and the conflict is listed in the toolbar dropdown.</t>
         </is>
@@ -4958,7 +4958,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>The toolbar conflict pill shows the issue count and opens a dropdown listing the conflicts</t>
+          <t>The toolbar conflict pill shows the count and opens a list</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Red/alarming styling is reserved for conflicts and genuine errors - never used for overtime</t>
+          <t>Red styling is only for conflicts and errors, never for overtime</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>When aggregate hours exceed capacity, an amber spill extends past the track's right edge with a tick at the 100% line</t>
+          <t>Over capacity, an amber spill extends past the track's right edge</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>The 'OT' text tag appears whenever any single technician exceeds their own daily hours - even when the day's aggregate is under capacity</t>
+          <t>'OT' text tag appears when one technician exceeds their own daily hours</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Hovering a capacity bar shows a per-technician breakdown, with overtime technicians highlighted in amber</t>
+          <t>Hovering a capacity bar shows a per-technician breakdown</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5300,7 +5300,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Shift hover tooltip shows customer, unit/vehicle/VIN, date and time, technician, scope, up to 3 line names, and a progress bar</t>
+          <t>Shift hover tooltip shows the full shift summary incl. up to 3 line names</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>A conflicted shift's tooltip shows the conflict icon and the conflict reason in amber</t>
+          <t>A conflicted shift's tooltip shows the icon and reason in amber</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5396,7 +5396,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Event hover tooltip shows the event name with its grey category dot, date and time range, and technician</t>
+          <t>Event hover tooltip shows name, grey category dot, time range and tech</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Tooltips open after a short hover delay, dismiss on mouse-leave, and are read-only - clicking still opens the modal</t>
+          <t>Tooltips open after a hover delay, dismiss on mouse-leave, are read-only</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>The tooltip flips above the block or shifts horizontally to stay within the viewport - it is never clipped</t>
+          <t>The tooltip flips or shifts to stay within the viewport - never clipped</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Left/right arrows navigate by day, week, or month depending on the active range, and the date label shows the current range</t>
+          <t>Left/right arrows step by day, week, or month to match the active range</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Toolbar search fades non-matching blocks and highlights matching ones (customer, WO number, unit, technician, line name)</t>
+          <t>Toolbar search highlights matching blocks and fades non-matching ones</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>'My Shifts' filters the grid to only the current user's shifts, hiding all other technician rows</t>
+          <t>'My Shifts' filters the grid to only the current user's shifts</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Dragging a shift to another technician row reassigns it - target tech added to the line's roster, source removed, with a confirmation modal</t>
+          <t>Dragging a shift to another technician row reassigns it, with a confirm modal</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Deleting a middle shift of a series asks for scope with all three options, each stating the hours returned</t>
+          <t>Deleting a middle shift of a series offers all three scope options</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -6293,7 +6293,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>'This shift only' removes that day, the series keeps the gap, and the hours return to the estimate's remaining</t>
+          <t>'This shift only' removes that day and the series keeps the gap</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6344,7 +6344,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>'This and everything after' removes from the clicked shift onward, keeping earlier shifts</t>
+          <t>'This and everything after' removes from the clicked shift onward</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Scope options adapt to position: first and last shifts of a series each show only two options</t>
+          <t>Scope options adapt: the first and last shift each show only two</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Schedule: View grants the full read experience - page, all three views, mini calendar, search, filter, tooltips, read-only modals</t>
+          <t>Schedule: View grants the full read-only experience across the whole page</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14.1 (Schedule: View), §14.3)</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14.1 (Schedule: View), §14.3)</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14.1 (Schedule: View - editing affordances hidden or disabled))</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14.1 (Schedule: View - editing affordances hidden or disabled))</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14.1 (When Schedule: View is OFF))</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14.1 (When Schedule: View is OFF))</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14.1 (Schedule: Edit))</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14.1 (Schedule: Edit))</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -7452,7 +7452,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Edit without Delete: the user can create and modify but cannot remove - delete action and trash icon hidden</t>
+          <t>Edit without Delete: the user can create and modify but not remove</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14.1 (Schedule: Delete - without it))</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14.1 (Schedule: Delete - without it))</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -7502,7 +7502,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Schedule: Delete unlocks deleting shifts and events, including the three series-aware scopes</t>
+          <t>Schedule: Delete unlocks deleting shifts and events</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14.1 (Schedule: Delete))</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14.1 (Schedule: Delete))</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
@@ -7553,7 +7553,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>The permission tiers depend on each other: Delete requires Edit, and Edit requires View</t>
+          <t>Permission tiers nest: Delete requires Edit, Edit requires View</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14 (Delete requires Edit and Edit requires View))</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14 (Delete requires Edit and Edit requires View))</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -7602,7 +7602,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Schedule access without Work Orders: View - sidebar hides the WO list and drill-down; mini calendar stays; grid shifts remain usable</t>
+          <t>Schedule without Work Orders: View - the sidebar hides the work order list</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7652,7 +7652,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>No own-only restriction: every Schedule: View user sees ALL technicians' shifts and events</t>
+          <t>No own-only restriction: a View user sees ALL technicians' shifts</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14.3)</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14.3)</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -7700,7 +7700,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Grid rows are department-based: any staff member in a visible department appears as a row, regardless of role</t>
+          <t>Grid rows are department-based, not role-based</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Clocking into work order line tasks is gated by the staff record's 'Time Clock' setting, not the permission model</t>
+          <t>Clocking into line tasks is gated by the staff 'Time Clock' setting</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7795,7 +7795,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>With Work Orders: View OFF, work-order-derived details on shifts (customer, lines, money fields) are hidden or masked</t>
+          <t>With Work Orders: View OFF, work order details on shifts are hidden</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Below 960px the grid scrolls horizontally, and the sidebar collapses on narrow viewports</t>
+          <t>Below 960px the grid scrolls sideways and the sidebar collapses</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>SV-8686 (§11 (Responsiveness))</t>
+          <t>SV-8686,SV-8687 (§11 (Responsiveness - grid scrolls horizontally below 960px; sidebar collapses))</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>SV-8686 (§11 (Performance - virtualization))</t>
+          <t>SV-8687 (§11 (Performance - sidebar list and line drill-down virtualize at 50+ items))</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr"/>
@@ -7945,7 +7945,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>The grid renders smoothly at full load - 15 technicians × 7 days with several shifts per cell</t>
+          <t>The grid renders smoothly at full load - 15 technicians over 7 days</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -8045,7 +8045,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Scheduled hours, the estimate, and actual (clocked) hours are three separate quantities that are not forced to reconcile</t>
+          <t>Scheduled, estimated and actual clocked hours are three separate numbers</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (tech-plan §3 FR-015 data migration)</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (tech-plan §3 FR-015 data migration)</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr"/>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (tech-plan §4 Dashboard FR-016)</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (tech-plan §4 Dashboard FR-016)</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr"/>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (tech-plan §4 WO-create AppointmentScheduler)</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (tech-plan §4 WO-create AppointmentScheduler)</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (tech-plan §3 WO-primary location resolution)</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (tech-plan §3 WO-primary location resolution)</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14 + tech-plan §4 NFR-003 permissions)</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14 + tech-plan §4 NFR-003 permissions)</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§14 + tech-plan D6/NFR-002 no pricing)</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14 + tech-plan D6/NFR-002 no pricing)</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (tech-plan NFR-001 location scoping)</t>
+          <t>SV-8685 [epic - cross-cutting, no single-story owner] (tech-plan NFR-001 location scoping)</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
+  <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2148,19 +2148,23 @@
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Drag that line onto the technician's cell and create the shift.
-2. Open the same work order's line (in the sidebar drill-down and/or on the Work Orders page) and check its technician roster.</t>
+2. Open the same work order's line (in the sidebar drill-down and/or on the Work Orders page) and check its technician roster.
+3. Drag the SAME line onto a different technician's cell and create a second shift (drag the line from the sidebar again - do NOT drag the shift block you just created, that would move it instead).
+4. Look at that line's technician roster again.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. The technician now appears on that line's labor roster - the schedule and the work order stay in sync automatically.
 2. The sidebar line row's avatar stack/count updates to include the technician.
-3. If the line previously showed 'Needs techs', the badge is gone.</t>
+3. If the line previously showed 'Needs techs', the badge is gone.
+4. Dragging the same line onto a second technician adds that technician to the line's roster as well - the technician who was already there stays on it.
+5. Nothing asks you to swap or replace the technician who was already there, and no limit is reached on how many technicians a line can have.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>SV-8688 (§1.2 (Goals - roster sync), §4.3 (roster add), §7)</t>
+          <t>SV-8688 (§1.2 Goals - roster sync · §4.3 roster add + no swap flow · §7; spec v23 2026-07-30)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -7845,38 +7849,92 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>Default roles start at the Schedule level the spec names (view-only vs edit)</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in as an admin who can view and edit the roles and their permissions.
+2. You can sign in (or switch) to a user who holds each role you need to check.
+3. Write down each role's current Schedule permissions before you change anything, and put them back afterwards.</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the roles screen where each role's permissions are listed.
+2. Take these roles one at a time - Technician, Parts Manager, Parts Tech, Office, Time Clock - use 'Reset To Template' so the role is back at its default, then read its Schedule permissions (View, Edit, Delete).
+3. Do the same for these roles - Service Manager, Senior Service Advisor, Service Advisor, Foreman - and read their Schedule permissions.
+4. Sign in as a user with one of the roles from step 2 and try to drag a work order onto the grid.
+5. Sign in as a user with one of the roles from step 3 and try the same drag.
+6. Put every role's permissions back the way you found them.</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>1. Technician, Parts Manager, Parts Tech, Office and Time Clock each have Schedule View turned ON and Schedule Edit and Schedule Delete turned OFF.
+2. Service Manager, Senior Service Advisor, Service Advisor and Foreman each have Schedule Edit turned ON (so they also have View).
+3. The user from step 4 gets the read-only schedule - nothing can be dragged onto the grid and no shift can be created.
+4. The user from step 5 can drag a work order onto the grid and create a shift.</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 [epic - cross-cutting - no single-story owner] (§14.1 default role tiers - view-only role list + edit role list; spec v23 2026-07-30)</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
           <t>Below 960px the grid scrolls sideways and the sidebar collapses</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in week view with shifts visible.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Resize the browser window to just under 960px wide.
 2. Try to reach the right-hand days of the grid.
 3. Narrow the window further and watch the sidebar.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. Below the 960px minimum supported width, the grid scrolls horizontally rather than breaking.
 2. All days remain reachable by horizontal scroll.
@@ -7884,287 +7942,287 @@
 4. No content becomes permanently unreachable and nothing errors.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>SV-8686,SV-8687 (§11 (Responsiveness - grid scrolls horizontally below 960px; sidebar collapses))</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>The sidebar work order list and line drill-down stay smooth with 50+ items</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. 50 or more open work orders exist (seed ZZAUTOTEST orders if the environment lacks them), including one order with many approved lines.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the full work order list top to bottom quickly.
 2. Open the many-line order's drill-down and scroll it.
 3. Type in the search while the long list is shown.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
 3. Search stays responsive on the long list.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§11 (Performance - sidebar list and line drill-down virtualize at 50+ items))</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>The grid renders smoothly at full load - 15 technicians over 7 days</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. The schedule is loaded to roughly the spec's stated scale: around 15 technician rows across a week with several shifts per cell (seed ZZAUTOTEST shifts as needed).
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the grid vertically and horizontally.
 2. Switch between Day, Week, and Month.
 3. Hover several blocks and open/close a modal.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. The grid renders and scrolls smoothly at this scale.
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§11 (Performance))</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Shop closures do NOT block spread in V1 - shifts can land on closure days</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shop closure (holiday/inventory day) is defined at the shop level on a working weekday inside the planned spread window (set it up; remove after).
 3. A large job (multi-day scope) is ready to spread.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step across a window that contains a shop closure day.
 2. Expand the preview and find the closure day.
 3. Confirm the spread and check the grid.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. The closure day is NOT struck through or skipped by the spread in V1.
 2. A shift CAN be placed on the shop closure day (only weekend days with no business hours are skipped).
 3. The end date follows the normal daily distribution - no extra day is added for the closure.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§12 (Shop closures), §4.5)</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Scheduled, estimated and actual clocked hours are three separate numbers</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A line has estimate 10h; a technician has 6h scheduled against it and some different amount of time actually clocked (seed what is possible).</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Open the shift's detail modal.
 2. Compare the scheduled hours, the estimate, and the logged/actual time.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. All three quantities are shown/derivable and may differ from one another.
 2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§4.5 (three separate quantities), §12)</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>A multi-week series keeps the same local start time across the clock change</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. The shop's location observes daylight saving (clocks change); the next clock-change date is known (e.g. the November change).
 3. A job large enough to spread across the clock-change date exists.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Spread the job across a window that includes the clock-change date (shifts before and after it).
 2. Open shifts from before the change and from after the change and read their start times.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. Every shift in the series starts at the SAME local wall-clock time (e.g. 8:00 AM) on both sides of the clock change.
 2. No shift in the series silently moves an hour earlier or later after the change date.</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§4.5 + tech-plan D2 NFR-005 DST)</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Schedule and all its dialogs display correctly in dark mode</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser; the app's dark mode / theme toggle is available.
 2. The Schedule page has shifts, an event, a conflict, and capacity bars visible.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. Switch the app to dark mode.
 2. Look over the Schedule grid: shift blocks, event cards, capacity bars, conflict styling, tooltips.
@@ -8172,7 +8230,7 @@
 4. Switch back to light mode and spot-check again.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every part of the Schedule stays readable - no white-on-white or black-on-black text, no unreadable labels or invisible icons.
 2. Every dialog and popover opened from the Schedule follows the dark theme too.
@@ -8180,239 +8238,239 @@
 4. Switching back to light mode restores the normal look with nothing stuck in dark colours.</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§11 (Dark theme - user-selectable Light / Dark, persisted per user))</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Shifts and events created before the Schedule rewrite still appear after it</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. This case runs around the Schedule rewrite release: before the release, note (or create) a handful of scheduled shifts and calendar events - including at least one future-dated one - with their technician, day, and time.
 2. The release (which replaces the Schedule behind the scenes) has been deployed.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. After the release, open the Schedule and navigate to the dates of the noted entries.
 2. Compare each noted shift and event against what the grid now shows.
 3. Open a couple of them to check their details.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. Every shift and event that existed before the release is still there after it - same technician, same day, same time, same work order.
 2. Events are still events and shifts are still shifts (nothing changed kind or vanished).
 3. Their details open normally and are editable/deletable like any other entry.</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting, no single-story owner] (tech-plan §3 FR-015 data migration)</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Dashboard shows one schedule row per work order even with many shifts</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. One work order has been spread across MANY days for a technician (e.g. a 2-week series - 10+ daily shifts).</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Open the Dashboard and find its schedule/today sections.
 2. Look for the spread work order in those sections.
 3. Count how many rows that one work order produces.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. The Dashboard shows that work order as ONE row (covering the whole scheduled span), not one row per daily shift.
 2. Note for the tester: before this release the Dashboard duplicated such a work order once per scheduled day - showing one combined row now is the intended fix, do not report it as a missing-rows bug.
 3. Work orders with a single shift are unaffected.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting, no single-story owner] (tech-plan §4 Dashboard FR-016)</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>A work order created with an appointment shows up on the Schedule board</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. You can create a work order and set its appointment/scheduling details during creation.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order and give it an appointment (a scheduled date/time) as part of the creation flow.
 2. Open the Schedule and navigate to that date.
 3. Find the new work order on the board.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The appointment created with the work order appears on the Schedule board at the chosen date/time.
 2. It behaves like any other scheduled entry (opens, moves, deletes normally).
 3. It also appears in the Dashboard's schedule section for that day.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting, no single-story owner] (tech-plan §4 WO-create AppointmentScheduler)</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>A multi-location technician's shift appears only on the work order's location</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. A technician is enrolled at TWO locations (set this up if needed).
 3. A work order belonging to location A has a shift scheduled on that technician.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Open the Schedule while working in location A and find the technician's shift.
 2. Switch to location B and open its Schedule for the same date.
 3. Look for the same shift on location B's board.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. The shift appears on location A's board (the location the work order belongs to).
 2. The shift does NOT appear on location B's board, even though the technician is enrolled there too.
 3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting, no single-story owner] (tech-plan §3 WO-primary location resolution)</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Work order form offers a Priority (High/Medium/Low) that drives the sidebar</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release (which adds the Priority field) is deployed.
 2. You can create/edit a work order.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order create/edit form and find the Priority field.
 2. Read its default value on a brand-new work order.
@@ -8420,7 +8478,7 @@
 4. Open the Schedule sidebar, find that work order's card, and apply the Priority = High filter.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. The work order form offers a Priority choice of High, Medium, Low.
 2. A new work order has NO priority pre-selected by default.
@@ -8428,50 +8486,50 @@
 4. A work order with no priority set simply shows none (it is not treated as an error).</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§5.1 + tech-plan FR-P4 WO priority)</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>API - Schedule reads need View; writes need Edit; deletes need Delete (403)</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build (new /api/schedule endpoints) is deployed.
 2. Three test users exist: one with NO Schedule permission, one with Schedule: View only, one with Schedule: View + Edit (but not Delete).
 3. A shift id from the current location is known.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. As the user with NO Schedule permission, call GET /api/schedule/board?from=&amp;to= for the current week.
 2. As the View-only user, call the same GET, then try POST /api/schedule/shifts (a minimal single-shift body) and PATCH /api/schedule/shifts/{id}.
 3. As the View+Edit user, repeat the POST and PATCH, then try DELETE /api/schedule/shifts/{id}?scope=shift.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. No Schedule permission: the board GET is refused with HTTP 403.
 2. View-only: the board GET returns HTTP 200 with the grid data; the POST and PATCH are refused with HTTP 403.
@@ -8479,42 +8537,42 @@
 4. Each refusal is a clean 403 response - never a server error.</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14 + tech-plan §4 NFR-003 permissions)</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>API - Series past 8 weeks returns 409 until acknowledged; over 120 shifts 422</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed; an API session with Schedule: Edit exists.
 2. A schedulable work order line id and a technician staff id are known.</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. POST /api/schedule/shifts with a spread whose window exceeds 8 weeks (56 calendar days), WITHOUT acknowledgeLongSeries.
 2. Repeat the same POST with acknowledgeLongSeries=true.
@@ -8522,7 +8580,7 @@
 4. Check the board for leftovers after the refused calls.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. The over-8-week create is refused with HTTP 409 (a 'series too long' error) - nothing is created.
 2. With acknowledgeLongSeries=true the same request succeeds (HTTP 201) and returns the full materialized series under one series id.
@@ -8530,112 +8588,112 @@
 4. Refused calls leave no partial series behind.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§4.5 + tech-plan D8 error cases)</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>API - No pricing fields in Schedule responses; WO details need Work Orders View</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed.
 2. A shift covering work order lines exists.
 3. Two API users: one with Schedule: View + Work Orders: View, one with Schedule: View but WITHOUT Work Orders: View.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. As the full user, call GET /api/schedule/board, GET /api/schedule/shifts/{id}, and GET /api/schedule/work-orders and search the raw responses for money fields (price, cost, rate, total, $ amounts).
 2. As the user WITHOUT Work Orders: View, call GET /api/schedule/board and GET /api/schedule/shifts/{id} and read the work-order-derived fields (customer, unit, VIN, lines).</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. No Schedule response contains any pricing/money field for ANY caller - the schedule never returns labor, totals, or dollar amounts.
 2. For the caller without Work Orders: View, the work-order-derived details (customer, unit, VIN, line names) are absent/empty in the response itself - not just hidden on screen.
 3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting, no single-story owner] (§14 + tech-plan D6/NFR-002 no pricing)</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>API - A shift from another location returns 404, not another shop's data</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed.
 2. Two locations exist; a shift exists at location B; your API session is scoped to location A.
 3. The location-B shift's id is known (create it while switched to B, then switch back to A).</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. While scoped to location A, call GET /api/schedule/shifts/{id} with the location-B shift id.
 2. Also try PATCH /api/schedule/shifts/{id} on the same id.
 3. Call GET /api/schedule/board for location A's current week.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. The foreign-location GET is refused as not found (HTTP 404) - the response reveals nothing about the other location's shift.
 2. The PATCH on the foreign id is refused the same way (404) - no cross-location edit is possible.
 3. Location A's board contains only location A's shifts - nothing from location B leaks in.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting, no single-story owner] (tech-plan NFR-001 location scoping)</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule V1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Schedule V1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +526,9 @@
           <t>1. Schedule is listed as a top-level navigation item alongside Work Orders, Customers, Parts, and Reports.
 2. Clicking it opens the Schedule screen.
 3. The left panel is the work order sidebar: a mini calendar at the top and a work order list beneath it.
-4. The main area is the schedule grid showing technician rows, with a toolbar above it.</t>
+4. The main area is the schedule grid showing technician rows, with a toolbar above it.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3, §3.1, §3.2).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -577,7 +579,9 @@
           <t>1. Day: the grid shows a 24-hour timeline per technician row, with shifts positioned at their times.
 2. Week: the grid shows a 7-column Monday-to-Sunday layout with stacked shift chips per cell.
 3. Month: the grid shows a compact calendar with per-day capacity bars and shift chips.
-4. The same shifts remain visible (appropriately rendered) in all three views.</t>
+4. The same shifts remain visible (appropriately rendered) in all three views.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §6).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -626,7 +630,9 @@
         <is>
           <t>1. Rows are grouped by department, each group under its own header (for example a services group and an administration group - the actual names come from the shop's own departments).
 2. Each department's technicians are listed beneath that department's header.
-3. Every staff member assigned to a visible department appears as a row, regardless of their role.</t>
+3. Every staff member assigned to a visible department appears as a row, regardless of their role.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §14.4).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -674,7 +680,9 @@
         <is>
           <t>1. Collapsing hides that department's technician rows (the group header stays visible).
 2. Expanding shows the technician rows again, unchanged.
-3. Other department groups are unaffected.</t>
+3. Other department groups are unaffected.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -720,7 +728,9 @@
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. No such toggle exists - the department-grouped rows are the only grid grouping.
-2. Department visibility is controlled only through the department toggles in the 'Filter and Display' dropdown.</t>
+2. Department visibility is controlled only through the department toggles in the 'Filter and Display' dropdown.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -769,7 +779,9 @@
         <is>
           <t>1. An unassigned row/lane appears within the grid itself - it is not a separate tray or panel outside the grid.
 2. Shifts without a technician sit in this row.
-3. The unassigned shift uses the same block layout as regular shifts (customer, unit, line name / line count) - it simply has no technician.</t>
+3. The unassigned shift uses the same block layout as regular shifts (customer, unit, line name / line count) - it simply has no technician.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -817,7 +829,9 @@
         <is>
           <t>1. The main grid navigates to show the clicked date (the containing day/week/month depending on the active view).
 2. The toolbar date label updates to the new range.
-3. The clicked date is highlighted as the selected date in the mini calendar.</t>
+3. The clicked date is highlighted as the selected date in the mini calendar.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -866,7 +880,9 @@
         <is>
           <t>1. A picker opens showing a grid of month buttons plus arrows to step the year back and forward.
 2. Choosing a month shows that month in the mini calendar.
-3. The main grid can then be navigated by clicking a date in the newly shown month.</t>
+3. The main grid can then be navigated by clicking a date in the newly shown month.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.2).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -914,7 +930,9 @@
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. The calendar grid collapses (hides), leaving more room for the work order list below.
-2. Clicking again expands the calendar grid back.</t>
+2. Clicking again expands the calendar grid back.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -963,7 +981,9 @@
         <is>
           <t>1. The selected date is visually highlighted.
 2. Today's date has its own distinct indicator, different from the selection.
-3. Hovering a week row highlights that whole week row.</t>
+3. Hovering a week row highlights that whole week row.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.2).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1013,7 +1033,9 @@
         <is>
           <t>1. Work orders appear as a single flat list of cards (one list, no tab split).
 2. The list scrolls when there are more cards than fit.
-3. There are no Assigned/Unassigned tabs - assignment is available only as a filter behind the 'Filter' button.</t>
+3. There are no Assigned/Unassigned tabs - assignment is available only as a filter behind the 'Filter' button.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1064,7 +1086,9 @@
 2. Top right: the line count plus the hours estimate.
 3. Below: the customer name in bold, then the unit number.
 4. A lead technician row with the technician's avatar and name.
-5. A colored left border whose color reflects the work order's status.</t>
+5. A colored left border whose color reflects the work order's status.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1117,7 +1141,9 @@
 2. Customer-name search shows only cards for that customer.
 3. Unit-number search shows only cards with that unit.
 4. Technician-name search shows only cards where that technician appears on the card.
-5. All four searchable fields (WO number, customer, unit, technician) are fields visible on the card itself.</t>
+5. All four searchable fields (WO number, customer, unit, technician) are fields visible on the card itself.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1166,7 +1192,9 @@
         <is>
           <t>1. The list narrows live with each keystroke - no Enter press or apply button is needed.
 2. Deleting characters widens the results again.
-3. With very many work orders, the list may load further results in pages as you scroll - that is expected, not a fault.</t>
+3. With very many work orders, the list may load further results in pages as you scroll - that is expected, not a fault.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1215,7 +1243,9 @@
         <is>
           <t>1. No work order cards are shown.
 2. The app does not error; the sidebar remains usable.
-3. Clearing the search restores the full list.</t>
+3. Clearing the search restores the full list.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1265,7 +1295,9 @@
         <is>
           <t>1. The filter panel offers three groups: Assignment (Assigned, Unassigned), Status (the work order statuses supported in the app), and Priority (High, Medium, Low).
 2. Applying a filter narrows the flat card list.
-3. The 'Filters' button shows a badge with the number of active filters.</t>
+3. The 'Filters' button shows a badge with the number of active filters.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1315,7 +1347,9 @@
         <is>
           <t>1. Unassigned: only work orders without an assigned technician remain in the list.
 2. Assigned: only work orders with a technician assigned remain.
-3. There are no Assigned/Unassigned tabs - this filter is the only assignment split.</t>
+3. There are no Assigned/Unassigned tabs - this filter is the only assignment split.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1, §3.1).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1365,7 +1399,9 @@
         <is>
           <t>1. The Status group lists the work order statuses the app supports.
 2. Only work orders in the chosen status remain in the card list.
-3. The card left-border colors of the remaining cards are consistent with that status.</t>
+3. The card left-border colors of the remaining cards are consistent with that status.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1414,7 +1450,9 @@
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. The Priority group offers High, Medium, and Low.
-2. Only High-priority work orders remain in the list.</t>
+2. Only High-priority work orders remain in the list.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1462,7 +1500,9 @@
         <is>
           <t>1. All applied filters are removed at once.
 2. The full work order list is shown again.
-3. The active-count badge on the 'Filter' button disappears (or shows zero).</t>
+3. The active-count badge on the 'Filter' button disappears (or shows zero).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1511,7 +1551,9 @@
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. The list shows only work orders that match BOTH the text search and the structured filter.
-2. Removing either the search text or the filter widens the list to the remaining condition.</t>
+2. Removing either the search text or the filter widens the list to the remaining condition.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1564,7 +1606,9 @@
 2. The header of the drill-down shows the work order id.
 3. The header also shows the line count, and it matches the number of approved lines.
 4. A back control is shown to return to the card list.
-5. Clicking back restores the work order card list.</t>
+5. Clicking back restores the work order card list.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1613,7 +1657,9 @@
         <is>
           <t>1. Every approved line is listed.
 2. The unapproved line does NOT appear anywhere in the schedule sidebar.
-3. The header's line count matches the approved lines only.</t>
+3. The header's line count matches the approved lines only.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1662,7 +1708,9 @@
         <is>
           <t>1. The row shows the line's title and its estimated hours.
 2. The current technician roster is shown as an avatar stack plus a count; there is no cap on how many technicians a line can have.
-3. Each line row has its own drag handle, so it can be dragged independently onto the grid.</t>
+3. Each line row has its own drag handle, so it can be dragged independently onto the grid.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §8.1).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1711,7 +1759,9 @@
         <is>
           <t>1. The technician-less line shows a 'Needs techs' badge.
 2. The line with a technician does not show the badge.
-3. After a technician is scheduled onto the badge-bearing line, the badge goes away.</t>
+3. After a technician is scheduled onto the badge-bearing line, the badge goes away.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1760,7 +1810,9 @@
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Typing a line title narrows the list to matching lines.
-2. Typing the customer name returns no results - the line search matches line titles only (the list is already scoped to one work order, so customer/unit/WO fields are not searched).</t>
+2. Typing the customer name returns no results - the line search matches line titles only (the list is already scoped to one work order, so customer/unit/WO fields are not searched).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1810,7 +1862,9 @@
         <is>
           <t>1. Two chips are shown - All and Unscheduled - each with a count.
 2. Unscheduled lists only the lines that have no shifts yet, and its count matches.
-3. All lists every approved line, and its count matches the drill-down header's line count.</t>
+3. All lists every approved line, and its count matches the drill-down header's line count.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1860,7 +1914,9 @@
           <t>1. A shift is created immediately in that cell - no scope picker and no spread step appears.
 2. The shift block shows the customer name, unit number, and the line's name.
 3. The technician is added to that line's labor roster on the work order.
-4. A toast with an Undo option appears.</t>
+4. A toast with an Undo option appears.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §1.2, §7).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1909,7 +1965,9 @@
         <is>
           <t>1. A scope picker popover opens, anchored to the cell you dropped on.
 2. It offers 'Schedule whole work order' at the top, the individual line rows beneath, and a 'Select multiple' control.
-3. No shift is created until a scope is chosen.</t>
+3. No shift is created until a scope is chosen.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.3).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1959,7 +2017,9 @@
         <is>
           <t>1. A single-line shift for exactly that line is created directly - no scope picker appears.
 2. The block's last text line shows that line's name.
-3. The technician is added to that line's roster only (not to the order's other lines).</t>
+3. The technician is added to that line's roster only (not to the order's other lines).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2009,7 +2069,9 @@
         <is>
           <t>1. The spread step opens (step 2 of the same modal) to distribute the hours across consecutive working days.
 2. Its header shows the chosen scope and a 'Change scope' back-link.
-3. No shifts exist yet until the spread is confirmed.</t>
+3. No shifts exist yet until the spread is confirmed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.5).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2057,7 +2119,9 @@
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. The shift is created straight away - the spread step does NOT appear.
-2. The shift sits on the dropped day only.</t>
+2. The shift sits on the dropped day only.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2106,7 +2170,9 @@
         <is>
           <t>1. The cell currently under the cursor highlights as a drop target.
 2. A ghost block follows the drag showing the line name and its hours.
-3. Releasing outside any valid cell creates nothing.</t>
+3. Releasing outside any valid cell creates nothing.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2159,7 +2225,9 @@
 2. The sidebar line row's avatar stack/count updates to include the technician.
 3. If the line previously showed 'Needs techs', the badge is gone.
 4. Dragging the same line onto a second technician adds that technician to the line's roster as well - the technician who was already there stays on it.
-5. Nothing asks you to swap or replace the technician who was already there, and no limit is reached on how many technicians a line can have.</t>
+5. Nothing asks you to swap or replace the technician who was already there, and no limit is reached on how many technicians a line can have.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§1.2, §4.3, §7).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2207,7 +2275,9 @@
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. The item can be placed onto a cell without holding a drag - clicking arms it, and clicking a cell places it.
-2. The result is the same as the equivalent drag-and-drop (scope picker / spread step rules apply the same way).</t>
+2. The result is the same as the equivalent drag-and-drop (scope picker / spread step rules apply the same way).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2259,7 +2329,9 @@
 2. It is labeled with the order's line count and total hours (matching the sum of the approved lines).
 3. The picker is anchored to the cell that was dropped on.
 4. Each line row shows the line title and its estimated hours.
-5. Rows for lines that already have technicians show the current roster as an avatar stack plus count.</t>
+5. Rows for lines that already have technicians show the current roster as an avatar stack plus count.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2309,7 +2381,9 @@
         <is>
           <t>1. One shift is created covering all of the order's approved lines.
 2. The block's last text line reads 'N Lines' (with N = the line count).
-3. The technician is added to the roster of every one of those lines.</t>
+3. The technician is added to the roster of every one of those lines.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3, §4.4).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2358,7 +2432,9 @@
         <is>
           <t>1. A single-line shift for that line is created immediately - no extra confirmation step.
 2. The picker closes.
-3. The block's last text line shows the line's name.</t>
+3. The block's last text line shows the line's name.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2413,7 +2489,9 @@
 2. A confirm bar appears with a running tally of the selection - the count of lines and their combined hours (in the spec's example format, 'Create shift · 2 lines · 6h').
 3. 'Select all' ticks every line - the tally equals the whole order (same line count and hours as 'Schedule whole work order').
 4. Cancel leaves checkbox mode and returns to the normal single-tap line list without creating anything.
-5. Confirming creates ONE shift covering the ticked lines, and the technician is added to those lines' rosters only.</t>
+5. Confirming creates ONE shift covering the ticked lines, and the technician is added to those lines' rosters only.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2461,7 +2539,9 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1. The shift starts at the technician's own configured start time (6:00 AM in the example), not the shop's business-hours start.</t>
+          <t>1. The shift starts at the technician's own configured start time (6:00 AM in the example), not the shop's business-hours start.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2509,7 +2589,9 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. The shift starts at the shop's business-hours start time.</t>
+          <t>1. The shift starts at the shop's business-hours start time.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2557,7 +2639,9 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. The shift starts at 7:00 AM - the general default working day (7:00 AM to 7:00 PM) applies.</t>
+          <t>1. The shift starts at 7:00 AM - the general default working day (7:00 AM to 7:00 PM) applies.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2605,7 +2689,9 @@
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. The shift starts at the time position where it was dropped (not at the technician-hours/business-hours default).
-2. The start time aligns to the timeline position (see the 15-minute snapping case).</t>
+2. The start time aligns to the timeline position (see the 15-minute snapping case).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2654,7 +2740,9 @@
         <is>
           <t>1. An unassigned shift is created in the Unassigned row for that day.
 2. It has no technician (and no technician is added to the line's roster by this drop).
-3. The block uses the same anatomy as a regular shift (customer, unit, line name / 'N Lines').</t>
+3. The block uses the same anatomy as a regular shift (customer, unit, line name / 'N Lines').
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2, §3.2).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2702,7 +2790,9 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. The unassigned shift starts at the shop's business-hours start (there is no technician whose hours could apply).</t>
+          <t>1. The unassigned shift starts at the shop's business-hours start (there is no technician whose hours could apply).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2752,7 +2842,9 @@
         <is>
           <t>1. The shift is now assigned to that technician (it leaves the Unassigned row and sits in the technician's row).
 2. The technician is added to the affected line's roster.
-3. The technician's own working hours now apply to the shift's timing.</t>
+3. The technician's own working hours now apply to the shift's timing.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2805,7 +2897,9 @@
 2. Its header shows the chosen scope (which lines / how many hours).
 3. A 'Change scope' back-link is present.
 4. Clicking 'Change scope' takes the modal back to the scope picker (step 1) without creating anything.
-5. Choosing a new scope updates the spread step's header and hours accordingly.</t>
+5. Choosing a new scope updates the spread step's header and hours accordingly.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2855,7 +2949,9 @@
           <t>1. The selector defaults to 'Full estimate'.
 2. The options include 'Full estimate', '1 week', '2 weeks', 'Until a date…', and 'Specific hours…'.
 3. 'Full estimate', '1 week', and '2 weeks' apply on selection with no extra fields - the modal stays to one line for these.
-4. The preview summary updates to match each selection.</t>
+4. The preview summary updates to match each selection.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2903,7 +2999,9 @@
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. Choosing 'Until a date…' reveals a single 'finish by' date field (this is the only custom control shown).
-2. Picking a date updates the preview so the series ends by that date.</t>
+2. Picking a date updates the preview so the series ends by that date.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2950,7 +3048,9 @@
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. Choosing 'Specific hours…' reveals an hours stepper control.
-2. The preview updates to spread exactly the entered hours across working days.</t>
+2. The preview updates to spread exactly the entered hours across working days.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3000,7 +3100,9 @@
         <is>
           <t>1. The start date defaults to the earliest working day.
 2. It can be changed; technician B's series then starts after A's series ends (sequential, not parallel).
-3. B's series is created from the adjusted start date onward.</t>
+3. B's series is created from the adjusted start date onward.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3051,7 +3153,9 @@
           <t>1. Daily shifts are sized to the technician's own working hours (8h each in the example).
 2. Weekends are skipped ONLY when the technician has no business hours set for them; if the tech has hours on a weekend day (e.g. Saturday hours) that day is NOT skipped.
 3. Shop closures and public holidays are NOT skipped in V1 - shifts can be placed on those days.
-4. The end date is a result of the daily distribution (for 40h at 8h/day starting Monday, the series ends on the fifth working day).</t>
+4. The end date is a result of the daily distribution (for 40h at 8h/day starting Monday, the series ends on the fifth working day).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3100,7 +3204,9 @@
         <is>
           <t>1. Collapsed: a one-line summary in the spirit of the spec's example '20 shifts · Jun 15 to Jul 13 · skips weekends + 2 days'.
 2. Expanded: a week-by-week breakdown of the planned shifts.
-3. Skipped days are struck through and show the reason they are skipped - in V1 the only skip reason is a weekend day with no working hours set.</t>
+3. Skipped days are struck through and show the reason they are skipped - in V1 the only skip reason is a weekend day with no working hours set.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3150,7 +3256,9 @@
           <t>1. One daily shift is created per planned working day, together forming a linked series.
 2. The shifts render as one connected banner (see the series-banner cases).
 3. Each daily shift keeps its own day and hours.
-4. A toast with Undo appears.</t>
+4. A toast with Undo appears.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §4.6, §8.2).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3199,7 +3307,9 @@
         <is>
           <t>1. Technician B gets a full 40h series of their own - the estimate is spread again in full, not reduced by A's booking.
 2. There is no shared 'remaining hours' counter across technicians and no splitting of a shift.
-3. Planned hours across technicians may now exceed the estimate - this is expected and produces no error (progress is driven by clocked-in time).</t>
+3. Planned hours across technicians may now exceed the estimate - this is expected and produces no error (progress is driven by clocked-in time).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3251,7 +3361,9 @@
           <t>1. Going past 8 weeks does not silently succeed: a warning about the very long series appears and asks you to confirm before the shifts are created.
 2. After you confirm the warning, the long series is created normally.
 3. A single spread that would create more than 120 daily shifts is refused outright - no confirmation can override it, and no shifts are created for that attempt.
-4. No half-created series is left behind after a refused attempt.</t>
+4. No half-created series is left behind after a refused attempt.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3301,7 +3413,9 @@
         <is>
           <t>1. The series renders as one continuous bar wrapping across the week rows.
 2. It is labeled once at the start (including the technician); later weeks show a faded 'continues'-style label instead of repeating the full label.
-3. Weekend columns inside the series are empty (no bar) when no business hours are set for those weekend days.</t>
+3. Weekend columns inside the series are empty (no bar) when no business hours are set for those weekend days.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3351,7 +3465,9 @@
         <is>
           <t>1. One banner spans the working days of that week in the technician's row.
 2. Chevrons at the banner's edges indicate the series continues beyond the visible week (both sides, on a middle week).
-3. A 'week N of M' cue shows the position within the series.</t>
+3. A 'week N of M' cue shows the position within the series.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3399,7 +3515,9 @@
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The day shows a single time-positioned block (no spanning bar - only one day is visible).
-2. The block carries a cue in the spirit of 'part of an M-week job' indicating it belongs to a longer series.</t>
+2. The block carries a cue in the spirit of 'part of an M-week job' indicating it belongs to a longer series.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3449,7 +3567,9 @@
         <is>
           <t>1. Each series day contributes its own daily hours to that day's capacity bar (the series is not counted as one lump).
 2. The overlapping day is flagged as a Double-booked conflict, exactly as it would be for standalone shifts.
-3. The detail modal shows that single day's shift (its own day and hours) while indicating it belongs to the series.</t>
+3. The detail modal shows that single day's shift (its own day and hours) while indicating it belongs to the series.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6, §8.2).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3498,7 +3618,9 @@
           <t>1. Line 1: the customer name.
 2. Line 2: the unit number.
 3. Last line: the name of the scheduled line.
-4. No work order number appears on the block.</t>
+4. No work order number appears on the block.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3548,7 +3670,9 @@
         <is>
           <t>1. The whole-order block reads '4 Lines'.
 2. The subset block reads '2 Lines' - the block does not distinguish whole-order from subset beyond the count.
-3. Each detail modal lists exactly which lines the shift covers.</t>
+3. Each detail modal lists exactly which lines the shift covers.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4, §12).</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3597,7 +3721,9 @@
         <is>
           <t>1. The unconflicted block shows NO icons and NO work order number - only its text lines.
 2. The conflicted block shows the conflict (warning) icon on its first line - and that is the only icon that ever appears on a block.
-3. No scope icons distinguish whole-order from subset shifts.</t>
+3. No scope icons distinguish whole-order from subset shifts.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3648,7 +3774,9 @@
           <t>1. Both shifts are created and shown on the same day for the same technician - multiple same-day shifts from different work orders are allowed.
 2. Both shifts sit in the same single lane, one after the other.
 3. The row stays at its normal height.
-4. No conflict is flagged for back-to-back (non-intersecting) shifts.</t>
+4. No conflict is flagged for back-to-back (non-intersecting) shifts.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7, §12).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3696,7 +3824,9 @@
         <is>
           <t>1. The two overlapping shifts render in separate stacked lanes - they never visually collide.
 2. The row grows in height to fit the lanes.
-3. The overlap is also flagged as a Double-booked conflict (stacking reads as 'resolve me').</t>
+3. The overlap is also flagged as a Double-booked conflict (stacking reads as 'resolve me').
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7, §4.11).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3746,7 +3876,9 @@
           <t>1. At most 3 lanes are visible.
 2. The remaining overlapping shifts collapse into a '+N more' affordance (here '+2 more').
 3. Clicking it opens a popover listing the hidden shifts.
-4. The hidden shifts can be opened from that popover.</t>
+4. The hidden shifts can be opened from that popover.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3796,7 +3928,9 @@
         <is>
           <t>1. All three views handle the overlap without blocks visually colliding.
 2. Week and month views reach the '+N more' overflow sooner than day view (their cells are narrower), but the same cap-and-overflow model applies.
-3. The overflow affordance opens the hidden-shifts popover in each view.</t>
+3. The overflow affordance opens the hidden-shifts popover in each view.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3849,7 +3983,9 @@
 2. The start used is the earliest technician's configured start; if no tech hours are set, business hours; otherwise 7:00 AM - so no shifts sit off-screen to the left.
 3. Your manual scroll position stays put - nothing jumps you back to the morning while you remain on the same day.
 4. The timeline is not stuck at the start - it remains a full 24-hour scrollable timeline (midnight to midnight).
-5. Only navigating to another day re-triggers the auto-scroll.</t>
+5. Only navigating to another day re-triggers the auto-scroll.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3898,7 +4034,9 @@
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. In day view, the date/time header bar stays stuck to the top while the rows scroll beneath it - you always know which time column you are looking at.
-2. The same sticky-header behavior applies in week view.</t>
+2. The same sticky-header behavior applies in week view.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3949,7 +4087,9 @@
           <t>1. The shift moves along the timeline as you drag.
 2. The released start time snaps to a 15-minute interval (for example 9:15, 9:30 - never 9:22).
 3. The duration is unchanged by a horizontal move.
-4. A toast with Undo appears for the move.</t>
+4. A toast with Undo appears for the move.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8, §7).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4000,7 +4140,9 @@
           <t>1. Dragging the right edge extends/shortens the end time (start unchanged).
 2. Dragging the left edge adjusts the start time (end unchanged).
 3. The resulting times land on 15-minute increments.
-4. The shift's duration on the grid matches the modal's start/end.</t>
+4. The shift's duration on the grid matches the modal's start/end.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4049,7 +4191,9 @@
         <is>
           <t>1. A vertical line marks the current time on the timeline.
 2. Its position matches the actual clock time.
-3. Hovering the now line while your pointer is over the grid shows a label (the current time).</t>
+3. Hovering the now line while your pointer is over the grid shows a label (the current time).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4098,7 +4242,9 @@
         <is>
           <t>1. A detail panel opens for the shift.
 2. It shows the customer name, unit number, the VIN (below unit and asset), and the work order id.
-3. The VIN is visible here even though the grid's VIN toggle is off - the modal always shows it.</t>
+3. The VIN is visible here even though the grid's VIN toggle is off - the modal always shows it.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §9).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4149,7 +4295,9 @@
           <t>1. The time pickers offer 15-minute increments (for example 8:00, 8:15, 8:30, 8:45).
 2. Saving/applying the change updates the shift's times.
 3. Changing the date moves the shift to the chosen day.
-4. The grid block reflects the new date/times.</t>
+4. The grid block reflects the new date/times.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4198,7 +4346,9 @@
         <is>
           <t>1. The assigned technician is shown.
 2. A progress indication compares time logged against the estimate (logged hours vs estimated hours).
-3. The numbers are consistent with the line's actual logged time and estimate.</t>
+3. The numbers are consistent with the line's actual logged time and estimate.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9).</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4248,7 +4398,9 @@
           <t>1. The 'Work Order Lines' section shows the line count and a scope summary of what the shift covers.
 2. Exactly the 2 scheduled lines are listed (not all 4), each showing its line number, title, hours, and a status pill only.
 3. No labor figures and no total dollar amount appear anywhere in the modal.
-4. This is where whole-order vs subset scope is spelled out (the grid block only says 'N Lines').</t>
+4. This is where whole-order vs subset scope is spelled out (the grid block only says 'N Lines').
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §4.4). The current behaviour follows a later product owner decision dated 2026-07-22.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4297,7 +4449,9 @@
         <is>
           <t>1. The estimated hours field is editable directly in the modal.
 2. The new value persists after closing and re-opening.
-3. Dependent displays (progress vs estimate) reflect the new value.</t>
+3. Dependent displays (progress vs estimate) reflect the new value.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9).</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4347,7 +4501,9 @@
           <t>1. The note is added and shown in the modal.
 2. The edit is saved and displayed.
 3. The delete removes the note.
-4. Notes are kept per work order (the same note is visible from another shift of the same work order).</t>
+4. Notes are kept per work order (the same note is visible from another shift of the same work order).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9).</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4398,7 +4554,9 @@
           <t>1. A conflict banner is shown in the modal describing the conflict.
 2. It offers an 'Adjust' action.
 3. 'Adjust' leads to a way to resolve the conflict (for example changing the shift's time).
-4. An unconflicted shift's modal shows no such banner.</t>
+4. An unconflicted shift's modal shows no such banner.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4447,7 +4605,9 @@
         <is>
           <t>1. The modal offers a Delete action (a trash icon in the header) and a close (x) icon - and no other actions.
 2. There is no 'Reassign' action in the modal; reassignment is done by dragging a shift to another technician row (covered by its own case).
-3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).</t>
+3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §7).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4497,7 +4657,9 @@
           <t>1. A menu opens at the spot you clicked and contains 'Create Event'.
 2. The event modal opens with the clicked cell's technician and date pre-set.
 3. Saving creates an event block on that technician's day.
-4. A toast with Undo appears.</t>
+4. A toast with Undo appears.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7).</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4546,7 +4708,9 @@
         <is>
           <t>1. Left-clicking empty day-view space opens the cell menu; choosing 'Create Event' starts creation at the time you clicked.
 2. A live preview block is shown while creating, and dragging resizes it.
-3. Completing creates the event at the previewed time/duration.</t>
+3. Completing creates the event at the previewed time/duration.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10).</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4598,7 +4762,9 @@
 2. The event saves with the entered values.
 3. Re-opening the event shows the saved values.
 4. With all-day ON, specific start/end times are not required (the time fields are disabled or hidden).
-5. The event is created as an all-day block for that technician and day.</t>
+5. The event is created as an all-day block for that technician and day.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §8.1).</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4648,7 +4814,9 @@
         <is>
           <t>1. Dropping on another technician reassigns the event to them.
 2. Dropping on another day moves it to that day.
-3. Each move produces a toast with Undo.</t>
+3. Each move produces a toast with Undo.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7).</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4696,7 +4864,9 @@
         <is>
           <t>1. The event card is a white/neutral card with a thin, even border on all four sides and NO colored left rail (the left rail is the shift's cue).
 2. It has a small grey-filled rounded chip on the left containing a calendar icon, and two lines of text beside it: the event name, then the time range in secondary text.
-3. The shift reads as a tinted color-filled block with a colored left rail - the two types are separable at a glance, not by color alone.</t>
+3. The shift reads as a tinted color-filled block with a colored left rail - the two types are separable at a glance, not by color alone.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10).</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4746,7 +4916,9 @@
         <is>
           <t>1. The default event color is neutral/grey.
 2. The color picker offers the same custom color palette as shifts (shared picker with editable labels).
-3. Choosing a color tints the card and the icon chip in matching tones, the same way a colored shift is tinted.</t>
+3. Choosing a color tints the card and the icon chip in matching tones, the same way a colored shift is tinted.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §10).</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4796,7 +4968,9 @@
         <is>
           <t>1. Adding the event DOES increase that day's capacity bar fill - the event's hours are counted alongside shift hours (a 2-hour meeting uses up 2 hours of the technician's available time).
 2. The event does NOT create a double-booked or overlap conflict with the shift, and the toolbar conflict count does not increase because of it.
-3. The two behave differently on purpose: an event uses up capacity, but it is never flagged as a conflict.</t>
+3. The two behave differently on purpose: an event uses up capacity, but it is never flagged as a conflict.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §4.11, §4.12).</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4847,7 +5021,9 @@
           <t>1. The overlap is detected as a Double-booked conflict.
 2. A warning icon appears on the affected block(s).
 3. The toolbar conflict pill's count increases.
-4. The conflict is listed in the pill's dropdown.</t>
+4. The conflict is listed in the pill's dropdown.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11).</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -4896,7 +5072,9 @@
         <is>
           <t>1. The shift is created but flagged as a conflict because the day is outside the technician's configured working days (the reason sentence reads in the spirit of 'Scheduled on a weekend (outside working days)' - it names the technician's own working days, not a fixed Monday-to-Friday window).
 2. If the technician's working days DO include that day (for example Saturday hours are configured), a shift on that day is NOT flagged.
-3. The warning icon appears on the block and the conflict is listed in the toolbar dropdown.</t>
+3. The warning icon appears on the block and the conflict is listed in the toolbar dropdown.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11).</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -4948,7 +5126,9 @@
           <t>1. The shift is flagged as a before-hours conflict, with a reason sentence in the spirit of 'Starts before working hours', measured against that technician's own configured working-day START time (not a fixed hour).
 2. The shift is flagged as an after-hours conflict, with a reason sentence in the spirit of 'Extends past working hours', measured against that technician's own configured working-day END time (not a fixed hour).
 3. Both the start and the end follow the hierarchy technician hours, then shop business hours, then the general default working day of 7:00 AM to 7:00 PM.
-4. Warning icon on the block in each case; the conflict appears in the toolbar dropdown.</t>
+4. Warning icon on the block in each case; the conflict appears in the toolbar dropdown.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.2).</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -4999,7 +5179,9 @@
           <t>1. The pill shows the current number of scheduling issues.
 2. Clicking opens a dropdown listing each conflict.
 3. The list covers all current conflicts (count matches the pill).
-4. Resolving a conflict (for example moving the shift) reduces the count - detection is continuous.</t>
+4. Resolving a conflict (for example moving the shift) reduces the count - detection is continuous.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §6).</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5047,7 +5229,9 @@
       <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. The grid navigates to the relevant technician and day.
-2. The conflicted shift is brought into view.</t>
+2. The conflicted shift is brought into view.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11).</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5095,7 +5279,9 @@
       <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. Overtime is signaled with the 'OT' text tag and amber tones - NOT red or alarming styling.
-2. Red/alarming styling appears only for conflicts and genuine errors.</t>
+2. Red/alarming styling appears only for conflicts and genuine errors.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.12).</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5146,7 +5332,9 @@
         <is>
           <t>1. Each day header shows a capacity bar; the blue fill represents total technician-hours booked - shift hours PLUS event hours - divided by total available (sum of all techs' working hours).
 2. A more heavily booked day shows a longer blue fill; the fill never exceeds the track (clamped at 100%).
-3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.</t>
+3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12).</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5193,7 +5381,9 @@
       <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. An amber segment extends past the right edge of the track, showing the excess.
-2. A tick marks the 100% line where the track ends.</t>
+2. A tick marks the 100% line where the track ends.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12).</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5241,7 +5431,9 @@
         <is>
           <t>1. An 'OT' tag appears for the day even though the aggregate bar is under 100%.
 2. The tag is text, not a color-only signal.
-3. Overtime (per-technician) and capacity (aggregate) are independent signals.</t>
+3. Overtime (per-technician) and capacity (aggregate) are independent signals.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12, §11).</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5290,7 +5482,9 @@
         <is>
           <t>1. A tooltip shows a per-technician breakdown: assigned hours vs that technician's capacity.
 2. The overtime technician's entry is highlighted in amber.
-3. The numbers agree with the shifts actually on the grid.</t>
+3. The numbers agree with the shifts actually on the grid.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5339,7 +5533,9 @@
         <is>
           <t>1. The tooltip shows: the customer name; unit, vehicle, and VIN (the tooltip shows the VIN whenever the unit has one, regardless of the 'VIN Number' toggle); the date and time range; the technician; and a scope summary ('N lines · Xh' style).
 2. The individual line names appear as a short list capped at 3, with a '+N more lines' row for the rest (here '+2 more lines'); line statuses are NOT shown.
-3. A time-logged progress bar shows logged vs estimated hours ('X / Yh' style).</t>
+3. A time-logged progress bar shows logged vs estimated hours ('X / Yh' style).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). The current behaviour follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5386,7 +5582,9 @@
       <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. The customer name line includes the conflict icon.
-2. The conflict reason is shown in amber.</t>
+2. The conflict reason is shown in amber.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13).</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5434,7 +5632,9 @@
         <is>
           <t>1. The tooltip shows the event name with its category dot (grey for a default event).
 2. The date and time range are shown.
-3. The technician is shown.</t>
+3. The technician is shown.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13).</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5486,7 +5686,9 @@
           <t>1. A quick pass does not flash tooltips - the tooltip opens only after a short hover delay (spec: roughly 300 to 500ms).
 2. It dismisses when the mouse leaves the block.
 3. The tooltip is read-only (no buttons/actions inside it).
-4. Clicking the block opens the full detail modal as normal.</t>
+4. Clicking the block opens the full detail modal as normal.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13).</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5535,7 +5737,9 @@
         <is>
           <t>1. When there is not enough room below, the tooltip opens ABOVE the block instead.
 2. Near a side edge, the tooltip shifts horizontally to stay fully within the viewport.
-3. No part of the tooltip is clipped off-screen.</t>
+3. No part of the tooltip is clipped off-screen.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13).</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5582,7 +5786,9 @@
       <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The grid jumps to the range containing the current date (today's day, this week, or this month depending on the active view).
-2. The date label updates accordingly.</t>
+2. The date label updates accordingly.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6).</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5632,7 +5838,9 @@
           <t>1. Week view: each arrow click moves one whole week; the label shows the week range (spec's example format: 'Jul 14 to 20, 2026').
 2. Day view: each click moves one day; the label shows that day.
 3. Month view: each click moves one month; the label shows that month.
-4. The label always matches what the grid displays.</t>
+4. The label always matches what the grid displays.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6).</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5683,7 +5891,9 @@
           <t>1. Blocks that match the search are highlighted; blocks that do not match fade.
 2. All five fields match: customer name, work order number, unit number, technician name, and line name.
 3. Matching blocks stay in place on the grid (search visually filters; it does not remove or rearrange).
-4. Clearing the search restores all blocks to normal.</t>
+4. Clearing the search restores all blocks to normal.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6).</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5731,7 +5941,9 @@
         <is>
           <t>1. The dropdown is checkbox style and contains: a toggle per department, 'My Shifts', and 'VIN'.
 2. Defaults: all department toggles ON, 'My Shifts' OFF, 'VIN' OFF.
-3. There is no separate departments-only control - this dropdown replaces it.</t>
+3. There is no separate departments-only control - this dropdown replaces it.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6, §9).</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5781,7 +5993,9 @@
         <is>
           <t>1. The turned-off department's group (header and technician rows) disappears from the grid.
 2. Other departments are unaffected.
-3. Turning it back on restores the group.</t>
+3. Turning it back on restores the group.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9).</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5832,7 +6046,9 @@
           <t>1. Only shifts assigned to you remain visible; all other technician rows and their shifts are hidden.
 2. Turning it off restores the full grid.
 3. This is a personal convenience filter only - it does not change what you are permitted to see (default is OFF, everyone's shifts visible).
-4. For a user who has no technician/staff record of their own, the 'My Shifts' option is not shown at all.</t>
+4. For a user who has no technician/staff record of their own, the 'My Shifts' option is not shown at all.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §14.3).</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -5885,7 +6101,9 @@
 2. 'VIN Number' on: the VIN appears as an additional line on blocks in day and week views.
 3. Month view blocks never show the VIN, even with the toggle on (space constraints).
 4. In day view with the VIN on, the lane height grows to fit the extra VIN line and no block text is clipped or cut off.
-5. The 'VIN Number' toggle affects the block only - the tooltip and the modal always show the VIN when the unit has one.</t>
+5. The 'VIN Number' toggle affects the block only - the tooltip and the modal always show the VIN when the unit has one.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §4.4, §4.8). The current behaviour follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -5937,7 +6155,9 @@
           <t>1. Six toggles are offered: Business Hours, Capacity Bars, Events, Tech Hours, Saturday, Sunday.
 2. Defaults: Business Hours OFF, Capacity Bars ON, Events ON, Tech Hours OFF, Saturday ON, Sunday ON.
 3. Capacity Bars OFF: the capacity bars disappear from the column headers; ON: they reappear with the same values.
-4. Events OFF: event blocks disappear from the grid while shifts remain; ON: the events reappear unchanged.</t>
+4. Events OFF: event blocks disappear from the grid while shifts remain; ON: the events reappear unchanged.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6, §9, §4.12).</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -5987,7 +6207,9 @@
         <is>
           <t>1. With the toggle on, the hours OUTSIDE the working day are shaded with a grey overlay.
 2. Working hours remain unshaded.
-3. Turning it off removes the shading.</t>
+3. Turning it off removes the shading.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §4.8).</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6036,7 +6258,9 @@
         <is>
           <t>1. Each technician's working hours are displayed next to their name in the row header.
 2. The hours match the technicians' configured hours.
-3. Turning it off hides the hours again.</t>
+3. Turning it off hides the hours again.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9).</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6085,7 +6309,9 @@
         <is>
           <t>1. Saturday off: the Saturday column is removed (6 columns remain).
 2. Sunday off too: 5 weekday columns remain (Monday to Friday).
-3. Both back on: the full Monday-to-Sunday 7-column week returns.</t>
+3. Both back on: the full Monday-to-Sunday 7-column week returns.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §3.2).</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6136,7 +6362,9 @@
           <t>1. A confirmation modal appears for the cross-technician move.
 2. After confirming, the shift sits on technician B's row.
 3. Technician B is added to the affected line's roster and technician A is removed from it.
-4. A toast with Undo appears.</t>
+4. A toast with Undo appears.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §12).</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6187,7 +6415,9 @@
 2. It contains ONLY two items: 'Create Event' and 'New Work Order'.
 3. There is no 'View Day' item - it was removed from the menu.
 4. There is no 'New Shift' item - it was removed from the menu.
-5. This menu is opened by a normal left-click - right-clicking the cell does not open it.</t>
+5. This menu is opened by a normal left-click - right-clicking the cell does not open it.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §14.1).</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6234,7 +6464,9 @@
       <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. The menu offers a 'New Work Order' item.
-2. Choosing it directs the user to create a work order (a toast / prompt pointing to the Work Orders tab).</t>
+2. Choosing it directs the user to create a work order (a toast / prompt pointing to the Work Orders tab).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §4.10).</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6283,7 +6515,9 @@
         <is>
           <t>1. A scope prompt appears with three options: this shift only, this and everything after, and the whole series.
 2. Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').
-3. The prompt uses routine, lightweight styling - not alarming destructive styling.</t>
+3. The prompt uses routine, lightweight styling - not alarming destructive styling.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6334,7 +6568,9 @@
           <t>1. Only that day's shift is removed.
 2. The series keeps the gap - the remaining shifts do NOT shuffle to close it.
 3. The removed day's hours return to the estimate's remaining (scheduled hours drop by that day's hours).
-4. An undo toast appears.</t>
+4. An undo toast appears.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6383,7 +6619,9 @@
         <is>
           <t>1. The third shift and every later shift of the series are removed.
 2. The first two shifts remain untouched.
-3. An undo toast appears.</t>
+3. An undo toast appears.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6432,7 +6670,9 @@
         <is>
           <t>1. All of technician A's series shifts are removed.
 2. Technician B's independent series is untouched (the scope is per technician's series).
-3. An undo toast appears.</t>
+3. An undo toast appears.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6483,7 +6723,9 @@
           <t>1. First shift: two options ('this and after' would equal 'whole series', so only two are shown).
 2. Last shift: two options ('this and after' would equal 'this only').
 3. Middle shift: all three options.
-4. Cancelling leaves the series unchanged in every case.</t>
+4. Cancelling leaves the series unchanged in every case.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6531,7 +6773,9 @@
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
-2. The shift is deleted and an undo toast appears.</t>
+2. The shift is deleted and an undo toast appears.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6580,7 +6824,9 @@
         <is>
           <t>1. Untouched, a toast that has an Undo action persists about 7 seconds; a toast without Undo persists about 4 seconds, before dismissing.
 2. While the cursor is over it, the toast stays (does not auto-dismiss).
-3. After the cursor leaves, it dismisses.</t>
+3. After the cursor leaves, it dismisses.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11).</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6634,7 +6880,9 @@
 2. Undo after delete: the shift is back exactly where it was.
 3. Undo after move: the shift returns to its original day/time.
 4. Undo after reassign: the shift returns to the original technician, and the line's roster is restored (original tech back on, target tech off).
-5. Every destructive action is undoable within the toast's lifetime.</t>
+5. Every destructive action is undoable within the toast's lifetime.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11).</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6686,7 +6934,9 @@
           <t>1. The delete took effect immediately: after the refresh the shift is gone even though Undo was never clicked - closing or refreshing does not cancel the action.
 2. The move also stuck after the refresh - the shift is on the new day.
 3. Clicking Undo within the toast's lifetime reverses the action (the deleted shift comes back).
-4. Note for the tester: Undo works by performing a reversing action, not by holding the change back - a change surviving a refresh before Undo is expected, not a bug.</t>
+4. Note for the tester: Undo works by performing a reversing action, not by holding the change back - a change surviving a refresh before Undo is expected, not a bug.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -6738,7 +6988,9 @@
 2. Same for the time picker and the note edit - each sub-picker closes first and the modal stays open.
 3. Escape with no open sub-picker closes the modal itself.
 4. With two layers open, the FIRST Escape closes only the topmost layer, and the SECOND Escape closes the next layer down.
-5. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).</t>
+5. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6791,7 +7043,9 @@
           <t>1. In each confirmable dialog, Enter confirms it - equivalent to clicking its confirm action.
 2. The confirmed action takes effect (spread created / reassigned / event saved / delete applied).
 3. In the note editor, Enter inserts a new line in the note - it does NOT confirm or close the dialog.
-4. The multiline note can be completed and saved normally.</t>
+4. The multiline note can be completed and saved normally.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6840,7 +7094,9 @@
         <is>
           <t>1. Focus moves through the modal's interactive elements with visible focus rings.
 2. Focus stays trapped inside the modal (wraps back to its first control) until the modal closes.
-3. On the page, toolbar and sidebar controls are reachable by keyboard.</t>
+3. On the page, toolbar and sidebar controls are reachable by keyboard.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11).</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -6888,7 +7144,9 @@
       <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. Both the single shift and the multi-week series render in the default blue.
-2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.</t>
+2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10).</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6940,7 +7198,9 @@
           <t>1. The shift's block re-renders in the chosen color.
 2. The color provides three consistent tones: background fill, text color, and accent (left border).
 3. The color is per SHIFT, not per work order - the other shift from the same work order keeps its own (default blue) color and does not change.
-4. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).</t>
+4. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10, §4.9, §4.4).</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -6990,7 +7250,9 @@
         <is>
           <t>1. Each color's label can be edited.
 2. The renamed label shows for the whole shop - the same picker opened elsewhere shows 'ZZAUTOTEST Rush'.
-3. Shifts and events share the same custom palette with the same labels.</t>
+3. Shifts and events share the same custom palette with the same labels.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10, §4.10).</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7043,7 +7305,9 @@
 2. Turning it ON reveals a per-day working-hours editor for the shop.
 3. There is one row per day of the week, Monday through Sunday.
 4. Each day has a From time and a To time you can set.
-5. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).</t>
+5. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7092,7 +7356,9 @@
         <is>
           <t>1. Edit Staff Member shows a toggle labelled 'Set custom hours for this technician'.
 2. The toggle is OFF by default (no custom hours set).
-3. Turning it ON reveals a per-day working-hours editor for that technician.</t>
+3. Turning it ON reveals a per-day working-hours editor for that technician.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7126,7 +7392,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>1. The shop has business hours set (/02).
+          <t>1. The shop has business hours set for the shop.
 2. A technician has the 'Set custom hours for this technician' toggle OFF.</t>
         </is>
       </c>
@@ -7139,7 +7405,9 @@
       <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. With no custom hours, the technician's working hours fall back to the shop business hours.
-2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.</t>
+2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7187,7 +7455,9 @@
         <is>
           <t>1. 'Add hours' appends an additional From-To range to that day (to support split shifts).
 2. The added range starts empty (no From/To pre-filled).
-3. Each added range can be removed individually.</t>
+3. Each added range can be removed individually.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7238,7 +7508,9 @@
 2. An inline message reads 'These hours overlap. Adjust the times so they don't conflict.'
 3. Save is disabled while the overlap exists.
 4. The incomplete row (empty From/To) is ignored by the overlap check - it does not raise the overlap error.
-5. Save is not blocked by an incomplete row on its own (only genuine overlaps disable Save).</t>
+5. Save is not blocked by an incomplete row on its own (only genuine overlaps disable Save).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7290,7 +7562,9 @@
           <t>1. The Schedule page opens and all three views work.
 2. The mini calendar, search, and filters all work.
 3. ALL technicians' shifts and events are visible (not just the user's own).
-4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.</t>
+4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1, §14.3).</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7342,7 +7616,9 @@
           <t>1. No drag handles are offered and nothing can be dragged from the sidebar onto the grid.
 2. Shift blocks cannot be moved or resized - no drop targets or resize handles appear.
 3. No creation menu opens at all - there is no 'Create Event' and no 'New Work Order' offered.
-4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.</t>
+4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7389,7 +7665,9 @@
       <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule top-level nav item is not shown at all.
-2. The rest of the app works normally for the role.</t>
+2. The rest of the app works normally for the role.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7442,7 +7720,9 @@
 2. Shift and event creation works, including via the menu opened by left-clicking empty grid space in both week and day view.
 3. Reassignment between technicians works.
 4. Edge-resize and horizontal drag work in day view.
-5. Modal fields are editable and save.</t>
+5. Modal fields are editable and save.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7492,7 +7772,9 @@
         <is>
           <t>1. The delete action and the trash icon are hidden in the shift modal.
 2. Events likewise offer no delete.
-3. No path exists to remove shifts or events - while creating and modifying still work.</t>
+3. No path exists to remove shifts or events - while creating and modifying still work.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7543,7 +7825,9 @@
           <t>1. The delete action is available and works for shifts.
 2. Series deletion offers its scopes (this shift / this and after / whole series).
 3. Events can be deleted too.
-4. Undo toasts appear (restore the items via Undo to clean up).</t>
+4. Undo toasts appear (restore the items via Undo to clean up).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7592,7 +7876,9 @@
         <is>
           <t>1. Edit cannot be granted without View (the admin UI enforces or auto-selects the dependency).
 2. Delete cannot be granted without Edit.
-3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).</t>
+3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14).</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7642,7 +7928,9 @@
         <is>
           <t>1. The sidebar hides the work order list and the line drill-down; the mini calendar remains available.
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
-3. New work orders cannot be dragged on - the WO list is simply not visible.</t>
+3. New work orders cannot be dragged on - the WO list is simply not visible.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.2).</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7690,7 +7978,9 @@
       <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
-2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.</t>
+2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.3).</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7738,7 +8028,9 @@
       <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
-2. The staff member without a department does not appear as a row.</t>
+2. The staff member without a department does not appear as a row.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.4).</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7785,7 +8077,9 @@
       <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. The Time-Clock-ON staff member can clock in.
-2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.</t>
+2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.4).</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7835,7 +8129,9 @@
         <is>
           <t>1. Work-order-derived details (customer, the scheduled line list, and any money-bearing fields) are hidden or masked wherever they would normally appear - on the block, in the tooltip, and in the modal.
 2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
-3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.</t>
+3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.2). The current behaviour follows a later product owner decision dated 2026-07-22.</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7889,7 +8185,9 @@
           <t>1. Technician, Parts Manager, Parts Tech, Office and Time Clock each have Schedule View turned ON and Schedule Edit and Schedule Delete turned OFF.
 2. Service Manager, Senior Service Advisor, Service Advisor and Foreman each have Schedule Edit turned ON (so they also have View).
 3. The user from step 4 gets the read-only schedule - nothing can be dragged onto the grid and no shift can be created.
-4. The user from step 5 can drag a work order onto the grid and create a shift.</t>
+4. The user from step 5 can drag a work order onto the grid and create a shift.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -7939,7 +8237,9 @@
           <t>1. Below the 960px minimum supported width, the grid scrolls horizontally rather than breaking.
 2. All days remain reachable by horizontal scroll.
 3. On narrow viewports the sidebar collapses.
-4. No content becomes permanently unreachable and nothing errors.</t>
+4. No content becomes permanently unreachable and nothing errors.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11).</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -7989,7 +8289,9 @@
         <is>
           <t>1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
-3. Search stays responsive on the long list.</t>
+3. Search stays responsive on the long list.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11).</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8039,7 +8341,9 @@
         <is>
           <t>1. The grid renders and scrolls smoothly at this scale.
 2. View switches complete without long hangs.
-3. Tooltips and modals stay responsive.</t>
+3. Tooltips and modals stay responsive.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11).</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8089,7 +8393,9 @@
         <is>
           <t>1. The closure day is NOT struck through or skipped by the spread in V1.
 2. A shift CAN be placed on the shop closure day (only weekend days with no business hours are skipped).
-3. The end date follows the normal daily distribution - no extra day is added for the closure.</t>
+3. The end date follows the normal daily distribution - no extra day is added for the closure.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§12, §4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8136,7 +8442,9 @@
       <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. All three quantities are shown/derivable and may differ from one another.
-2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).</t>
+2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12).</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8184,7 +8492,9 @@
       <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. Every shift in the series starts at the SAME local wall-clock time (e.g. 8:00 AM) on both sides of the clock change.
-2. No shift in the series silently moves an hour earlier or later after the change date.</t>
+2. No shift in the series silently moves an hour earlier or later after the change date.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8235,7 +8545,9 @@
           <t>1. In dark mode every part of the Schedule stays readable - no white-on-white or black-on-black text, no unreadable labels or invisible icons.
 2. Every dialog and popover opened from the Schedule follows the dark theme too.
 3. Conflict and overtime cues remain distinguishable (they never rely on colour alone - text/icon still present).
-4. Switching back to light mode restores the normal look with nothing stuck in dark colours.</t>
+4. Switching back to light mode restores the normal look with nothing stuck in dark colours.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11).</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8284,7 +8596,9 @@
         <is>
           <t>1. Every shift and event that existed before the release is still there after it - same technician, same day, same time, same work order.
 2. Events are still events and shifts are still shifts (nothing changed kind or vanished).
-3. Their details open normally and are editable/deletable like any other entry.</t>
+3. Their details open normally and are editable/deletable like any other entry.
+---
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan. No numbered requirement in the Schedule specification version 23 covers this point yet.</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8333,7 +8647,9 @@
         <is>
           <t>1. The Dashboard shows that work order as ONE row (covering the whole scheduled span), not one row per daily shift.
 2. Note for the tester: before this release the Dashboard duplicated such a work order once per scheduled day - showing one combined row now is the intended fix, do not report it as a missing-rows bug.
-3. Work orders with a single shift are unaffected.</t>
+3. Work orders with a single shift are unaffected.
+---
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan. No numbered requirement in the Schedule specification version 23 covers this point yet.</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8382,7 +8698,9 @@
         <is>
           <t>1. The appointment created with the work order appears on the Schedule board at the chosen date/time.
 2. It behaves like any other scheduled entry (opens, moves, deletes normally).
-3. It also appears in the Dashboard's schedule section for that day.</t>
+3. It also appears in the Dashboard's schedule section for that day.
+---
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan. No numbered requirement in the Schedule specification version 23 covers this point yet.</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8432,7 +8750,9 @@
         <is>
           <t>1. The shift appears on location A's board (the location the work order belongs to).
 2. The shift does NOT appear on location B's board, even though the technician is enrolled there too.
-3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.</t>
+3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.
+---
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan. No numbered requirement in the Schedule specification version 23 covers this point yet.</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8483,7 +8803,9 @@
           <t>1. The work order form offers a Priority choice of High, Medium, Low.
 2. A new work order has NO priority pre-selected by default.
 3. After saving, the Schedule sidebar reflects the chosen priority and the Priority filter finds the work order under High.
-4. A work order with no priority set simply shows none (it is not treated as an error).</t>
+4. A work order with no priority set simply shows none (it is not treated as an error).
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8534,7 +8856,9 @@
           <t>1. No Schedule permission: the board GET is refused with HTTP 403.
 2. View-only: the board GET returns HTTP 200 with the grid data; the POST and PATCH are refused with HTTP 403.
 3. View + Edit: the POST and PATCH succeed (HTTP 201/200); the DELETE is refused with HTTP 403 because the user lacks Schedule: Delete.
-4. Each refusal is a clean 403 response - never a server error.</t>
+4. Each refusal is a clean 403 response - never a server error.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14).</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8585,7 +8909,9 @@
           <t>1. The over-8-week create is refused with HTTP 409 (a 'series too long' error) - nothing is created.
 2. With acknowledgeLongSeries=true the same request succeeds (HTTP 201) and returns the full materialized series under one series id.
 3. The over-120-shift request is refused with HTTP 422 even WITH the acknowledgement - the hard cap cannot be overridden.
-4. Refused calls leave no partial series behind.</t>
+4. Refused calls leave no partial series behind.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan.</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8634,7 +8960,9 @@
         <is>
           <t>1. No Schedule response contains any pricing/money field for ANY caller - the schedule never returns labor, totals, or dollar amounts.
 2. For the caller without Work Orders: View, the work-order-derived details (customer, unit, VIN, line names) are absent/empty in the response itself - not just hidden on screen.
-3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.</t>
+3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). The current behaviour follows a later product owner decision dated 2026-07-22.</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8684,7 +9012,9 @@
         <is>
           <t>1. The foreign-location GET is refused as not found (HTTP 404) - the response reveals nothing about the other location's shift.
 2. The PATCH on the foreign id is refused the same way (404) - no cross-location edit is possible.
-3. Location A's board contains only location A's shifts - nothing from location B leaks in.</t>
+3. Location A's board contains only location A's shifts - nothing from location B leaks in.
+---
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan. No numbered requirement in the Schedule specification version 23 covers this point yet.</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -523,12 +523,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Schedule is listed as a top-level navigation item alongside Work Orders, Customers, Parts, and Reports.
+          <t xml:space="preserve">1. Schedule is listed as a top-level navigation item alongside Work Orders, Customers, Parts, and Reports.
 2. Clicking it opens the Schedule screen.
 3. The left panel is the work order sidebar: a mini calendar at the top and a work order list beneath it.
 4. The main area is the schedule grid showing technician rows, with a toolbar above it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3, §3.1, §3.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3, §3.1, §3.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -576,12 +578,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. Day: the grid shows a 24-hour timeline per technician row, with shifts positioned at their times.
+          <t xml:space="preserve">1. Day: the grid shows a 24-hour timeline per technician row, with shifts positioned at their times.
 2. Week: the grid shows a 7-column Monday-to-Sunday layout with stacked shift chips per cell.
 3. Month: the grid shows a compact calendar with per-day capacity bars and shift chips.
 4. The same shifts appear in all three views - each one drawn to suit that view: positioned on the hour line in Day, as a chip in the day column in Week, and as a compact chip in Month.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.2, §6).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §6). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -615,32 +619,26 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser.&lt;/li&gt;
-&lt;li&gt;Staff members are assigned to at least two different departments (adjust staff records if needed, restore after).&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page in week view.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser.
+2. Staff members are assigned to at least two different departments (adjust staff records if needed, restore after).
+3. You are on the Schedule page in week view.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Read the technician rows in the grid from top to bottom.&lt;/li&gt;
-&lt;li&gt;Note how the rows are grouped.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Read the technician rows in the grid from top to bottom.
+2. Note how the rows are grouped.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;Rows are grouped by department, each group under its own header (for example a services group and an administration group - the actual names come from the shop's own departments).&lt;/li&gt;
-&lt;li&gt;Each department's technicians are listed beneath that department's header.&lt;/li&gt;
-&lt;li&gt;Every staff member assigned to a visible department appears as a row, regardless of their role.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.2, §14.4).</t>
+          <t xml:space="preserve">1. Rows are grouped by department, each group under its own header (for example a services group and an administration group - the actual names come from the shop's own departments).
+2. Each department's technicians are listed beneath that department's header.
+3. Every staff member assigned to a visible department appears as a row, regardless of their role.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §14.4). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -686,11 +684,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. Collapsing hides that department's technician rows (the group header stays visible).
+          <t xml:space="preserve">1. Collapsing hides that department's technician rows (the group header stays visible).
 2. Expanding shows the technician rows again, unchanged.
 3. Other department groups are unaffected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -724,29 +724,23 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Schedule page.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Look through the grid toolbar and its dropdowns for any control that switches the grid between a department-grouped view and a flat technician-only view.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Look through the grid toolbar and its dropdowns for any control that switches the grid between a department-grouped view and a flat technician-only view.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;No such toggle exists - the department-grouped rows are the only grid grouping.&lt;/li&gt;
-&lt;li&gt;Department visibility is controlled only through the department toggles in the 'Filter and Display' dropdown.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.2).</t>
+          <t xml:space="preserve">1. No such toggle exists - the department-grouped rows are the only grid grouping.
+2. Department visibility is controlled only through the department toggles in the 'Filter and Display' dropdown.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -780,32 +774,26 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page.&lt;/li&gt;
-&lt;li&gt;At least one unassigned shift exists (a user with Edit permission drops a work order onto the Unassigned row first).&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Schedule page.
+3. At least one unassigned shift exists (a user with Edit permission drops a work order onto the Unassigned row first).</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Look for the unassigned row inside the schedule grid.&lt;/li&gt;
-&lt;li&gt;Note where the unassigned shift is displayed.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Look for the unassigned row inside the schedule grid.
+2. Note where the unassigned shift is displayed.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;An unassigned row/lane appears within the grid itself - it is not a separate tray or panel outside the grid.&lt;/li&gt;
-&lt;li&gt;Shifts without a technician sit in this row.&lt;/li&gt;
-&lt;li&gt;The unassigned shift uses the same block layout as regular shifts (customer, unit, line name / line count) - it simply has no technician.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2).</t>
+          <t xml:space="preserve">1. An unassigned row/lane appears within the grid itself - it is not a separate tray or panel outside the grid.
+2. Shifts without a technician sit in this row.
+3. The unassigned shift uses the same block layout as regular shifts (customer, unit, line name / line count) - it simply has no technician.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -839,31 +827,25 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page with the mini calendar visible in the left sidebar.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Schedule page with the mini calendar visible in the left sidebar.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;In the mini calendar, click a date in a different week from the one currently shown in the grid.&lt;/li&gt;
-&lt;li&gt;Look at the main grid and its date label.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. In the mini calendar, click a date in a different week from the one currently shown in the grid.
+2. Look at the main grid and its date label.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;The main grid navigates to show the clicked date (the containing day/week/month depending on the active view).&lt;/li&gt;
-&lt;li&gt;The toolbar date label updates to the new range.&lt;/li&gt;
-&lt;li&gt;The clicked date is highlighted as the selected date in the mini calendar.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2).</t>
+          <t xml:space="preserve">1. The main grid navigates to show the clicked date (the containing day/week/month depending on the active view).
+2. The toolbar date label updates to the new range.
+3. The clicked date is highlighted as the selected date in the mini calendar.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -910,11 +892,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. A picker opens showing a grid of month buttons plus arrows to step the year back and forward.
+          <t xml:space="preserve">1. A picker opens showing a grid of month buttons plus arrows to step the year back and forward.
 2. Choosing a month shows that month in the mini calendar.
 3. The main grid can then be navigated by clicking a date in the newly shown month.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§5.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -961,10 +945,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. The calendar grid collapses (hides), leaving more room for the work order list below.
+          <t xml:space="preserve">1. The calendar grid collapses (hides), leaving more room for the work order list below.
 2. Clicking again expands the calendar grid back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1011,11 +997,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. The selected date is visually highlighted.
+          <t xml:space="preserve">1. The selected date is visually highlighted.
 2. Today's date has its own distinct indicator, different from the selection.
 3. Hovering a week row highlights that whole week row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§5.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1049,33 +1037,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser with Schedule: View and Work Orders: View.&lt;/li&gt;
-&lt;li&gt;Several open work orders exist (create ZZAUTOTEST work orders if needed).&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser with Schedule: View and Work Orders: View.
+2. Several open work orders exist (create ZZAUTOTEST work orders if needed).
+3. You are on the Schedule page.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Look at the work order list beneath the mini calendar.&lt;/li&gt;
-&lt;li&gt;Scroll the list.&lt;/li&gt;
-&lt;li&gt;Look for any Assigned/Unassigned tabs above the list.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Look at the work order list beneath the mini calendar.
+2. Scroll the list.
+3. Look for any Assigned/Unassigned tabs above the list.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;Work orders appear as a single flat list of cards (one list, no tab split).&lt;/li&gt;
-&lt;li&gt;The list scrolls when there are more cards than fit.&lt;/li&gt;
-&lt;li&gt;There are no Assigned/Unassigned tabs - assignment is available only as a filter behind the 'Filter' button.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1).</t>
+          <t xml:space="preserve">1. Work orders appear as a single flat list of cards (one list, no tab split).
+2. The list scrolls when there are more cards than fit.
+3. There are no Assigned/Unassigned tabs - assignment is available only as a filter behind the 'Filter' button.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1122,13 +1104,15 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. Top left: the work order number, shown in an accent color.
+          <t xml:space="preserve">1. Top left: the work order number, shown in an accent color.
 2. Top right: the line count plus the hours estimate.
 3. Below: the customer name in bold, then the unit number.
 4. A lead technician row with the technician's avatar and name.
 5. A colored left border whose color reflects the work order's status.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1177,14 +1161,16 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. Work-order-number search narrows the list to the card(s) whose work order number matches what you typed, and cards that do not match disappear.
-2. Customer-name search shows only cards for that customer.
+          <t xml:space="preserve">1. Work-order-number search narrows the list to the card(s) whose work order number matches what you typed, and cards that do not match disappear.
+2. Customer-name search shows only cards for that customer, and it works with the full multi-word name (for example 'Vuchester Retail').
 3. Unit-number search shows only cards with that unit.
-4. Technician-name search shows only cards where that technician appears on the card.
-5. All four searchable fields (WO number, customer, unit, technician) are fields visible on the card itself.
-Note for the tester: searching the number exactly as the card shows it (for example S-9379) does work. Searching the longer shop-prefixed form (for example S8685-9379) returns nothing; that is already raised as SV-8841 (https://shopview.atlassian.net/browse/SV-8841) and is not part of this test.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
+4. Technician-name search shows only cards where that technician is on the work order - and it must work when you type the technician's name the way the card shows it, first name and last name together (for example 'Andrew Wade').
+Known issue on the build tested: typing a technician's FULL name returns nothing at all. 'Andrew' on its own finds 12 work orders and 'Wade' on its own finds the same 12, but 'Andrew Wade' finds 0, and so do 'andrew wade' and 'Wade Andrew'. It is not a general problem with spaces - the full customer name 'Vuchester Retail' finds 21 work orders correctly. That is already raised with the developers as SV-8873 (https://shopview.atlassian.net/browse/SV-8873). Mark this test FAILED.
+Note for the tester: searching the number exactly as the card shows it (for example S-15875) does work, and so does the bare number (15875). Searching the longer shop-prefixed form (for example S8685-15875) returns nothing; that is already raised as SV-8841 (https://shopview.atlassian.net/browse/SV-8841), so do not raise it again.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). It was verified against the build v3.5-be42149 on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8873)
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1231,11 +1217,13 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. The list narrows live with each keystroke - no Enter press or apply button is needed.
+          <t xml:space="preserve">1. The list narrows live with each keystroke - no Enter press or apply button is needed.
 2. Deleting characters widens the results again.
 3. With very many work orders, the list may load further results in pages as you scroll - that is expected, not a fault.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1282,11 +1270,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. No work order cards are shown.
+          <t xml:space="preserve">1. No work order cards are shown.
 2. The app does not error; the sidebar remains usable.
 3. Clearing the search restores the full list.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1334,11 +1324,13 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. The filter panel offers three groups: Assignment (Assigned, Unassigned), Status (the work order statuses supported in the app), and Priority (High, Medium, Low).
+          <t xml:space="preserve">1. The filter panel offers three groups: Assignment (Assigned, Unassigned), Status (the work order statuses supported in the app), and Priority (High, Medium, Low).
 2. Applying a filter narrows the flat card list.
 3. The 'Filters' button shows a badge with the number of active filters.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1386,11 +1378,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. Unassigned: only work orders without an assigned technician remain in the list.
+          <t xml:space="preserve">1. Unassigned: only work orders without an assigned technician remain in the list.
 2. Assigned: only work orders with a technician assigned remain.
 3. There are no Assigned/Unassigned tabs - this filter is the only assignment split.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§5.1, §3.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1, §3.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1438,11 +1432,15 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1. The Status group lists the work order statuses the app supports.
-2. Only work orders in the chosen status remain in the card list.
-3. The card left-border colors of the remaining cards are consistent with that status.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
+          <t xml:space="preserve">1. The Status group lists the work order statuses the app supports.
+2. Only work orders in the chosen status remain in the card list - no work order of any other status is shown.
+3. Choosing more than one status shows the work orders of all the chosen statuses together.
+4. The card left-border colours of the remaining cards are consistent with that status.
+Note for the tester: this shop's schedule list only holds work orders in two statuses, Approved and Review, so most of the other choices correctly come back empty. An empty list for a status no work order is in is the right answer, not a fault.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). It was verified against the build v3.5-be42149 on 8/5/2026.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1490,10 +1488,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. The Priority group offers High, Medium, and Low.
+          <t xml:space="preserve">1. The Priority group offers High, Medium, and Low.
 2. Only High-priority work orders remain in the list.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). It was verified against the build v3.5-be42149 on 8/5/2026.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1539,12 +1539,14 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. All applied filters are removed at once.
+          <t xml:space="preserve">1. All applied filters are removed at once.
 2. The full work order list is shown again.
 3. The active-count badge on the 'Filter' button disappears (or shows zero).
 Known issue on the build tested: The popover has no "Clear all" control: filters are cleared by unchecking each box, and the Filters button carries no active-count badge either. Spec 5.1: "Filters live behind a 'Filter' button (with an active-count badge) ... and 'Clear all' resets in one click." This is already raised with the developers as SV-8857 (https://shopview.atlassian.net/browse/SV-8857). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8857)
+</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1592,10 +1594,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. The list shows only work orders that match BOTH the text search and the structured filter.
+          <t xml:space="preserve">1. The list shows only work orders that match BOTH the text search and the structured filter.
 2. Removing either the search text or the filter widens the list to the remaining condition.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§5.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). It was verified against the build v3.5-be42149 on 8/5/2026.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1644,13 +1648,15 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. The card list is replaced, in the same place, by that work order's lines (no new page or popup).
+          <t xml:space="preserve">1. The card list is replaced, in the same place, by that work order's lines (no new page or popup).
 2. The header of the drill-down shows the work order id.
 3. The header also shows the line count, and it matches the number of approved lines.
 4. A back control is shown to return to the card list.
 5. Clicking back restores the work order card list.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1697,11 +1703,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1. Every line the drill-down lists is a line that has been approved. In practice that means you will see lines badged 'Authorized' and lines badged 'Complete', because a completed line was approved before it was worked.
+          <t xml:space="preserve">1. Every line the drill-down lists is a line that has been approved. In practice that means you will see lines badged 'Authorized' and lines badged 'Complete', because a completed line was approved before it was worked.
 2. No line that has never been approved appears anywhere in the schedule sidebar - for example a line still sitting on an estimate, or one that was declined.
-3. The line count in the drill-down header matches the number of lines actually listed.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
+3. The line count in the drill-down header matches the number of APPROVED lines on the work order - a line that was never approved is neither listed nor counted.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). It was verified against the build v3.5-be42149 on 8/5/2026.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1748,11 +1756,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1. The row shows the line's title and its estimated hours.
+          <t xml:space="preserve">1. The row shows the line's title and its estimated hours.
 2. The current technician roster is shown as an avatar stack plus a count; there is no cap on how many technicians a line can have.
 3. Each line row has its own drag handle, so it can be dragged independently onto the grid.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1, §8.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §8.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1799,11 +1809,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1. The technician-less line shows a 'Needs techs' badge.
+          <t xml:space="preserve">1. The technician-less line shows a 'Needs techs' badge.
 2. The line with a technician does not show the badge.
 3. After a technician is scheduled onto the badge-bearing line, the badge goes away.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1851,10 +1863,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. Typing a line title narrows the list to matching lines.
+          <t xml:space="preserve">1. Typing a line title narrows the list to matching lines.
 2. Typing the customer name returns no results - the line search matches line titles only (the list is already scoped to one work order, so customer/unit/WO fields are not searched).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1902,11 +1916,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1. Two chips are shown - All and Unscheduled - each with a count.
+          <t xml:space="preserve">1. Two chips are shown - All and Unscheduled - each with a count.
 2. Unscheduled lists only the lines that have no shifts yet, and its count matches.
 3. All lists every approved line, and its count matches the drill-down header's line count.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1940,33 +1956,27 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser with Schedule: Edit.&lt;/li&gt;
-&lt;li&gt;A ZZAUTOTEST work order exists with exactly ONE approved line whose estimated hours fit within one working day of the target technician.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page in week view.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. A ZZAUTOTEST work order exists with exactly ONE approved line whose estimated hours fit within one working day of the target technician.
+3. You are on the Schedule page in week view.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Drag that work order's card from the sidebar.&lt;/li&gt;
-&lt;li&gt;Drop it onto a technician's cell on a working day.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Drag that work order's card from the sidebar.
+2. Drop it onto a technician's cell on a working day.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;A shift is created immediately in that cell - no scope picker and no spread step appears.&lt;/li&gt;
-&lt;li&gt;The shift block shows the customer name, unit number, and the line's name.&lt;/li&gt;
-&lt;li&gt;The technician is added to that line's labor roster on the work order.&lt;/li&gt;
-&lt;li&gt;A toast with an Undo option appears.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.1, §1.2, §7).</t>
+          <t xml:space="preserve">1. A shift is created immediately in that cell - no scope picker and no spread step appears.
+2. The shift block shows the customer name, unit number, and the line's name.
+3. The technician is added to that line's labor roster on the work order.
+4. A toast with an Undo option appears.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §1.2, §7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2013,11 +2023,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1. A scope picker popover opens, anchored to the cell you dropped on.
+          <t xml:space="preserve">1. A scope picker popover opens, anchored to the cell you dropped on.
 2. It offers 'Schedule whole work order' at the top, the individual line rows beneath, and a 'Select multiple' control.
 3. No shift is created until a scope is chosen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.3).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.3). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2065,11 +2077,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. A single-line shift for exactly that line is created directly - no scope picker appears.
+          <t xml:space="preserve">1. A single-line shift for exactly that line is created directly - no scope picker appears.
 2. The block's last text line shows that line's name.
 3. The technician is added to that line's roster only (not to the order's other lines).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2117,11 +2131,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. The spread step opens (step 2 of the same modal) to distribute the hours across consecutive working days.
+          <t xml:space="preserve">1. The spread step opens (step 2 of the same modal) to distribute the hours across consecutive working days.
 2. Its header shows the chosen scope and a 'Change scope' back-link.
 3. No shifts exist yet until the spread is confirmed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.5).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.5). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2168,10 +2184,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. The shift is created straight away - the spread step does NOT appear.
+          <t xml:space="preserve">1. The shift is created straight away - the spread step does NOT appear.
 2. The shift sits on the dropped day only.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2218,12 +2236,14 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1. The cell currently under the cursor highlights as a drop target.
+          <t xml:space="preserve">1. The cell currently under the cursor highlights as a drop target.
 2. A ghost block follows the drag showing the line name and its hours.
 3. Releasing outside any valid cell creates nothing.
 Known issue on the build tested: During a sidebar drag, .fc-highlight count was 0 and no ghost/mirror element carrying the line name existed. Spec 7: "Drop-target cells highlight, and a ghost block shows the line name and hours." NOTE an intra-grid move DOES show a mirror (fc-event-mirror), so the gap is specific to dragging from the sidebar. This is already raised with the developers as SV-8840 (https://shopview.atlassian.net/browse/SV-8840). Until it is fixed this test will fail - mark it FAILED and link SV-8840; do not raise a new ticket.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8840)
+</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2272,13 +2292,15 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1. The technician now appears on that line's labor roster - the schedule and the work order stay in sync automatically.
+          <t xml:space="preserve">1. The technician now appears on that line's labor roster - the schedule and the work order stay in sync automatically.
 2. The sidebar line row's avatar stack/count updates to include the technician.
 3. If the line previously showed 'Needs techs', the badge is gone.
 4. Dragging the same line onto a second technician adds that technician to the line's roster as well - the technician who was already there stays on it.
 5. Nothing asks you to swap or replace the technician who was already there, and no limit is reached on how many technicians a line can have.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§1.2, §4.3, §7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§1.2, §4.3, §7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2325,11 +2347,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. The item can be placed onto a cell without holding a drag - clicking arms it, and clicking a cell places it.
+          <t xml:space="preserve">1. The item can be placed onto a cell without holding a drag - clicking arms it, and clicking a cell places it.
 2. The result is the same as the equivalent drag-and-drop (scope picker / spread step rules apply the same way).
-Not built on the build tested: Spec 11 requires "drag-and-drop has a click-to-arm alternative". This makes the drag-and-drop cases unautomatable without real pointer emulation. It has no developer ticket yet - report it to the QA lead rather than raising one yourself. Mark this test BLOCKED - not failed - because the feature it checks does not exist yet on this build.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7, §11).</t>
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). It was verified against the build v3.5-be42149 on 8/5/2026.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2377,13 +2400,15 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. The 'Schedule whole work order' option sits pinned at the top of the picker and looks visually distinct from the line rows.
+          <t xml:space="preserve">1. The 'Schedule whole work order' option sits pinned at the top of the picker and looks visually distinct from the line rows.
 2. It is labeled with the order's line count and total hours (matching the sum of the approved lines).
 3. The picker is anchored to the cell that was dropped on.
 4. Each line row shows the line title and its estimated hours.
 5. Rows for lines that already have technicians show the current roster as an avatar stack plus count.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.3).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). It was verified against the build v3.5-be42149 on 8/5/2026.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2431,11 +2456,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. One shift is created covering all of the order's approved lines.
+          <t xml:space="preserve">1. One shift is created covering all of the order's approved lines.
 2. The block's last text line reads 'N Lines' (with N = the line count).
 3. The technician is added to the roster of every one of those lines.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.3, §4.4).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3, §4.4). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2482,11 +2509,13 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1. A single-line shift for that line is created immediately - no extra confirmation step.
+          <t xml:space="preserve">1. A single-line shift for that line is created immediately - no extra confirmation step.
 2. The picker closes.
 3. The block's last text line shows the line's name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.3).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2537,13 +2566,16 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. 'Select multiple' switches the line rows into tick boxes - one per line.
-2. A bar appears at the bottom of the picker with a running tally of what is ticked, in the form '2 selected · 6h', and it updates as you tick and untick rows.
-3. The confirm button in that bar reads 'Schedule'.
-4. Pressing 'Schedule' creates ONE shift covering exactly the ticked lines, and the technician is added to those lines' rosters only - not to the other lines.
-5. There is no 'Select all' button and no 'Cancel' button. To leave without creating anything, close the picker with its X or press Escape.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.3).</t>
+          <t xml:space="preserve">1. 'Select multiple' switches the line rows into tick boxes - one per line.
+2. A bar appears at the bottom of the picker with a running tally of what is ticked - the number of lines and their combined hours, in the specification's example shape 'Create shift - 2 lines - 6h'.
+3. A 'Select all' shortcut ticks every line, giving the same line count and hours as choosing the whole work order.
+4. A 'Cancel' control leaves tick-box mode and returns you to the ordinary single-tap line list, without creating anything and without closing the picker.
+5. Confirming creates ONE shift covering exactly the ticked lines, and the technician is added to those lines' rosters only - not to the other lines.
+Known issue on the build tested: in tick-box mode the bottom bar reads '1 selected - 1h' and its confirm button reads 'Schedule'; there is NO 'Select all' button and NO 'Cancel' button anywhere in the picker - the only way out is the X in the corner, which closes the whole picker instead of returning you to the single-tap list. The 'All 2' chip higher up is the All / Unscheduled filter and does not tick anything. Specification 4.3 asks for "a running tally ("Create shift - 2 lines - 6h"), a "Select all" shortcut (equivalent to whole order), and Cancel (returns to the fast single-tap list)". That is already raised with the developers as SV-8886 (https://shopview.atlassian.net/browse/SV-8886). Mark this test FAILED.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). It was verified against the build v3.5-be42149 on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8886)
+</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2577,32 +2609,26 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser with Schedule: Edit.&lt;/li&gt;
-&lt;li&gt;A technician has configured working hours that DIFFER from the shop's business hours (for example tech 6:00 AM start vs shop 8:00 AM) - set this up first and restore after.&lt;/li&gt;
-&lt;li&gt;A schedulable work order line exists.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page in week view.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. A technician has configured working hours that DIFFER from the shop's business hours (for example tech 6:00 AM start vs shop 8:00 AM) - set this up first and restore after.
+3. A schedulable work order line exists.
+4. You are on the Schedule page in week view.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Drop the line onto that technician's cell (week view - not a day-view timeline drop).&lt;/li&gt;
-&lt;li&gt;Open the created shift's detail and read its start time.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Drop the line onto that technician's cell (week view - not a day-view timeline drop).
+2. Open the created shift's detail and read its start time.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;The shift starts at the technician's own configured start time (6:00 AM in the example), not the shop's business-hours start.&lt;/li&gt;
-&lt;/ol&gt;
+          <t xml:space="preserve">1. The shift starts at the technician's own configured start time (6:00 AM in the example), not the shop's business-hours start.
 Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2650,10 +2676,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. The shift starts at the shop's business-hours start time.
+          <t xml:space="preserve">1. The shift starts at the shop's business-hours start time.
 This test cannot be run on the build tested: the shop has NO business hours set (the Edit Location toggle is off, and turning it on would change a shared setting for every other tester on this estate), so the middle rung of the section 4.2 hierarchy cannot be exercised without a change nobody has authorised. The rung above and below are both verified. Turning the toggle on was driven and then abandoned WITHOUT saving. Mark it BLOCKED - not failed - and say which of these you could not set up.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: HOLD - needs shop business hours switched on, which is a shared setting on this estate
+</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2701,10 +2729,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. The shift starts at 7:00 AM - the general default working day (7:00 AM to 7:00 PM) applies.
+          <t xml:space="preserve">1. The shift starts at 7:00 AM - the general default working day (7:00 AM to 7:00 PM) applies.
 Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2751,10 +2781,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1. The shift starts at the time position where it was dropped (not at the technician-hours/business-hours default).
+          <t xml:space="preserve">1. The shift starts at the time position where it was dropped (not at the technician-hours/business-hours default).
 2. The start time aligns to the timeline position (see the 15-minute snapping case).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2801,11 +2833,13 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1. An unassigned shift is created in the Unassigned row for that day.
+          <t xml:space="preserve">1. An unassigned shift is created in the Unassigned row for that day.
 2. It has no technician (and no technician is added to the line's roster by this drop).
 3. The block uses the same anatomy as a regular shift (customer, unit, line name / 'N Lines').
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2, §3.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2, §3.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2853,10 +2887,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. The unassigned shift starts at the shop's business-hours start (there is no technician whose hours could apply).
+          <t xml:space="preserve">1. The unassigned shift starts at the shop's business-hours start (there is no technician whose hours could apply).
 Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2904,11 +2940,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. The shift is now assigned to that technician (it leaves the Unassigned row and sits in the technician's row).
+          <t xml:space="preserve">1. The shift is now assigned to that technician (it leaves the Unassigned row and sits in the technician's row).
 2. The technician is added to the affected line's roster.
 3. The technician's own working hours now apply to the shift's timing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2957,13 +2995,15 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. The spread step appears as step 2 of the same modal.
+          <t xml:space="preserve">1. The spread step appears as step 2 of the same modal.
 2. Its header shows the chosen scope (which lines / how many hours).
 3. A 'Change scope' back-link is present.
 4. Clicking 'Change scope' takes the modal back to the scope picker (step 1) without creating anything.
 5. Choosing a new scope updates the spread step's header and hours accordingly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3010,12 +3050,14 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. The selector defaults to 'Full estimate'.
+          <t xml:space="preserve">1. The selector defaults to 'Full estimate'.
 2. The options include 'Full estimate', '1 week', '2 weeks', 'Until a date…', and 'Specific hours…'.
 3. 'Full estimate', '1 week', and '2 weeks' apply on selection with no extra fields - the modal stays to one line for these.
 4. The preview summary updates to match each selection.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3062,10 +3104,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. Choosing 'Until a date…' reveals a single 'finish by' date field (this is the only custom control shown).
+          <t xml:space="preserve">1. Choosing 'Until a date…' reveals a single 'finish by' date field (this is the only custom control shown).
 2. Picking a date updates the preview so the series ends by that date.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3111,10 +3155,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. Choosing 'Specific hours…' reveals an hours stepper control.
+          <t xml:space="preserve">1. Choosing 'Specific hours…' reveals an hours stepper control.
 2. The preview updates to spread exactly the entered hours across working days.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3162,12 +3208,14 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. The start date defaults to the earliest working day.
+          <t xml:space="preserve">1. The start date defaults to the earliest working day.
 2. It can be changed; technician B's series then starts after A's series ends (sequential, not parallel).
 3. B's series is created from the adjusted start date onward.
 Known issue on the build tested: There is no Start date control in the spread step at all - the start comes solely from the cell the work order was dropped on and cannot be adjusted. Spec 4.5: "Start date. Defaults to the earliest working day. Adjusting it is how a second technician's series can be made sequential (starting after the first) rather than parallel." Without it the sequential-series workflow the spec describes is impossible. This is already raised with the developers as SV-8855 (https://shopview.atlassian.net/browse/SV-8855). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8855)
+</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3215,13 +3263,15 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1. Daily shifts are sized to the technician's own working hours (8h each in the example).
+          <t xml:space="preserve">1. Daily shifts are sized to the technician's own working hours (8h each in the example).
 2. Weekends are skipped ONLY when the technician has no business hours set for them; if the tech has hours on a weekend day (e.g. Saturday hours) that day is NOT skipped.
 3. Shop closures and public holidays are NOT skipped in V1 - shifts can be placed on those days.
 4. The end date is a result of the daily distribution (for 40h at 8h/day starting Monday, the series ends on the fifth working day).
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The specification says this two different ways and no ruling exists yet, so mark this test BLOCKED - not failed - and leave it out of the automation suite. The open question and its evidence are recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md.</t>
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The specification says this two different ways and no ruling exists yet, so mark this test BLOCKED - not failed - and leave it out of the automation suite. The open question and its evidence are recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
+</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3268,11 +3318,13 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. Collapsed: a one-line summary in the spirit of the spec's example '20 shifts · Jun 15 to Jul 13 · skips weekends + 2 days'.
+          <t xml:space="preserve">1. Collapsed: a one-line summary in the spirit of the spec's example '20 shifts · Jun 15 to Jul 13 · skips weekends + 2 days'.
 2. Expanded: a week-by-week breakdown of the planned shifts.
 3. Skipped days are struck through and show the reason they are skipped - in V1 the only skip reason is a weekend day with no working hours set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md.</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3319,12 +3371,14 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1. One daily shift is created per planned working day, together forming a linked series.
+          <t xml:space="preserve">1. One daily shift is created per planned working day, together forming a linked series.
 2. The shifts render as one connected banner (see the series-banner cases).
 3. Each daily shift keeps its own day and hours.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5, §4.6, §8.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §4.6, §8.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3371,11 +3425,13 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. Technician B gets a full 40h series of their own - the estimate is spread again in full, not reduced by A's booking.
+          <t xml:space="preserve">1. Technician B gets a full 40h series of their own - the estimate is spread again in full, not reduced by A's booking.
 2. There is no shared 'remaining hours' counter across technicians and no splitting of a shift.
 3. Planned hours across technicians may now exceed the estimate - this is expected and produces no error (progress is driven by clocked-in time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3424,13 +3480,15 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. Going past 8 weeks does not silently succeed: a warning about the very long series appears and asks you to confirm before the shifts are created.
+          <t xml:space="preserve">1. Going past 8 weeks does not silently succeed: a warning about the very long series appears and asks you to confirm before the shifts are created.
 2. After you confirm the warning, the long series is created normally.
 3. A single spread that would create more than 120 daily shifts is refused outright - no confirmation can override it, and no shifts are created for that attempt.
 4. No half-created series is left behind after a refused attempt.
 Not built on the build tested: A 76h 36m spread produced 7 shifts with no warning and nothing asking you to confirm, and nothing on this build refuses or questions a very long series. The 8-week / 120-shift limits come from the engineering technical plan, not from the Schedule specification. It has no developer ticket yet - report it to the QA lead rather than raising one yourself. Mark this test BLOCKED - not failed - because the feature it checks does not exist yet on this build.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md.</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: HOLD - the feature is not built yet
+</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3478,11 +3536,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. The series renders as one continuous bar wrapping across the week rows.
+          <t xml:space="preserve">1. The series renders as one continuous bar wrapping across the week rows.
 2. It is labeled once at the start (including the technician); later weeks show a faded 'continues'-style label instead of repeating the full label.
 3. Weekend columns inside the series are empty (no bar) when no business hours are set for those weekend days.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.6).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3530,12 +3590,14 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. One banner spans the working days of that week in the technician's row.
+          <t xml:space="preserve">1. One banner spans the working days of that week in the technician's row.
 2. Chevrons at the banner's edges indicate the series continues beyond the visible week (both sides, on a middle week).
 3. A 'week N of M' cue shows the position within the series.
 Known issue on the build tested: the Week view does draw one banner - the first day of the run carries the customer name, the line count and the words 'Part of a series', and each following day carries a small 'continues' marker - but there are no arrows at the edges of the banner and no 'week N of M' wording anywhere. Separately, none of those blocks can be clicked open in the Week view; that half is raised with the developers as SV-8849 (https://shopview.atlassian.net/browse/SV-8849). The missing arrows and the missing 'week N of M' have been reported to the QA lead and have no ticket yet. Mark this test FAILED, link SV-8849 and say in your comment which parts you saw; do not raise a new ticket.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.6).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8849)
+</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3582,10 +3644,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. The day shows a single time-positioned block (no spanning bar - only one day is visible).
+          <t xml:space="preserve">1. The day shows a single time-positioned block (no spanning bar - only one day is visible).
 2. The block carries a cue in the spirit of 'part of an M-week job' indicating it belongs to a longer series.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.6).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3633,11 +3697,13 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. Each series day contributes its own daily hours to that day's capacity bar (the series is not counted as one lump).
+          <t xml:space="preserve">1. Each series day contributes its own daily hours to that day's capacity bar (the series is not counted as one lump).
 2. The overlapping day is flagged as a Double-booked conflict, exactly as it would be for standalone shifts.
 3. The detail modal shows that single day's shift (its own day and hours) while indicating it belongs to the series.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.6, §8.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6, §8.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3671,32 +3737,26 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser.&lt;/li&gt;
-&lt;li&gt;A single-line shift exists on the grid (VIN toggle off).&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page in week view.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser.
+2. A single-line shift exists on the grid (VIN toggle off).
+3. You are on the Schedule page in week view.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Read the shift block's text lines from top to bottom.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Read the shift block's text lines from top to bottom.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;Line 1: the customer name.&lt;/li&gt;
-&lt;li&gt;Line 2: the unit number.&lt;/li&gt;
-&lt;li&gt;Last line: the name of the scheduled line.&lt;/li&gt;
-&lt;li&gt;No work order number appears on the block.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.4).</t>
+          <t xml:space="preserve">1. Line 1: the customer name.
+2. Line 2: the unit number.
+3. Last line: the name of the scheduled line.
+4. No work order number appears on the block.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3744,11 +3804,13 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. The whole-order block reads '4 Lines'.
+          <t xml:space="preserve">1. The whole-order block reads '4 Lines'.
 2. The subset block reads '2 Lines' - the block does not distinguish whole-order from subset beyond the count.
 3. Each detail modal lists exactly which lines the shift covers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.4, §12).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4, §12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3795,11 +3857,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. The unconflicted block shows NO icons and NO work order number - only its text lines.
+          <t xml:space="preserve">1. The unconflicted block shows NO icons and NO work order number - only its text lines.
 2. The conflicted block shows the conflict (warning) icon on its first line - and that is the only icon that ever appears on a block.
 3. No scope icons distinguish whole-order from subset shifts.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.4).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3847,12 +3911,14 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1. Both shifts are created and shown on the same day for the same technician - multiple same-day shifts from different work orders are allowed.
+          <t xml:space="preserve">1. Both shifts are created and shown on the same day for the same technician - multiple same-day shifts from different work orders are allowed.
 2. Both shifts sit in the same single lane, one after the other.
 3. The row stays at its normal height.
 4. No conflict is flagged for back-to-back (non-intersecting) shifts.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.7, §12).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7, §12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3898,11 +3964,13 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1. The two overlapping shifts render in separate stacked lanes - they never visually collide.
+          <t xml:space="preserve">1. The two overlapping shifts render in separate stacked lanes - they never visually collide.
 2. The row grows in height to fit the lanes.
 3. The overlap is also flagged as a Double-booked conflict (stacking reads as 'resolve me').
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.7, §4.11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7, §4.11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3949,12 +4017,14 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1. At most 3 lanes are visible.
+          <t xml:space="preserve">1. At most 3 lanes are visible.
 2. The remaining overlapping shifts collapse into a '+N more' affordance (here '+2 more').
 3. Clicking it opens a popover listing the hidden shifts.
 4. The hidden shifts can be opened from that popover.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4002,12 +4072,14 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. All three views handle the overlap without blocks visually colliding.
+          <t xml:space="preserve">1. All three views handle the overlap without blocks visually colliding.
 2. Week and month views reach the '+N more' overflow sooner than day view (their cells are narrower), but the same cap-and-overflow model applies.
 3. The overflow affordance opens the hidden-shifts popover in each view.
 Known issue on the build tested: Lane stacking and the "+N more" link appear in day, week and month view - but clicking "+1 more" opens a popover headed with just the date ("August 2, 2026") whose body contains only the day cell and its capacity bar and lists NO shifts (0 schedule-block elements inside it). Spec 4.7: "Additional overlapping shifts collapse into a '+N more' affordance that opens a popover listing the hidden shifts." The hidden shifts are unreachable. This is already raised with the developers as SV-8850 (https://shopview.atlassian.net/browse/SV-8850). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8850)
+</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4056,14 +4128,16 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1. On load and on each day navigation, the timeline is auto-scrolled so the working-day start sits at the left edge of the visible area, with a small buffer (roughly 30 to 60 minutes) before it.
+          <t xml:space="preserve">1. On load and on each day navigation, the timeline is auto-scrolled so the working-day start sits at the left edge of the visible area, with a small buffer (roughly 30 to 60 minutes) before it.
 2. The start used is the earliest technician's configured start; if no tech hours are set, business hours; otherwise 7:00 AM - so no shifts sit off-screen to the left.
 3. Your manual scroll position stays put - nothing jumps you back to the morning while you remain on the same day.
 4. The timeline is not stuck at the start - it remains a full 24-hour scrollable timeline (midnight to midnight).
 5. Only navigating to another day re-triggers the auto-scroll.
 Known issue on the build tested: Day view opens with the scroller at scrollLeft 3 and the first slot "12 AM", and it is still 3 after stepping a day. Spec 4.8: "On initial day-view load and when navigating to a new day, the timeline auto-scrolls so the working-day start sits at the left edge of the visible area (with a small 30 to 60 minute buffer before it)." This is already raised with the developers as SV-8837 (https://shopview.atlassian.net/browse/SV-8837). Until it is fixed this test will fail - mark it FAILED and link SV-8837; do not raise a new ticket.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.8).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8837)
+</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4111,10 +4185,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1. In day view, the date/time header bar stays stuck to the top while the rows scroll beneath it - you always know which time column you are looking at.
+          <t xml:space="preserve">1. In day view, the date/time header bar stays stuck to the top while the rows scroll beneath it - you always know which time column you are looking at.
 2. The same sticky-header behavior applies in week view.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.8).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4162,13 +4238,15 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. The shift moves along the timeline as you drag.
+          <t xml:space="preserve">1. The shift moves along the timeline as you drag.
 2. The released start time snaps to a 15-minute interval (for example 9:15, 9:30 - never 9:22).
 3. The duration is unchanged by a horizontal move.
 4. A toast with Undo appears for the move.
 Known issue on the build tested: A 24px horizontal drag - about half an hour at this zoom - moved the shift a full hour instead of the half hour you dragged it. Spec 4.8: "Horizontal drag to move a shift's start time (snaps to 15-minute intervals)." This is already raised with the developers as SV-8856 (https://shopview.atlassian.net/browse/SV-8856). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.8, §7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8, §7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8856)
+</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4216,12 +4294,14 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1. Dragging the right edge extends/shortens the end time (start unchanged).
+          <t xml:space="preserve">1. Dragging the right edge extends/shortens the end time (start unchanged).
 2. Dragging the left edge adjusts the start time (end unchanged).
 3. The resulting times land on 15-minute increments.
 4. The shift's duration on the grid matches the modal's start/end.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.8).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4268,12 +4348,14 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1. A vertical line marks the current time on the timeline.
+          <t xml:space="preserve">1. A vertical line marks the current time on the timeline.
 2. Its position matches the actual clock time.
 3. Hovering the now line while your pointer is over the grid shows a label (the current time).
 Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.8).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4307,32 +4389,26 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser.&lt;/li&gt;
-&lt;li&gt;A shift exists for a unit that has a VIN; the VIN toggle in 'Filter and Display' is OFF.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser.
+2. A shift exists for a unit that has a VIN; the VIN toggle in 'Filter and Display' is OFF.
+3. You are on the Schedule page.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Click the shift block.&lt;/li&gt;
-&lt;li&gt;Read the modal's identity section.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Click the shift block.
+2. Read the modal's identity section.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;A detail panel opens for the shift.&lt;/li&gt;
-&lt;li&gt;It shows the customer name, unit number, the VIN (below unit and asset), and the work order id.&lt;/li&gt;
-&lt;li&gt;The VIN is visible here even though the grid's VIN toggle is off - the modal always shows it.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.9, §9).</t>
+          <t xml:space="preserve">1. A detail panel opens for the shift.
+2. It shows the customer name, unit number, the VIN (below unit and asset), and the work order id.
+3. The VIN is visible here even though the grid's VIN toggle is off - the modal always shows it.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §9). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4380,13 +4456,15 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1. The time pickers offer 15-minute increments (for example 8:00, 8:15, 8:30, 8:45).
+          <t xml:space="preserve">1. The time pickers offer 15-minute increments (for example 8:00, 8:15, 8:30, 8:45).
 2. Saving/applying the change updates the shift's times.
 3. Changing the date moves the shift to the chosen day.
 4. The grid block reflects the new date/times.
 Known issue on the build tested: the start and end time boxes accept and offer EVERY minute, not quarter-hours - you can set 8:07 if you want to. This is already raised with the developers as SV-8833 (https://shopview.atlassian.net/browse/SV-8833). Until it is fixed this test will fail - mark it FAILED and link SV-8833; do not raise a new ticket. One thing in that ticket is NOT a fault: the little clock icon inside the box is simply how the browser draws a time box, so ignore that part.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.9).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8833)
+</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4433,12 +4511,14 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1. The assigned technician is shown.
+          <t xml:space="preserve">1. The assigned technician is shown.
 2. A progress indication compares time logged against the estimate (logged hours vs estimated hours).
 3. The numbers are consistent with the line's actual logged time and estimate.
-Known issue on the build tested: TECHNICIAN shows the avatar and name correctly. TIME LOGGED read "40h 19m / 40h 19m" with a full bar on a shift where nothing had been clocked (the work order reported 0 actual hours), and "1h / 1h" on another. Spec 4.9 asks for "Time logged vs estimate (progress)". It has been reported to the QA lead but has no developer ticket yet. Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.9).</t>
+Known issue on the build tested: TECHNICIAN shows the avatar and name correctly. TIME LOGGED read "40h 19m / 40h 19m" with a full bar on a shift where nothing had been clocked (the work order reported 0 actual hours), and "1h / 1h" on another. Spec 4.9 asks for "Time logged vs estimate (progress)". That is already raised with the developers as SV-8834 (https://shopview.atlassian.net/browse/SV-8834). Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8834)
+</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4485,13 +4565,15 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. The 'Work Order Lines' section shows the line count and a scope summary of what the shift covers.
+          <t xml:space="preserve">1. The 'Work Order Lines' section shows the line count and a scope summary of what the shift covers.
 2. Exactly the 2 scheduled lines are listed (not all 4), each showing its line number, title, hours, and a status pill only.
 3. No labor figures and no total dollar amount appear anywhere in the modal.
 4. This is where whole-order vs subset scope is spelled out (the grid block only says 'N Lines').
 Note for the tester: the absence of any money figure is CORRECT and is what this test expects. The product owner ruled on 22 July 2026 that no total in dollars is shown anywhere on the Schedule. If you see no money figure, pass this test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.9, §4.4). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md.</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §4.4). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4538,12 +4620,14 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1. The estimated hours field is editable directly in the modal.
+          <t xml:space="preserve">1. The estimated hours field is editable directly in the modal.
 2. The new value persists after closing and re-opening.
 3. Dependent displays (progress vs estimate) reflect the new value.
 Known issue on the build tested: No inline editor exists on the estimated hours: the scope chip "Single line - 1h" and the per-line hours are plain text with no click target, no edit affordance and no input. Spec 4.9: "Estimated hours with inline edit." This is already raised with the developers as SV-8829 (https://shopview.atlassian.net/browse/SV-8829). Until it is fixed this test will fail - mark it FAILED and link SV-8829; do not raise a new ticket.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.9).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8829)
+</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4590,12 +4674,14 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1. The note is added and shown in the modal.
+          <t xml:space="preserve">1. The note is added and shown in the modal.
 2. The edit is saved and displayed.
 3. The delete removes the note.
 4. Notes are kept per work order (the same note is visible from another shift of the same work order).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.9).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4643,13 +4729,15 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1. A conflict banner is shown in the modal describing the conflict.
+          <t xml:space="preserve">1. A conflict banner is shown in the modal describing the conflict.
 2. It offers an 'Adjust' action.
 3. 'Adjust' leads to a way to resolve the conflict (for example changing the shift's time).
 4. An unconflicted shift's modal shows no such banner.
 Known issue on the build tested: The conflict banner renders - "warning_amber / Scheduling conflict / Not a working day" - but there is NO Adjust action: the modal's only controls are the delete bin, close, the colour selector, Add Note and Open Work Order. Spec 4.9: "A conflict banner with an 'Adjust' action when the shift is conflicted." This is already raised with the developers as SV-8852 (https://shopview.atlassian.net/browse/SV-8852). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.9).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8852)
+</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4696,11 +4784,13 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1. The modal offers a Delete action (a trash icon in the header) and a close (x) icon - and no other actions.
+          <t xml:space="preserve">1. The modal offers a Delete action (a trash icon in the header) and a close (x) icon - and no other actions.
 2. There is no 'Reassign' action in the modal; reassignment is done by dragging a shift to another technician row (covered by its own case).
 3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.9, §7). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md.</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §7). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4747,12 +4837,14 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. A menu opens at the spot you clicked and contains 'Create Event'.
+          <t xml:space="preserve">1. A menu opens at the spot you clicked and contains 'Create Event'.
 2. The event modal opens with the clicked cell's technician and date pre-set.
 3. Saving creates an event block on that technician's day.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4799,12 +4891,14 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1. Left-clicking empty day-view space opens the cell menu; choosing 'Create Event' starts creation at the time you clicked.
+          <t xml:space="preserve">1. Left-clicking empty day-view space opens the cell menu; choosing 'Create Event' starts creation at the time you clicked.
 2. A live preview block is shown while creating, and dragging resizes it.
 3. Completing creates the event at the previewed time/duration.
 Not built on the build tested: Spec 4.10: "Day view shows a live preview block while creating, with drag-to-resize." It has no developer ticket yet - report it to the QA lead rather than raising one yourself. Mark this test BLOCKED - not failed - because the feature it checks does not exist yet on this build.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.10).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: HOLD - the feature is not built yet
+</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4852,13 +4946,15 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>1. The modal contains: name, date, start/end time, an all-day toggle, and a color category.
+          <t xml:space="preserve">1. The modal contains: name, date, start/end time, an all-day toggle, and a color category.
 2. The event saves with the entered values.
 3. Re-opening the event shows the saved values.
 4. With all-day ON, specific start/end times are not required (the time fields are disabled or hidden).
 5. The event is created as an all-day block for that technician and day.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.10, §8.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §8.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4906,11 +5002,13 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1. Dropping on another technician reassigns the event to them.
+          <t xml:space="preserve">1. Dropping on another technician reassigns the event to them.
 2. Dropping on another day moves it to that day.
 3. Each move produces a toast with Undo.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4956,11 +5054,13 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>1. The event card is a white/neutral card with a thin, even border on all four sides and NO colored left rail (the left rail is the shift's cue).
+          <t xml:space="preserve">1. The event card is a white/neutral card with a thin, even border on all four sides and NO colored left rail (the left rail is the shift's cue).
 2. It has a small grey-filled rounded chip on the left containing a calendar icon, and two lines of text beside it: the event name, then the time range in secondary text.
 3. The shift reads as a tinted color-filled block with a colored left rail - the two types are separable at a glance, not by color alone.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.10).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5008,11 +5108,13 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1. The default event color is neutral/grey.
+          <t xml:space="preserve">1. The default event color is neutral/grey.
 2. The color picker offers the same custom color palette as shifts (shared picker with editable labels).
 3. Choosing a color tints the card and the icon chip in matching tones, the same way a colored shift is tinted.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.10, §10).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §10). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5060,11 +5162,13 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1. Adding the event DOES increase that day's capacity bar fill - the event's hours are counted alongside shift hours (a 2-hour meeting uses up 2 hours of the technician's available time).
+          <t xml:space="preserve">1. Adding the event DOES increase that day's capacity bar fill - the event's hours are counted alongside shift hours (a 2-hour meeting uses up 2 hours of the technician's available time).
 2. The event does NOT create a double-booked or overlap conflict with the shift, and the toolbar conflict count does not increase because of it.
 3. The two behave differently on purpose: an event uses up capacity, but it is never flagged as a conflict.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.10, §4.11, §4.12).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §4.11, §4.12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5098,34 +5202,28 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser with Schedule: Edit.&lt;/li&gt;
-&lt;li&gt;Two different work orders have schedulable lines.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page; note the toolbar conflict pill's current count.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. Two different work orders have schedulable lines.
+3. You are on the Schedule page; note the toolbar conflict pill's current count.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Schedule work order 1 on a technician for a given time.&lt;/li&gt;
-&lt;li&gt;Schedule work order 2 on the SAME technician overlapping the same time.&lt;/li&gt;
-&lt;li&gt;Look at the two blocks and the toolbar conflict pill.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Schedule work order 1 on a technician for a given time.
+2. Schedule work order 2 on the SAME technician overlapping the same time.
+3. Look at the two blocks and the toolbar conflict pill.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;The overlap is detected as a Double-booked conflict.&lt;/li&gt;
-&lt;li&gt;A warning icon appears on the affected block(s).&lt;/li&gt;
-&lt;li&gt;The toolbar conflict pill's count increases.&lt;/li&gt;
-&lt;li&gt;The conflict is listed in the pill's dropdown.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.11).</t>
+          <t xml:space="preserve">1. The overlap is detected as a Double-booked conflict.
+2. A warning icon appears on the affected block(s).
+3. The toolbar conflict pill's count increases.
+4. The conflict is listed in the pill's dropdown.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5172,11 +5270,13 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1. The shift is created but flagged as a conflict because the day is outside the technician's configured working days (the reason sentence reads in the spirit of 'Scheduled on a weekend (outside working days)' - it names the technician's own working days, not a fixed Monday-to-Friday window).
+          <t xml:space="preserve">1. The shift is created but flagged as a conflict because the day is outside the technician's configured working days (the reason sentence reads in the spirit of 'Scheduled on a weekend (outside working days)' - it names the technician's own working days, not a fixed Monday-to-Friday window).
 2. If the technician's working days DO include that day (for example Saturday hours are configured), a shift on that day is NOT flagged.
 3. The warning icon appears on the block and the conflict is listed in the toolbar dropdown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5225,12 +5325,14 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>1. The shift is flagged as a before-hours conflict, with a reason sentence in the spirit of 'Starts before working hours', measured against that technician's own configured working-day START time (not a fixed hour).
+          <t xml:space="preserve">1. The shift is flagged as a before-hours conflict, with a reason sentence in the spirit of 'Starts before working hours', measured against that technician's own configured working-day START time (not a fixed hour).
 2. The shift is flagged as an after-hours conflict, with a reason sentence in the spirit of 'Extends past working hours', measured against that technician's own configured working-day END time (not a fixed hour).
 3. Both the start and the end follow the hierarchy technician hours, then shop business hours, then the general default working day of 7:00 AM to 7:00 PM.
 4. Warning icon on the block in each case; the conflict appears in the toolbar dropdown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5278,12 +5380,14 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1. The pill shows the current number of scheduling issues.
+          <t xml:space="preserve">1. The pill shows the current number of scheduling issues.
 2. Clicking opens a dropdown listing each conflict.
 3. The list covers all current conflicts (count matches the pill).
 4. Resolving a conflict (for example moving the shift) reduces the count - detection is continuous.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.11, §6).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §6). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5330,10 +5434,12 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1. The grid navigates to the relevant technician and day.
+          <t xml:space="preserve">1. The grid navigates to the relevant technician and day.
 2. The conflicted shift is brought into view.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5380,10 +5486,12 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1. Overtime is signaled with the 'OT' text tag and amber tones - NOT red or alarming styling.
+          <t xml:space="preserve">1. Overtime is signaled with the 'OT' text tag and amber tones - NOT red or alarming styling.
 2. Red/alarming styling appears only for conflicts and genuine errors.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.12).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5432,11 +5540,13 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1. Each day header shows a capacity bar; the blue fill represents total technician-hours booked - shift hours PLUS event hours - divided by total available (sum of all techs' working hours).
+          <t xml:space="preserve">1. Each day header shows a capacity bar; the blue fill represents total technician-hours booked - shift hours PLUS event hours - divided by total available (sum of all techs' working hours).
 2. A more heavily booked day shows a longer blue fill; the fill never exceeds the track (clamped at 100%).
 3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.12).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5482,10 +5592,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1. An amber segment extends past the right edge of the track, showing the excess.
+          <t xml:space="preserve">1. An amber segment extends past the right edge of the track, showing the excess.
 2. A tick marks the 100% line where the track ends.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.12).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5531,11 +5643,13 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1. An 'OT' tag appears for the day even though the aggregate bar is under 100%.
+          <t xml:space="preserve">1. An 'OT' tag appears for the day even though the aggregate bar is under 100%.
 2. The tag is text, not a color-only signal.
 3. Overtime (per-technician) and capacity (aggregate) are independent signals.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.12, §11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12, §11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5582,11 +5696,13 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1. A tooltip shows a per-technician breakdown: assigned hours vs that technician's capacity.
+          <t xml:space="preserve">1. A tooltip shows a per-technician breakdown: assigned hours vs that technician's capacity.
 2. The overtime technician's entry is highlighted in amber.
 3. The numbers agree with the shifts actually on the grid.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.12).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5620,33 +5736,27 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser.&lt;/li&gt;
-&lt;li&gt;A multi-line shift exists covering 5 lines, with some time logged, for a unit that has a VIN.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page in week view.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser.
+2. A multi-line shift exists covering 5 lines, with some time logged, for a unit that has a VIN.
+3. You are on the Schedule page in week view.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Hover over the shift block and wait briefly for the tooltip.&lt;/li&gt;
-&lt;li&gt;Read the tooltip from top to bottom.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Hover over the shift block and wait briefly for the tooltip.
+2. Read the tooltip from top to bottom.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;The tooltip shows: the customer name; unit, vehicle, and VIN (the tooltip shows the VIN whenever the unit has one, regardless of the 'VIN Number' toggle); the date and time range; the technician; and a scope summary ('N lines · Xh' style).&lt;/li&gt;
-&lt;li&gt;The individual line names appear as a short list capped at 3, with a '+N more lines' row for the rest (here '+2 more lines'); line statuses are NOT shown.&lt;/li&gt;
-&lt;li&gt;A time-logged progress bar shows logged vs estimated hours ('X / Yh' style).&lt;/li&gt;
-&lt;/ol&gt;
+          <t xml:space="preserve">1. The tooltip shows: the customer name; unit, vehicle, and VIN (the tooltip shows the VIN whenever the unit has one, regardless of the 'VIN Number' toggle); the date and time range; the technician; and a scope summary ('N lines · Xh' style).
+2. The individual line names appear as a short list capped at 3, with a '+N more lines' row for the rest (here '+2 more lines'); line statuses are NOT shown.
+3. A time-logged progress bar shows logged vs estimated hours ('X / Yh' style).
 Known issue on the build tested: The tooltip listed ALL FIVE line names on the 5-line series shift with no "+N more lines" row. Spec 4.13: "the individual line names as a short list capped at 3 with a '+N more lines' row". Everything else matched: customer, unit and VIN, date and time range, technician, scope summary "5 lines - 12h" and the progress bar. VIN appears with the toggle off, per Branko 2026-07-31. It has been reported to the QA lead but has no developer ticket yet. Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.13). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md.</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (no ticket - accepted, see the decisions register)
+</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5692,10 +5802,12 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1. The customer name line includes the conflict icon.
+          <t xml:space="preserve">1. The customer name line includes the conflict icon.
 2. The conflict reason is shown in amber.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.13).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5741,11 +5853,13 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1. The tooltip shows the event name with its category dot (grey for a default event).
+          <t xml:space="preserve">1. The tooltip shows the event name with its category dot (grey for a default event).
 2. The date and time range are shown.
 3. The technician is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.13).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5794,12 +5908,14 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>1. A quick pass does not flash tooltips - the tooltip opens only after a short hover delay (spec: roughly 300 to 500ms).
+          <t xml:space="preserve">1. A quick pass does not flash tooltips - the tooltip opens only after a short hover delay (spec: roughly 300 to 500ms).
 2. It dismisses when the mouse leaves the block.
 3. The tooltip is read-only (no buttons/actions inside it).
 4. Clicking the block opens the full detail modal as normal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.13).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5846,11 +5962,13 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1. When there is not enough room below, the tooltip opens ABOVE the block instead.
+          <t xml:space="preserve">1. When there is not enough room below, the tooltip opens ABOVE the block instead.
 2. Near a side edge, the tooltip shifts horizontally to stay fully within the viewport.
 3. No part of the tooltip is clipped off-screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.13).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5884,30 +6002,24 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page, navigated several weeks away from today.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Schedule page, navigated several weeks away from today.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Click the 'Today' button in the grid toolbar.&lt;/li&gt;
-&lt;li&gt;Look at the grid and the date label.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Click the 'Today' button in the grid toolbar.
+2. Look at the grid and the date label.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;The grid jumps to the range containing the current date (today's day, this week, or this month depending on the active view).&lt;/li&gt;
-&lt;li&gt;The date label updates accordingly.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§6).</t>
+          <t xml:space="preserve">1. The grid jumps to the range containing the current date (today's day, this week, or this month depending on the active view).
+2. The date label updates accordingly.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5954,12 +6066,14 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1. Week view: each arrow click moves one whole week; the label shows the week range (spec's example format: 'Jul 14 to 20, 2026').
+          <t xml:space="preserve">1. Week view: each arrow click moves one whole week; the label shows the week range (spec's example format: 'Jul 14 to 20, 2026').
 2. Day view: each click moves one day; the label shows that day.
 3. Month view: each click moves one month; the label shows that month.
 4. The label always matches what the grid displays.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§6).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6007,13 +6121,15 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>1. Blocks that match the search are highlighted; blocks that do not match fade.
+          <t xml:space="preserve">1. Blocks that match the search are highlighted; blocks that do not match fade.
 2. All five fields match: customer name, work order number, unit number, technician name, and line name.
 3. Matching blocks stay in place on the grid (search visually filters; it does not remove or rearrange).
 4. Clearing the search restores all blocks to normal.
-Known issue on the build tested: Typing "Pamill" in the toolbar search left only the 6 matching blocks in the grid, each gaining schedule-block--match; the non-matching blocks were REMOVED from the page, not faded. Spec 6: "Non-matching blocks fade; matching blocks highlight." Also worth knowing: the toolbar search field carries the placeholder "Search work orders..." - the same words as the sidebar search - which is easy to confuse. It has been reported to the QA lead but has no developer ticket yet. Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§6).</t>
+Known issue on the build tested: Typing "Pamill" in the toolbar search left only the 6 matching blocks in the grid, each gaining schedule-block--match; the non-matching blocks were REMOVED from the page, not faded. Spec 6: "Non-matching blocks fade; matching blocks highlight." Also worth knowing: the toolbar search field carries the placeholder "Search work orders..." - the same words as the sidebar search - which is easy to confuse. That is already raised with the developers as SV-8874 (https://shopview.atlassian.net/browse/SV-8874). Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8874)
+</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6059,11 +6175,13 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown is checkbox style and contains: a toggle per department, 'My Shifts', and 'VIN'.
+          <t xml:space="preserve">1. The dropdown is checkbox style and contains: a toggle per department, 'My Shifts', and 'VIN'.
 2. Defaults: all department toggles ON, 'My Shifts' OFF, 'VIN' OFF.
 3. There is no separate departments-only control - this dropdown replaces it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§6, §9).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6, §9). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6111,11 +6229,13 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>1. The turned-off department's group (header and technician rows) disappears from the grid.
+          <t xml:space="preserve">1. The turned-off department's group (header and technician rows) disappears from the grid.
 2. Other departments are unaffected.
 3. Turning it back on restores the group.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§9).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6163,12 +6283,14 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1. Only shifts assigned to you remain visible; all other technician rows and their shifts are hidden.
+          <t xml:space="preserve">1. Only shifts assigned to you remain visible; all other technician rows and their shifts are hidden.
 2. Turning it off restores the full grid.
 3. This is a personal convenience filter only - it does not change what you are permitted to see (default is OFF, everyone's shifts visible).
 4. For a user who has no technician/staff record of their own, the 'My Shifts' option is not shown at all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§9, §14.3).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §14.3). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6217,14 +6339,16 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1. 'VIN Number' off: no VIN line on the block (the block shows its three normal lines) - but the hover tooltip still shows the VIN, and the detail modal still shows the VIN.
+          <t xml:space="preserve">1. 'VIN Number' off: no VIN line on the block (the block shows its three normal lines) - but the hover tooltip still shows the VIN, and the detail modal still shows the VIN.
 2. 'VIN Number' on: the VIN appears as an additional line on blocks in day and week views.
 3. Month view blocks never show the VIN, even with the toggle on (space constraints).
 4. In day view with the VIN on, the lane height grows to fit the extra VIN line and no block text is clipped or cut off.
 5. The 'VIN Number' toggle affects the block only - the tooltip and the modal always show the VIN when the unit has one.
 Note for the tester: the VIN staying visible in the hover summary and in the shift window while the VIN switch is off is CORRECT and is what this test expects. The product owner ruled on 31 July 2026 that the VIN is always visible on hover regardless of the switch. If you see it there, pass this test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§9, §4.4, §4.8). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md.</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §4.4, §4.8). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6273,13 +6397,15 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1. Six toggles are offered: Business Hours, Capacity Bars, Events, Tech Hours, Saturday, Sunday.
+          <t xml:space="preserve">1. Six toggles are offered: Business Hours, Capacity Bars, Events, Tech Hours, Saturday, Sunday.
 2. Defaults: Business Hours OFF, Capacity Bars ON, Events ON, Tech Hours OFF, Saturday ON, Sunday ON.
 3. Capacity Bars OFF: the capacity bars disappear from the column headers; ON: they reappear with the same values.
 4. Events OFF: event blocks disappear from the grid while shifts remain; ON: the events reappear unchanged.
 Known issue on the build tested: Observed defaults: Business Hours ON, Tech Hours OFF, Capacity Planning ON, Events ON, Show Saturday ON, Show Sunday ON. The spec 9 table requires Business Hours OFF. The other five match. The Business Hours half of this is already raised with the developers as SV-8827 (https://shopview.atlassian.net/browse/SV-8827); that same ticket also says Tech Hours starts ON, which it does not on this build. Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§6, §9, §4.12).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6, §9, §4.12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8827)
+</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6327,11 +6453,13 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1. With the toggle on, the hours OUTSIDE the working day are shaded with a grey overlay.
+          <t xml:space="preserve">1. With the toggle on, the hours OUTSIDE the working day are shaded with a grey overlay.
 2. Working hours remain unshaded.
 3. Turning it off removes the shading.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§9, §4.8).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §4.8). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6378,12 +6506,14 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1. Each technician's working hours are displayed next to their name in the row header.
+          <t xml:space="preserve">1. Each technician's working hours are displayed next to their name in the row header.
 2. The hours match the technicians' configured hours.
 3. Turning it off hides the hours again.
 Known issue on the build tested: Toggling Tech Hours produced no observable change at all: the technician rows still show only initials, name and job title, and the shaded-cell count was identical before, during and after (2 / 2 / 2) - including for Ayesha Khan, the one technician who has custom hours. Spec 9: "Tech Hours | Off | Displays each technician's working hours next to their name." This is already raised with the developers as SV-8851 (https://shopview.atlassian.net/browse/SV-8851). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§9).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8851)
+</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6430,11 +6560,13 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>1. Saturday off: the Saturday column is removed (6 columns remain).
+          <t xml:space="preserve">1. Saturday off: the Saturday column is removed (6 columns remain).
 2. Sunday off too: 5 weekday columns remain (Monday to Friday).
 3. Both back on: the full Monday-to-Sunday 7-column week returns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§9, §3.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §3.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6468,34 +6600,28 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser with Schedule: Edit.&lt;/li&gt;
-&lt;li&gt;A shift exists on technician A; note the affected line's roster.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page in week view.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. A shift exists on technician A; note the affected line's roster.
+3. You are on the Schedule page in week view.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Drag the shift block from technician A's row to technician B's row.&lt;/li&gt;
-&lt;li&gt;Confirm the move in the confirmation modal.&lt;/li&gt;
-&lt;li&gt;Check the line's roster on the work order.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Drag the shift block from technician A's row to technician B's row.
+2. Confirm the move in the confirmation modal.
+3. Check the line's roster on the work order.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;A confirmation modal appears for the cross-technician move.&lt;/li&gt;
-&lt;li&gt;After confirming, the shift sits on technician B's row.&lt;/li&gt;
-&lt;li&gt;Technician B is added to the affected line's roster and technician A is removed from it.&lt;/li&gt;
-&lt;li&gt;A toast with Undo appears.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7, §12).</t>
+          <t xml:space="preserve">1. A confirmation modal appears for the cross-technician move.
+2. After confirming, the shift sits on technician B's row.
+3. Technician B is added to the affected line's roster and technician A is removed from it.
+4. A toast with Undo appears.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6542,13 +6668,15 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>1. A dropdown menu opens at the spot you clicked.
+          <t xml:space="preserve">1. A dropdown menu opens at the spot you clicked.
 2. It contains ONLY two items: 'Create Event' and 'New Work Order'.
 3. There is no 'View Day' item - it was removed from the menu.
 4. There is no 'New Shift' item - it was removed from the menu.
 5. This menu is opened by a normal left-click - right-clicking the cell does not open it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7, §14.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §14.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6594,10 +6722,12 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1. The menu offers a 'New Work Order' item.
+          <t xml:space="preserve">1. The menu offers a 'New Work Order' item.
 2. Choosing it directs the user to create a work order (a toast / prompt pointing to the Work Orders tab).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7, §4.10).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §4.10). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6631,32 +6761,26 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser with Schedule: Delete.&lt;/li&gt;
-&lt;li&gt;A series of at least 3 shifts exists for one technician.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser with Schedule: Delete.
+2. A series of at least 3 shifts exists for one technician.
+3. You are on the Schedule page.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Delete a MIDDLE shift of the series (via the detail modal's Delete).&lt;/li&gt;
-&lt;li&gt;Read the scope options offered (do not confirm yet).&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Delete a MIDDLE shift of the series (via the detail modal's Delete).
+2. Read the scope options offered (do not confirm yet).</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;A scope prompt appears with three options: this shift only, this and everything after, and the whole series.&lt;/li&gt;
-&lt;li&gt;Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').&lt;/li&gt;
-&lt;li&gt;The prompt uses routine, lightweight styling - not alarming destructive styling.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
+          <t xml:space="preserve">1. A scope prompt appears with three options: this shift only, this and everything after, and the whole series.
+2. Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').
+3. The prompt uses routine, lightweight styling - not alarming destructive styling.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6704,12 +6828,14 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>1. Only that day's shift is removed.
+          <t xml:space="preserve">1. Only that day's shift is removed.
 2. The series keeps the gap - the remaining shifts do NOT shuffle to close it.
 3. The removed day's hours return to the estimate's remaining (scheduled hours drop by that day's hours).
 4. An undo toast appears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6756,11 +6882,13 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>1. The third shift and every later shift of the series are removed.
+          <t xml:space="preserve">1. The third shift and every later shift of the series are removed.
 2. The first two shifts remain untouched.
 3. An undo toast appears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6807,11 +6935,13 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1. All of technician A's series shifts are removed.
+          <t xml:space="preserve">1. All of technician A's series shifts are removed.
 2. Technician B's independent series is untouched (the scope is per technician's series).
 3. An undo toast appears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6859,12 +6989,14 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>1. First shift: two options ('this and after' would equal 'whole series', so only two are shown).
+          <t xml:space="preserve">1. First shift: two options ('this and after' would equal 'whole series', so only two are shown).
 2. Last shift: two options ('this and after' would equal 'this only').
 3. Middle shift: all three options.
 4. Cancelling leaves the series unchanged in every case.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6911,10 +7043,12 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
+          <t xml:space="preserve">1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
 2. The shift is deleted and an undo toast appears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6961,11 +7095,13 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>1. Untouched, a toast that has an Undo action persists about 7 seconds; a toast without Undo persists about 4 seconds, before dismissing.
+          <t xml:space="preserve">1. Untouched, a toast that has an Undo action persists about 7 seconds; a toast without Undo persists about 4 seconds, before dismissing.
 2. While the cursor is over it, the toast stays (does not auto-dismiss).
 3. After the cursor leaves, it dismisses.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7, §11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -7015,13 +7151,15 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>1. Each of the four actions (create, delete, move, reassign) produces a toast notification, and every toast offers an Undo option.
+          <t xml:space="preserve">1. Each of the four actions (create, delete, move, reassign) produces a toast notification, and every toast offers an Undo option.
 2. Undo after delete: the shift is back exactly where it was.
 3. Undo after move: the shift returns to its original day/time.
 4. Undo after reassign: the shift returns to the original technician, and the line's roster is restored (original tech back on, target tech off).
 5. Every destructive action is undoable within the toast's lifetime.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7, §11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7070,12 +7208,14 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>1. The delete took effect immediately: after the refresh the shift is gone even though Undo was never clicked - closing or refreshing does not cancel the action.
+          <t xml:space="preserve">1. The delete took effect immediately: after the refresh the shift is gone even though Undo was never clicked - closing or refreshing does not cancel the action.
 2. The move also stuck after the refresh - the shift is on the new day.
 3. Clicking Undo within the toast's lifetime reverses the action (the deleted shift comes back).
 4. Note for the tester: Undo works by performing a reversing action, not by holding the change back - a change surviving a refresh before Undo is expected, not a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7123,14 +7263,16 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>1. Escape with the color picker open closes only the color picker - the modal stays open.
+          <t xml:space="preserve">1. Escape with the color picker open closes only the color picker - the modal stays open.
 2. Same for the time picker and the note edit - each sub-picker closes first and the modal stays open.
 3. Escape with no open sub-picker closes the modal itself.
 4. With two layers open, the FIRST Escape closes only the topmost layer, and the SECOND Escape closes the next layer down.
 5. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).
 Known issue on the build tested: Escape closes the shift detail modal and both toolbar popovers, but does NOT close the "Delete from this series?" dialog (tried twice, once with focus moved inside it) and does NOT close the "Reassign shift" dialog. Spec 7 names both first in its stacking order: "Escape closes the topmost open modal or popover, following a defined stacking order (delete scope, reassign, spread, ...)". This is already raised with the developers as SV-8853 (https://shopview.atlassian.net/browse/SV-8853). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8853)
+</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7180,13 +7322,15 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>1. In each confirmable dialog, Enter confirms it - equivalent to clicking its confirm action.
+          <t xml:space="preserve">1. In each confirmable dialog, Enter confirms it - equivalent to clicking its confirm action.
 2. The confirmed action takes effect (spread created / reassigned / event saved / delete applied).
 3. In the note editor, Enter inserts a new line in the note - it does NOT confirm or close the dialog.
 4. The multiline note can be completed and saved normally.
 Known issue on the build tested: Enter on the open "Reassign shift" dialog did nothing - the dialog stayed open and no toast appeared. Spec 7: "Enter confirms the active confirmable dialog (delete scope, reassign, spread, event create/edit)." The "not inside a textarea" half cannot be reached while Enter confirms nothing. This is already raised with the developers as SV-8853 (https://shopview.atlassian.net/browse/SV-8853). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§7).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8853)
+</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7233,11 +7377,13 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>1. Focus moves through the modal's interactive elements with visible focus rings.
+          <t xml:space="preserve">1. Focus moves through the modal's interactive elements with visible focus rings.
 2. Focus stays trapped inside the modal (wraps back to its first control) until the modal closes.
 3. On the page, toolbar and sidebar controls are reachable by keyboard.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7271,31 +7417,25 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in on a desktop browser with Schedule: Edit.&lt;/li&gt;
-&lt;li&gt;You are on the Schedule page.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+2. You are on the Schedule page.</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Create a normal single-day shift without touching any color option.&lt;/li&gt;
-&lt;li&gt;Create a multi-week series without touching any color option.&lt;/li&gt;
-&lt;li&gt;Look at both on the grid.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Create a normal single-day shift without touching any color option.
+2. Create a multi-week series without touching any color option.
+3. Look at both on the grid.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;Both the single shift and the multi-week series render in the default blue.&lt;/li&gt;
-&lt;li&gt;No special color is auto-applied to long jobs - blue is the default for ALL shifts.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§10).</t>
+          <t xml:space="preserve">1. Both the single shift and the multi-week series render in the default blue.
+2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7344,12 +7484,14 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>1. The shift's block re-renders in the chosen color.
+          <t xml:space="preserve">1. The shift's block re-renders in the chosen color.
 2. The color provides three consistent tones: background fill, text color, and accent (left border).
 3. The color is per SHIFT, not per work order - the other shift from the same work order keeps its own (default blue) color and does not change.
 4. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§10, §4.9, §4.4).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10, §4.9, §4.4). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7397,11 +7539,13 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>1. Each color's label can be edited.
+          <t xml:space="preserve">1. Each color's label can be edited.
 2. The renamed label shows for the whole shop - the same picker opened elsewhere shows 'ZZAUTOTEST Rush'.
 3. Shifts and events share the same custom palette with the same labels.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§10, §4.10).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10, §4.10). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7450,13 +7594,15 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>1. Edit Location shows a toggle labelled 'Set business hours for this shop', and it is OFF by default (no business hours set).
+          <t xml:space="preserve">1. Edit Location shows a toggle labelled 'Set business hours for this shop', and it is OFF by default (no business hours set).
 2. Turning it ON reveals a per-day working-hours editor for the shop.
 3. There is one row per day of the week, Monday through Sunday.
 4. Each day has a From time and a To time you can set.
 5. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7503,11 +7649,13 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>1. Edit Staff Member shows a toggle labelled 'Set custom hours for this technician'.
+          <t xml:space="preserve">1. Edit Staff Member shows a toggle labelled 'Set custom hours for this technician'.
 2. The toggle is OFF by default (no custom hours set).
 3. Turning it ON reveals a per-day working-hours editor for that technician.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7553,10 +7701,12 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>1. With no custom hours, the technician's working hours fall back to the shop business hours.
+          <t xml:space="preserve">1. With no custom hours, the technician's working hours fall back to the shop business hours.
 2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7602,11 +7752,13 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>1. 'Add hours' appends an additional From-To range to that day (to support split shifts).
+          <t xml:space="preserve">1. 'Add hours' appends an additional From-To range to that day (to support split shifts).
 2. The added range starts empty (no From/To pre-filled).
 3. Each added range can be removed individually.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7653,13 +7805,15 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>1. The offending (overlapping) range is flagged in red.
+          <t xml:space="preserve">1. The offending (overlapping) range is flagged in red.
 2. An inline message reads 'These hours overlap. Adjust the times so they don't conflict.'
 3. Save is disabled while the overlap exists.
 4. The incomplete row (empty From/To) is ignored by the overlap check - it does not raise the overlap error.
 5. Save is not blocked by an incomplete row on its own (only genuine overlaps disable Save).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7693,35 +7847,29 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;A test user's role has Schedule: View but NOT Edit (assign a suitable system role or a purpose-made custom role; restore after).&lt;/li&gt;
-&lt;li&gt;Shifts and events exist on the grid, created by an Edit-capable user.&lt;/li&gt;
-&lt;li&gt;You are signed in AS that View-only user on a desktop browser.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. A test user's role has Schedule: View but NOT Edit (assign a suitable system role or a purpose-made custom role; restore after).
+2. Shifts and events exist on the grid, created by an Edit-capable user.
+3. You are signed in AS that View-only user on a desktop browser.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Open the Schedule page.&lt;/li&gt;
-&lt;li&gt;Switch between Day, Week, and Month.&lt;/li&gt;
-&lt;li&gt;Use the mini calendar, the toolbar search, and the sidebar filter.&lt;/li&gt;
-&lt;li&gt;Hover a shift for its tooltip, then click it to open the detail modal.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Open the Schedule page.
+2. Switch between Day, Week, and Month.
+3. Use the mini calendar, the toolbar search, and the sidebar filter.
+4. Hover a shift for its tooltip, then click it to open the detail modal.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;The Schedule page opens and all three views work.&lt;/li&gt;
-&lt;li&gt;The mini calendar, search, and filters all work.&lt;/li&gt;
-&lt;li&gt;ALL technicians' shifts and events are visible (not just the user's own).&lt;/li&gt;
-&lt;li&gt;Tooltips show on hover, and the shift/event detail modals open in read-only mode.&lt;/li&gt;
-&lt;/ol&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.1, §14.3).</t>
+          <t xml:space="preserve">1. The Schedule page opens and all three views work.
+2. The mini calendar, search, and filters all work.
+3. ALL technicians' shifts and events are visible (not just the user's own).
+4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1, §14.3). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7770,12 +7918,14 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1. No drag handles are offered and nothing can be dragged from the sidebar onto the grid.
+          <t xml:space="preserve">1. No drag handles are offered and nothing can be dragged from the sidebar onto the grid.
 2. Shift blocks cannot be moved or resized - no drop targets or resize handles appear.
 3. No creation menu opens at all - there is no 'Create Event' and no 'New Work Order' offered.
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7821,10 +7971,12 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>1. The Schedule top-level nav item is not shown at all.
+          <t xml:space="preserve">1. The Schedule top-level nav item is not shown at all.
 2. The rest of the app works normally for the role.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7873,13 +8025,15 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>1. Drag-and-drop from the sidebar, the scope picker, and the spread modal all work.
+          <t xml:space="preserve">1. Drag-and-drop from the sidebar, the scope picker, and the spread modal all work.
 2. Shift and event creation works, including via the menu opened by left-clicking empty grid space in both week and day view.
 3. Reassignment between technicians works.
 4. Edge-resize and horizontal drag work in day view.
 5. Modal fields are editable and save.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7927,11 +8081,13 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>1. The delete action and the trash icon are hidden in the shift modal.
+          <t xml:space="preserve">1. The delete action and the trash icon are hidden in the shift modal.
 2. Events likewise offer no delete.
 3. No path exists to remove shifts or events - while creating and modifying still work.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7979,12 +8135,14 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>1. The delete action is available and works for shifts.
+          <t xml:space="preserve">1. The delete action is available and works for shifts.
 2. Series deletion offers its scopes (this shift / this and after / whole series).
 3. Events can be deleted too.
 4. Undo toasts appear (restore the items via Undo to clean up).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -8031,11 +8189,13 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>1. Edit cannot be granted without View (the admin UI enforces or auto-selects the dependency).
+          <t xml:space="preserve">1. Edit cannot be granted without View (the admin UI enforces or auto-selects the dependency).
 2. Delete cannot be granted without Edit.
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -8083,12 +8243,14 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>1. The sidebar hides the work order list and the line drill-down; the mini calendar remains available.
+          <t xml:space="preserve">1. The sidebar hides the work order list and the line drill-down; the mini calendar remains available.
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
 3. New work orders cannot be dragged on - the WO list is simply not visible.
 Known issue on the build tested: a user who has the Schedule but has NOT been given Work Orders: View still sees the whole work order list in the left-hand panel - 18 cards showing the customer name, the unit number, how many lines the job has, the hours estimate and the lead technician. It should be hidden for them. This is already raised with the developers as SV-8854 (https://shopview.atlassian.net/browse/SV-8854). Until it is fixed this test will fail - mark it FAILED and link SV-8854; do not raise a new ticket.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.2).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.2). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (SV-8854)
+</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8135,10 +8297,12 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
+          <t xml:space="preserve">1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.3).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.3). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8185,10 +8349,12 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
+          <t xml:space="preserve">1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
 2. The staff member without a department does not appear as a row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.4).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.4). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8234,10 +8400,12 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>1. The Time-Clock-ON staff member can clock in.
+          <t xml:space="preserve">1. The Time-Clock-ON staff member can clock in.
 2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.4).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.4). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8285,11 +8453,13 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>1. Work-order-derived details (customer, the scheduled line list, and any money-bearing fields) are hidden or masked wherever they would normally appear - on the block, in the tooltip, and in the modal.
+          <t xml:space="preserve">1. Work-order-derived details (customer, the scheduled line list, and any money-bearing fields) are hidden or masked wherever they would normally appear - on the block, in the tooltip, and in the modal.
 2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
 3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.2). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md.</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.2). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8340,12 +8510,14 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>1. Technician, Parts Manager, Parts Tech, Office and Time Clock each have Schedule View turned ON and Schedule Edit and Schedule Delete turned OFF.
+          <t xml:space="preserve">1. Technician, Parts Manager, Parts Tech, Office and Time Clock each have Schedule View turned ON and Schedule Edit and Schedule Delete turned OFF.
 2. Service Manager, Senior Service Advisor, Service Advisor and Foreman each have Schedule Edit turned ON (so they also have View).
 3. The user from step 4 gets the read-only schedule - nothing can be dragged onto the grid and no shift can be created.
 4. The user from step 5 can drag a work order onto the grid and create a shift.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14.1).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8392,13 +8564,15 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>1. Below the 960px minimum supported width, the grid scrolls horizontally rather than breaking.
+          <t xml:space="preserve">1. Below the 960px minimum supported width, the grid scrolls horizontally rather than breaking.
 2. All days remain reachable by horizontal scroll.
 3. On narrow viewports the sidebar collapses.
 4. No content becomes permanently unreachable and nothing errors.
 Known issue on the build tested: At a 900px viewport the sidebar stays 288px wide and the whole page scrolls sideways (documentElement.scrollWidth 1041) rather than only the grid. Spec 11: "Minimum supported width is 960px (the grid scrolls horizontally below that), and the sidebar collapses on narrow viewports." 900px is below the supported minimum, so this is a low-severity observation, not a release blocker. It has been reported to the QA lead but has no developer ticket yet. Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY - EXPECT FAIL (no ticket - accepted, see the decisions register)
+</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8446,11 +8620,13 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
+          <t xml:space="preserve">1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
 3. Search stays responsive on the long list.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8498,11 +8674,13 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>1. The grid renders and scrolls smoothly at this scale.
+          <t xml:space="preserve">1. The grid renders and scrolls smoothly at this scale.
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8550,12 +8728,14 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>1. The closure day is NOT struck through or skipped by the spread in V1.
+          <t xml:space="preserve">1. The closure day is NOT struck through or skipped by the spread in V1.
 2. A shift CAN be placed on the shop closure day (only weekend days with no business hours are skipped).
 3. The end date follows the normal daily distribution - no extra day is added for the closure.
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The specification says this two different ways and no ruling exists yet, so mark this test BLOCKED - not failed - and leave it out of the automation suite. The open question and its evidence are recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md
----
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§12, §4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md.</t>
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The specification says this two different ways and no ruling exists yet, so mark this test BLOCKED - not failed - and leave it out of the automation suite. The open question and its evidence are recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§12, §4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
+</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8601,10 +8781,12 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>1. All three quantities are shown/derivable and may differ from one another.
+          <t xml:space="preserve">1. All three quantities are shown/derivable and may differ from one another.
 2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8651,11 +8833,13 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>1. Every shift in the series starts at the SAME local wall-clock time (e.g. 8:00 AM) on both sides of the clock change.
+          <t xml:space="preserve">1. Every shift in the series starts at the SAME local wall-clock time (e.g. 8:00 AM) on both sides of the clock change.
 2. No shift in the series silently moves an hour earlier or later after the change date.
 This test cannot be run on the build tested: the next Mountain-time clock change is 2026-11-01, outside any window the QA data covers, and the seeded clock cannot be moved on this estate. Worse, the finding is currently untestable in principle because every Schedule time renders in UTC (see the new time ticket) - so a clock-change test would measure the bug, not the requirement. Re-run once the timezone fix ships. Mark it BLOCKED - not failed - and say which of these you could not set up.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: HOLD - needs a real daylight-saving clock change, the next one is 1 November 2026
+</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8703,12 +8887,14 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>1. In dark mode every part of the Schedule stays readable - no white-on-white or black-on-black text, no unreadable labels or invisible icons.
+          <t xml:space="preserve">1. In dark mode every part of the Schedule stays readable - no white-on-white or black-on-black text, no unreadable labels or invisible icons.
 2. Every dialog and popover opened from the Schedule follows the dark theme too.
 3. Conflict and overtime cues remain distinguishable (they never rely on colour alone - text/icon still present).
 4. Switching back to light mode restores the normal look with nothing stuck in dark colours.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§11).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8755,11 +8941,13 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>1. Every shift and event that existed before the release is still there after it - same technician, same day, same time, same work order.
+          <t xml:space="preserve">1. Every shift and event that existed before the release is still there after it - same technician, same day, same time, same work order.
 2. Events are still events and shifts are still shifts (nothing changed kind or vanished).
 3. Their details open normally and are editable/deletable like any other entry.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point.</t>
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8806,11 +8994,13 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>1. The Dashboard shows that work order as ONE row (covering the whole scheduled span), not one row per daily shift.
+          <t xml:space="preserve">1. The Dashboard shows that work order as ONE row (covering the whole scheduled span), not one row per daily shift.
 2. Note for the tester: before this release the Dashboard duplicated such a work order once per scheduled day - showing one combined row now is the intended fix, do not report it as a missing-rows bug.
 3. Work orders with a single shift are unaffected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point.</t>
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8857,11 +9047,13 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>1. The appointment created with the work order appears on the Schedule board at the chosen date/time.
+          <t xml:space="preserve">1. The appointment created with the work order appears on the Schedule board at the chosen date/time.
 2. It behaves like any other scheduled entry (opens, moves, deletes normally).
 3. It also appears in the Dashboard's schedule section for that day.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point.</t>
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8909,11 +9101,13 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>1. The shift appears on location A's board (the location the work order belongs to).
+          <t xml:space="preserve">1. The shift appears on location A's board (the location the work order belongs to).
 2. The shift does NOT appear on location B's board, even though the technician is enrolled there too.
 3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point.</t>
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8961,12 +9155,14 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>1. The work order form offers a Priority choice of High, Medium, Low.
+          <t xml:space="preserve">1. The work order form offers a Priority choice of High, Medium, Low.
 2. A new work order has NO priority pre-selected by default.
 3. After saving, the Schedule sidebar reflects the chosen priority and the Priority filter finds the work order under High.
 4. A work order with no priority set simply shows none (it is not treated as an error).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point.</t>
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -9014,12 +9210,14 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>1. No Schedule permission: the board GET is refused with HTTP 403.
+          <t xml:space="preserve">1. No Schedule permission: the board GET is refused with HTTP 403.
 2. View-only: the board GET returns HTTP 200 with the grid data; the POST and PATCH are refused with HTTP 403.
 3. View + Edit: the POST and PATCH succeed (HTTP 201/200); the DELETE is refused with HTTP 403 because the user lacks Schedule: Delete.
 4. Each refusal is a clean 403 response - never a server error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14).</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -9067,13 +9265,15 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>1. The over-8-week create is refused with HTTP 409 (a 'series too long' error) - nothing is created.
+          <t xml:space="preserve">1. The over-8-week create is refused with HTTP 409 (a 'series too long' error) - nothing is created.
 2. With acknowledgeLongSeries=true the same request succeeds (HTTP 201) and returns the full materialized series under one series id.
 3. The over-120-shift request is refused with HTTP 422 even WITH the acknowledgement - the hard cap cannot be overridden.
 4. Refused calls leave no partial series behind.
 Not built on the build tested: No 409 and no 422 exists on this build. The 8-week / 120-shift caps are engineering-tech-plan text with no Schedule-specification requirement behind them. It has no developer ticket yet - report it to the QA lead rather than raising one yourself. Mark this test BLOCKED - not failed - because the feature it checks does not exist yet on this build.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md.</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: HOLD - the feature is not built yet
+</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -9120,11 +9320,13 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>1. No Schedule response contains any pricing/money field for ANY caller - the schedule never returns labor, totals, or dollar amounts.
+          <t xml:space="preserve">1. No Schedule response contains any pricing/money field for ANY caller - the schedule never returns labor, totals, or dollar amounts.
 2. For the caller without Work Orders: View, the work-order-derived details (customer, unit, VIN, line names) are absent/empty in the response itself - not just hidden on screen.
 3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the Schedule specification version 23 (§14). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/branko-answers-2026-07-31/answers-ingested.md.</t>
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9172,11 +9374,13 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>1. The foreign-location GET is refused as not found (HTTP 404) - the response reveals nothing about the other location's shift.
+          <t xml:space="preserve">1. The foreign-location GET is refused as not found (HTTP 404) - the response reveals nothing about the other location's shift.
 2. The PATCH on the foreign id is refused the same way (404) - no cross-location edit is possible.
 3. Location A's board contains only location A's shifts - nothing from location B leaks in.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (v3.5-4873abe), and as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/main/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point.</t>
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. It was last checked against build v3.5-4873abe on 8/4/2026; the branch has since been rebuilt to v3.5-be42149 and this case has not been re-checked against it.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -528,7 +528,7 @@
 3. The left panel is the work order sidebar: a mini calendar at the top and a work order list beneath it.
 4. The main area is the schedule grid showing technician rows, with a toolbar above it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3, §3.1, §3.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3, §3.1, §3.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -582,9 +582,13 @@
 2. Week: the grid shows a 7-column Monday-to-Sunday layout with stacked shift chips per cell.
 3. Month: the grid shows a compact calendar with per-day capacity bars and shift chips.
 4. The same shifts appear in all three views - each one drawn to suit that view: positioned on the hour line in Day, as a chip in the day column in Week, and as a compact chip in Month.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §6). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+What you should see today: Week view runs Sunday to Saturday. The seven columns read Sunday Aug 2, Monday Aug 3, and so on to Saturday Aug 8, instead of starting on Monday. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8826
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §6). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8826)
 </t>
         </is>
       </c>
@@ -636,7 +640,7 @@
 2. Each department's technicians are listed beneath that department's header.
 3. Every staff member assigned to a visible department appears as a row, regardless of their role.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §14.4). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §14.4). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -688,7 +692,7 @@
 2. Expanding shows the technician rows again, unchanged.
 3. Other department groups are unaffected.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -738,7 +742,7 @@
           <t xml:space="preserve">1. No such toggle exists - the department-grouped rows are the only grid grouping.
 2. Department visibility is controlled only through the department toggles in the 'Filter and Display' dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -791,7 +795,7 @@
 2. Shifts without a technician sit in this row.
 3. The unassigned shift uses the same block layout as regular shifts (customer, unit, line name / line count) - it simply has no technician.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -844,9 +848,12 @@
           <t xml:space="preserve">1. The Schedule page opens.
 2. Of the three buttons Day, Week and Month, the one that is switched on (highlighted) is Day.
 3. The grid shows the Day layout: a 24-hour timeline for each technician row, with shifts placed at their times.
-Known issue on the build checked: the Schedule opens on Week view instead - Week is the highlighted button and the grid draws the 7-column week layout. This is already raised with the developers as SV-8863 (https://shopview.atlassian.net/browse/SV-8863) and has been accepted for fixing. Until it is fixed this test will fail - mark it FAILED and link SV-8863; do not raise a new ticket.
----
-This is the expected behaviour as per epic SV-8685 and the acceptance criterion of its story SV-8686, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 23 does not say which view the page opens on, so this expectation comes from the story rather than the specification. Last checked against build v3.5-d122eef on 8/5/2026.
+What you should see today: The Schedule opens on Week view. Week is the highlighted button and the grid draws the seven-column week layout. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8863
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the acceptance criterion of its story SV-8686, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 23 does not say which view the page opens on, so this expectation comes from the story rather than the specification. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8863)
 </t>
         </is>
@@ -898,7 +905,7 @@
 2. The toolbar date label updates to the new range.
 3. The clicked date is highlighted as the selected date in the mini calendar.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -951,7 +958,7 @@
 2. Choosing a month shows that month in the mini calendar.
 3. The main grid can then be navigated by clicking a date in the newly shown month.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1003,7 +1010,7 @@
           <t xml:space="preserve">1. The calendar grid collapses (hides), leaving more room for the work order list below.
 2. Clicking again expands the calendar grid back.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1056,7 +1063,7 @@
 2. Today's date has its own distinct indicator, different from the selection.
 3. Hovering a week row highlights that whole week row.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1110,7 +1117,7 @@
 2. The list scrolls when there are more cards than fit.
 3. There are no Assigned/Unassigned tabs - assignment is available only as a filter behind the 'Filter' button.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1165,7 +1172,7 @@
 4. A lead technician row with the technician's avatar and name.
 5. A colored left border whose color reflects the work order's status.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1220,10 +1227,13 @@
 2. Customer-name search shows only cards for that customer, and it works with the full multi-word name (for example 'Vuchester Retail').
 3. Unit-number search shows only cards with that unit.
 4. Technician-name search shows only cards where that technician is on the work order - and it must work when you type the technician's name the way the card shows it, first name and last name together (for example 'Andrew Wade').
-Known issue on the build tested: typing a technician's FULL name returns nothing at all. 'Andrew' on its own finds 12 work orders and 'Wade' on its own finds the same 12, but 'Andrew Wade' finds 0, and so do 'andrew wade' and 'Wade Andrew'. It is not a general problem with spaces - the full customer name 'Vuchester Retail' finds 21 work orders correctly. That is already raised with the developers as SV-8873 (https://shopview.atlassian.net/browse/SV-8873). Mark this test FAILED.
 Note for the tester: searching the number exactly as the card shows it (for example S-15875) does work, and so does the bare number (15875). Searching the longer shop-prefixed form (for example S8685-15875) returns nothing; that is already raised as SV-8841 (https://shopview.atlassian.net/browse/SV-8841), so do not raise it again.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-be42149 on 8/5/2026.
+What you should see today: Typing a technician's full name finds nothing. 'Andrew' on its own finds 14 work orders and 'Wade' on its own finds the same 14, but 'Andrew Wade' finds 0, and so do 'andrew wade' and 'Wade Andrew'. A full customer name such as 'Vuchester Retail' works, so it is not a problem with spaces. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8873
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8873)
 </t>
         </is>
@@ -1276,7 +1286,7 @@
 2. Deleting characters widens the results again.
 3. With very many work orders, the list may load further results in pages as you scroll - that is expected, not a fault.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1329,7 +1339,7 @@
 2. The app does not error; the sidebar remains usable.
 3. Clearing the search restores the full list.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1383,7 +1393,7 @@
 2. Applying a filter narrows the flat card list.
 3. The 'Filters' button shows a badge with the number of active filters.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1437,7 +1447,7 @@
 2. Assigned: only work orders with a technician assigned remain.
 3. There are no Assigned/Unassigned tabs - this filter is the only assignment split.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1, §3.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1, §3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1493,7 +1503,7 @@
 4. The card left-border colours of the remaining cards are consistent with that status.
 Note for the tester: this shop's schedule list only holds work orders in two statuses, Approved and Review, so most of the other choices correctly come back empty. An empty list for a status no work order is in is the right answer, not a fault.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-be42149 on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1546,7 +1556,7 @@
           <t xml:space="preserve">1. The Priority group offers High, Medium, and Low.
 2. Only High-priority work orders remain in the list.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-be42149 on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1597,10 +1607,9 @@
           <t xml:space="preserve">1. All applied filters are removed at once.
 2. The full work order list is shown again.
 3. The active-count badge on the 'Filter' button disappears (or shows zero).
-Known issue on the build tested: The popover has no "Clear all" control: filters are cleared by unchecking each box, and the Filters button carries no active-count badge either. Spec 5.1: "Filters live behind a 'Filter' button (with an active-count badge) ... and 'Clear all' resets in one click." This is already raised with the developers as SV-8857 (https://shopview.atlassian.net/browse/SV-8857). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8857)
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1652,7 +1661,7 @@
           <t xml:space="preserve">1. The list shows only work orders that match BOTH the text search and the structured filter.
 2. Removing either the search text or the filter widens the list to the remaining condition.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-be42149 on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1709,7 +1718,7 @@
 4. A back control is shown to return to the card list.
 5. Clicking back restores the work order card list.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1762,7 +1771,7 @@
 2. No line that has never been approved appears anywhere in the schedule sidebar - for example a line still sitting on an estimate, or one that was declined.
 3. The line count in the drill-down header matches the number of APPROVED lines on the work order - a line that was never approved is neither listed nor counted.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-be42149 on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1815,7 +1824,7 @@
 2. The current technician roster is shown as an avatar stack plus a count; there is no cap on how many technicians a line can have.
 3. Each line row has its own drag handle, so it can be dragged independently onto the grid.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §8.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §8.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1868,7 +1877,7 @@
 2. The line with a technician does not show the badge.
 3. After a technician is scheduled onto the badge-bearing line, the badge goes away.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1921,7 +1930,7 @@
           <t xml:space="preserve">1. Typing a line title narrows the list to matching lines.
 2. Typing the customer name returns no results - the line search matches line titles only (the list is already scoped to one work order, so customer/unit/WO fields are not searched).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1975,7 +1984,7 @@
 2. Unscheduled lists only the lines that have no shifts yet, and its count matches.
 3. All lists every approved line, and its count matches the drill-down header's line count.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2029,7 +2038,7 @@
 3. The technician is added to that line's labor roster on the work order.
 4. A toast with an Undo option appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §1.2, §7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §1.2, §7). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2082,7 +2091,7 @@
 2. It offers 'Schedule whole work order' at the top, the individual line rows beneath, and a 'Select multiple' control.
 3. No shift is created until a scope is chosen.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.3). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.3). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2136,7 +2145,7 @@
 2. The block's last text line shows that line's name.
 3. The technician is added to that line's roster only (not to the order's other lines).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2190,7 +2199,7 @@
 2. Its header shows the chosen scope and a 'Change scope' back-link.
 3. No shifts exist yet until the spread is confirmed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.5). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2242,7 +2251,7 @@
           <t xml:space="preserve">1. The shift is created straight away - the spread step does NOT appear.
 2. The shift sits on the dropped day only.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2294,9 +2303,12 @@
           <t xml:space="preserve">1. The cell currently under the cursor highlights as a drop target.
 2. A ghost block follows the drag showing the line name and its hours.
 3. Releasing outside any valid cell creates nothing.
-Known issue on the build tested: During a sidebar drag, .fc-highlight count was 0 and no ghost/mirror element carrying the line name existed. Spec 7: "Drop-target cells highlight, and a ghost block shows the line name and hours." NOTE an intra-grid move DOES show a mirror (fc-event-mirror), so the gap is specific to dragging from the sidebar. This is already raised with the developers as SV-8840 (https://shopview.atlassian.net/browse/SV-8840). Until it is fixed this test will fail - mark it FAILED and link SV-8840; do not raise a new ticket.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-4873abe on 8/4/2026.
+What you should see today: Nothing highlights and nothing follows the cursor while you drag a line from the list on the left onto the grid. No cell lights up as a drop target, and the faint shape that does follow the cursor is empty - it does not show the line name or the hours. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8840
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8840)
 </t>
         </is>
@@ -2353,7 +2365,7 @@
 4. Dragging the same line onto a second technician adds that technician to the line's roster as well - the technician who was already there stays on it.
 5. Nothing asks you to swap or replace the technician who was already there, and no limit is reached on how many technicians a line can have.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§1.2, §4.3, §7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§1.2, §4.3, §7). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2404,9 +2416,13 @@
         <is>
           <t xml:space="preserve">1. The item can be placed onto a cell without holding a drag - clicking arms it, and clicking a cell places it.
 2. The result is the same as the equivalent drag-and-drop (scope picker / spread step rules apply the same way).
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). Last checked against build v3.5-be42149 on 8/5/2026.
-AUTOMATION: READY
+What you should see today: There is no way to place a job by clicking. The work order card in the panel on the left has no button on it at all - not when you hover it, and not inside its line list - so dragging is the only way to schedule anything. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8957
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8957)
 </t>
         </is>
       </c>
@@ -2465,7 +2481,7 @@
 What was seen on the build checked: the card lifts and follows the mouse, but no day box shows as a drop target and releasing does nothing at all - no scope picker, no shift, no message. The same drag of the same work order in Week view does open the scope picker, so the difference is Month view itself.
 ---
 This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.2), which describe dragging a work order from the sidebar onto a cell in the grid and the order of preference for the start time. Neither that specification nor story SV-8688 says whether Month view accepts the drop, so that point is an open product-owner question rather than a settled requirement. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: HOLD - waiting on the product owner's answer on SV-8870 about whether Month view accepts the drag
+AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
 </t>
         </is>
       </c>
@@ -2520,7 +2536,7 @@
 4. Each line row shows the line title and its estimated hours.
 5. Rows for lines that already have technicians show the current roster as an avatar stack plus count.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). Last checked against build v3.5-be42149 on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2574,7 +2590,7 @@
 2. The block's last text line reads 'N Lines' (with N = the line count).
 3. The technician is added to the roster of every one of those lines.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3, §4.4). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3, §4.4). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2627,7 +2643,7 @@
 2. The picker closes.
 3. The block's last text line shows the line's name.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2685,10 +2701,9 @@
 3. A 'Select all' shortcut ticks every line, giving the same line count and hours as choosing the whole work order.
 4. A 'Cancel' control leaves tick-box mode and returns you to the ordinary single-tap line list, without creating anything and without closing the picker.
 5. Confirming creates ONE shift covering exactly the ticked lines, and the technician is added to those lines' rosters only - not to the other lines.
-Known issue on the build tested: in tick-box mode the bottom bar reads '1 selected - 1h' and its confirm button reads 'Schedule'; there is NO 'Select all' button and NO 'Cancel' button anywhere in the picker - the only way out is the X in the corner, which closes the whole picker instead of returning you to the single-tap list. The 'All 2' chip higher up is the All / Unscheduled filter and does not tick anything. Specification 4.3 asks for "a running tally ("Create shift - 2 lines - 6h"), a "Select all" shortcut (equivalent to whole order), and Cancel (returns to the fast single-tap list)". That is already raised with the developers as SV-8886 (https://shopview.atlassian.net/browse/SV-8886). Mark this test FAILED.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). Last checked against build v3.5-be42149 on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8886)
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -2740,7 +2755,7 @@
           <t xml:space="preserve">1. The shift starts at the technician's own configured start time (6:00 AM in the example), not the shop's business-hours start.
 Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2791,10 +2806,9 @@
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The shift starts at the shop's business-hours start time.
-This test cannot be run on the build tested: the shop has NO business hours set (the Edit Location toggle is off, and turning it on would change a shared setting for every other tester on this estate), so the middle rung of the section 4.2 hierarchy cannot be exercised without a change nobody has authorised. The rung above and below are both verified. Turning the toggle on was driven and then abandoned WITHOUT saving. Mark it BLOCKED - not failed - and say which of these you could not set up.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: HOLD - needs shop business hours switched on, which is a shared setting on this estate
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2844,9 +2858,8 @@
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The shift starts at 7:00 AM - the general default working day (7:00 AM to 7:00 PM) applies.
-Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2897,8 +2910,9 @@
         <is>
           <t xml:space="preserve">1. The shift starts at the time position where it was dropped (not at the technician-hours/business-hours default).
 2. The start time aligns to the timeline position (see the 15-minute snapping case).
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+Note for the tester: every time on the Schedule is currently shown six hours later than the time it was booked for. That is already reported as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Read the position on the timeline rather than the printed time, and do not raise it again.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2951,7 +2965,7 @@
 2. It has no technician (and no technician is added to the line's roster by this drop).
 3. The block uses the same anatomy as a regular shift (customer, unit, line name / 'N Lines').
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2, §3.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2, §3.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3002,9 +3016,8 @@
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The unassigned shift starts at the shop's business-hours start (there is no technician whose hours could apply).
-Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3057,9 +3070,13 @@
           <t xml:space="preserve">1. The shift is now assigned to that technician (it leaves the Unassigned row and sits in the technician's row).
 2. The technician is added to the affected line's roster.
 3. The technician's own working hours now apply to the shift's timing.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+What you should see today: Giving an unassigned job to a technician quietly changes its saved start time to six hours earlier. A job booked for 7:00 in the morning is saved as 1:00 in the morning after it is assigned, with no warning. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8924
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8924)
 </t>
         </is>
       </c>
@@ -3115,7 +3132,7 @@
 4. Clicking 'Change scope' takes the modal back to the scope picker (step 1) without creating anything.
 5. Choosing a new scope updates the spread step's header and hours accordingly.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3169,7 +3186,7 @@
 3. 'Full estimate', '1 week', and '2 weeks' apply on selection with no extra fields - the modal stays to one line for these.
 4. The preview summary updates to match each selection.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3221,7 +3238,7 @@
           <t xml:space="preserve">1. Choosing 'Until a date…' reveals a single 'finish by' date field (this is the only custom control shown).
 2. Picking a date updates the preview so the series ends by that date.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3272,7 +3289,7 @@
           <t xml:space="preserve">1. Choosing 'Specific hours…' reveals an hours stepper control.
 2. The preview updates to spread exactly the entered hours across working days.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3325,10 +3342,9 @@
           <t xml:space="preserve">1. The start date defaults to the earliest working day.
 2. It can be changed; technician B's series then starts after A's series ends (sequential, not parallel).
 3. B's series is created from the adjusted start date onward.
-Known issue on the build tested: There is no Start date control in the spread step at all - the start comes solely from the cell the work order was dropped on and cannot be adjusted. Spec 4.5: "Start date. Defaults to the earliest working day. Adjusting it is how a second technician's series can be made sequential (starting after the first) rather than parallel." Without it the sequential-series workflow the spec describes is impossible. This is already raised with the developers as SV-8855 (https://shopview.atlassian.net/browse/SV-8855). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8855)
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -3381,9 +3397,8 @@
 2. Weekends are skipped ONLY when the technician has no business hours set for them; if the tech has hours on a weekend day (e.g. Saturday hours) that day is NOT skipped.
 3. Shop closures and public holidays are NOT skipped in V1 - shifts can be placed on those days.
 4. The end date is a result of the daily distribution (for 40h at 8h/day starting Monday, the series ends on the fifth working day).
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The specification says this two different ways and no ruling exists yet, so mark this test BLOCKED - not failed - and leave it out of the automation suite. The open question and its evidence are recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-4873abe on 8/4/2026.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
 </t>
         </is>
@@ -3436,8 +3451,8 @@
 2. Expanded: a week-by-week breakdown of the planned shifts.
 3. Skipped days are struck through and show the reason they are skipped - in V1 the only skip reason is a weekend day with no working hours set.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -3490,8 +3505,8 @@
 3. Each daily shift keeps its own day and hours.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §4.6, §8.2). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §4.6, §8.2). Last checked against build v3.5-d122eef on 8/5/2026.
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -3543,7 +3558,7 @@
 2. There is no shared 'remaining hours' counter across technicians and no splitting of a shift.
 3. Planned hours across technicians may now exceed the estimate - this is expected and produces no error (progress is driven by clocked-in time).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3598,10 +3613,9 @@
 2. After you confirm the warning, the long series is created normally.
 3. A single spread that would create more than 120 daily shifts is refused outright - no confirmation can override it, and no shifts are created for that attempt.
 4. No half-created series is left behind after a refused attempt.
-Not built on the build tested: A 76h 36m spread produced 7 shifts with no warning and nothing asking you to confirm, and nothing on this build refuses or questions a very long series. The 8-week / 120-shift limits come from the engineering technical plan, not from the Schedule specification. It has no developer ticket yet - report it to the QA lead rather than raising one yourself. Mark this test BLOCKED - not failed - because the feature it checks does not exist yet on this build.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: HOLD - the feature is not built yet
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-d122eef on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3653,9 +3667,13 @@
           <t xml:space="preserve">1. The series renders as one continuous bar wrapping across the week rows.
 2. It is labeled once at the start (including the technician); later weeks show a faded 'continues'-style label instead of repeating the full label.
 3. Weekend columns inside the series are empty (no bar) when no business hours are set for those weekend days.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+What you should see today: In Month view the bar for a multi-day job does not say whose it is. It reads, for example, 'Xiriver Apparel  24069  19 Lines  Part of a series' with no technician name anywhere on it. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8958
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8958)
 </t>
         </is>
       </c>
@@ -3707,10 +3725,9 @@
           <t xml:space="preserve">1. One banner spans the working days of that week in the technician's row.
 2. Chevrons at the banner's edges indicate the series continues beyond the visible week (both sides, on a middle week).
 3. A 'week N of M' cue shows the position within the series.
-Known issue on the build tested: the Week view does draw one banner - the first day of the run carries the customer name, the line count and the words 'Part of a series', and each following day carries a small 'continues' marker - but there are no arrows at the edges of the banner and no 'week N of M' wording anywhere. Separately, none of those blocks can be clicked open in the Week view; that half is raised with the developers as SV-8849 (https://shopview.atlassian.net/browse/SV-8849). The missing arrows and the missing 'week N of M' have been reported to the QA lead and have no ticket yet. Mark this test FAILED, link SV-8849 and say in your comment which parts you saw; do not raise a new ticket.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8849)
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3761,7 +3778,7 @@
           <t xml:space="preserve">1. The day shows a single time-positioned block (no spanning bar - only one day is visible).
 2. The block carries a cue in the spirit of 'part of an M-week job' indicating it belongs to a longer series.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3815,7 +3832,7 @@
 2. The overlapping day is flagged as a Double-booked conflict, exactly as it would be for standalone shifts.
 3. The detail modal shows that single day's shift (its own day and hours) while indicating it belongs to the series.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6, §8.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6, §8.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3868,7 +3885,7 @@
 3. Last line: the name of the scheduled line.
 4. No work order number appears on the block.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3922,7 +3939,7 @@
 2. The subset block reads '2 Lines' - the block does not distinguish whole-order from subset beyond the count.
 3. Each detail modal lists exactly which lines the shift covers.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4, §12). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4, §12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3975,7 +3992,7 @@
 2. The conflicted block shows the conflict (warning) icon on its first line - and that is the only icon that ever appears on a block.
 3. No scope icons distinguish whole-order from subset shifts.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4030,7 +4047,7 @@
 3. The row stays at its normal height.
 4. No conflict is flagged for back-to-back (non-intersecting) shifts.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7, §12). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7, §12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4082,7 +4099,7 @@
 2. The row grows in height to fit the lanes.
 3. The overlap is also flagged as a Double-booked conflict (stacking reads as 'resolve me').
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7, §4.11). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7, §4.11). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4136,7 +4153,7 @@
 3. Clicking it opens a popover listing the hidden shifts.
 4. The hidden shifts can be opened from that popover.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4189,10 +4206,9 @@
           <t xml:space="preserve">1. All three views handle the overlap without blocks visually colliding.
 2. Week and month views reach the '+N more' overflow sooner than day view (their cells are narrower), but the same cap-and-overflow model applies.
 3. The overflow affordance opens the hidden-shifts popover in each view.
-Known issue on the build tested: Lane stacking and the "+N more" link appear in day, week and month view - but clicking "+1 more" opens a popover headed with just the date ("August 2, 2026") whose body contains only the day cell and its capacity bar and lists NO shifts (0 schedule-block elements inside it). Spec 4.7: "Additional overlapping shifts collapse into a '+N more' affordance that opens a popover listing the hidden shifts." The hidden shifts are unreachable. This is already raised with the developers as SV-8850 (https://shopview.atlassian.net/browse/SV-8850). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8850)
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4247,9 +4263,12 @@
 3. Your manual scroll position stays put - nothing jumps you back to the morning while you remain on the same day.
 4. The timeline is not stuck at the start - it remains a full 24-hour scrollable timeline (midnight to midnight).
 5. Only navigating to another day re-triggers the auto-scroll.
-Known issue on the build tested: Day view opens with the scroller at scrollLeft 3 and the first slot "12 AM", and it is still 3 after stepping a day. Spec 4.8: "On initial day-view load and when navigating to a new day, the timeline auto-scrolls so the working-day start sits at the left edge of the visible area (with a small 30 to 60 minute buffer before it)." This is already raised with the developers as SV-8837 (https://shopview.atlassian.net/browse/SV-8837). Until it is fixed this test will fail - mark it FAILED and link SV-8837; do not raise a new ticket.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-4873abe on 8/4/2026.
+What you should see today: Day view opens showing midnight at the left-hand edge instead of the start of the working day. The working day starts at 6:00 AM, but 12 AM sits at the left edge, and stepping to the next day leaves it at midnight again. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8837
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8837)
 </t>
         </is>
@@ -4302,7 +4321,7 @@
           <t xml:space="preserve">1. In day view, the date/time header bar stays stuck to the top while the rows scroll beneath it - you always know which time column you are looking at.
 2. The same sticky-header behavior applies in week view.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4356,10 +4375,9 @@
 2. The released start time snaps to a 15-minute interval (for example 9:15, 9:30 - never 9:22).
 3. The duration is unchanged by a horizontal move.
 4. A toast with Undo appears for the move.
-Known issue on the build tested: A 24px horizontal drag - about half an hour at this zoom - moved the shift a full hour instead of the half hour you dragged it. Spec 4.8: "Horizontal drag to move a shift's start time (snaps to 15-minute intervals)." This is already raised with the developers as SV-8856 (https://shopview.atlassian.net/browse/SV-8856). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8, §7). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8856)
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8, §7). Last checked against build v3.5-d122eef on 8/5/2026.
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -4413,7 +4431,7 @@
 3. The resulting times land on 15-minute increments.
 4. The shift's duration on the grid matches the modal's start/end.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4465,9 +4483,8 @@
           <t xml:space="preserve">1. A vertical line marks the current time on the timeline.
 2. Its position matches the actual clock time.
 3. Hovering the now line while your pointer is over the grid shows a label (the current time).
-Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-4873abe on 8/4/2026.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4520,7 +4537,7 @@
 2. It shows the customer name, unit number, the VIN (below unit and asset), and the work order id.
 3. The VIN is visible here even though the grid's VIN toggle is off - the modal always shows it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §9). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §9). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4574,9 +4591,12 @@
 2. Saving/applying the change updates the shift's times.
 3. Changing the date moves the shift to the chosen day.
 4. The grid block reflects the new date/times.
-Known issue on the build tested: the start and end time boxes accept and offer EVERY minute, not quarter-hours - you can set 8:07 if you want to. This is already raised with the developers as SV-8833 (https://shopview.atlassian.net/browse/SV-8833). Until it is fixed this test will fail - mark it FAILED and link SV-8833; do not raise a new ticket. One thing in that ticket is NOT a fault: the little clock icon inside the box is simply how the browser draws a time box, so ignore that part.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-4873abe on 8/4/2026.
+What you should see today: The start and end time boxes accept any minute you like, not quarter hours. Typing 08:07 is accepted and it is still 08:07 after you click away. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8833
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8833)
 </t>
         </is>
@@ -4628,9 +4648,12 @@
           <t xml:space="preserve">1. The assigned technician is shown.
 2. A progress indication compares time logged against the estimate (logged hours vs estimated hours).
 3. The numbers are consistent with the line's actual logged time and estimate.
-Known issue on the build tested: TECHNICIAN shows the avatar and name correctly. TIME LOGGED read "40h 19m / 40h 19m" with a full bar on a shift where nothing had been clocked (the work order reported 0 actual hours), and "1h / 1h" on another. Spec 4.9 asks for "Time logged vs estimate (progress)". That is already raised with the developers as SV-8834 (https://shopview.atlassian.net/browse/SV-8834). Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-4873abe on 8/4/2026.
+What you should see today: The time-logged figure shows as fully complete when nothing has been clocked. A shift created moments earlier, on a line nobody has ever clocked into, reads 'TIME LOGGED 1h / 1h' with a full bar. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8834
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8834)
 </t>
         </is>
@@ -4685,7 +4708,7 @@
 4. This is where whole-order vs subset scope is spelled out (the grid block only says 'N Lines').
 Note for the tester: the absence of any money figure is CORRECT and is what this test expects. The product owner ruled on 22 July 2026 that no total in dollars is shown anywhere on the Schedule. If you see no money figure, pass this test.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §4.4). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §4.4). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4737,10 +4760,9 @@
           <t xml:space="preserve">1. The estimated hours field is editable directly in the modal.
 2. The new value persists after closing and re-opening.
 3. Dependent displays (progress vs estimate) reflect the new value.
-Known issue on the build tested: No inline editor exists on the estimated hours: the scope chip "Single line - 1h" and the per-line hours are plain text with no click target, no edit affordance and no input. Spec 4.9: "Estimated hours with inline edit." This is already raised with the developers as SV-8829 (https://shopview.atlassian.net/browse/SV-8829). Until it is fixed this test will fail - mark it FAILED and link SV-8829; do not raise a new ticket.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8829)
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-d122eef on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4793,8 +4815,8 @@
 3. The delete removes the note.
 4. Notes are kept per work order (the same note is visible from another shift of the same work order).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-d122eef on 8/5/2026.
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -4847,9 +4869,12 @@
 2. It offers an 'Adjust' action.
 3. 'Adjust' leads to a way to resolve the conflict (for example changing the shift's time).
 4. An unconflicted shift's modal shows no such banner.
-Known issue on the build tested: The conflict banner renders - "warning_amber / Scheduling conflict / Not a working day" - but there is NO Adjust action: the modal's only controls are the delete bin, close, the colour selector, Add Note and Open Work Order. Spec 4.9: "A conflict banner with an 'Adjust' action when the shift is conflicted." This is already raised with the developers as SV-8852 (https://shopview.atlassian.net/browse/SV-8852). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-4873abe on 8/4/2026.
+What you should see today: The clash warning appears but gives you no way to fix it. On a shift whose reason is 'Double-booked with ...', 'Extends past working hours' or 'Not a working day' there is no Adjust button - eight clashing shifts were checked and not one offered it. An Adjust button does exist for one other reason ('Starts before working hours'), so do not be surprised to see it there. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8852
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8852)
 </t>
         </is>
@@ -4902,7 +4927,7 @@
 2. There is no 'Reassign' action in the modal; reassignment is done by dragging a shift to another technician row (covered by its own case).
 3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §7). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §7). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4956,7 +4981,7 @@
 3. Saving creates an event block on that technician's day.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5008,10 +5033,9 @@
           <t xml:space="preserve">1. Left-clicking empty day-view space opens the cell menu; choosing 'Create Event' starts creation at the time you clicked.
 2. A live preview block is shown while creating, and dragging resizes it.
 3. Completing creates the event at the previewed time/duration.
-Not built on the build tested: Spec 4.10: "Day view shows a live preview block while creating, with drag-to-resize." It has no developer ticket yet - report it to the QA lead rather than raising one yourself. Mark this test BLOCKED - not failed - because the feature it checks does not exist yet on this build.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: HOLD - the feature is not built yet
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10). Last checked against build v3.5-d122eef on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5066,7 +5090,7 @@
 4. With all-day ON, specific start/end times are not required (the time fields are disabled or hidden).
 5. The event is created as an all-day block for that technician and day.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §8.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §8.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5120,8 +5144,8 @@
 2. Dropping on another day moves it to that day.
 3. Each move produces a toast with Undo.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7). Last checked against build v3.5-d122eef on 8/5/2026.
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -5172,7 +5196,7 @@
 2. It has a small grey-filled rounded chip on the left containing a calendar icon, and two lines of text beside it: the event name, then the time range in secondary text.
 3. The shift reads as a tinted color-filled block with a colored left rail - the two types are separable at a glance, not by color alone.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5226,7 +5250,7 @@
 2. The color picker offers the same custom color palette as shifts (shared picker with editable labels).
 3. Choosing a color tints the card and the icon chip in matching tones, the same way a colored shift is tinted.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §10). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §10). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5280,7 +5304,7 @@
 2. The event does NOT create a double-booked or overlap conflict with the shift, and the toolbar conflict count does not increase because of it.
 3. The two behave differently on purpose: an event uses up capacity, but it is never flagged as a conflict.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §4.11, §4.12). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §4.11, §4.12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5335,7 +5359,7 @@
 3. The toolbar conflict pill's count increases.
 4. The conflict is listed in the pill's dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5388,7 +5412,7 @@
 2. If the technician's working days DO include that day (for example Saturday hours are configured), a shift on that day is NOT flagged.
 3. The warning icon appears on the block and the conflict is listed in the toolbar dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5444,7 +5468,7 @@
 3. Both the start and the end follow the hierarchy technician hours, then shop business hours, then the general default working day of 7:00 AM to 7:00 PM.
 4. Warning icon on the block in each case; the conflict appears in the toolbar dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5499,7 +5523,7 @@
 3. The list covers all current conflicts (count matches the pill).
 4. Resolving a conflict (for example moving the shift) reduces the count - detection is continuous.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §6). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §6). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5551,7 +5575,7 @@
           <t xml:space="preserve">1. The grid navigates to the relevant technician and day.
 2. The conflicted shift is brought into view.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5603,7 +5627,7 @@
           <t xml:space="preserve">1. Overtime is signaled with the 'OT' text tag and amber tones - NOT red or alarming styling.
 2. Red/alarming styling appears only for conflicts and genuine errors.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.12). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5658,7 +5682,7 @@
 2. A more heavily booked day shows a longer blue fill; the fill never exceeds the track (clamped at 100%).
 3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5709,7 +5733,7 @@
           <t xml:space="preserve">1. An amber segment extends past the right edge of the track, showing the excess.
 2. A tick marks the 100% line where the track ends.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5761,7 +5785,7 @@
 2. The tag is text, not a color-only signal.
 3. Overtime (per-technician) and capacity (aggregate) are independent signals.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12, §11). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12, §11). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5814,7 +5838,7 @@
 2. The overtime technician's entry is highlighted in amber.
 3. The numbers agree with the shifts actually on the grid.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5868,8 +5892,8 @@
 3. A time-logged progress bar shows logged vs estimated hours ('X / Yh' style).
 Known issue on the build tested: The tooltip listed ALL FIVE line names on the 5-line series shift with no "+N more lines" row. Spec 4.13: "the individual line names as a short list capped at 3 with a '+N more lines' row". Everything else matched: customer, unit and VIN, date and time range, technician, scope summary "5 lines - 12h" and the progress bar. VIN appears with the toggle off, per Branko 2026-07-31. It has been reported to the QA lead but has no developer ticket yet. Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (no ticket - accepted, see the decisions register)
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5918,9 +5942,13 @@
         <is>
           <t xml:space="preserve">1. The customer name line includes the conflict icon.
 2. The conflict reason is shown in amber.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+What you should see today: The clash warning is at the bottom of the hover tooltip instead of next to the customer name. The first row is just the customer name with no warning mark; the warning only appears in the last row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8959
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8959)
 </t>
         </is>
       </c>
@@ -5970,9 +5998,13 @@
           <t xml:space="preserve">1. The tooltip shows the event name with its category dot (grey for a default event).
 2. The date and time range are shown.
 3. The technician is shown.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+What you should see today: The event's hover tooltip has no grey dot next to the event name. It shows the name, the date and time range and the technician, and no dot at all. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8893
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8893)
 </t>
         </is>
       </c>
@@ -6027,7 +6059,7 @@
 3. The tooltip is read-only (no buttons/actions inside it).
 4. Clicking the block opens the full detail modal as normal.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6080,7 +6112,7 @@
 2. Near a side edge, the tooltip shifts horizontally to stay fully within the viewport.
 3. No part of the tooltip is clipped off-screen.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6131,7 +6163,7 @@
           <t xml:space="preserve">1. The grid jumps to the range containing the current date (today's day, this week, or this month depending on the active view).
 2. The date label updates accordingly.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6185,7 +6217,7 @@
 3. Month view: each click moves one month; the label shows that month.
 4. The label always matches what the grid displays.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6239,9 +6271,12 @@
 2. All five fields match: customer name, work order number, unit number, technician name, and line name.
 3. Matching blocks stay in place on the grid (search visually filters; it does not remove or rearrange).
 4. Clearing the search restores all blocks to normal.
-Known issue on the build tested: Typing "Pamill" in the toolbar search left only the 6 matching blocks in the grid, each gaining schedule-block--match; the non-matching blocks were REMOVED from the page, not faded. Spec 6: "Non-matching blocks fade; matching blocks highlight." Also worth knowing: the toolbar search field carries the placeholder "Search work orders..." - the same words as the sidebar search - which is easy to confuse. That is already raised with the developers as SV-8874 (https://shopview.atlassian.net/browse/SV-8874). Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). Last checked against build v3.5-4873abe on 8/4/2026.
+What you should see today: Searching in the grid removes the shifts that do not match instead of fading them. The non-matching blocks disappear from the grid entirely rather than staying visible and dimmed. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8874
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8874)
 </t>
         </is>
@@ -6293,7 +6328,7 @@
 2. Defaults: all department toggles ON, 'My Shifts' OFF, 'VIN' OFF.
 3. There is no separate departments-only control - this dropdown replaces it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6, §9). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6, §9). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6347,7 +6382,7 @@
 2. Other departments are unaffected.
 3. Turning it back on restores the group.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6402,8 +6437,8 @@
 3. This is a personal convenience filter only - it does not change what you are permitted to see (default is OFF, everyone's shifts visible).
 4. For a user who has no technician/staff record of their own, the 'My Shifts' option is not shown at all.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §14.3). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a user with no staff record of their own
 </t>
         </is>
       </c>
@@ -6459,9 +6494,13 @@
 4. In day view with the VIN on, the lane height grows to fit the extra VIN line and no block text is clipped or cut off.
 5. The 'VIN Number' toggle affects the block only - the tooltip and the modal always show the VIN when the unit has one.
 Note for the tester: the VIN staying visible in the hover summary and in the shift window while the VIN switch is off is CORRECT and is what this test expects. The product owner ruled on 31 July 2026 that the VIN is always visible on hover regardless of the switch. If you see it there, pass this test.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §4.4, §4.8). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+What you should see today: Month view prints the VIN on shift blocks when the VIN switch is on. It should be left off in Month view because the blocks are small. Day and Week views are correct. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8941
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §4.4, §4.8). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8941)
 </t>
         </is>
       </c>
@@ -6515,9 +6554,12 @@
 2. Defaults: Business Hours OFF, Capacity Bars ON, Events ON, Tech Hours OFF, Saturday ON, Sunday ON.
 3. Capacity Bars OFF: the capacity bars disappear from the column headers; ON: they reappear with the same values.
 4. Events OFF: event blocks disappear from the grid while shifts remain; ON: the events reappear unchanged.
-Known issue on the build tested: Observed defaults: Business Hours ON, Tech Hours OFF, Capacity Planning ON, Events ON, Show Saturday ON, Show Sunday ON. The spec 9 table requires Business Hours OFF. The other five match. The Business Hours half of this is already raised with the developers as SV-8827 (https://shopview.atlassian.net/browse/SV-8827); that same ticket also says Tech Hours starts ON, which it does not on this build. Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6, §9, §4.12). Last checked against build v3.5-4873abe on 8/4/2026.
+What you should see today: Business Hours starts switched ON in View Options when it should start switched off. The other five options in that menu do start in the right position. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8827
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6, §9, §4.12). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8827)
 </t>
         </is>
@@ -6571,7 +6613,7 @@
 2. Working hours remain unshaded.
 3. Turning it off removes the shading.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §4.8). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §4.8). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6623,9 +6665,12 @@
           <t xml:space="preserve">1. Each technician's working hours are displayed next to their name in the row header.
 2. The hours match the technicians' configured hours.
 3. Turning it off hides the hours again.
-Known issue on the build tested: Toggling Tech Hours produced no observable change at all: the technician rows still show only initials, name and job title, and the shaded-cell count was identical before, during and after (2 / 2 / 2) - including for Ayesha Khan, the one technician who has custom hours. Spec 9: "Tech Hours | Off | Displays each technician's working hours next to their name." This is already raised with the developers as SV-8851 (https://shopview.atlassian.net/browse/SV-8851). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9). Last checked against build v3.5-4873abe on 8/4/2026.
+What you should see today: Turning on Tech Hours in View Options changes nothing you can see. None of the technician rows shows its working hours, on any day. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8851
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8851)
 </t>
         </is>
@@ -6678,7 +6723,7 @@
 2. Sunday off too: 5 weekday columns remain (Monday to Friday).
 3. Both back on: the full Monday-to-Sunday 7-column week returns.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §3.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §3.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6733,7 +6778,7 @@
 3. Technician B is added to the affected line's roster and technician A is removed from it.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §12). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §12). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6788,7 +6833,7 @@
 4. There is no 'New Shift' item - it was removed from the menu.
 5. This menu is opened by a normal left-click - right-clicking the cell does not open it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §14.1). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6839,7 +6884,7 @@
           <t xml:space="preserve">1. The menu offers a 'New Work Order' item.
 2. Choosing it directs the user to create a work order (a toast / prompt pointing to the Work Orders tab).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §4.10). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6895,10 +6940,13 @@
           <t xml:space="preserve">1. The block lifts and follows the mouse as you drag it.
 2. When you release it on the other technician's row, a small window asks you to confirm the move to that technician - the same confirmation you get when you move an ordinary shift.
 3. After you confirm, the block sits in the new technician's row, that technician is added to the work order line's technician list, and the previous one is taken off it.
-Known issue on the build checked: the block does lift and move while you drag it, but on release it jumps straight back to the technician it started on - no confirmation window and no toast. An ordinary shift that is not part of a series, dragged between the same two technician rows, does ask for confirmation ("Move this shift to MQ Test Tech Qamar?"), so the problem is specific to series blocks. This is already raised with the developers as SV-8867 (https://shopview.atlassian.net/browse/SV-8867). Until it is fixed this test will fail - mark it FAILED and link SV-8867; do not raise a new ticket.
 Why this test covers Week view only: the specification describes reassignment as dragging a shift from one technician row to another, and Month view has no technician rows at all - it is a calendar of day boxes. Whether reassignment should be possible in Month view is therefore part of the open question on SV-8867 and is deliberately not asserted here.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §12): dragging a shift block from one technician row to another reassigns it and a confirmation handles cross-technician moves, and a series is a grouping over ordinary daily shifts rather than a different kind of thing, so an ordinary shift's behaviour applies to a series member too. Story SV-8692 covers series-aware deletion only and says nothing about reassignment. Last checked against build v3.5-d122eef on 8/5/2026.
+What you should see today: A shift that is part of a repeating series cannot be moved to another technician in Week or Month view - the block lifts, moves, and then springs back to where it was. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8867
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §12): dragging a shift block from one technician row to another reassigns it and a confirmation handles cross-technician moves, and a series is a grouping over ordinary daily shifts rather than a different kind of thing, so an ordinary shift's behaviour applies to a series member too. Story SV-8692 covers series-aware deletion only and says nothing about reassignment. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8867)
 </t>
         </is>
@@ -6951,7 +6999,7 @@
 2. Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').
 3. The prompt uses routine, lightweight styling - not alarming destructive styling.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7006,7 +7054,7 @@
 3. The removed day's hours return to the estimate's remaining (scheduled hours drop by that day's hours).
 4. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7059,7 +7107,7 @@
 2. The first two shifts remain untouched.
 3. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7112,7 +7160,7 @@
 2. Technician B's independent series is untouched (the scope is per technician's series).
 3. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7167,7 +7215,7 @@
 3. Middle shift: all three options.
 4. Cancelling leaves the series unchanged in every case.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7219,7 +7267,7 @@
           <t xml:space="preserve">1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
 2. The shift is deleted and an undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7272,7 +7320,7 @@
 2. While the cursor is over it, the toast stays (does not auto-dismiss).
 3. After the cursor leaves, it dismisses.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7330,7 +7378,7 @@
 4. Undo after reassign: the shift returns to the original technician, and the line's roster is restored (original tech back on, target tech off).
 5. Every destructive action is undoable within the toast's lifetime.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7386,7 +7434,7 @@
 3. Clicking Undo within the toast's lifetime reverses the action (the deleted shift comes back).
 4. Note for the tester: Undo works by performing a reversing action, not by holding the change back - a change surviving a refresh before Undo is expected, not a bug.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7441,10 +7489,9 @@
 3. Escape with no open sub-picker closes the modal itself.
 4. With two layers open, the FIRST Escape closes only the topmost layer, and the SECOND Escape closes the next layer down.
 5. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).
-Known issue on the build tested: Escape closes the shift detail modal and both toolbar popovers, but does NOT close the "Delete from this series?" dialog (tried twice, once with focus moved inside it) and does NOT close the "Reassign shift" dialog. Spec 7 names both first in its stacking order: "Escape closes the topmost open modal or popover, following a defined stacking order (delete scope, reassign, spread, ...)". This is already raised with the developers as SV-8853 (https://shopview.atlassian.net/browse/SV-8853). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8853)
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7499,10 +7546,9 @@
 2. The confirmed action takes effect (spread created / reassigned / event saved / delete applied).
 3. In the note editor, Enter inserts a new line in the note - it does NOT confirm or close the dialog.
 4. The multiline note can be completed and saved normally.
-Known issue on the build tested: Enter on the open "Reassign shift" dialog did nothing - the dialog stayed open and no toast appeared. Spec 7: "Enter confirms the active confirmable dialog (delete scope, reassign, spread, event create/edit)." The "not inside a textarea" half cannot be reached while Enter confirms nothing. This is already raised with the developers as SV-8853 (https://shopview.atlassian.net/browse/SV-8853). Mark this test FAILED and put the ticket number in your run comment; do not raise a new ticket for it.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8853)
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7554,7 +7600,7 @@
 2. Focus stays trapped inside the modal (wraps back to its first control) until the modal closes.
 3. On the page, toolbar and sidebar controls are reachable by keyboard.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7606,7 +7652,7 @@
           <t xml:space="preserve">1. Both the single shift and the multi-week series render in the default blue.
 2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7662,7 +7708,7 @@
 3. The color is per SHIFT, not per work order - the other shift from the same work order keeps its own (default blue) color and does not change.
 4. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10, §4.9, §4.4). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10, §4.9, §4.4). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7716,7 +7762,7 @@
 2. The renamed label shows for the whole shop - the same picker opened elsewhere shows 'ZZAUTOTEST Rush'.
 3. Shifts and events share the same custom palette with the same labels.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10, §4.10). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10, §4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7773,7 +7819,7 @@
 4. Each day has a From time and a To time you can set.
 5. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7826,7 +7872,7 @@
 2. The toggle is OFF by default (no custom hours set).
 3. Turning it ON reveals a per-day working-hours editor for that technician.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7877,7 +7923,7 @@
           <t xml:space="preserve">1. With no custom hours, the technician's working hours fall back to the shop business hours.
 2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7929,7 +7975,7 @@
 2. The added range starts empty (no From/To pre-filled).
 3. Each added range can be removed individually.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7984,7 +8030,7 @@
 4. The incomplete row (empty From/To) is ignored by the overlap check - it does not raise the overlap error.
 5. Save is not blocked by an incomplete row on its own (only genuine overlaps disable Save).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8040,8 +8086,8 @@
 3. ALL technicians' shifts and events are visible (not just the user's own).
 4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1, §14.3). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1, §14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a view-only user
 </t>
         </is>
       </c>
@@ -8096,8 +8142,8 @@
 3. No creation menu opens at all - there is no 'Create Event' and no 'New Work Order' offered.
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a view-only user
 </t>
         </is>
       </c>
@@ -8147,8 +8193,8 @@
           <t xml:space="preserve">1. The Schedule top-level nav item is not shown at all.
 2. The rest of the app works normally for the role.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a user without the Schedule permission
 </t>
         </is>
       </c>
@@ -8204,8 +8250,8 @@
 4. Edge-resize and horizontal drag work in day view.
 5. Modal fields are editable and save.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as an edit-without-delete user
 </t>
         </is>
       </c>
@@ -8258,8 +8304,8 @@
 2. Events likewise offer no delete.
 3. No path exists to remove shifts or events - while creating and modifying still work.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as an edit-without-delete user
 </t>
         </is>
       </c>
@@ -8313,8 +8359,8 @@
 3. Events can be deleted too.
 4. Undo toasts appear (restore the items via Undo to clean up).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a delete-capable user
 </t>
         </is>
       </c>
@@ -8366,7 +8412,7 @@
 2. Delete cannot be granted without Edit.
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8419,10 +8465,9 @@
           <t xml:space="preserve">1. The sidebar hides the work order list and the line drill-down; the mini calendar remains available.
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
 3. New work orders cannot be dragged on - the WO list is simply not visible.
-Known issue on the build tested: a user who has the Schedule but has NOT been given Work Orders: View still sees the whole work order list in the left-hand panel - 18 cards showing the customer name, the unit number, how many lines the job has, the hours estimate and the lead technician. It should be hidden for them. This is already raised with the developers as SV-8854 (https://shopview.atlassian.net/browse/SV-8854). Until it is fixed this test will fail - mark it FAILED and link SV-8854; do not raise a new ticket.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.2). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8854)
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
       </c>
@@ -8473,8 +8518,8 @@
           <t xml:space="preserve">1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.3). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a view-only technician
 </t>
         </is>
       </c>
@@ -8525,7 +8570,7 @@
           <t xml:space="preserve">1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
 2. The staff member without a department does not appear as a row.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.4). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.4). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8576,8 +8621,8 @@
           <t xml:space="preserve">1. The Time-Clock-ON staff member can clock in.
 2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.4). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.4). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as each of the two staff members
 </t>
         </is>
       </c>
@@ -8630,8 +8675,8 @@
 2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
 3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.2). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.2). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
       </c>
@@ -8688,8 +8733,8 @@
 3. The user from step 4 gets the read-only schedule - nothing can be dragged onto the grid and no shift can be created.
 4. The user from step 5 can drag a work order onto the grid and create a shift.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a holder of each permission level
 </t>
         </is>
       </c>
@@ -8741,10 +8786,13 @@
 2. All days remain reachable by horizontal scroll.
 3. On narrow viewports the sidebar collapses.
 4. No content becomes permanently unreachable and nothing errors.
-Known issue on the build tested: At a 900px viewport the sidebar stays 288px wide and the whole page scrolls sideways (documentElement.scrollWidth 1041) rather than only the grid. Spec 11: "Minimum supported width is 960px (the grid scrolls horizontally below that), and the sidebar collapses on narrow viewports." 900px is below the supported minimum, so this is a low-severity observation, not a release blocker. It has been reported to the QA lead but has no developer ticket yet. Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (no ticket - accepted, see the decisions register)
+What you should see today: The whole page slides sideways instead of just the grid, and the panel on the left never folds away. At 960 pixels wide - which is the narrowest width the Schedule is meant to support - the page is still 1030 pixels wide and the panel is still its full width. Narrowing further changes neither. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8942
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8942)
 </t>
         </is>
       </c>
@@ -8796,9 +8844,13 @@
           <t xml:space="preserve">1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
 3. Search stays responsive on the long list.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+What you should see today: The list of work orders on the left does not scroll continuously. It shows 18 cards with a 'Load More' button at the bottom, even though 91 work orders exist. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8913
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8913)
 </t>
         </is>
       </c>
@@ -8851,7 +8903,7 @@
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8904,10 +8956,9 @@
           <t xml:space="preserve">1. The closure day is NOT struck through or skipped by the spread in V1.
 2. A shift CAN be placed on the shop closure day (only weekend days with no business hours are skipped).
 3. The end date follows the normal daily distribution - no extra day is added for the closure.
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The specification says this two different ways and no ruling exists yet, so mark this test BLOCKED - not failed - and leave it out of the automation suite. The open question and its evidence are recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§12, §4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§12, §4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - waiting on the product owner's answer, and the shop-closure setting does not exist in the build
 </t>
         </is>
       </c>
@@ -8957,7 +9008,7 @@
           <t xml:space="preserve">1. All three quantities are shown/derivable and may differ from one another.
 2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9008,10 +9059,13 @@
         <is>
           <t xml:space="preserve">1. Every shift in the series starts at the SAME local wall-clock time (e.g. 8:00 AM) on both sides of the clock change.
 2. No shift in the series silently moves an hour earlier or later after the change date.
-This test cannot be run on the build tested: the next Mountain-time clock change is 2026-11-01, outside any window the QA data covers, and the seeded clock cannot be moved on this estate. Worse, the finding is currently untestable in principle because every Schedule time renders in UTC (see the new time ticket) - so a clock-change test would measure the bug, not the requirement. Re-run once the timezone fix ships. Mark it BLOCKED - not failed - and say which of these you could not set up.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: HOLD - needs a real daylight-saving clock change, the next one is 1 November 2026
+What you should see today: The start times on either side of the clock change do not read the same. The same job reads 12 PM before 1 November and 1 PM after it. The times are stored correctly underneath - it is the times shown on screen that are wrong, and every Schedule time is shown six hours late for the same reason. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8848
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8848)
 </t>
         </is>
       </c>
@@ -9065,7 +9119,7 @@
 3. Conflict and overtime cues remain distinguishable (they never rely on colour alone - text/icon still present).
 4. Switching back to light mode restores the normal look with nothing stuck in dark colours.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9118,8 +9172,8 @@
 2. Events are still events and shifts are still shifts (nothing changed kind or vanished).
 3. Their details open normally and are editable/deletable like any other entry.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - cannot be run now - it needs shifts noted BEFORE the release, and the release is already deployed
 </t>
         </is>
       </c>
@@ -9171,8 +9225,8 @@
 2. Note for the tester: before this release the Dashboard duplicated such a work order once per scheduled day - showing one combined row now is the intended fix, do not report it as a missing-rows bug.
 3. Work orders with a single shift are unaffected.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - the Dashboard section this test needs does not exist in the build
 </t>
         </is>
       </c>
@@ -9224,8 +9278,8 @@
 2. It behaves like any other scheduled entry (opens, moves, deletes normally).
 3. It also appears in the Dashboard's schedule section for that day.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - work order creation offers no appointment in the build
 </t>
         </is>
       </c>
@@ -9278,7 +9332,7 @@
 2. The shift does NOT appear on location B's board, even though the technician is enrolled there too.
 3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9333,8 +9387,8 @@
 3. After saving, the Schedule sidebar reflects the chosen priority and the Priority filter finds the work order under High.
 4. A work order with no priority set simply shows none (it is not treated as an error).
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - the Priority field this test needs does not exist in the build
 </t>
         </is>
       </c>
@@ -9388,8 +9442,8 @@
 3. View + Edit: the POST and PATCH succeed (HTTP 201/200); the DELETE is refused with HTTP 403 because the user lacks Schedule: Delete.
 4. Each refusal is a clean 403 response - never a server error.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs three separate sign-ins, one per permission level
 </t>
         </is>
       </c>
@@ -9442,10 +9496,9 @@
 2. With acknowledgeLongSeries=true the same request succeeds (HTTP 201) and returns the full materialized series under one series id.
 3. The over-120-shift request is refused with HTTP 422 even WITH the acknowledgement - the hard cap cannot be overridden.
 4. Refused calls leave no partial series behind.
-Not built on the build tested: No 409 and no 422 exists on this build. The 8-week / 120-shift caps are engineering-tech-plan text with no Schedule-specification requirement behind them. It has no developer ticket yet - report it to the QA lead rather than raising one yourself. Mark this test BLOCKED - not failed - because the feature it checks does not exist yet on this build.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: HOLD - the feature is not built yet
+---
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9497,8 +9550,8 @@
 2. For the caller without Work Orders: View, the work-order-derived details (customer, unit, VIN, line names) are absent/empty in the response itself - not just hidden on screen.
 3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-4873abe on 8/4/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
       </c>
@@ -9551,7 +9604,7 @@
 2. The PATCH on the foreign id is refused the same way (404) - no cross-location edit is possible.
 3. Location A's board contains only location A's shifts - nothing from location B leaks in.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-4873abe on 8/4/2026.
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
 3. The left panel is the work order sidebar: a mini calendar at the top and a work order list beneath it.
 4. The main area is the schedule grid showing technician rows, with a toolbar above it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3, §3.1, §3.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3, §3.1, §3.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -564,16 +564,18 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. You are on the Schedule page.
-3. At least one shift exists on the current week (create one first if needed, or have a colleague with Edit permission create it).</t>
+3. At least one shift exists on the current week (create one first if needed, or have a colleague with Edit permission create it).
+</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. In the grid toolbar, click Day on the Day / Week / Month segmented control.
+          <t xml:space="preserve">1. In the grid toolbar, click Day on the Day / Week / Month segmented control.
 2. Click Week.
-3. Click Month.</t>
+3. Click Month.
+</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -587,7 +589,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §6). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2, §6). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8826)
 </t>
         </is>
@@ -640,7 +642,7 @@
 2. Each department's technicians are listed beneath that department's header.
 3. Every staff member assigned to a visible department appears as a row, regardless of their role.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §14.4). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2, §14.4). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -676,14 +678,16 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
-2. You are on the Schedule page with at least one department group visible containing technicians.</t>
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
+2. You are on the Schedule page with at least one department group visible containing technicians.
+</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Click a department group header to collapse it.
-2. Click the same header again to expand it.</t>
+          <t xml:space="preserve">1. Click a department group header to collapse it.
+2. Click the same header again to expand it.
+</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -692,7 +696,7 @@
 2. Expanding shows the technician rows again, unchanged.
 3. Other department groups are unaffected.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -742,7 +746,7 @@
           <t xml:space="preserve">1. No such toggle exists - the department-grouped rows are the only grid grouping.
 2. Department visibility is controlled only through the department toggles in the 'Filter and Display' dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -795,7 +799,7 @@
 2. Shifts without a technician sit in this row.
 3. The unassigned shift uses the same block layout as regular shifts (customer, unit, line name / line count) - it simply has no technician.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2, §4.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -853,7 +857,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the acceptance criterion of its story SV-8686, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 23 does not say which view the page opens on, so this expectation comes from the story rather than the specification. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the acceptance criterion of its story SV-8686, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 27 does not say which view the page opens on, so this expectation comes from the story rather than the specification. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8863)
 </t>
         </is>
@@ -905,7 +909,7 @@
 2. The toolbar date label updates to the new range.
 3. The clicked date is highlighted as the selected date in the mini calendar.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1, §5.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -941,15 +945,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
-2. You are on the Schedule page with the mini calendar visible.</t>
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
+2. You are on the Schedule page with the mini calendar visible.
+</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. Open the mini calendar's month/year picker.
+          <t xml:space="preserve">1. Open the mini calendar's month/year picker.
 2. Use the year arrows to move to another year.
-3. Pick a different month from the grid of month buttons.</t>
+3. Pick a different month from the grid of month buttons.
+</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -958,7 +964,7 @@
 2. Choosing a month shows that month in the mini calendar.
 3. The main grid can then be navigated by clicking a date in the newly shown month.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -994,15 +1000,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
-2. You are on the Schedule page with the mini calendar expanded.</t>
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
+2. You are on the Schedule page with the mini calendar expanded.
+</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Click the chevron toggle on the mini calendar.
+          <t xml:space="preserve">1. Click the chevron toggle on the mini calendar.
 2. Look at the sidebar.
-3. Click the chevron again.</t>
+3. Click the chevron again.
+</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1010,7 +1018,7 @@
           <t xml:space="preserve">1. The calendar grid collapses (hides), leaving more room for the work order list below.
 2. Clicking again expands the calendar grid back.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1, §5.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1046,15 +1054,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. You are on the Schedule page with the mini calendar visible.
-3. The grid is on a date other than today (click a different date first).</t>
+3. The grid is on a date other than today (click a different date first).
+</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the mini calendar and find today's date and the selected date.
-2. Move the mouse over different week rows of the mini calendar.</t>
+          <t xml:space="preserve">1. Look at the mini calendar and find today's date and the selected date.
+2. Move the mouse over different week rows of the mini calendar.
+</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1063,7 +1073,7 @@
 2. Today's date has its own distinct indicator, different from the selection.
 3. Hovering a week row highlights that whole week row.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1117,7 +1127,7 @@
 2. The list scrolls when there are more cards than fit.
 3. There are no Assigned/Unassigned tabs - assignment is available only as a filter behind the 'Filter' button.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1, §5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1153,15 +1163,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. A work order exists with a customer, a unit, at least one approved line with estimated hours, and a lead technician assigned.
-3. You are on the Schedule page with the work order list visible.</t>
+3. You are on the Schedule page with the work order list visible.
+</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1. Find that work order's card in the sidebar list.
-2. Read the card from top to bottom.</t>
+          <t xml:space="preserve">1. Find that work order's card in the sidebar list.
+2. Read the card from top to bottom.
+</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1172,7 +1184,7 @@
 4. A lead technician row with the technician's avatar and name.
 5. A colored left border whose color reflects the work order's status.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1208,17 +1220,19 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. Work orders exist with different work order numbers and with distinct customer names, unit numbers, and lead technicians.
-3. You are on the Schedule page with the work order list visible.</t>
+3. You are on the Schedule page with the work order list visible.
+</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1. Click the 'Search work orders' field at the top of the list and type the number of one specific work order; note the results, then clear.
+          <t xml:space="preserve">1. Click the 'Search work orders' field at the top of the list and type the number of one specific work order; note the results, then clear.
 2. Type part of a customer name; note the results, then clear.
 3. Type a unit number; note the results, then clear.
-4. Type a technician's name; note the results.</t>
+4. Type a technician's name; note the results.
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1233,7 +1247,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8873)
 </t>
         </is>
@@ -1269,15 +1283,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. Several work orders exist.
-3. You are on the Schedule page with the work order list visible.</t>
+3. You are on the Schedule page with the work order list visible.
+</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Type a search term into 'Search work orders' one character at a time.
-2. Watch the list while typing (do not press Enter).</t>
+          <t xml:space="preserve">1. Type a search term into 'Search work orders' one character at a time.
+2. Watch the list while typing (do not press Enter).
+</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1286,7 +1302,7 @@
 2. Deleting characters widens the results again.
 3. With very many work orders, the list may load further results in pages as you scroll - that is expected, not a fault.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1322,15 +1338,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
-2. You are on the Schedule page with the work order list visible.</t>
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
+2. You are on the Schedule page with the work order list visible.
+</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. In 'Search work orders', type a nonsense string that matches nothing (for example 'zzzxq999').
+          <t xml:space="preserve">1. In 'Search work orders', type a nonsense string that matches nothing (for example 'zzzxq999').
 2. Look at the list.
-3. Clear the search.</t>
+3. Clear the search.
+</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1339,7 +1357,7 @@
 2. The app does not error; the sidebar remains usable.
 3. Clearing the search restores the full list.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1393,7 +1411,7 @@
 2. Applying a filter narrows the flat card list.
 3. The 'Filters' button shows a badge with the number of active filters.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1429,16 +1447,18 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. At least one work order has a technician assigned and at least one has none.
-3. You are on the Schedule page with the work order list visible.</t>
+3. You are on the Schedule page with the work order list visible.
+</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Open the 'Filter' panel and choose Unassigned under Assignment.
+          <t xml:space="preserve">1. Open the 'Filter' panel and choose Unassigned under Assignment.
 2. Read the list.
-3. Switch to Assigned and read the list again.</t>
+3. Switch to Assigned and read the list again.
+</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1447,7 +1467,7 @@
 2. Assigned: only work orders with a technician assigned remain.
 3. There are no Assigned/Unassigned tabs - this filter is the only assignment split.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1, §3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1, §3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1483,16 +1503,18 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. Work orders exist in at least two different statuses.
-3. You are on the Schedule page with the work order list visible.</t>
+3. You are on the Schedule page with the work order list visible.
+</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Open the 'Filter' panel.
+          <t xml:space="preserve">1. Open the 'Filter' panel.
 2. Choose one status under Status.
-3. Read the list.</t>
+3. Read the list.
+</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1503,7 +1525,7 @@
 4. The card left-border colours of the remaining cards are consistent with that status.
 Note for the tester: this shop's schedule list only holds work orders in two statuses, Approved and Review, so most of the other choices correctly come back empty. An empty list for a status no work order is in is the right answer, not a fault.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1539,16 +1561,18 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. Work orders exist with different priorities (High and Low at minimum).
-3. You are on the Schedule page with the work order list visible.</t>
+3. You are on the Schedule page with the work order list visible.
+</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Open the 'Filter' panel.
+          <t xml:space="preserve">1. Open the 'Filter' panel.
 2. Choose High under Priority.
-3. Read the list.</t>
+3. Read the list.
+</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1556,7 +1580,7 @@
           <t xml:space="preserve">1. The Priority group offers High, Medium, and Low.
 2. Only High-priority work orders remain in the list.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1592,14 +1616,16 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
-2. You are on the Schedule page and have applied at least two filters (for example an Assignment and a Priority filter).</t>
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
+2. You are on the Schedule page and have applied at least two filters (for example an Assignment and a Priority filter).
+</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Clear all'.
-2. Look at the list and the 'Filter' button.</t>
+          <t xml:space="preserve">1. Click 'Clear all'.
+2. Look at the list and the 'Filter' button.
+</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1608,7 +1634,7 @@
 2. The full work order list is shown again.
 3. The active-count badge on the 'Filter' button disappears (or shows zero).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1644,16 +1670,18 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. Several work orders exist for the same customer in different statuses.
-3. You are on the Schedule page with the work order list visible.</t>
+3. You are on the Schedule page with the work order list visible.
+</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1. Type a customer name into 'Search work orders'.
+          <t xml:space="preserve">1. Type a customer name into 'Search work orders'.
 2. With the search still applied, open 'Filter' and choose one status.
-3. Read the list.</t>
+3. Read the list.
+</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1661,7 +1689,7 @@
           <t xml:space="preserve">1. The list shows only work orders that match BOTH the text search and the structured filter.
 2. Removing either the search text or the filter widens the list to the remaining condition.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1718,7 +1746,7 @@
 4. A back control is shown to return to the card list.
 5. Clicking back restores the work order card list.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1754,15 +1782,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. A ZZAUTOTEST work order exists with at least one APPROVED line and at least one UNAPPROVED line (create/adjust it first).
-3. You are on the Schedule page.</t>
+3. You are on the Schedule page.
+</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Open that work order's drill-down in the sidebar.
-2. Compare the lines listed against the work order's actual lines.</t>
+          <t xml:space="preserve">1. Open that work order's drill-down in the sidebar.
+2. Compare the lines listed against the work order's actual lines.
+</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1771,7 +1801,7 @@
 2. No line that has never been approved appears anywhere in the schedule sidebar - for example a line still sitting on an estimate, or one that was declined.
 3. The line count in the drill-down header matches the number of APPROVED lines on the work order - a line that was never approved is neither listed nor counted.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1807,15 +1837,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+          <t xml:space="preserve">1. You are signed in on a desktop browser with Schedule: Edit.
 2. A work order exists whose approved lines have estimated hours; at least one line has several technicians on its roster.
-3. You are on the Schedule page with the drill-down open.</t>
+3. You are on the Schedule page with the drill-down open.
+</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Read one line row.
-2. Look at a line with multiple technicians on it.</t>
+          <t xml:space="preserve">1. Read one line row.
+2. Look at a line with multiple technicians on it.
+</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1824,7 +1856,7 @@
 2. The current technician roster is shown as an avatar stack plus a count; there is no cap on how many technicians a line can have.
 3. Each line row has its own drag handle, so it can be dragged independently onto the grid.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §8.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1, §8.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1860,15 +1892,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. A work order exists with an approved line that has NO technician on its roster and another approved line that has at least one.
-3. You are on the Schedule page with the drill-down open.</t>
+3. You are on the Schedule page with the drill-down open.
+</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the line with no technician.
-2. Look at the line that has a technician.</t>
+          <t xml:space="preserve">1. Look at the line with no technician.
+2. Look at the line that has a technician.
+</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1877,7 +1911,7 @@
 2. The line with a technician does not show the badge.
 3. After a technician is scheduled onto the badge-bearing line, the badge goes away.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1913,16 +1947,18 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. A work order exists with several approved lines with distinct titles.
-3. You are on the Schedule page with the drill-down open.</t>
+3. You are on the Schedule page with the drill-down open.
+</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. In the drill-down's line search box, type part of one line's title.
+          <t xml:space="preserve">1. In the drill-down's line search box, type part of one line's title.
 2. Read the results.
-3. Clear it and type the customer's name instead.</t>
+3. Clear it and type the customer's name instead.
+</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1930,7 +1966,7 @@
           <t xml:space="preserve">1. Typing a line title narrows the list to matching lines.
 2. Typing the customer name returns no results - the line search matches line titles only (the list is already scoped to one work order, so customer/unit/WO fields are not searched).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1966,16 +2002,18 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser.
+          <t xml:space="preserve">1. You are signed in on a desktop browser.
 2. A work order exists where at least one approved line already has a shift on the grid and at least one approved line has none.
-3. You are on the Schedule page with the drill-down open.</t>
+3. You are on the Schedule page with the drill-down open.
+</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1. Read the two filter chips and their counts.
+          <t xml:space="preserve">1. Read the two filter chips and their counts.
 2. Click the Unscheduled chip.
-3. Click the All chip.</t>
+3. Click the All chip.
+</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1984,7 +2022,7 @@
 2. Unscheduled lists only the lines that have no shifts yet, and its count matches.
 3. All lists every approved line, and its count matches the drill-down header's line count.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.1, §5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1, §5.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2038,7 +2076,7 @@
 3. The technician is added to that line's labor roster on the work order.
 4. A toast with an Undo option appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §1.2, §7). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1, §1.2, §7). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2091,7 +2129,7 @@
 2. It offers 'Schedule whole work order' at the top, the individual line rows beneath, and a 'Select multiple' control.
 3. No shift is created until a scope is chosen.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.3). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1, §4.3). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2145,7 +2183,7 @@
 2. The block's last text line shows that line's name.
 3. The technician is added to that line's roster only (not to the order's other lines).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2199,7 +2237,7 @@
 2. Its header shows the chosen scope and a 'Change scope' back-link.
 3. No shifts exist yet until the spread is confirmed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1, §4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2251,7 +2289,7 @@
           <t xml:space="preserve">1. The shift is created straight away - the spread step does NOT appear.
 2. The shift sits on the dropped day only.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2308,7 +2346,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8840)
 </t>
         </is>
@@ -2365,14 +2403,14 @@
 4. Dragging the same line onto a second technician adds that technician to the line's roster as well - the technician who was already there stays on it.
 5. Nothing asks you to swap or replace the technician who was already there, and no limit is reached on how many technicians a line can have.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§1.2, §4.3, §7). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§1.2, §4.3, §7). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8688 (§1.2 Goals - roster sync · §4.3 roster add + no swap flow · §7; spec v23 2026-07-30)</t>
+          <t>SV-8688 (§1.2 Goals - roster sync · §4.3 roster add + no swap flow · §7; spec v27 2026-08-07)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2421,7 +2459,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8957)
 </t>
         </is>
@@ -2477,10 +2515,10 @@
           <t xml:space="preserve">1. While the card is held over a day box, that day box shows it is a drop target.
 2. Releasing on the day box books the work order onto that day, exactly as dropping it does in Week view: because this work order has more than one line, the scope picker opens so you can choose the whole order, one line, or several lines.
 3. After you confirm a scope, a shift appears in that day box, and its start time comes from the usual order of preference - the technician's own working hours first, otherwise the shop's business hours, otherwise 7:00 AM.
-Please read before running this test: what should happen in MONTH view specifically has not been settled yet. The Schedule specification version 23 says that a work order is dragged from the sidebar onto a cell in the grid without naming which view, and the acceptance criterion of story SV-8688 names only Week view. The question has been put to the product owner on SV-8870 (https://shopview.atlassian.net/browse/SV-8870), together with the point that Month view invites the user to drag ("Nothing is scheduled in this range. Drag a work order from the list to book it."). Until the product owner answers, treat a failure here as already reported under SV-8870 - mark it FAILED and link SV-8870; do not raise a new ticket.
+Please read before running this test: what should happen in MONTH view specifically has not been settled yet. The Schedule specification version 27 says that a work order is dragged from the sidebar onto a cell in the grid without naming which view, and the acceptance criterion of story SV-8688 names only Week view. The question has been put to the product owner on SV-8870 (https://shopview.atlassian.net/browse/SV-8870), together with the point that Month view invites the user to drag ("Nothing is scheduled in this range. Drag a work order from the list to book it."). Until the product owner answers, treat a failure here as already reported under SV-8870 - mark it FAILED and link SV-8870; do not raise a new ticket.
 What was seen on the build checked: the card lifts and follows the mouse, but no day box shows as a drop target and releasing does nothing at all - no scope picker, no shift, no message. The same drag of the same work order in Week view does open the scope picker, so the difference is Month view itself.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.1, §4.2), which describe dragging a work order from the sidebar onto a cell in the grid and the order of preference for the start time. Neither that specification nor story SV-8688 says whether Month view accepts the drop, so that point is an open product-owner question rather than a settled requirement. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1, §4.2), which describe dragging a work order from the sidebar onto a cell in the grid and the order of preference for the start time. Neither that specification nor story SV-8688 says whether Month view accepts the drop, so that point is an open product-owner question rather than a settled requirement. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
 </t>
         </is>
@@ -2536,7 +2574,7 @@
 4. Each line row shows the line title and its estimated hours.
 5. Rows for lines that already have technicians show the current roster as an avatar stack plus count.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2590,7 +2628,7 @@
 2. The block's last text line reads 'N Lines' (with N = the line count).
 3. The technician is added to the roster of every one of those lines.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3, §4.4). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.3, §4.4). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2643,7 +2681,7 @@
 2. The picker closes.
 3. The block's last text line shows the line's name.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2702,7 +2740,7 @@
 4. A 'Cancel' control leaves tick-box mode and returns you to the ordinary single-tap line list, without creating anything and without closing the picker.
 5. Confirming creates ONE shift covering exactly the ticked lines, and the technician is added to those lines' rosters only - not to the other lines.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -2755,7 +2793,7 @@
           <t xml:space="preserve">1. The shift starts at the technician's own configured start time (6:00 AM in the example), not the shop's business-hours start.
 Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2807,7 +2845,7 @@
         <is>
           <t xml:space="preserve">1. The shift starts at the shop's business-hours start time.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2859,7 +2897,7 @@
         <is>
           <t xml:space="preserve">1. The shift starts at 7:00 AM - the general default working day (7:00 AM to 7:00 PM) applies.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2912,7 +2950,7 @@
 2. The start time aligns to the timeline position (see the 15-minute snapping case).
 Note for the tester: every time on the Schedule is currently shown six hours later than the time it was booked for. That is already reported as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Read the position on the timeline rather than the printed time, and do not raise it again.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2965,7 +3003,7 @@
 2. It has no technician (and no technician is added to the line's roster by this drop).
 3. The block uses the same anatomy as a regular shift (customer, unit, line name / 'N Lines').
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2, §3.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2, §3.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3017,7 +3055,7 @@
         <is>
           <t xml:space="preserve">1. The unassigned shift starts at the shop's business-hours start (there is no technician whose hours could apply).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3075,7 +3113,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§3.2, §4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2, §4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8924)
 </t>
         </is>
@@ -3111,17 +3149,19 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in on a desktop browser with Schedule: Edit.
+          <t xml:space="preserve">1. You are signed in on a desktop browser with Schedule: Edit.
 2. A multi-line work order exists with a scope that exceeds the technician's daily hours.
-3. You are on the Schedule page in week view.</t>
+3. You are on the Schedule page in week view.
+</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1. Drop the work order on a technician, choose the large scope, and reach the spread step.
+          <t xml:space="preserve">1. Drop the work order on a technician, choose the large scope, and reach the spread step.
 2. Read the spread step's header.
 3. Click 'Change scope'.
-4. Choose a different scope and continue.</t>
+4. Choose a different scope and continue.
+</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3132,7 +3172,7 @@
 4. Clicking 'Change scope' takes the modal back to the scope picker (step 1) without creating anything.
 5. Choosing a new scope updates the spread step's header and hours accordingly.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3186,7 +3226,7 @@
 3. 'Full estimate', '1 week', and '2 weeks' apply on selection with no extra fields - the modal stays to one line for these.
 4. The preview summary updates to match each selection.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3238,7 +3278,7 @@
           <t xml:space="preserve">1. Choosing 'Until a date…' reveals a single 'finish by' date field (this is the only custom control shown).
 2. Picking a date updates the preview so the series ends by that date.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3289,7 +3329,7 @@
           <t xml:space="preserve">1. Choosing 'Specific hours…' reveals an hours stepper control.
 2. The preview updates to spread exactly the entered hours across working days.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3343,7 +3383,7 @@
 2. It can be changed; technician B's series then starts after A's series ends (sequential, not parallel).
 3. B's series is created from the adjusted start date onward.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -3398,7 +3438,7 @@
 3. Shop closures and public holidays are NOT skipped in V1 - shifts can be placed on those days.
 4. The end date is a result of the daily distribution (for 40h at 8h/day starting Monday, the series ends on the fifth working day).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5, §12). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
 </t>
         </is>
@@ -3451,7 +3491,7 @@
 2. Expanded: a week-by-week breakdown of the planned shifts.
 3. Skipped days are struck through and show the reason they are skipped - in V1 the only skip reason is a weekend day with no working hours set.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -3505,7 +3545,7 @@
 3. Each daily shift keeps its own day and hours.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §4.6, §8.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5, §4.6, §8.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -3558,7 +3598,7 @@
 2. There is no shared 'remaining hours' counter across technicians and no splitting of a shift.
 3. Planned hours across technicians may now exceed the estimate - this is expected and produces no error (progress is driven by clocked-in time).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5, §12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3614,7 +3654,7 @@
 3. A single spread that would create more than 120 daily shifts is refused outright - no confirmation can override it, and no shifts are created for that attempt.
 4. No half-created series is left behind after a refused attempt.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3672,7 +3712,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.6). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8958)
 </t>
         </is>
@@ -3726,7 +3766,7 @@
 2. Chevrons at the banner's edges indicate the series continues beyond the visible week (both sides, on a middle week).
 3. A 'week N of M' cue shows the position within the series.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.6). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3778,7 +3818,7 @@
           <t xml:space="preserve">1. The day shows a single time-positioned block (no spanning bar - only one day is visible).
 2. The block carries a cue in the spirit of 'part of an M-week job' indicating it belongs to a longer series.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.6). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3832,7 +3872,7 @@
 2. The overlapping day is flagged as a Double-booked conflict, exactly as it would be for standalone shifts.
 3. The detail modal shows that single day's shift (its own day and hours) while indicating it belongs to the series.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.6, §8.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.6, §8.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3885,7 +3925,7 @@
 3. Last line: the name of the scheduled line.
 4. No work order number appears on the block.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.4). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3939,7 +3979,7 @@
 2. The subset block reads '2 Lines' - the block does not distinguish whole-order from subset beyond the count.
 3. Each detail modal lists exactly which lines the shift covers.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4, §12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.4, §12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3992,7 +4032,7 @@
 2. The conflicted block shows the conflict (warning) icon on its first line - and that is the only icon that ever appears on a block.
 3. No scope icons distinguish whole-order from subset shifts.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.4). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.4). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4047,7 +4087,7 @@
 3. The row stays at its normal height.
 4. No conflict is flagged for back-to-back (non-intersecting) shifts.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7, §12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.7, §12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4099,7 +4139,7 @@
 2. The row grows in height to fit the lanes.
 3. The overlap is also flagged as a Double-booked conflict (stacking reads as 'resolve me').
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7, §4.11). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.7, §4.11). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4153,7 +4193,7 @@
 3. Clicking it opens a popover listing the hidden shifts.
 4. The hidden shifts can be opened from that popover.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4207,7 +4247,7 @@
 2. Week and month views reach the '+N more' overflow sooner than day view (their cells are narrower), but the same cap-and-overflow model applies.
 3. The overflow affordance opens the hidden-shifts popover in each view.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4268,7 +4308,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.8). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8837)
 </t>
         </is>
@@ -4321,7 +4361,7 @@
           <t xml:space="preserve">1. In day view, the date/time header bar stays stuck to the top while the rows scroll beneath it - you always know which time column you are looking at.
 2. The same sticky-header behavior applies in week view.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4376,7 +4416,7 @@
 3. The duration is unchanged by a horizontal move.
 4. A toast with Undo appears for the move.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8, §7). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.8, §7). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -4431,7 +4471,7 @@
 3. The resulting times land on 15-minute increments.
 4. The shift's duration on the grid matches the modal's start/end.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4484,7 +4524,7 @@
 2. Its position matches the actual clock time.
 3. Hovering the now line while your pointer is over the grid shows a label (the current time).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4537,7 +4577,7 @@
 2. It shows the customer name, unit number, the VIN (below unit and asset), and the work order id.
 3. The VIN is visible here even though the grid's VIN toggle is off - the modal always shows it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §9). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9, §9). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4596,7 +4636,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8833)
 </t>
         </is>
@@ -4653,7 +4693,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8834)
 </t>
         </is>
@@ -4708,7 +4748,7 @@
 4. This is where whole-order vs subset scope is spelled out (the grid block only says 'N Lines').
 Note for the tester: the absence of any money figure is CORRECT and is what this test expects. The product owner ruled on 22 July 2026 that no total in dollars is shown anywhere on the Schedule. If you see no money figure, pass this test.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §4.4). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9, §4.4). Version 23 of that specification asked for the lines to carry 'labor/total figures'. Version 25, published on 6 August 2026, changed that to 'labor/status figures', so the specification and this test now agree that no money figure is shown; the specification still asks for a labor figure, which this test does not expect, and on that one point the behaviour above follows the product owner's later decision of 22 July 2026, recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4761,7 +4801,7 @@
 2. The new value persists after closing and re-opening.
 3. Dependent displays (progress vs estimate) reflect the new value.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4815,7 +4855,7 @@
 3. The delete removes the note.
 4. Notes are kept per work order (the same note is visible from another shift of the same work order).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -4874,7 +4914,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8852)
 </t>
         </is>
@@ -4927,7 +4967,7 @@
 2. There is no 'Reassign' action in the modal; reassignment is done by dragging a shift to another technician row (covered by its own case).
 3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.9, §7). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9, §7). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4981,7 +5021,7 @@
 3. Saving creates an event block on that technician's day.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10, §7). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5034,7 +5074,7 @@
 2. A live preview block is shown while creating, and dragging resizes it.
 3. Completing creates the event at the previewed time/duration.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5090,7 +5130,7 @@
 4. With all-day ON, specific start/end times are not required (the time fields are disabled or hidden).
 5. The event is created as an all-day block for that technician and day.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §8.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10, §8.1). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5144,7 +5184,7 @@
 2. Dropping on another day moves it to that day.
 3. Each move produces a toast with Undo.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §7). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10, §7). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -5196,7 +5236,7 @@
 2. It has a small grey-filled rounded chip on the left containing a calendar icon, and two lines of text beside it: the event name, then the time range in secondary text.
 3. The shift reads as a tinted color-filled block with a colored left rail - the two types are separable at a glance, not by color alone.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5250,7 +5290,7 @@
 2. The color picker offers the same custom color palette as shifts (shared picker with editable labels).
 3. Choosing a color tints the card and the icon chip in matching tones, the same way a colored shift is tinted.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §10). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10, §10). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5304,7 +5344,7 @@
 2. The event does NOT create a double-booked or overlap conflict with the shift, and the toolbar conflict count does not increase because of it.
 3. The two behave differently on purpose: an event uses up capacity, but it is never flagged as a conflict.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.10, §4.11, §4.12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10, §4.11, §4.12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5359,7 +5399,7 @@
 3. The toolbar conflict pill's count increases.
 4. The conflict is listed in the pill's dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5412,7 +5452,7 @@
 2. If the technician's working days DO include that day (for example Saturday hours are configured), a shift on that day is NOT flagged.
 3. The warning icon appears on the block and the conflict is listed in the toolbar dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5468,7 +5508,7 @@
 3. Both the start and the end follow the hierarchy technician hours, then shop business hours, then the general default working day of 7:00 AM to 7:00 PM.
 4. Warning icon on the block in each case; the conflict appears in the toolbar dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11, §4.2). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5523,7 +5563,7 @@
 3. The list covers all current conflicts (count matches the pill).
 4. Resolving a conflict (for example moving the shift) reduces the count - detection is continuous.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §6). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11, §6). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5575,7 +5615,7 @@
           <t xml:space="preserve">1. The grid navigates to the relevant technician and day.
 2. The conflicted shift is brought into view.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5627,7 +5667,7 @@
           <t xml:space="preserve">1. Overtime is signaled with the 'OT' text tag and amber tones - NOT red or alarming styling.
 2. Red/alarming styling appears only for conflicts and genuine errors.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.11, §4.12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11, §4.12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5682,7 +5722,7 @@
 2. A more heavily booked day shows a longer blue fill; the fill never exceeds the track (clamped at 100%).
 3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5733,7 +5773,7 @@
           <t xml:space="preserve">1. An amber segment extends past the right edge of the track, showing the excess.
 2. A tick marks the 100% line where the track ends.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5785,7 +5825,7 @@
 2. The tag is text, not a color-only signal.
 3. Overtime (per-technician) and capacity (aggregate) are independent signals.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12, §11). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.12, §11). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5834,11 +5874,11 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A tooltip shows a per-technician breakdown: assigned hours vs that technician's capacity.
+          <t xml:space="preserve">1. A tooltip shows a breakdown for each assigned technician: assigned hours vs that technician's capacity. (Version 26 of the specification, published 7 August 2026, narrowed this from 'per-technician' to 'per-assigned technician'.)
 2. The overtime technician's entry is highlighted in amber.
 3. The numbers agree with the shifts actually on the grid.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5892,7 +5932,7 @@
 3. A time-logged progress bar shows logged vs estimated hours ('X / Yh' style).
 Known issue on the build tested: The tooltip listed ALL FIVE line names on the 5-line series shift with no "+N more lines" row. Spec 4.13: "the individual line names as a short list capped at 3 with a '+N more lines' row". Everything else matched: customer, unit and VIN, date and time range, technician, scope summary "5 lines - 12h" and the progress bar. VIN appears with the toggle off, per Branko 2026-07-31. It has been reported to the QA lead but has no developer ticket yet. Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.13). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5947,7 +5987,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.13). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8959)
 </t>
         </is>
@@ -6003,7 +6043,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.13). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8893)
 </t>
         </is>
@@ -6059,7 +6099,7 @@
 3. The tooltip is read-only (no buttons/actions inside it).
 4. Clicking the block opens the full detail modal as normal.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.13). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6112,7 +6152,7 @@
 2. Near a side edge, the tooltip shifts horizontally to stay fully within the viewport.
 3. No part of the tooltip is clipped off-screen.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.13). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.13). Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6128,144 +6168,449 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>Panel button sits left of Today and its tooltip names what it will do</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Grid Toolbar</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser, with the window at least 960 pixels wide.
+2. Your role has the Schedule: View permission.
+3. You are on the Schedule page, and the left panel is showing - that is the strip down the left-hand side holding the small month calendar and the list of work orders.</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at the row of buttons directly above the grid, to the right of the left panel.
+2. Find the button at the far-left end of that row, before the Today button.
+3. Rest your mouse pointer on that button and read the tooltip that appears.
+4. Click the button once, so the left panel is hidden.
+5. Rest your mouse pointer on the same button again and read the tooltip.
+6. Compare the picture on the button now with the picture that was on it at step 3.
+7. Click the button once more.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. There is a button at the far-left end of that row, to the left of the Today button.
+2. It sits above the grid's left-hand column - the one headed Department that carries the technician names and their small round profile pictures - so it reads as belonging to the panel it controls.
+3. It sits together with the date controls: the Today button and the left and right arrows.
+4. The button shows a small picture only, with no border or box drawn around it, in the same muted grey as the other icon buttons in that row.
+5. While the left panel is showing, the tooltip reads: Hide panel
+6. After you click it and the panel is hidden, the tooltip reads: Show panel
+7. The picture on the button is exactly the same in both states - only the tooltip changes.
+8. Clicking the button at step 4 hides the left panel, and clicking it again at step 7 shows it.
+Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
+---
+This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse and §6 Grid toolbar). Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: HOLD - the panel collapse control is not in the build
+</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§5.3 Panel collapse - the control: position; borderless icon; tooltip wording. §6 Grid toolbar - Panel toggle row)</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Panel button hides the left panel and the grid widens into the space</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Grid Toolbar</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser, with the window at least 960 pixels wide.
+2. Your role has the Schedule: View permission.
+3. You are on the Schedule page, the left panel is showing, and there are some shifts visible in the grid.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>1. Note roughly how much of the screen the grid takes up and how much of it you can see across.
+2. Look at the join between the left panel and the grid.
+3. Click the panel button at the far-left end of the row of buttons above the grid, to the left of Today.
+4. Watch what happens to the left panel and to the grid as it closes.
+5. Look again at the area where the left panel used to be.
+6. Click the same button a second time.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The left panel closes with a short, smooth sliding movement as its width shrinks - it does not disappear in one jump.
+2. The dividing line between the panel and the grid goes away with it, leaving no leftover line, seam or empty strip where the panel used to be.
+3. The grid grows into the space the panel gave up and lays itself out again in the wider area, so you can see more of the grid than you could before.
+4. Clicking the button a second time brings the panel back to its normal width, and the grid goes back to the size it was at step 1.
+Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
+---
+This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse and §3.1 Left panel: work order sidebar). Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: HOLD - the panel collapse control is not in the build
+</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§5.3 Panel collapse - Behavior; §3.1 - collapsed from the grid toolbar handing its width to the grid)</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>What you had set up in the left panel survives hiding and showing it</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Grid Toolbar</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser, with the window at least 960 pixels wide.
+2. Your role has the Schedule: View permission.
+3. You are on the Schedule page and the left panel is showing.
+4. There are enough work orders in the list that it has to be scrolled to see them all.</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>1. In the small month calendar at the top of the left panel, click a date that is not today.
+2. In the Search work orders box, type part of a customer name so that the list of work orders narrows.
+3. Scroll the work order list down a little way.
+4. Click one of the work order cards, so the panel swaps from the list of work orders to that order's list of lines.
+5. Click the panel button above the grid, to the left of Today, to hide the left panel.
+6. Click the same button again to show the panel.
+7. Check each of the four things you set up in steps 1 to 4.</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The panel comes back showing the same things you left in it. Nothing has been reset, cleared or reloaded from scratch - while it was hidden its contents were only out of sight, not thrown away.
+2. The date you picked in the small month calendar is still the selected date.
+3. The text you typed is still in the Search work orders box, and the list is still narrowed by it.
+4. The list is still scrolled to roughly the position you left it at.
+5. The panel comes back showing that work order's lines, not the full list of work orders - it returns to whichever of the two views was open when you hid it.
+6. The work order you had opened is still the selected one.
+Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
+---
+This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse and §3.1 Left panel: work order sidebar). Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: HOLD - the panel collapse control is not in the build
+</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§5.3 Panel collapse - State preservation; §3.1 - without losing panel state)</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Menus and pop-up windows reposition when the left panel is hidden</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Grid Toolbar</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser, with the window at least 960 pixels wide.
+2. Your role has the Schedule: View permission.
+3. You are on the Schedule page, the left panel is showing, and there is at least one shift in the grid.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>1. With the left panel still showing, open something that pops open over the page - for example click a shift in the grid to open its details window.
+2. Note where it sits on the screen, then close it.
+3. Click the panel button above the grid, to the left of Today, to hide the left panel.
+4. Open the same pop-up again.
+5. Look at where it sits on the screen now.</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. With the panel hidden, the pop-up no longer keeps clear of the space the panel used to take up. It sits against the edge of the browser window with a normal margin instead.
+2. The whole pop-up is on screen: nothing is cut off at an edge, pushed outside the window, or left floating with a large empty gap beside it.
+3. The pop-up behaves normally otherwise - you can read it, use its buttons, and close it.
+Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
+---
+This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse, Popovers and modals). Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: HOLD - the panel collapse control is not in the build
+</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§5.3 Panel collapse - Popovers and modals)</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Hiding the panel lasts for the rest of your sign-in but is not saved</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Grid Toolbar</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser, with the window at least 960 pixels wide.
+2. Your role has the Schedule: View permission.
+3. You are on the Schedule page and the left panel is showing.
+4. You know the password for the account you are signed in with, because this test signs out and back in.
+5. For the last step only, you also need a SECOND sign-in for a different person who can see the Schedule. If you do not have one, do steps 1 to 6 and mark the last point Blocked rather than guessing.</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>1. Click the panel button above the grid, to the left of Today, to hide the left panel.
+2. Go to another page - for example Work Orders - and then come back to Schedule.
+3. Check whether the left panel is hidden or showing.
+4. Sign out of the ShopView App completely.
+5. Sign back in with the same account and open Schedule.
+6. Check whether the left panel is hidden or showing.
+7. On a different computer or a private browsing window, sign in as the second person, open Schedule, and check whether their left panel is hidden or showing.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. At step 3, still in the same sign-in, the left panel is still hidden. The choice is remembered while you stay signed in.
+2. At step 6, after signing out and back in, the left panel is showing again. The choice is not carried over into a new sign-in: it is a working-mode preference for the session you are in, not a saved view setting.
+3. At step 7, the second person's left panel is showing as normal. Your choice applied only to you and did not change what anybody else sees.
+Still to be confirmed, and it affects the second point above. The product owner's description of 7 August says this choice lasts only for the current sign-in. Separately, the design review of 5 August asks for the Schedule's view settings to be stored per user so they survive signing out and back in. Those are two different promises. The question has been put to the product owner and has not been answered yet, so the second point follows the written specification for now. If the answer is that it should survive signing out, the second point will change.
+Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
+---
+This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse, Persistence). Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: HOLD - the panel collapse control is not in the build
+</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§5.3 Panel collapse - Persistence; session-scoped per user for build)</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>'Today' button jumps the grid to the current date</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Grid Toolbar</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page, navigated several weeks away from today.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Click the 'Today' button in the grid toolbar.
 2. Look at the grid and the date label.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The grid jumps to the range containing the current date (today's day, this week, or this month depending on the active view).
 2. The date label updates accordingly.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§6). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§6 (Today button))</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Left/right arrows step by day, week, or month to match the active range</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Grid Toolbar</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. In week view, click the right arrow and read the date label.
 2. Switch to day view and click the right arrow.
 3. Switch to month view and click the left arrow.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Week view: each arrow click moves one whole week; the label shows the week range (spec's example format: 'Jul 14 to 20, 2026').
 2. Day view: each click moves one day; the label shows that day.
 3. Month view: each click moves one month; the label shows that month.
 4. The label always matches what the grid displays.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§6). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§6 (Left/right arrows,Date label))</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Toolbar search highlights matching blocks and fades non-matching ones</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Grid Toolbar</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Several shifts exist on the visible range for different customers/orders/technicians.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Type a customer name into the toolbar search; look at the grid.
 2. Clear, then search a work order number, a unit number, a technician name, and a line name in turn.
 3. Clear the search.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Blocks that match the search are highlighted; blocks that do not match fade.
 2. All five fields match: customer name, work order number, unit number, technician name, and line name.
@@ -6276,209 +6621,209 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§6). Points 1, 3 and 4 above come from version 23 of that specification, which said 'Non-matching blocks fade; matching blocks highlight'. Version 24, published on 6 August 2026, removed that sentence, and the live version now describes the search only as filtering the grid blocks. Point 2 (the five fields that are matched) is unchanged and still in the live version. The expectation above therefore still follows the older wording and needs the product owner to confirm which one stands. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8874)
 </t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§6 (Search))</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>'Filter &amp; Display' dropdown combines department toggles, My Shifts, and VIN</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Open the 'Filter &amp; Display' dropdown in the grid toolbar.
 2. Read its contents and default states.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The dropdown is checkbox style and contains: a toggle per department, 'My Shifts', and 'VIN'.
 2. Defaults: all department toggles ON, 'My Shifts' OFF, 'VIN' OFF.
 3. There is no separate departments-only control - this dropdown replaces it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6, §9). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§6, §9). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§6,§9 (Filter and Display dropdown))</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Department toggles show or hide individual department groups in the grid</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. At least two department groups are visible in the grid.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. In 'Filter and Display', turn OFF one department's toggle.
 2. Look at the grid.
 3. Turn it back ON.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The turned-off department's group (header and technician rows) disappears from the grid.
 2. Other departments are unaffected.
 3. Turning it back on restores the group.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (Department toggles))</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>'My Shifts' filters the grid to only the current user's shifts</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser as a user who appears as a technician row and has at least one shift.
 2. Other technicians also have shifts on the visible range.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. In 'Filter and Display', turn ON 'My Shifts'.
 2. Look at the grid.
 3. Turn it OFF again.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Only shifts assigned to you remain visible; all other technician rows and their shifts are hidden.
 2. Turning it off restores the full grid.
 3. This is a personal convenience filter only - it does not change what you are permitted to see (default is OFF, everyone's shifts visible).
 4. For a user who has no technician/staff record of their own, the 'My Shifts' option is not shown at all.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9, §14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user with no staff record of their own
 </t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (My Shifts),§14.3)</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>'VIN Number' toggle gates the block VIN only - tooltip and modal always show it</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. A shift exists for a unit with a VIN; the VIN toggle is OFF.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. With 'VIN Number' off: read the block in week view, hover for the tooltip, then open the detail modal.
 2. Turn 'VIN Number' ON in 'Filter and Display'.
@@ -6486,7 +6831,7 @@
 4. In day view, compare the height of the shift's lane with the toggle off and on.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. 'VIN Number' off: no VIN line on the block (the block shows its three normal lines) - but the hover tooltip still shows the VIN, and the detail modal still shows the VIN.
 2. 'VIN Number' on: the VIN appears as an additional line on blocks in day and week views.
@@ -6499,48 +6844,48 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §4.4, §4.8). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9, §4.4, §4.8). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8941)
 </t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (VIN),§4.4); SV-8690 (§4.4,§9 (VIN option)); SV-8694 (§4.8 (Lane height with VIN))</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>'View Options': six toggles with defaults; Capacity Bars and Events flip</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in week view with no view options changed yet (fresh state).
 3. At least one event and some shifts exist in the visible range, so capacity bars have fill.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. Open 'View Options' in the grid toolbar.
 2. Read each toggle and its state.
@@ -6548,7 +6893,7 @@
 4. Turn OFF Events, look at the grid, then turn it back ON.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Six toggles are offered: Business Hours, Capacity Bars, Events, Tech Hours, Saturday, Sunday.
 2. Defaults: Business Hours OFF, Capacity Bars ON, Events ON, Tech Hours OFF, Saturday ON, Sunday ON.
@@ -6559,108 +6904,108 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§6, §9, §4.12). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§6, §9, §4.12). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8827)
 </t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§6,§9 (View Options popover,Capacity Bars,Events),§4.12)</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Business Hours toggle shades non-working hours in day view</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. The shop has working hours set.
 3. You are on the Schedule page in DAY view with Business Hours OFF.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Note the timeline background outside working hours.
 2. Turn ON Business Hours in 'View Options'.
 3. Look at the timeline again.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With the toggle on, the hours OUTSIDE the working day are shaded with a grey overlay.
 2. Working hours remain unshaded.
 3. Turning it off removes the shading.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §4.8). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9, §4.8). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (Business Hours),§4.8 (Business-hours shading))</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Tech Hours toggle displays each technician's working hours next to their name</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. Technicians have configured working hours.
 3. You are on the Schedule page with Tech Hours OFF (default).</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. Turn ON Tech Hours in 'View Options'.
 2. Look at the technician rows.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each technician's working hours are displayed next to their name in the row header.
 2. The hours match the technicians' configured hours.
@@ -6670,162 +7015,162 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8851)
 </t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (Tech Hours))</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Saturday and Sunday toggles include or exclude the weekend columns</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Filter and Display and View Options</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in WEEK view with Saturday and Sunday ON (default) - 7 columns visible.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Turn OFF Saturday in 'View Options'; look at the grid.
 2. Turn OFF Sunday too; look again.
 3. Turn both back ON.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Saturday off: the Saturday column is removed (6 columns remain).
 2. Sunday off too: 5 weekday columns remain (Monday to Friday).
 3. Both back on: the full Monday-to-Sunday 7-column week returns.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§9, §3.2). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9, §3.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§9 (Saturday,Sunday),§3.2 (Week view))</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Dragging a shift to another technician row reassigns it, with a confirm modal</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift exists on technician A; note the affected line's roster.
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. Drag the shift block from technician A's row to technician B's row.
 2. Confirm the move in the confirmation modal.
 3. Check the line's roster on the work order.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A confirmation modal appears for the cross-technician move.
 2. After confirming, the shift sits on technician B's row.
 3. Technician B is added to the affected line's roster and technician A is removed from it.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §12). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §12). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>SV-8695 (§7 (Shift reassignment),§12)</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Left-click empty grid space opens a menu: Create Event and New Work Order</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page in week view (the same menu is offered in month view).
 3. Schedulable work order lines exist.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. Left-click an empty spot in a technician's grid cell (not on an existing shift or event block).
 2. Read the menu items.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A dropdown menu opens at the spot you clicked.
 2. It contains ONLY two items: 'Create Event' and 'New Work Order'.
@@ -6833,92 +7178,92 @@
 4. There is no 'New Shift' item - it was removed from the menu.
 5. This menu is opened by a normal left-click - right-clicking the cell does not open it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 (left-click menu on empty grid space; View Day and New Shift removed),§14.1 (creation via the cell menu))</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>'New Work Order' in the cell menu points the user to the Work Orders tab</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Schedule grid.
 2. The cell menu already shows 'Create Event' and 'New Work Order'.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. Left-click an empty spot in a grid cell.
 2. Choose 'New Work Order' from the menu.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The menu offers a 'New Work Order' item.
 2. Choosing it directs the user to create a work order (a toast / prompt pointing to the Work Orders tab).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 / §4.10 New Work Order cell-menu shortcut)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Week view: a shift that is part of a repeating series can be reassigned</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Reassignment and Context Menu</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser (window at least 960px wide).
 2. Your role has the Schedule: Edit permission.
@@ -6927,7 +7272,7 @@
 5. A second technician has a row on the same screen - use MQ Test Tech Qamar.</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. Find one block of the series in the week grid (it is labelled "Part of a series" or "Week 1 of 2").
 2. Press and hold the mouse on that block.
@@ -6935,7 +7280,7 @@
 4. Look at what appears, and then at which technician's row the block is in.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The block lifts and follows the mouse as you drag it.
 2. When you release it on the other technician's row, a small window asks you to confirm the move to that technician - the same confirmation you get when you move an ordinary shift.
@@ -6946,422 +7291,422 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §12): dragging a shift block from one technician row to another reassigns it and a confirmation handles cross-technician moves, and a series is a grouping over ordinary daily shifts rather than a different kind of thing, so an ordinary shift's behaviour applies to a series member too. Story SV-8692 covers series-aware deletion only and says nothing about reassignment. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §12): dragging a shift block from one technician row to another reassigns it and a confirmation handles cross-technician moves, and a series is a grouping over ordinary daily shifts rather than a different kind of thing, so an ordinary shift's behaviour applies to a series member too. Story SV-8692 covers series-aware deletion only and says nothing about reassignment. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8867)
 </t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>SV-8867 (§7 shift reassignment + §12 series is a grouping over ordinary shifts)</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Deleting a middle shift of a series offers all three scope options</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists for one technician.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Delete a MIDDLE shift of the series (via the detail modal's Delete).
 2. Read the scope options offered (do not confirm yet).</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A scope prompt appears with three options: this shift only, this and everything after, and the whole series.
 2. Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').
 3. The prompt uses routine, lightweight styling - not alarming destructive styling.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (Series-aware deletion))</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>'This shift only' removes that day and the series keeps the gap</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists; note the total scheduled hours.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Delete a middle shift with the 'this shift only' scope.
 2. Look at the series on the grid.
 3. Check the scheduled hours.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Only that day's shift is removed.
 2. The series keeps the gap - the remaining shifts do NOT shuffle to close it.
 3. The removed day's hours return to the estimate's remaining (scheduled hours drop by that day's hours).
 4. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (This shift only))</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>'This and everything after' removes from the clicked shift onward</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 4 shifts exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Delete the series' THIRD shift with the 'this and everything after' scope.
 2. Look at the series on the grid.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The third shift and every later shift of the series are removed.
 2. The first two shifts remain untouched.
 3. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (This and everything after))</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>'The whole series' removes all of the series' shifts for that technician</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. The SAME work order has a series on technician A and an independent series on technician B.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. Delete one of technician A's series shifts with the 'whole series' scope.
 2. Look at both technicians' rows.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. All of technician A's series shifts are removed.
 2. Technician B's independent series is untouched (the scope is per technician's series).
 3. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (The whole series - 'for that technician'))</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Scope options adapt: the first and last shift each show only two</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A series of at least 3 shifts exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Start deleting the FIRST shift of the series; read the options, then cancel.
 2. Start deleting the LAST shift; read the options, then cancel.
 3. Start deleting a MIDDLE shift; read the options, then cancel.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. First shift: two options ('this and after' would equal 'whole series', so only two are shown).
 2. Last shift: two options ('this and after' would equal 'this only').
 3. Middle shift: all three options.
 4. Cancelling leaves the series unchanged in every case.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (options adapt to position))</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Deleting a standalone (non-series) shift does not ask for a series scope</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A single standalone shift (not part of any series) exists.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Watch what is asked.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
 2. The shift is deleted and an undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>SV-8692 (§7 (derived - scope prompt is for series shifts))</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Toast lasts ~7s with Undo (about 4s without); stays on hover, goes on leave</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. Perform an action that shows a toast (for example move a shift) and let the toast sit untouched - time how long it stays.
 2. Trigger another toast and hold the cursor OVER it well past its normal lifetime.
 3. Move the cursor off the toast.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Untouched, a toast that has an Undo action persists about 7 seconds; a toast without Undo persists about 4 seconds, before dismissing.
 2. While the cursor is over it, the toast stays (does not auto-dismiss).
 3. After the cursor leaves, it dismisses.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>SV-8688 (§7 (Toast notifications),§11 (Undo))</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Every create/delete/move/reassign toasts with Undo, and Undo restores</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. Schedulable lines exist and a shift exists; note its technician, day, and time.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. Create a shift and watch for the toast.
 2. Delete the shift, watch for the toast, then click Undo on it.
@@ -7370,7 +7715,7 @@
 5. Check the line's roster after the reassign undo.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each of the four actions (create, delete, move, reassign) produces a toast notification, and every toast offers an Undo option.
 2. Undo after delete: the shift is back exactly where it was.
@@ -7378,48 +7723,48 @@
 4. Undo after reassign: the shift returns to the original technician, and the line's roster is restored (original tech back on, target tech off).
 5. Every destructive action is undoable within the toast's lifetime.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>SV-8688 (§7 (Toast notifications),§11 (Undo))</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Schedule actions save immediately - Undo reverses them, closing does not cancel</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Deletion, Series Scopes and Undo</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. A shift exists on the grid; note its technician, day, and time.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. Delete the shift. While the Undo toast is still showing, refresh the page WITHOUT clicking Undo.
 2. Check the grid for the shift.
@@ -7427,54 +7772,54 @@
 4. Finally do one more delete and this time click Undo before the toast disappears.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The delete took effect immediately: after the refresh the shift is gone even though Undo was never clicked - closing or refreshing does not cancel the action.
 2. The move also stuck after the refresh - the shift is on the new day.
 3. Clicking Undo within the toast's lifetime reverses the action (the deleted shift comes back).
 4. Note for the tester: Undo works by performing a reversing action, not by holding the change back - a change surviving a refresh before Undo is expected, not a bug.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7), which requires the toast and its Undo. That specification does not say how Undo works underneath, so the point above - that the action is already saved and Undo reverses it rather than holding it back - comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>SV-8688 (§7 toast/undo + tech-plan D10)</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Escape closes the topmost open modal or popover, following the stacking order</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Open the shift detail modal, then open the color picker inside it and press Escape.
 2. Open the time picker inside the modal and press Escape; then start editing a note and press Escape.
@@ -7482,7 +7827,7 @@
 4. Open the shift detail modal again with a popover from elsewhere on top of it, and press Escape twice.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Escape with the color picker open closes only the color picker - the modal stays open.
 2. Same for the time picker and the note edit - each sub-picker closes first and the modal stays open.
@@ -7490,48 +7835,48 @@
 4. With two layers open, the FIRST Escape closes only the topmost layer, and the SECOND Escape closes the next layer down.
 5. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 (Keyboard support - Escape,including within the shift modal))</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Enter confirms the active dialog, but not inside a note textarea</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Delete.
 2. Shifts/series and events exist to exercise the dialogs.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step for a large job, press Enter.
 2. Open the reassign dialog for a shift, choose a technician, press Enter.
@@ -7540,160 +7885,160 @@
 5. Open a shift's detail modal, click into the note editor, type a line of note text and press Enter, then type a second line.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. In each confirmable dialog, Enter confirms it - equivalent to clicking its confirm action.
 2. The confirmed action takes effect (spread created / reassigned / event saved / delete applied).
 3. In the note editor, Enter inserts a new line in the note - it does NOT confirm or close the dialog.
 4. The multiline note can be completed and saved normally.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§7 (Keyboard support - Enter; Enter does not fire inside textareas))</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Modals trap focus and all interactive elements are keyboard-reachable</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Keyboard Interactions</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's detail modal is open.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Press Tab repeatedly and watch where focus goes.
 2. Continue tabbing past the last control in the modal.
 3. Close the modal and Tab through the schedule page's toolbar and sidebar controls.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Focus moves through the modal's interactive elements with visible focus rings.
 2. Focus stays trapped inside the modal (wraps back to its first control) until the modal closes.
 3. On the page, toolbar and sidebar controls are reachable by keyboard.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§11 (Accessibility))</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Blue is the default color for all shifts, including long and multi-week jobs</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Create a normal single-day shift without touching any color option.
 2. Create a multi-week series without touching any color option.
 3. Look at both on the grid.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Both the single shift and the multi-week series render in the default blue.
 2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§10). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§10)</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Shift modal color picker recolors that shift only, in matching tones</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. Two shifts from the SAME work order exist (for example on different technicians).
 3. One of those shifts' detail modal is open.</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Open the color picker in the modal.
 2. Choose a non-default color.
@@ -7701,54 +8046,54 @@
 4. Compare that shift with the other shift from the same work order.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The shift's block re-renders in the chosen color.
 2. The color provides three consistent tones: background fill, text color, and accent (left border).
 3. The color is per SHIFT, not per work order - the other shift from the same work order keeps its own (default blue) color and does not change.
 4. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10, §4.9, §4.4). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§10, §4.9, §4.4). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§10,§4.9 (Color picker)); SV-8690 (§4.4,§10)</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Color labels are editable per shop</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Color System</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shift's or event's color picker is open.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Find the editable label of one color in the picker.
 2. Rename it (for example to 'ZZAUTOTEST Rush').
@@ -7756,53 +8101,53 @@
 4. Restore the original label.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each color's label can be edited.
 2. The renamed label shows for the whole shop - the same picker opened elsewhere shows 'ZZAUTOTEST Rush'.
 3. Shifts and events share the same custom palette with the same labels.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§10, §4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§10, §4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>SV-8700 (§10 (Color labels are editable per shop),§4.10 (shared picker))</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Business-hours toggle reveals a per-day (Mon-Sun) From-To editor</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App with access to location settings.
 2. You are on the Edit Location screen for a shop.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Find the business hours setting on Edit Location and read its default state.
 2. Turn the 'Set business hours for this shop' toggle ON.
@@ -7811,7 +8156,7 @@
 5. Save the location settings.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Edit Location shows a toggle labelled 'Set business hours for this shop', and it is OFF by default (no business hours set).
 2. Turning it ON reveals a per-day working-hours editor for the shop.
@@ -7819,202 +8164,202 @@
 4. Each day has a From time and a To time you can set.
 5. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - business hours toggle,per-day From/To editor)</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Edit Staff has a 'Set custom hours for this technician' toggle, off by default</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with access to staff settings.
 2. You open the Edit Staff Member screen for a technician.</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Open the Edit Staff Member screen for a technician.
 2. Find the custom-hours setting and read its default state.
 3. Turn the 'Set custom hours for this technician' toggle ON.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Edit Staff Member shows a toggle labelled 'Set custom hours for this technician'.
 2. The toggle is OFF by default (no custom hours set).
 3. Turning it ON reveals a per-day working-hours editor for that technician.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - technician custom-hours toggle)</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>A technician with no custom hours inherits the shop business hours</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. The shop has business hours set for the shop.
 2. A technician has the 'Set custom hours for this technician' toggle OFF.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the technician has no custom hours set.
 2. Schedule a shift for that technician and check start-time defaults / before-after-hours conflicts against the shop business hours.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With no custom hours, the technician's working hours fall back to the shop business hours.
 2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - inherit shop hours when no custom hours)</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>'Add hours' appends a removable second range for split shifts, starting empty</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. You are in the per-day working-hours editor (location or technician) with a day's first range set.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. On one day, click 'Add hours'.
 2. Read the new range that appears.
 3. Set the second range, then remove it.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. 'Add hours' appends an additional From-To range to that day (to support split shifts).
 2. The added range starts empty (no From/To pre-filled).
 3. Each added range can be removed individually.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - Add hours split shifts)</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Overlapping hour ranges block Save; incomplete rows are ignored</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Working Hours Settings</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. You are in the per-day working-hours editor with at least two ranges on one day.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Set two ranges on the same day so their times overlap.
 2. Look at the offending range and the Save button.
@@ -8022,7 +8367,7 @@
 4. Look at the validation state and the Save button again.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The offending (overlapping) range is flagged in red.
 2. An inline message reads 'These hours overlap. Adjust the times so they don't conflict.'
@@ -8030,48 +8375,48 @@
 4. The incomplete row (empty From/To) is ignored by the overlap check - it does not raise the overlap error.
 5. Save is not blocked by an incomplete row on its own (only genuine overlaps disable Save).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>SV-8699 (§4.2 Working Hours - overlap validation; incomplete rows ignored by overlap check)</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Schedule: View grants the full read-only experience across the whole page</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit (assign a suitable system role or a purpose-made custom role; restore after).
 2. Shifts and events exist on the grid, created by an Edit-capable user.
 3. You are signed in AS that View-only user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Open the Schedule page.
 2. Switch between Day, Week, and Month.
@@ -8079,55 +8424,55 @@
 4. Hover a shift for its tooltip, then click it to open the detail modal.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Schedule page opens and all three views work.
 2. The mini calendar, search, and filters all work.
 3. ALL technicians' shifts and events are visible (not just the user's own).
 4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1, §14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1, §14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a view-only user
 </t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14.1 (Schedule: View),§14.3)</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>View-only: every editing affordance is hidden or disabled</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View but NOT Edit.
 2. Shifts, a series, and events exist on the grid.
 3. You are signed in AS that View-only user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Look for drag handles on sidebar lines and try to drag a work order card onto the grid.
 2. Try dragging an existing shift block (move/reassign) and look for resize handles in day view.
@@ -8135,105 +8480,105 @@
 4. Open a shift's detail modal and inspect its fields and actions.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. No drag handles are offered and nothing can be dragged from the sidebar onto the grid.
 2. Shift blocks cannot be moved or resized - no drop targets or resize handles appear.
 3. No creation menu opens at all - there is no 'Create Event' and no 'New Work Order' offered.
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a view-only user
 </t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14.1 (Schedule: View - editing affordances hidden or disabled))</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>With Schedule: View OFF, the Schedule top-level nav item is hidden entirely</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: View OFF (no Schedule permission).
 2. You are signed in AS that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Look at the app's main navigation.
 2. Search the nav for any Schedule entry.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Schedule top-level nav item is not shown at all.
 2. The rest of the app works normally for the role.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user without the Schedule permission
 </t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14.1 (When Schedule: View is OFF))</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Schedule: Edit unlocks all creation and modification interactions</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit (and View) but NOT Delete.
 2. Work orders with approved lines exist; you are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Drag a work order from the sidebar onto a technician cell and complete the scope picker (and spread modal for a large job).
 2. Left-click an empty spot in a cell and create an event via 'Create Event'; do the same on the timeline in day view.
@@ -8242,7 +8587,7 @@
 5. Edit fields in the shift and event detail modals.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Drag-and-drop from the sidebar, the scope picker, and the spread modal all work.
 2. Shift and event creation works, including via the menu opened by left-clicking empty grid space in both week and day view.
@@ -8250,473 +8595,473 @@
 4. Edge-resize and horizontal drag work in day view.
 5. Modal fields are editable and save.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as an edit-without-delete user
 </t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14.1 (Schedule: Edit))</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Edit without Delete: the user can create and modify but not remove</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Edit but NOT Delete.
 2. A shift, a series, and an event exist (some created by this user).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Open a shift's detail modal and look for the delete action / trash icon.
 2. Open an event's modal and look for a delete action.
 3. Try to find ANY way to remove a shift or event.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The delete action and the trash icon are hidden in the shift modal.
 2. Events likewise offer no delete.
 3. No path exists to remove shifts or events - while creating and modifying still work.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as an edit-without-delete user
 </t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14.1 (Schedule: Delete - without it))</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Schedule: Delete unlocks deleting shifts and events</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule: Delete.
 2. A standalone shift, a series, and an event exist.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Delete the standalone shift.
 2. Delete a series shift and read the scope options.
 3. Delete the event.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The delete action is available and works for shifts.
 2. Series deletion offers its scopes (this shift / this and after / whole series).
 3. Events can be deleted too.
 4. Undo toasts appear (restore the items via Undo to clean up).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a delete-capable user
 </t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14.1 (Schedule: Delete))</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Permission tiers nest: Delete requires Edit, Edit requires View</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as an admin who can edit custom roles.
 2. A ZZAUTOTEST custom role exists (create one; delete after).</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. In the role's Schedule permissions, try to enable Edit while View is off.
 2. Try to enable Delete while Edit is off.
 3. Enable View, then Edit, then Delete in order.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Edit cannot be granted without View (the admin UI enforces or auto-selects the dependency).
 2. Delete cannot be granted without Edit.
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14 (Delete requires Edit and Edit requires View))</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Schedule without Work Orders: View - the sidebar hides the work order list</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF.
 2. Shifts already exist on the grid.
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Look at the left sidebar.
 2. Interact with the shifts already on the grid (hover, open modal, and - if the role has Edit - move one).
 3. Try to find any way to drag a new work order onto the grid.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The sidebar hides the work order list and the line drill-down; the mini calendar remains available.
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
 3. New work orders cannot be dragged on - the WO list is simply not visible.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.2). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§14.2)</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>No own-only restriction: a View user sees ALL technicians' shifts</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. Shifts and events exist for SEVERAL different technicians.
 2. A test user with a low-tier View-only role exists (and is themselves one of the technicians).
 3. You are signed in AS that user, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Read the grid across all departments and technicians.
 2. Check 'My Shifts' in 'Filter and Display' is OFF (default).</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a view-only technician
 </t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14.3)</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Grid rows are department-based, not role-based</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. A staff member with a NON-technician role (for example Office) is assigned to a department that is visible on the schedule (set up; restore after).
 2. Another staff member has NO department assignment.
 3. You are signed in on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Look for the department-assigned Office staff member among the grid rows.
 2. Look for the staff member with no department.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
 2. The staff member without a department does not appear as a row.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.4). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.4). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§14.4)</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Clocking into line tasks is gated by the staff 'Time Clock' setting</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. Two staff members exist: one with the 'Time Clock' setting ON on their staff record, one with it OFF (set up; restore after).
 2. Both appear as schedule rows and have shifts on work order lines.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. As (or with) the Time-Clock-ON staff member, attempt to clock into their work order line task.
 2. As (or with) the Time-Clock-OFF staff member, attempt the same.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Time-Clock-ON staff member can clock in.
 2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.4). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.4). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as each of the two staff members
 </t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§14.4 (Time Clock setting))</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>With Work Orders: View OFF, work order details on shifts are hidden</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. A test user's role has Schedule access but Work Orders: View OFF (assign a suitable role; restore after).
 2. Shifts already exist on the grid, created by a fully-permissioned user, for units that have customers, scheduled lines, and a VIN.
 3. You are signed in AS that user on a desktop browser, on the Schedule page.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. Look at a shift block on the grid and read its text lines.
 2. Hover the shift for its tooltip.
 3. Open the shift's detail modal and read the work-order-derived fields.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Work-order-derived details (customer, the scheduled line list, and any money-bearing fields) are hidden or masked wherever they would normally appear - on the block, in the tooltip, and in the modal.
 2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
 3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.2). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.2). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§14.2 (Work Orders: View dependency))</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Default roles start at the Schedule level the spec names (view-only vs edit)</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as an admin who can view and edit the roles and their permissions.
 2. You can sign in (or switch) to a user who holds each role you need to check.
 3. Write down each role's current Schedule permissions before you change anything, and put them back afterwards.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Open the roles screen where each role's permissions are listed.
 2. Take these roles one at a time - Technician, Parts Manager, Parts Tech, Office, Time Clock - use 'Reset To Template' so the role is back at its default, then read its Schedule permissions (View, Edit, Delete).
@@ -8726,61 +9071,61 @@
 6. Put every role's permissions back the way you found them.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Technician, Parts Manager, Parts Tech, Office and Time Clock each have Schedule View turned ON and Schedule Edit and Schedule Delete turned OFF.
 2. Service Manager, Senior Service Advisor, Service Advisor and Foreman each have Schedule Edit turned ON (so they also have View).
 3. The user from step 4 gets the read-only schedule - nothing can be dragged onto the grid and no shift can be created.
 4. The user from step 5 can drag a work order onto the grid and create a shift.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a holder of each permission level
 </t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>SV-8685 [epic - cross-cutting - no single-story owner] (§14.1 default role tiers - view-only role list + edit role list; spec v23 2026-07-30)</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>SV-8685 [epic - cross-cutting - no single-story owner] (§14.1 default role tiers - view-only role list + edit role list; spec v27 2026-08-07)</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Below 960px the grid scrolls sideways and the sidebar collapses</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. You are on the Schedule page in week view with shifts visible.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Resize the browser window to just under 960px wide.
 2. Try to reach the right-hand days of the grid.
 3. Narrow the window further and watch the sidebar.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Below the 960px minimum supported width, the grid scrolls horizontally rather than breaking.
 2. All days remain reachable by horizontal scroll.
@@ -8791,55 +9136,55 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8942)
 </t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>SV-8686,SV-8687 (§11 (Responsiveness - grid scrolls horizontally below 960px; sidebar collapses))</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>The sidebar work order list and line drill-down stay smooth with 50+ items</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. 50 or more open work orders exist (seed ZZAUTOTEST orders if the environment lacks them), including one order with many approved lines.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the full work order list top to bottom quickly.
 2. Open the many-line order's drill-down and scroll it.
 3. Type in the search while the long list is shown.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
@@ -8849,213 +9194,213 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8913)
 </t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§11 (Performance - sidebar list and line drill-down virtualize at 50+ items))</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>The grid renders smoothly at full load - 15 technicians over 7 days</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
 2. The schedule is loaded to roughly the spec's stated scale: around 15 technician rows across a week with several shifts per cell (seed ZZAUTOTEST shifts as needed).
 3. You are on the Schedule page in week view.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the grid vertically and horizontally.
 2. Switch between Day, Week, and Month.
 3. Hover several blocks and open/close a modal.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The grid renders and scrolls smoothly at this scale.
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§11 (Performance))</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Shop closures do NOT block spread in V1 - shifts can land on closure days</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A shop closure (holiday/inventory day) is defined at the shop level on a working weekday inside the planned spread window (set it up; remove after).
 3. A large job (multi-day scope) is ready to spread.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Open the spread step across a window that contains a shop closure day.
 2. Expand the preview and find the closure day.
 3. Confirm the spread and check the grid.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The closure day is NOT struck through or skipped by the spread in V1.
 2. A shift CAN be placed on the shop closure day (only weekend days with no business hours are skipped).
 3. The end date follows the normal daily distribution - no extra day is added for the closure.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§12, §4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§12, §4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - waiting on the product owner's answer, and the shop-closure setting does not exist in the build
 </t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§12 (Shop closures),§4.5)</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Scheduled, estimated and actual clocked hours are three separate numbers</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. A line has estimate 10h; a technician has 6h scheduled against it and some different amount of time actually clocked (seed what is possible).</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. Open the shift's detail modal.
 2. Compare the scheduled hours, the estimate, and the logged/actual time.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. All three quantities are shown/derivable and may differ from one another.
 2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5, §12). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5, §12). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§4.5 (three separate quantities),§12)</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>A multi-week series keeps the same local start time across the clock change</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser with Schedule: Edit.
 2. The shop's location observes daylight saving (clocks change); the next clock-change date is known (e.g. the November change).
 3. A job large enough to spread across the clock-change date exists.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. Spread the job across a window that includes the clock-change date (shifts before and after it).
 2. Open shifts from before the change and from after the change and read their start times.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every shift in the series starts at the SAME local wall-clock time (e.g. 8:00 AM) on both sides of the clock change.
 2. No shift in the series silently moves an hour earlier or later after the change date.
@@ -9064,47 +9409,47 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5), which covers spreading work across days. That specification says nothing about clock changes or daylight saving - those words do not appear in it at all - so the point above comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8848)
 </t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§4.5 + tech-plan D2 NFR-005 DST)</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Schedule and all its dialogs display correctly in dark mode</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser; the app's dark mode / theme toggle is available.
 2. The Schedule page has shifts, an event, a conflict, and capacity bars visible.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. Switch the app to dark mode.
 2. Look over the Schedule grid: shift blocks, event cards, capacity bars, conflict styling, tooltips.
@@ -9112,267 +9457,323 @@
 4. Switch back to light mode and spot-check again.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. In dark mode every part of the Schedule stays readable - no white-on-white or black-on-black text, no unreadable labels or invisible icons.
 2. Every dialog and popover opened from the Schedule follows the dark theme too.
 3. Conflict and overtime cues remain distinguishable (they never rely on colour alone - text/icon still present).
 4. Switching back to light mode restores the normal look with nothing stuck in dark colours.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>SV-8685 (§11 (Dark theme - user-selectable Light / Dark,persisted per user))</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>On a narrow window the panel button still works and your choice holds</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Edge Cases and Responsiveness</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Your role has the Schedule: View permission.
+3. You are on the Schedule page.</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>1. Make the browser window narrower than 960 pixels wide. (The panel folding itself away on its own at that width is checked by a separate test - this test is about the button.)
+2. Find the panel button at the far-left end of the row of buttons above the grid and click it.
+3. Keep the window at that narrow width and carry on using the page - click a couple of dates in the small month calendar and scroll the grid.
+4. Now make the browser window wider again, back over 960 pixels.</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The panel button still works on a narrow window: it is not hidden, greyed out or unresponsive below 960 pixels, and clicking it shows the left panel by hand even at that width.
+2. The panel stays as you set it while you keep working at that width - moving around the page does not undo your choice.
+3. Your choice only stops applying when the window is resized back across the 960 pixel mark; at that point the page goes back to deciding for itself whether the panel is shown.
+Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
+---
+This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse, Narrow viewports). Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: HOLD - the panel collapse control is not in the build
+</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>SV-8686 (§5.3 Panel collapse - Narrow viewports; toggle works at any width and the manual choice holds until the next resize)</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Shifts and events created before the Schedule rewrite still appear after it</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. This case runs around the Schedule rewrite release: before the release, note (or create) a handful of scheduled shifts and calendar events - including at least one future-dated one - with their technician, day, and time.
 2. The release (which replaces the Schedule behind the scenes) has been deployed.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. After the release, open the Schedule and navigate to the dates of the noted entries.
 2. Compare each noted shift and event against what the grid now shows.
 3. Open a couple of them to check their details.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every shift and event that existed before the release is still there after it - same technician, same day, same time, same work order.
 2. Events are still events and shifts are still shifts (nothing changed kind or vanished).
 3. Their details open normally and are editable/deletable like any other entry.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - cannot be run now - it needs shifts noted BEFORE the release, and the release is already deployed
 </t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (tech-plan §3 FR-015 data migration)</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Dashboard shows one schedule row per work order even with many shifts</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. One work order has been spread across MANY days for a technician (e.g. a 2-week series - 10+ daily shifts).</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. Open the Dashboard and find its schedule/today sections.
 2. Look for the spread work order in those sections.
 3. Count how many rows that one work order produces.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Dashboard shows that work order as ONE row (covering the whole scheduled span), not one row per daily shift.
 2. Note for the tester: before this release the Dashboard duplicated such a work order once per scheduled day - showing one combined row now is the intended fix, do not report it as a missing-rows bug.
 3. Work orders with a single shift are unaffected.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - the Dashboard section this test needs does not exist in the build
 </t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (tech-plan §4 Dashboard FR-016)</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>A work order created with an appointment shows up on the Schedule board</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. You can create a work order and set its appointment/scheduling details during creation.</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order and give it an appointment (a scheduled date/time) as part of the creation flow.
 2. Open the Schedule and navigate to that date.
 3. Find the new work order on the board.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The appointment created with the work order appears on the Schedule board at the chosen date/time.
 2. It behaves like any other scheduled entry (opens, moves, deletes normally).
 3. It also appears in the Dashboard's schedule section for that day.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - work order creation offers no appointment in the build
 </t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (tech-plan §4 WO-create AppointmentScheduler)</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>A multi-location technician's shift appears only on the work order's location</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. A technician is enrolled at TWO locations (set this up if needed).
 3. A work order belonging to location A has a shift scheduled on that technician.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>1. Open the Schedule while working in location A and find the technician's shift.
 2. Switch to location B and open its Schedule for the same date.
 3. Look for the same shift on location B's board.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The shift appears on location A's board (the location the work order belongs to).
 2. The shift does NOT appear on location B's board, even though the technician is enrolled there too.
 3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (tech-plan §3 WO-primary location resolution)</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>Work order form offers a Priority (High/Medium/Low) that drives the sidebar</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release (which adds the Priority field) is deployed.
 2. You can create/edit a work order.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order create/edit form and find the Priority field.
 2. Read its default value on a brand-new work order.
@@ -9380,109 +9781,109 @@
 4. Open the Schedule sidebar, find that work order's card, and apply the Priority = High filter.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The work order form offers a Priority choice of High, Medium, Low.
 2. A new work order has NO priority pre-selected by default.
 3. After saving, the Schedule sidebar reflects the chosen priority and the Priority filter finds the work order under High.
 4. A work order with no priority set simply shows none (it is not treated as an error).
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - the Priority field this test needs does not exist in the build
 </t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§5.1 + tech-plan FR-P4 WO priority)</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>API - Schedule reads need View; writes need Edit; deletes need Delete (403)</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build (new /api/schedule endpoints) is deployed.
 2. Three test users exist: one with NO Schedule permission, one with Schedule: View only, one with Schedule: View + Edit (but not Delete).
 3. A shift id from the current location is known.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. As the user with NO Schedule permission, call GET /api/schedule/board?from=&amp;to= for the current week.
 2. As the View-only user, call the same GET, then try POST /api/schedule/shifts (a minimal single-shift body) and PATCH /api/schedule/shifts/{id}.
 3. As the View+Edit user, repeat the POST and PATCH, then try DELETE /api/schedule/shifts/{id}?scope=shift.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. No Schedule permission: the board GET is refused with HTTP 403.
 2. View-only: the board GET returns HTTP 200 with the grid data; the POST and PATCH are refused with HTTP 403.
 3. View + Edit: the POST and PATCH succeed (HTTP 201/200); the DELETE is refused with HTTP 403 because the user lacks Schedule: Delete.
 4. Each refusal is a clean 403 response - never a server error.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14), which sets the three permission levels. That specification does not describe what the server returns when a request is refused, so the refusal responses above come from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs three separate sign-ins, one per permission level
 </t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14 + tech-plan §4 NFR-003 permissions)</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>API - Series past 8 weeks returns 409 until acknowledged; over 120 shifts 422</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed; an API session with Schedule: Edit exists.
 2. A schedulable work order line id and a technician staff id are known.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>1. POST /api/schedule/shifts with a spread whose window exceeds 8 weeks (56 calendar days), WITHOUT acknowledgeLongSeries.
 2. Repeat the same POST with acknowledgeLongSeries=true.
@@ -9490,132 +9891,132 @@
 4. Check the board for leftovers after the refused calls.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The over-8-week create is refused with HTTP 409 (a 'series too long' error) - nothing is created.
 2. With acknowledgeLongSeries=true the same request succeeds (HTTP 201) and returns the full materialized series under one series id.
 3. The over-120-shift request is refused with HTTP 422 even WITH the acknowledgement - the hard cap cannot be overridden.
 4. Refused calls leave no partial series behind.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§4.5 + tech-plan D8 error cases)</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>API - No pricing fields in Schedule responses; WO details need Work Orders View</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed.
 2. A shift covering work order lines exists.
 3. Two API users: one with Schedule: View + Work Orders: View, one with Schedule: View but WITHOUT Work Orders: View.</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>1. As the full user, call GET /api/schedule/board, GET /api/schedule/shifts/{id}, and GET /api/schedule/work-orders and search the raw responses for money fields (price, cost, rate, total, $ amounts).
 2. As the user WITHOUT Work Orders: View, call GET /api/schedule/board and GET /api/schedule/shifts/{id} and read the work-order-derived fields (customer, unit, VIN, lines).</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. No Schedule response contains any pricing/money field for ANY caller - the schedule never returns labor, totals, or dollar amounts.
 2. For the caller without Work Orders: View, the work-order-derived details (customer, unit, VIN, line names) are absent/empty in the response itself - not just hidden on screen.
 3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 23 (§14). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14 + tech-plan D6/NFR-002 no pricing)</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>API - A shift from another location returns 404, not another shop's data</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed.
 2. Two locations exist; a shift exists at location B; your API session is scoped to location A.
 3. The location-B shift's id is known (create it while switched to B, then switch back to A).</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>1. While scoped to location A, call GET /api/schedule/shifts/{id} with the location-B shift id.
 2. Also try PATCH /api/schedule/shifts/{id} on the same id.
 3. Call GET /api/schedule/board for location A's current week.</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The foreign-location GET is refused as not found (HTTP 404) - the response reveals nothing about the other location's shift.
 2. The PATCH on the foreign id is refused the same way (404) - no cross-location edit is possible.
 3. Location A's board contains only location A's shifts - nothing from location B leaks in.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 23 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (tech-plan NFR-001 location scoping)</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J175"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
 3. The left panel is the work order sidebar: a mini calendar at the top and a work order list beneath it.
 4. The main area is the schedule grid showing technician rows, with a toolbar above it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3, §3.1, §3.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3, §3.1, §3.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -584,13 +584,9 @@
 2. Week: the grid shows a 7-column Monday-to-Sunday layout with stacked shift chips per cell.
 3. Month: the grid shows a compact calendar with per-day capacity bars and shift chips.
 4. The same shifts appear in all three views - each one drawn to suit that view: positioned on the hour line in Day, as a chip in the day column in Week, and as a compact chip in Month.
-What you should see today: Week view runs Sunday to Saturday. The seven columns read Sunday Aug 2, Monday Aug 3, and so on to Saturday Aug 8, instead of starting on Monday. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8826
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2, §6). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8826)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2, §6), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -642,7 +638,7 @@
 2. Each department's technicians are listed beneath that department's header.
 3. Every staff member assigned to a visible department appears as a row, regardless of their role.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2, §14.4). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2, §14.4), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -696,7 +692,7 @@
 2. Expanding shows the technician rows again, unchanged.
 3. Other department groups are unaffected.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -746,7 +742,7 @@
           <t xml:space="preserve">1. No such toggle exists - the department-grouped rows are the only grid grouping.
 2. Department visibility is controlled only through the department toggles in the 'Filter and Display' dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -799,7 +795,7 @@
 2. Shifts without a technician sit in this row.
 3. The unassigned shift uses the same block layout as regular shifts (customer, unit, line name / line count) - it simply has no technician.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2, §4.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2, §4.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -852,13 +848,9 @@
           <t xml:space="preserve">1. The Schedule page opens.
 2. Of the three buttons Day, Week and Month, the one that is switched on (highlighted) is Day.
 3. The grid shows the Day layout: a 24-hour timeline for each technician row, with shifts placed at their times.
-What you should see today: The Schedule opens on Week view. Week is the highlighted button and the grid draws the seven-column week layout. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8863
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the acceptance criterion of its story SV-8686, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 27 does not say which view the page opens on, so this expectation comes from the story rather than the specification. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8863)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the acceptance criterion of its story SV-8686, read on 11 August 2026, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 27 does not say which view the page opens on, so this expectation comes from the story rather than the specification. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -909,7 +901,7 @@
 2. The toolbar date label updates to the new range.
 3. The clicked date is highlighted as the selected date in the mini calendar.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1, §5.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1, §5.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -964,7 +956,7 @@
 2. Choosing a month shows that month in the mini calendar.
 3. The main grid can then be navigated by clicking a date in the newly shown month.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1018,7 +1010,7 @@
           <t xml:space="preserve">1. The calendar grid collapses (hides), leaving more room for the work order list below.
 2. Clicking again expands the calendar grid back.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1, §5.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1, §5.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1073,7 +1065,7 @@
 2. Today's date has its own distinct indicator, different from the selection.
 3. Hovering a week row highlights that whole week row.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1127,7 +1119,7 @@
 2. The list scrolls when there are more cards than fit.
 3. There are no Assigned/Unassigned tabs - assignment is available only as a filter behind the 'Filter' button.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1, §5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1, §5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1184,7 +1176,7 @@
 4. A lead technician row with the technician's avatar and name.
 5. A colored left border whose color reflects the work order's status.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1242,13 +1234,9 @@
 3. Unit-number search shows only cards with that unit.
 4. Technician-name search shows only cards where that technician is on the work order - and it must work when you type the technician's name the way the card shows it, first name and last name together (for example 'Andrew Wade').
 Note for the tester: searching the number exactly as the card shows it (for example S-15875) does work, and so does the bare number (15875). Searching the longer shop-prefixed form (for example S8685-15875) returns nothing; that is already raised as SV-8841 (https://shopview.atlassian.net/browse/SV-8841), so do not raise it again.
-What you should see today: Typing a technician's full name finds nothing. 'Andrew' on its own finds 14 work orders and 'Wade' on its own finds the same 14, but 'Andrew Wade' finds 0, and so do 'andrew wade' and 'Wade Andrew'. A full customer name such as 'Vuchester Retail' works, so it is not a problem with spaces. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8873
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8873)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1302,7 +1290,7 @@
 2. Deleting characters widens the results again.
 3. With very many work orders, the list may load further results in pages as you scroll - that is expected, not a fault.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1357,7 +1345,7 @@
 2. The app does not error; the sidebar remains usable.
 3. Clearing the search restores the full list.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1411,7 +1399,7 @@
 2. Applying a filter narrows the flat card list.
 3. The 'Filters' button shows a badge with the number of active filters.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1467,7 +1455,7 @@
 2. Assigned: only work orders with a technician assigned remain.
 3. There are no Assigned/Unassigned tabs - this filter is the only assignment split.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1, §3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1, §3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1525,7 +1513,7 @@
 4. The card left-border colours of the remaining cards are consistent with that status.
 Note for the tester: this shop's schedule list only holds work orders in two statuses, Approved and Review, so most of the other choices correctly come back empty. An empty list for a status no work order is in is the right answer, not a fault.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1580,7 +1568,7 @@
           <t xml:space="preserve">1. The Priority group offers High, Medium, and Low.
 2. Only High-priority work orders remain in the list.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1634,7 +1622,7 @@
 2. The full work order list is shown again.
 3. The active-count badge on the 'Filter' button disappears (or shows zero).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1689,7 +1677,7 @@
           <t xml:space="preserve">1. The list shows only work orders that match BOTH the text search and the structured filter.
 2. Removing either the search text or the filter widens the list to the remaining condition.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1746,7 +1734,7 @@
 4. A back control is shown to return to the card list.
 5. Clicking back restores the work order card list.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1801,7 +1789,7 @@
 2. No line that has never been approved appears anywhere in the schedule sidebar - for example a line still sitting on an estimate, or one that was declined.
 3. The line count in the drill-down header matches the number of APPROVED lines on the work order - a line that was never approved is neither listed nor counted.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1856,7 +1844,7 @@
 2. The current technician roster is shown as an avatar stack plus a count; there is no cap on how many technicians a line can have.
 3. Each line row has its own drag handle, so it can be dragged independently onto the grid.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1, §8.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1, §8.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1911,7 +1899,7 @@
 2. The line with a technician does not show the badge.
 3. After a technician is scheduled onto the badge-bearing line, the badge goes away.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1966,7 +1954,7 @@
           <t xml:space="preserve">1. Typing a line title narrows the list to matching lines.
 2. Typing the customer name returns no results - the line search matches line titles only (the list is already scoped to one work order, so customer/unit/WO fields are not searched).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2022,7 +2010,7 @@
 2. Unscheduled lists only the lines that have no shifts yet, and its count matches.
 3. All lists every approved line, and its count matches the drill-down header's line count.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.1, §5.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1, §5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2076,7 +2064,7 @@
 3. The technician is added to that line's labor roster on the work order.
 4. A toast with an Undo option appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1, §1.2, §7). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.1, §1.2, §7), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2129,7 +2117,7 @@
 2. It offers 'Schedule whole work order' at the top, the individual line rows beneath, and a 'Select multiple' control.
 3. No shift is created until a scope is chosen.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1, §4.3). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.1, §4.3), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2183,7 +2171,7 @@
 2. The block's last text line shows that line's name.
 3. The technician is added to that line's roster only (not to the order's other lines).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2237,7 +2225,7 @@
 2. Its header shows the chosen scope and a 'Change scope' back-link.
 3. No shifts exist yet until the spread is confirmed.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1, §4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.1, §4.5), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2289,7 +2277,7 @@
           <t xml:space="preserve">1. The shift is created straight away - the spread step does NOT appear.
 2. The shift sits on the dropped day only.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2341,13 +2329,9 @@
           <t xml:space="preserve">1. The cell currently under the cursor highlights as a drop target.
 2. A ghost block follows the drag showing the line name and its hours.
 3. Releasing outside any valid cell creates nothing.
-What you should see today: Nothing highlights and nothing follows the cursor while you drag a line from the list on the left onto the grid. No cell lights up as a drop target, and the faint shape that does follow the cursor is empty - it does not show the line name or the hours. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8840
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8840)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2403,7 +2387,7 @@
 4. Dragging the same line onto a second technician adds that technician to the line's roster as well - the technician who was already there stays on it.
 5. Nothing asks you to swap or replace the technician who was already there, and no limit is reached on how many technicians a line can have.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§1.2, §4.3, §7). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§1.2, §4.3, §7), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2454,13 +2438,9 @@
         <is>
           <t xml:space="preserve">1. The item can be placed onto a cell without holding a drag - clicking arms it, and clicking a cell places it.
 2. The result is the same as the equivalent drag-and-drop (scope picker / spread step rules apply the same way).
-What you should see today: There is no way to place a job by clicking. The work order card in the panel on the left has no button on it at all - not when you hover it, and not inside its line list - so dragging is the only way to schedule anything. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8957
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8957)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2518,7 +2498,7 @@
 Please read before running this test: what should happen in MONTH view specifically has not been settled yet. The Schedule specification version 27 says that a work order is dragged from the sidebar onto a cell in the grid without naming which view, and the acceptance criterion of story SV-8688 names only Week view. The question has been put to the product owner on SV-8870 (https://shopview.atlassian.net/browse/SV-8870), together with the point that Month view invites the user to drag ("Nothing is scheduled in this range. Drag a work order from the list to book it."). Until the product owner answers, treat a failure here as already reported under SV-8870 - mark it FAILED and link SV-8870; do not raise a new ticket.
 What was seen on the build checked: the card lifts and follows the mouse, but no day box shows as a drop target and releasing does nothing at all - no scope picker, no shift, no message. The same drag of the same work order in Week view does open the scope picker, so the difference is Month view itself.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.1, §4.2), which describe dragging a work order from the sidebar onto a cell in the grid and the order of preference for the start time. Neither that specification nor story SV-8688 says whether Month view accepts the drop, so that point is an open product-owner question rather than a settled requirement. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.1, §4.2), read on 11 August 2026, which describe dragging a work order from the sidebar onto a cell in the grid and the order of preference for the start time. Neither that specification nor story SV-8688 says whether Month view accepts the drop, so that point is an open product-owner question rather than a settled requirement. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
 </t>
         </is>
@@ -2574,7 +2554,7 @@
 4. Each line row shows the line title and its estimated hours.
 5. Rows for lines that already have technicians show the current roster as an avatar stack plus count.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.3), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2628,7 +2608,7 @@
 2. The block's last text line reads 'N Lines' (with N = the line count).
 3. The technician is added to the roster of every one of those lines.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.3, §4.4). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.3, §4.4), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2681,7 +2661,7 @@
 2. The picker closes.
 3. The block's last text line shows the line's name.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.3), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2740,7 +2720,7 @@
 4. A 'Cancel' control leaves tick-box mode and returns you to the ordinary single-tap line list, without creating anything and without closing the picker.
 5. Confirming creates ONE shift covering exactly the ticked lines, and the technician is added to those lines' rosters only - not to the other lines.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.3). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.3), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -2793,7 +2773,7 @@
           <t xml:space="preserve">1. The shift starts at the technician's own configured start time (6:00 AM in the example), not the shop's business-hours start.
 Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2845,7 +2825,7 @@
         <is>
           <t xml:space="preserve">1. The shift starts at the shop's business-hours start time.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2897,7 +2877,7 @@
         <is>
           <t xml:space="preserve">1. The shift starts at 7:00 AM - the general default working day (7:00 AM to 7:00 PM) applies.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2950,7 +2930,7 @@
 2. The start time aligns to the timeline position (see the 15-minute snapping case).
 Note for the tester: every time on the Schedule is currently shown six hours later than the time it was booked for. That is already reported as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Read the position on the timeline rather than the printed time, and do not raise it again.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3003,7 +2983,7 @@
 2. It has no technician (and no technician is added to the line's roster by this drop).
 3. The block uses the same anatomy as a regular shift (customer, unit, line name / 'N Lines').
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2, §3.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2, §3.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3055,7 +3035,7 @@
         <is>
           <t xml:space="preserve">1. The unassigned shift starts at the shop's business-hours start (there is no technician whose hours could apply).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3108,13 +3088,9 @@
           <t xml:space="preserve">1. The shift is now assigned to that technician (it leaves the Unassigned row and sits in the technician's row).
 2. The technician is added to the affected line's roster.
 3. The technician's own working hours now apply to the shift's timing.
-What you should see today: Giving an unassigned job to a technician quietly changes its saved start time to six hours earlier. A job booked for 7:00 in the morning is saved as 1:00 in the morning after it is assigned, with no warning. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8924
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§3.2, §4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8924)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2, §4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3172,7 +3148,7 @@
 4. Clicking 'Change scope' takes the modal back to the scope picker (step 1) without creating anything.
 5. Choosing a new scope updates the spread step's header and hours accordingly.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3226,7 +3202,7 @@
 3. 'Full estimate', '1 week', and '2 weeks' apply on selection with no extra fields - the modal stays to one line for these.
 4. The preview summary updates to match each selection.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3278,7 +3254,7 @@
           <t xml:space="preserve">1. Choosing 'Until a date…' reveals a single 'finish by' date field (this is the only custom control shown).
 2. Picking a date updates the preview so the series ends by that date.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3329,7 +3305,7 @@
           <t xml:space="preserve">1. Choosing 'Specific hours…' reveals an hours stepper control.
 2. The preview updates to spread exactly the entered hours across working days.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3383,7 +3359,7 @@
 2. It can be changed; technician B's series then starts after A's series ends (sequential, not parallel).
 3. B's series is created from the adjusted start date onward.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -3438,7 +3414,7 @@
 3. Shop closures and public holidays are NOT skipped in V1 - shifts can be placed on those days.
 4. The end date is a result of the daily distribution (for 40h at 8h/day starting Monday, the series ends on the fifth working day).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5, §12). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5, §12), read on 11 August 2026. That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
 </t>
         </is>
@@ -3491,7 +3467,7 @@
 2. Expanded: a week-by-week breakdown of the planned shifts.
 3. Skipped days are struck through and show the reason they are skipped - in V1 the only skip reason is a weekend day with no working hours set.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026. That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -3545,7 +3521,7 @@
 3. Each daily shift keeps its own day and hours.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5, §4.6, §8.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5, §4.6, §8.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -3598,7 +3574,7 @@
 2. There is no shared 'remaining hours' counter across technicians and no splitting of a shift.
 3. Planned hours across technicians may now exceed the estimate - this is expected and produces no error (progress is driven by clocked-in time).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5, §12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5, §12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3654,7 +3630,7 @@
 3. A single spread that would create more than 120 daily shifts is refused outright - no confirmation can override it, and no shifts are created for that attempt.
 4. No half-created series is left behind after a refused attempt.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026, with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3707,13 +3683,9 @@
           <t xml:space="preserve">1. The series renders as one continuous bar wrapping across the week rows.
 2. It is labeled once at the start (including the technician); later weeks show a faded 'continues'-style label instead of repeating the full label.
 3. Weekend columns inside the series are empty (no bar) when no business hours are set for those weekend days.
-What you should see today: In Month view the bar for a multi-day job does not say whose it is. It reads, for example, 'Xiriver Apparel  24069  19 Lines  Part of a series' with no technician name anywhere on it. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8958
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.6). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8958)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.6), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3766,7 +3738,7 @@
 2. Chevrons at the banner's edges indicate the series continues beyond the visible week (both sides, on a middle week).
 3. A 'week N of M' cue shows the position within the series.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.6). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.6), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3818,7 +3790,7 @@
           <t xml:space="preserve">1. The day shows a single time-positioned block (no spanning bar - only one day is visible).
 2. The block carries a cue in the spirit of 'part of an M-week job' indicating it belongs to a longer series.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.6). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.6), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3872,7 +3844,7 @@
 2. The overlapping day is flagged as a Double-booked conflict, exactly as it would be for standalone shifts.
 3. The detail modal shows that single day's shift (its own day and hours) while indicating it belongs to the series.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.6, §8.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.6, §8.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3925,7 +3897,7 @@
 3. Last line: the name of the scheduled line.
 4. No work order number appears on the block.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.4). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.4), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3979,7 +3951,7 @@
 2. The subset block reads '2 Lines' - the block does not distinguish whole-order from subset beyond the count.
 3. Each detail modal lists exactly which lines the shift covers.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.4, §12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.4, §12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4032,7 +4004,7 @@
 2. The conflicted block shows the conflict (warning) icon on its first line - and that is the only icon that ever appears on a block.
 3. No scope icons distinguish whole-order from subset shifts.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.4). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.4), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4087,7 +4059,7 @@
 3. The row stays at its normal height.
 4. No conflict is flagged for back-to-back (non-intersecting) shifts.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.7, §12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.7, §12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4139,7 +4111,7 @@
 2. The row grows in height to fit the lanes.
 3. The overlap is also flagged as a Double-booked conflict (stacking reads as 'resolve me').
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.7, §4.11). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.7, §4.11), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4191,16 +4163,17 @@
           <t xml:space="preserve">1. At most 3 lanes are visible.
 2. The remaining overlapping shifts collapse into a '+N more' affordance (here '+2 more').
 3. Clicking it opens a popover listing the hidden shifts.
-4. The hidden shifts can be opened from that popover.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.7). Last checked against build v3.5-7ec992f on 8/6/2026.
+4. You can tell the '+2 more' is something to click without relying on its colour: it carries the count as words you can read, and it is drawn as its own distinct shape - a small chip, pill or button - not just a differently coloured patch of the lane.
+5. The hidden shifts can be opened from that popover.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.7 Overlap and lane stacking and §11 Accessibility - the overflow uses shape), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>SV-8693 (§4.7)</t>
+          <t>SV-8693 (§4.7 lane cap and overflow + §11 the overflow uses shape - spec v27 2026-08-07)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -4247,7 +4220,7 @@
 2. Week and month views reach the '+N more' overflow sooner than day view (their cells are narrower), but the same cap-and-overflow model applies.
 3. The overflow affordance opens the hidden-shifts popover in each view.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4303,13 +4276,9 @@
 3. Your manual scroll position stays put - nothing jumps you back to the morning while you remain on the same day.
 4. The timeline is not stuck at the start - it remains a full 24-hour scrollable timeline (midnight to midnight).
 5. Only navigating to another day re-triggers the auto-scroll.
-What you should see today: Day view opens showing midnight at the left-hand edge instead of the start of the working day. The working day starts at 6:00 AM, but 12 AM sits at the left edge, and stepping to the next day leaves it at midnight again. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8837
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.8). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8837)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.8), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4361,7 +4330,7 @@
           <t xml:space="preserve">1. In day view, the date/time header bar stays stuck to the top while the rows scroll beneath it - you always know which time column you are looking at.
 2. The same sticky-header behavior applies in week view.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.8), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4416,7 +4385,7 @@
 3. The duration is unchanged by a horizontal move.
 4. A toast with Undo appears for the move.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.8, §7). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.8, §7), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -4471,7 +4440,7 @@
 3. The resulting times land on 15-minute increments.
 4. The shift's duration on the grid matches the modal's start/end.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.8), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4524,7 +4493,7 @@
 2. Its position matches the actual clock time.
 3. Hovering the now line while your pointer is over the grid shows a label (the current time).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.8). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.8), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4577,7 +4546,7 @@
 2. It shows the customer name, unit number, the VIN (below unit and asset), and the work order id.
 3. The VIN is visible here even though the grid's VIN toggle is off - the modal always shows it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9, §9). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9, §9), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4631,13 +4600,9 @@
 2. Saving/applying the change updates the shift's times.
 3. Changing the date moves the shift to the chosen day.
 4. The grid block reflects the new date/times.
-What you should see today: The start and end time boxes accept any minute you like, not quarter hours. Typing 08:07 is accepted and it is still 08:07 after you click away. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8833
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8833)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4688,13 +4653,9 @@
           <t xml:space="preserve">1. The assigned technician is shown.
 2. A progress indication compares time logged against the estimate (logged hours vs estimated hours).
 3. The numbers are consistent with the line's actual logged time and estimate.
-What you should see today: The time-logged figure shows as fully complete when nothing has been clocked. A shift created moments earlier, on a line nobody has ever clocked into, reads 'TIME LOGGED 1h / 1h' with a full bar. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8834
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8834)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4748,7 +4709,7 @@
 4. This is where whole-order vs subset scope is spelled out (the grid block only says 'N Lines').
 Note for the tester: the absence of any money figure is CORRECT and is what this test expects. The product owner ruled on 22 July 2026 that no total in dollars is shown anywhere on the Schedule. If you see no money figure, pass this test.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9, §4.4). Version 23 of that specification asked for the lines to carry 'labor/total figures'. Version 25, published on 6 August 2026, changed that to 'labor/status figures', so the specification and this test now agree that no money figure is shown; the specification still asks for a labor figure, which this test does not expect, and on that one point the behaviour above follows the product owner's later decision of 22 July 2026, recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9, §4.4), read on 11 August 2026. Version 23 of that specification asked for the lines to carry 'labor/total figures'. Version 25, published on 6 August 2026, changed that to 'labor/status figures', so the specification and this test now agree that no money figure is shown; the specification still asks for a labor figure, which this test does not expect, and on that one point the behaviour above follows the product owner's later decision of 22 July 2026, recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4801,7 +4762,7 @@
 2. The new value persists after closing and re-opening.
 3. Dependent displays (progress vs estimate) reflect the new value.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4855,7 +4816,7 @@
 3. The delete removes the note.
 4. Notes are kept per work order (the same note is visible from another shift of the same work order).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -4909,13 +4870,9 @@
 2. It offers an 'Adjust' action.
 3. 'Adjust' leads to a way to resolve the conflict (for example changing the shift's time).
 4. An unconflicted shift's modal shows no such banner.
-What you should see today: The clash warning appears but gives you no way to fix it. On a shift whose reason is 'Double-booked with ...', 'Extends past working hours' or 'Not a working day' there is no Adjust button - eight clashing shifts were checked and not one offered it. An Adjust button does exist for one other reason ('Starts before working hours'), so do not be surprised to see it there. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8852
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8852)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4967,7 +4924,7 @@
 2. There is no 'Reassign' action in the modal; reassignment is done by dragging a shift to another technician row (covered by its own case).
 3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.9, §7). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9, §7), read on 11 August 2026. That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5021,7 +4978,7 @@
 3. Saving creates an event block on that technician's day.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10, §7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10, §7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5074,7 +5031,7 @@
 2. A live preview block is shown while creating, and dragging resizes it.
 3. Completing creates the event at the previewed time/duration.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5130,7 +5087,7 @@
 4. With all-day ON, specific start/end times are not required (the time fields are disabled or hidden).
 5. The event is created as an all-day block for that technician and day.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10, §8.1). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10, §8.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5184,7 +5141,7 @@
 2. Dropping on another day moves it to that day.
 3. Each move produces a toast with Undo.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10, §7). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10, §7), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
@@ -5236,7 +5193,7 @@
 2. It has a small grey-filled rounded chip on the left containing a calendar icon, and two lines of text beside it: the event name, then the time range in secondary text.
 3. The shift reads as a tinted color-filled block with a colored left rail - the two types are separable at a glance, not by color alone.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5290,7 +5247,7 @@
 2. The color picker offers the same custom color palette as shifts (shared picker with editable labels).
 3. Choosing a color tints the card and the icon chip in matching tones, the same way a colored shift is tinted.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10, §10). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10, §10), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5344,7 +5301,7 @@
 2. The event does NOT create a double-booked or overlap conflict with the shift, and the toolbar conflict count does not increase because of it.
 3. The two behave differently on purpose: an event uses up capacity, but it is never flagged as a conflict.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.10, §4.11, §4.12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10, §4.11, §4.12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5399,7 +5356,7 @@
 3. The toolbar conflict pill's count increases.
 4. The conflict is listed in the pill's dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.11), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5452,7 +5409,7 @@
 2. If the technician's working days DO include that day (for example Saturday hours are configured), a shift on that day is NOT flagged.
 3. The warning icon appears on the block and the conflict is listed in the toolbar dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.11), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5508,7 +5465,7 @@
 3. Both the start and the end follow the hierarchy technician hours, then shop business hours, then the general default working day of 7:00 AM to 7:00 PM.
 4. Warning icon on the block in each case; the conflict appears in the toolbar dropdown.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11, §4.2). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.11, §4.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5563,7 +5520,7 @@
 3. The list covers all current conflicts (count matches the pill).
 4. Resolving a conflict (for example moving the shift) reduces the count - detection is continuous.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11, §6). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.11, §6), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5615,7 +5572,7 @@
           <t xml:space="preserve">1. The grid navigates to the relevant technician and day.
 2. The conflicted shift is brought into view.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.11), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5667,7 +5624,7 @@
           <t xml:space="preserve">1. Overtime is signaled with the 'OT' text tag and amber tones - NOT red or alarming styling.
 2. Red/alarming styling appears only for conflicts and genuine errors.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.11, §4.12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.11, §4.12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5722,7 +5679,7 @@
 2. A more heavily booked day shows a longer blue fill; the fill never exceeds the track (clamped at 100%).
 3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5773,7 +5730,7 @@
           <t xml:space="preserve">1. An amber segment extends past the right edge of the track, showing the excess.
 2. A tick marks the 100% line where the track ends.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5825,7 +5782,7 @@
 2. The tag is text, not a color-only signal.
 3. Overtime (per-technician) and capacity (aggregate) are independent signals.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.12, §11). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.12, §11), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5878,7 +5835,7 @@
 2. The overtime technician's entry is highlighted in amber.
 3. The numbers agree with the shifts actually on the grid.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.12). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5932,7 +5889,7 @@
 3. A time-logged progress bar shows logged vs estimated hours ('X / Yh' style).
 Known issue on the build tested: The tooltip listed ALL FIVE line names on the 5-line series shift with no "+N more lines" row. Spec 4.13: "the individual line names as a short list capped at 3 with a '+N more lines' row". Everything else matched: customer, unit and VIN, date and time range, technician, scope summary "5 lines - 12h" and the progress bar. VIN appears with the toggle off, per Branko 2026-07-31. It has been reported to the QA lead but has no developer ticket yet. Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.13). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.13), read on 11 August 2026. The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5982,13 +5939,9 @@
         <is>
           <t xml:space="preserve">1. The customer name line includes the conflict icon.
 2. The conflict reason is shown in amber.
-What you should see today: The clash warning is at the bottom of the hover tooltip instead of next to the customer name. The first row is just the customer name with no warning mark; the warning only appears in the last row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8959
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.13). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8959)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.13), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6038,13 +5991,9 @@
           <t xml:space="preserve">1. The tooltip shows the event name with its category dot (grey for a default event).
 2. The date and time range are shown.
 3. The technician is shown.
-What you should see today: The event's hover tooltip has no grey dot next to the event name. It shows the name, the date and time range and the technician, and no dot at all. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8893
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.13). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8893)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.13), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6099,7 +6048,7 @@
 3. The tooltip is read-only (no buttons/actions inside it).
 4. Clicking the block opens the full detail modal as normal.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.13). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.13), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6152,7 +6101,7 @@
 2. Near a side edge, the tooltip shifts horizontally to stay fully within the viewport.
 3. No part of the tooltip is clipped off-screen.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.13). Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.13), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6214,10 +6163,10 @@
 6. After you click it and the panel is hidden, the tooltip reads: Show panel
 7. The picture on the button is exactly the same in both states - only the tooltip changes.
 8. Clicking the button at step 4 hides the left panel, and clicking it again at step 7 shows it.
-Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
----
-This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse and §6 Grid toolbar). Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: HOLD - the panel collapse control is not in the build
+Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 7 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse and §6 Grid toolbar), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6273,10 +6222,10 @@
 2. The dividing line between the panel and the grid goes away with it, leaving no leftover line, seam or empty strip where the panel used to be.
 3. The grid grows into the space the panel gave up and lays itself out again in the wider area, so you can see more of the grid than you could before.
 4. Clicking the button a second time brings the panel back to its normal width, and the grid goes back to the size it was at step 1.
-Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
----
-This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse and §3.1 Left panel: work order sidebar). Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: HOLD - the panel collapse control is not in the build
+Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 6 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse and §3.1 Left panel: work order sidebar), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6336,10 +6285,10 @@
 4. The list is still scrolled to roughly the position you left it at.
 5. The panel comes back showing that work order's lines, not the full list of work orders - it returns to whichever of the two views was open when you hid it.
 6. The work order you had opened is still the selected one.
-Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
----
-This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse and §3.1 Left panel: work order sidebar). Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: HOLD - the panel collapse control is not in the build
+Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 7 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse and §3.1 Left panel: work order sidebar), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6393,10 +6342,10 @@
           <t xml:space="preserve">1. With the panel hidden, the pop-up no longer keeps clear of the space the panel used to take up. It sits against the edge of the browser window with a normal margin instead.
 2. The whole pop-up is on screen: nothing is cut off at an edge, pushed outside the window, or left floating with a large empty gap beside it.
 3. The pop-up behaves normally otherwise - you can read it, use its buttons, and close it.
-Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
----
-This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse, Popovers and modals). Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: HOLD - the panel collapse control is not in the build
+Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 5 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse, Popovers and modals), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6455,10 +6404,10 @@
 2. At step 6, after signing out and back in, the left panel is showing again. The choice is not carried over into a new sign-in: it is a working-mode preference for the session you are in, not a saved view setting.
 3. At step 7, the second person's left panel is showing as normal. Your choice applied only to you and did not change what anybody else sees.
 Still to be confirmed, and it affects the second point above. The product owner's description of 7 August says this choice lasts only for the current sign-in. Separately, the design review of 5 August asks for the Schedule's view settings to be stored per user so they survive signing out and back in. Those are two different promises. The question has been put to the product owner and has not been answered yet, so the second point follows the written specification for now. If the answer is that it should survive signing out, the second point will change.
-Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
----
-This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse, Persistence). Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: HOLD - the panel collapse control is not in the build
+Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 7 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse, Persistence), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6508,7 +6457,7 @@
           <t xml:space="preserve">1. The grid jumps to the range containing the current date (today's day, this week, or this month depending on the active view).
 2. The date label updates accordingly.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§6). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6562,7 +6511,7 @@
 3. Month view: each click moves one month; the label shows that month.
 4. The label always matches what the grid displays.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§6). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6578,7 +6527,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Toolbar search highlights matching blocks and fades non-matching ones</t>
+          <t>Toolbar search matches customer, work order, unit, technician and line names</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -6605,30 +6554,26 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>1. Type a customer name into the toolbar search; look at the grid.
-2. Clear, then search a work order number, a unit number, a technician name, and a line name in turn.
-3. Clear the search.</t>
+          <t>1. Type a customer name into the toolbar search, then look at the grid.
+2. Clear the search, then search a work order number, a unit number, a technician name and a line name in turn, looking at the grid after each one.</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Blocks that match the search are highlighted; blocks that do not match fade.
-2. All five fields match: customer name, work order number, unit number, technician name, and line name.
-3. Matching blocks stay in place on the grid (search visually filters; it does not remove or rearrange).
-4. Clearing the search restores all blocks to normal.
-What you should see today: Searching in the grid removes the shifts that do not match instead of fading them. The non-matching blocks disappear from the grid entirely rather than staying visible and dimmed. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8874
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§6). Points 1, 3 and 4 above come from version 23 of that specification, which said 'Non-matching blocks fade; matching blocks highlight'. Version 24, published on 6 August 2026, removed that sentence, and the live version now describes the search only as filtering the grid blocks. Point 2 (the five fields that are matched) is unchanged and still in the live version. The expectation above therefore still follows the older wording and needs the product owner to confirm which one stands. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8874)
+          <t xml:space="preserve">1. The toolbar search filters the blocks on the grid against what you typed.
+2. All five of these are matched against, so searching any one of them finds the blocks it belongs to: customer name, work order number, unit number, technician name, and line name.
+3. Note for the tester: the specification does not say what happens to the blocks that do NOT match - whether they stay on the grid faded out, or disappear until you clear the search. Do not pass or fail this test on that. Check only that searching each of the five things above finds the right blocks. What happens to the non-matching blocks is an open question with the product owner.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6, Search), read on 11 August 2026, which describes the search as filtering the grid blocks by matching against customer name, WO number, unit number, technician name, and line name.
+This case used to also expect matching blocks to highlight and non-matching blocks to fade. That sentence was in version 23 of the specification; version 24, published on 6 August 2026, deleted it, and it has not come back in versions 25, 26 or 27. Story SV-8686 does still ask for it, but that wording has not been touched since the story was created on 27 July 2026, so the specification's deletion is the newer decision and it is the one this case now follows.
+Last checked against build v3.5-7ec992f on 8/6/2026; the wording above was corrected on 11 August 2026 from the documents only, with no build opened.
+AUTOMATION: READY
 </t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>SV-8686 (§6 (Search))</t>
+          <t>SV-8686 (§6 (Search) - spec v27 2026-08-07)</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
@@ -6673,7 +6618,7 @@
 2. Defaults: all department toggles ON, 'My Shifts' OFF, 'VIN' OFF.
 3. There is no separate departments-only control - this dropdown replaces it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§6, §9). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6, §9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6727,7 +6672,7 @@
 2. Other departments are unaffected.
 3. Turning it back on restores the group.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6782,7 +6727,7 @@
 3. This is a personal convenience filter only - it does not change what you are permitted to see (default is OFF, everyone's shifts visible).
 4. For a user who has no technician/staff record of their own, the 'My Shifts' option is not shown at all.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9, §14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9, §14.3), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user with no staff record of their own
 </t>
         </is>
@@ -6839,13 +6784,9 @@
 4. In day view with the VIN on, the lane height grows to fit the extra VIN line and no block text is clipped or cut off.
 5. The 'VIN Number' toggle affects the block only - the tooltip and the modal always show the VIN when the unit has one.
 Note for the tester: the VIN staying visible in the hover summary and in the shift window while the VIN switch is off is CORRECT and is what this test expects. The product owner ruled on 31 July 2026 that the VIN is always visible on hover regardless of the switch. If you see it there, pass this test.
-What you should see today: Month view prints the VIN on shift blocks when the VIN switch is on. It should be left off in Month view because the blocks are small. Day and Week views are correct. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8941
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9, §4.4, §4.8). The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8941)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9, §4.4, §4.8), read on 11 August 2026. The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6899,13 +6840,9 @@
 2. Defaults: Business Hours OFF, Capacity Bars ON, Events ON, Tech Hours OFF, Saturday ON, Sunday ON.
 3. Capacity Bars OFF: the capacity bars disappear from the column headers; ON: they reappear with the same values.
 4. Events OFF: event blocks disappear from the grid while shifts remain; ON: the events reappear unchanged.
-What you should see today: Business Hours starts switched ON in View Options when it should start switched off. The other five options in that menu do start in the right position. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8827
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§6, §9, §4.12). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8827)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6, §9, §4.12), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6958,7 +6895,7 @@
 2. Working hours remain unshaded.
 3. Turning it off removes the shading.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9, §4.8). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9, §4.8), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7010,13 +6947,9 @@
           <t xml:space="preserve">1. Each technician's working hours are displayed next to their name in the row header.
 2. The hours match the technicians' configured hours.
 3. Turning it off hides the hours again.
-What you should see today: Turning on Tech Hours in View Options changes nothing you can see. None of the technician rows shows its working hours, on any day. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8851
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8851)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7068,7 +7001,7 @@
 2. Sunday off too: 5 weekday columns remain (Monday to Friday).
 3. Both back on: the full Monday-to-Sunday 7-column week returns.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§9, §3.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9, §3.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7123,7 +7056,7 @@
 3. Technician B is added to the affected line's roster and technician A is removed from it.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §12). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §12), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7178,7 +7111,7 @@
 4. There is no 'New Shift' item - it was removed from the menu.
 5. This menu is opened by a normal left-click - right-clicking the cell does not open it.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7229,7 +7162,7 @@
           <t xml:space="preserve">1. The menu offers a 'New Work Order' item.
 2. Choosing it directs the user to create a work order (a toast / prompt pointing to the Work Orders tab).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §4.10), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7286,13 +7219,9 @@
 2. When you release it on the other technician's row, a small window asks you to confirm the move to that technician - the same confirmation you get when you move an ordinary shift.
 3. After you confirm, the block sits in the new technician's row, that technician is added to the work order line's technician list, and the previous one is taken off it.
 Why this test covers Week view only: the specification describes reassignment as dragging a shift from one technician row to another, and Month view has no technician rows at all - it is a calendar of day boxes. Whether reassignment should be possible in Month view is therefore part of the open question on SV-8867 and is deliberately not asserted here.
-What you should see today: A shift that is part of a repeating series cannot be moved to another technician in Week or Month view - the block lifts, moves, and then springs back to where it was. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8867
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §12): dragging a shift block from one technician row to another reassigns it and a confirmation handles cross-technician moves, and a series is a grouping over ordinary daily shifts rather than a different kind of thing, so an ordinary shift's behaviour applies to a series member too. Story SV-8692 covers series-aware deletion only and says nothing about reassignment. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8867)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §12), read on 11 August 2026: dragging a shift block from one technician row to another reassigns it and a confirmation handles cross-technician moves, and a series is a grouping over ordinary daily shifts rather than a different kind of thing, so an ordinary shift's behaviour applies to a series member too. Story SV-8692 covers series-aware deletion only and says nothing about reassignment. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7344,7 +7273,7 @@
 2. Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').
 3. The prompt uses routine, lightweight styling - not alarming destructive styling.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7399,7 +7328,7 @@
 3. The removed day's hours return to the estimate's remaining (scheduled hours drop by that day's hours).
 4. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7452,7 +7381,7 @@
 2. The first two shifts remain untouched.
 3. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7505,7 +7434,7 @@
 2. Technician B's independent series is untouched (the scope is per technician's series).
 3. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7560,7 +7489,7 @@
 3. Middle shift: all three options.
 4. Cancelling leaves the series unchanged in every case.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7612,7 +7541,7 @@
           <t xml:space="preserve">1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
 2. The shift is deleted and an undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7665,7 +7594,7 @@
 2. While the cursor is over it, the toast stays (does not auto-dismiss).
 3. After the cursor leaves, it dismisses.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7723,7 +7652,7 @@
 4. Undo after reassign: the shift returns to the original technician, and the line's roster is restored (original tech back on, target tech off).
 5. Every destructive action is undoable within the toast's lifetime.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7, §11). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7779,7 +7708,7 @@
 3. Clicking Undo within the toast's lifetime reverses the action (the deleted shift comes back).
 4. Note for the tester: Undo works by performing a reversing action, not by holding the change back - a change surviving a refresh before Undo is expected, not a bug.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7), which requires the toast and its Undo. That specification does not say how Undo works underneath, so the point above - that the action is already saved and Undo reverses it rather than holding it back - comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026, which requires the toast and its Undo. That specification does not say how Undo works underneath, so the point above - that the action is already saved and Undo reverses it rather than holding it back - comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7835,7 +7764,7 @@
 4. With two layers open, the FIRST Escape closes only the topmost layer, and the SECOND Escape closes the next layer down.
 5. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7892,7 +7821,7 @@
 3. In the note editor, Enter inserts a new line in the note - it does NOT confirm or close the dialog.
 4. The multiline note can be completed and saved normally.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§7). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7945,7 +7874,7 @@
 2. Focus stays trapped inside the modal (wraps back to its first control) until the modal closes.
 3. On the page, toolbar and sidebar controls are reachable by keyboard.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7997,7 +7926,7 @@
           <t xml:space="preserve">1. Both the single shift and the multi-week series render in the default blue.
 2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§10). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§10), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8053,7 +7982,7 @@
 3. The color is per SHIFT, not per work order - the other shift from the same work order keeps its own (default blue) color and does not change.
 4. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§10, §4.9, §4.4). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§10, §4.9, §4.4), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8107,7 +8036,7 @@
 2. The renamed label shows for the whole shop - the same picker opened elsewhere shows 'ZZAUTOTEST Rush'.
 3. Shifts and events share the same custom palette with the same labels.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§10, §4.10). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§10, §4.10), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8164,7 +8093,7 @@
 4. Each day has a From time and a To time you can set.
 5. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8217,7 +8146,7 @@
 2. The toggle is OFF by default (no custom hours set).
 3. Turning it ON reveals a per-day working-hours editor for that technician.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8268,7 +8197,7 @@
           <t xml:space="preserve">1. With no custom hours, the technician's working hours fall back to the shop business hours.
 2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8320,7 +8249,7 @@
 2. The added range starts empty (no From/To pre-filled).
 3. Each added range can be removed individually.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8375,7 +8304,7 @@
 4. The incomplete row (empty From/To) is ignored by the overlap check - it does not raise the overlap error.
 5. Save is not blocked by an incomplete row on its own (only genuine overlaps disable Save).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8431,7 +8360,7 @@
 3. ALL technicians' shifts and events are visible (not just the user's own).
 4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1, §14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1, §14.3), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a view-only user
 </t>
         </is>
@@ -8487,7 +8416,7 @@
 3. No creation menu opens at all - there is no 'Create Event' and no 'New Work Order' offered.
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a view-only user
 </t>
         </is>
@@ -8538,7 +8467,7 @@
           <t xml:space="preserve">1. The Schedule top-level nav item is not shown at all.
 2. The rest of the app works normally for the role.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user without the Schedule permission
 </t>
         </is>
@@ -8595,7 +8524,7 @@
 4. Edge-resize and horizontal drag work in day view.
 5. Modal fields are editable and save.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as an edit-without-delete user
 </t>
         </is>
@@ -8649,7 +8578,7 @@
 2. Events likewise offer no delete.
 3. No path exists to remove shifts or events - while creating and modifying still work.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as an edit-without-delete user
 </t>
         </is>
@@ -8704,7 +8633,7 @@
 3. Events can be deleted too.
 4. Undo toasts appear (restore the items via Undo to clean up).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a delete-capable user
 </t>
         </is>
@@ -8757,7 +8686,7 @@
 2. Delete cannot be granted without Edit.
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8811,7 +8740,7 @@
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
 3. New work orders cannot be dragged on - the WO list is simply not visible.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.2). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
@@ -8863,7 +8792,7 @@
           <t xml:space="preserve">1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.3). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.3), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a view-only technician
 </t>
         </is>
@@ -8915,7 +8844,7 @@
           <t xml:space="preserve">1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
 2. The staff member without a department does not appear as a row.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.4). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.4), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8966,7 +8895,7 @@
           <t xml:space="preserve">1. The Time-Clock-ON staff member can clock in.
 2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.4). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.4), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as each of the two staff members
 </t>
         </is>
@@ -9020,7 +8949,7 @@
 2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
 3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.2). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.2), read on 11 August 2026. The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
@@ -9078,7 +9007,7 @@
 3. The user from step 4 gets the read-only schedule - nothing can be dragged onto the grid and no shift can be created.
 4. The user from step 5 can drag a work order onto the grid and create a shift.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14.1). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a holder of each permission level
 </t>
         </is>
@@ -9131,13 +9060,9 @@
 2. All days remain reachable by horizontal scroll.
 3. On narrow viewports the sidebar collapses.
 4. No content becomes permanently unreachable and nothing errors.
-What you should see today: The whole page slides sideways instead of just the grid, and the panel on the left never folds away. At 960 pixels wide - which is the narrowest width the Schedule is meant to support - the page is still 1030 pixels wide and the panel is still its full width. Narrowing further changes neither. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8942
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8942)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9189,13 +9114,9 @@
           <t xml:space="preserve">1. Scrolling stays smooth with no long freezes or blank stretches that fail to fill in (the list virtualizes at 50+ items).
 2. The drill-down behaves the same with many lines.
 3. Search stays responsive on the long list.
-What you should see today: The list of work orders on the left does not scroll continuously. It shows 18 cards with a 'Load More' button at the bottom, even though 91 work orders exist. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8913
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8913)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9248,7 +9169,7 @@
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9302,7 +9223,7 @@
 2. A shift CAN be placed on the shop closure day (only weekend days with no business hours are skipped).
 3. The end date follows the normal daily distribution - no extra day is added for the closure.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§12, §4.5). That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§12, §4.5), read on 11 August 2026. That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - waiting on the product owner's answer, and the shop-closure setting does not exist in the build
 </t>
         </is>
@@ -9353,7 +9274,7 @@
           <t xml:space="preserve">1. All three quantities are shown/derivable and may differ from one another.
 2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5, §12). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5, §12), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9404,13 +9325,9 @@
         <is>
           <t xml:space="preserve">1. Every shift in the series starts at the SAME local wall-clock time (e.g. 8:00 AM) on both sides of the clock change.
 2. No shift in the series silently moves an hour earlier or later after the change date.
-What you should see today: The start times on either side of the clock change do not read the same. The same job reads 12 PM before 1 November and 1 PM after it. The times are stored correctly underneath - it is the times shown on screen that are wrong, and every Schedule time is shown six hours late for the same reason. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8848
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5), which covers spreading work across days. That specification says nothing about clock changes or daylight saving - those words do not appear in it at all - so the point above comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8848)
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026, which covers spreading work across days. That specification says nothing about clock changes or daylight saving - those words do not appear in it at all - so the point above comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9464,14 +9381,14 @@
 3. Conflict and overtime cues remain distinguishable (they never rely on colour alone - text/icon still present).
 4. Switching back to light mode restores the normal look with nothing stuck in dark colours.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§11). Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>SV-8685 (§11 (Dark theme - user-selectable Light / Dark,persisted per user))</t>
+          <t>SV-8700 (§11 Dark theme - the Schedule and its dialogs render readably in dark mode and revert on switching back) and SV-8698 (§11 accessibility - overtime and conflict cues are not colour-only) - spec v27 2026-08-07</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
@@ -9480,32 +9397,152 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>Dark mode is chosen from the user menu and is remembered for you</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Edge Cases and Responsiveness</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Your role has the Schedule: View permission.
+3. You know the password for the account you are signed in with, because this test signs out and back in.
+4. The app is currently in light mode.</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the menu for your own account - the one under your name or profile picture at the top of the page - and look for the light / dark theme choice in it.
+2. Use that choice to switch the app to dark mode.
+3. Open the Schedule page and check it is in dark mode.
+4. Sign out of the ShopView App completely.
+5. Sign back in with the same account and open the Schedule page again.
+6. Check whether the Schedule is in light mode or dark mode.
+7. On a different computer, or in a private browsing window, sign in with the SAME account again and open the Schedule page.
+8. Check whether the Schedule is in light mode or dark mode there too.
+9. Switch back to light mode from the same menu when you have finished, so you leave the account as you found it.</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The light / dark theme choice is in your own account menu at the top of the page. You do not have to go into a settings page to find it.
+2. Choosing dark mode switches the app to dark mode straight away, and the Schedule page opens in dark mode.
+3. At step 6, after signing out and signing back in, the Schedule is STILL in dark mode. Your choice was remembered.
+4. At step 8, on the other computer or in the private window, the Schedule is ALSO in dark mode. The choice is remembered against your account, not against the one browser you set it in.
+5. Switching back to light mode at step 9 works the same way and is remembered in the same way.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8700 (requirement 5), read on 11 August 2026, and the Schedule specification version 27 (§11 Dark theme), read on 11 August 2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§11 Dark theme - chosen from user menu and persisted per user - spec v27 2026-08-07)</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>In dark mode pop-up windows still look raised above the page</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Edge Cases and Responsiveness</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Your role has the Schedule: View permission.
+3. The app is in dark mode.
+4. You are on the Schedule page in week view, with at least one shift in the grid.</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>1. Click a shift in the grid to open its details window, and look at where that window meets the page behind it.
+2. Close it, then open the View options menu from the row of buttons above the grid, and look at where that menu meets the page behind it.
+3. Rest your mouse pointer on a shift so its hover tooltip appears, and look at where the tooltip meets the page behind it.
+4. Switch the app to light mode and look at the same three things again, so you have something to compare against.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. In dark mode each of the three - the shift details window, the View options menu and the hover tooltip - is clearly separated from the page behind it. You can tell where it ends and the page begins.
+2. The separation comes from the pop-up itself: it sits on a slightly different shade from the page behind it, or has a visible edge or soft shadow around it.
+3. None of the three blends into the page so that its edges cannot be made out, and none of them is missing that separation entirely while the light-mode version has it.
+4. Nothing you check is unreadable, and no text or icon disappears into the background.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8700 (requirement 5), read on 11 August 2026, and the Schedule specification version 27 (§11 Dark theme), read on 11 August 2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>SV-8700 (§11 Dark theme - elevation and shadow swap so depth reads correctly - spec v27 2026-08-07)</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
           <t>On a narrow window the panel button still works and your choice holds</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Edge Cases and Responsiveness</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Your role has the Schedule: View permission.
 3. You are on the Schedule page.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. Make the browser window narrower than 960 pixels wide. (The panel folding itself away on its own at that width is checked by a separate test - this test is about the button.)
 2. Find the panel button at the far-left end of the row of buttons above the grid and click it.
@@ -9513,267 +9550,267 @@
 4. Now make the browser window wider again, back over 960 pixels.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The panel button still works on a narrow window: it is not hidden, greyed out or unresponsive below 960 pixels, and clicking it shows the left panel by hand even at that width.
 2. The panel stays as you set it while you keep working at that width - moving around the page does not undo your choice.
 3. Your choice only stops applying when the window is resized back across the 960 pixel mark; at that point the page goes back to deciding for itself whether the panel is shown.
-Not built yet. When this was checked on 11 August 2026 the Schedule toolbar had no panel button at all - the button furthest to the left above the grid is Today. Until that button exists this test cannot be run: mark it Blocked. If you do find a panel button, the feature has shipped - tell the QA lead so this note can be removed and the test run as written.
----
-This is the expected behaviour as per epic SV-8685, its story SV-8686, and the Schedule specification version 27 (§5.3 Panel collapse, Narrow viewports). Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: HOLD - the panel collapse control is not in the build
-</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
+Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 4 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse, Narrow viewports), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>SV-8686 (§5.3 Panel collapse - Narrow viewports; toggle works at any width and the manual choice holds until the next resize)</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Shifts and events created before the Schedule rewrite still appear after it</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. This case runs around the Schedule rewrite release: before the release, note (or create) a handful of scheduled shifts and calendar events - including at least one future-dated one - with their technician, day, and time.
 2. The release (which replaces the Schedule behind the scenes) has been deployed.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. After the release, open the Schedule and navigate to the dates of the noted entries.
 2. Compare each noted shift and event against what the grid now shows.
 3. Open a couple of them to check their details.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every shift and event that existed before the release is still there after it - same technician, same day, same time, same work order.
 2. Events are still events and shifts are still shifts (nothing changed kind or vanished).
 3. Their details open normally and are editable/deletable like any other entry.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - cannot be run now - it needs shifts noted BEFORE the release, and the release is already deployed
 </t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (tech-plan §3 FR-015 data migration)</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Dashboard shows one schedule row per work order even with many shifts</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. One work order has been spread across MANY days for a technician (e.g. a 2-week series - 10+ daily shifts).</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>1. Open the Dashboard and find its schedule/today sections.
 2. Look for the spread work order in those sections.
 3. Count how many rows that one work order produces.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Dashboard shows that work order as ONE row (covering the whole scheduled span), not one row per daily shift.
 2. Note for the tester: before this release the Dashboard duplicated such a work order once per scheduled day - showing one combined row now is the intended fix, do not report it as a missing-rows bug.
 3. Work orders with a single shift are unaffected.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - the Dashboard section this test needs does not exist in the build
 </t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (tech-plan §4 Dashboard FR-016)</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>A work order created with an appointment shows up on the Schedule board</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. You can create a work order and set its appointment/scheduling details during creation.</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order and give it an appointment (a scheduled date/time) as part of the creation flow.
 2. Open the Schedule and navigate to that date.
 3. Find the new work order on the board.</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The appointment created with the work order appears on the Schedule board at the chosen date/time.
 2. It behaves like any other scheduled entry (opens, moves, deletes normally).
 3. It also appears in the Dashboard's schedule section for that day.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - work order creation offers no appointment in the build
 </t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (tech-plan §4 WO-create AppointmentScheduler)</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>A multi-location technician's shift appears only on the work order's location</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release is deployed.
 2. A technician is enrolled at TWO locations (set this up if needed).
 3. A work order belonging to location A has a shift scheduled on that technician.</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. Open the Schedule while working in location A and find the technician's shift.
 2. Switch to location B and open its Schedule for the same date.
 3. Look for the same shift on location B's board.</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The shift appears on location A's board (the location the work order belongs to).
 2. The shift does NOT appear on location B's board, even though the technician is enrolled there too.
 3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (tech-plan §3 WO-primary location resolution)</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Work order form offers a Priority (High/Medium/Low) that drives the sidebar</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Cross-Module and Rewrite Regression</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite release (which adds the Priority field) is deployed.
 2. You can create/edit a work order.</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order create/edit form and find the Priority field.
 2. Read its default value on a brand-new work order.
@@ -9781,109 +9818,109 @@
 4. Open the Schedule sidebar, find that work order's card, and apply the Priority = High filter.</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The work order form offers a Priority choice of High, Medium, Low.
 2. A new work order has NO priority pre-selected by default.
 3. After saving, the Schedule sidebar reflects the chosen priority and the Priority filter finds the work order under High.
 4. A work order with no priority set simply shows none (it is not treated as an error).
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - the Priority field this test needs does not exist in the build
 </t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>SV-8687 (§5.1 + tech-plan FR-P4 WO priority)</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>API - Schedule reads need View; writes need Edit; deletes need Delete (403)</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build (new /api/schedule endpoints) is deployed.
 2. Three test users exist: one with NO Schedule permission, one with Schedule: View only, one with Schedule: View + Edit (but not Delete).
 3. A shift id from the current location is known.</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>1. As the user with NO Schedule permission, call GET /api/schedule/board?from=&amp;to= for the current week.
 2. As the View-only user, call the same GET, then try POST /api/schedule/shifts (a minimal single-shift body) and PATCH /api/schedule/shifts/{id}.
 3. As the View+Edit user, repeat the POST and PATCH, then try DELETE /api/schedule/shifts/{id}?scope=shift.</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. No Schedule permission: the board GET is refused with HTTP 403.
 2. View-only: the board GET returns HTTP 200 with the grid data; the POST and PATCH are refused with HTTP 403.
 3. View + Edit: the POST and PATCH succeed (HTTP 201/200); the DELETE is refused with HTTP 403 because the user lacks Schedule: Delete.
 4. Each refusal is a clean 403 response - never a server error.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14), which sets the three permission levels. That specification does not describe what the server returns when a request is refused, so the refusal responses above come from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14), read on 11 August 2026, which sets the three permission levels. That specification does not describe what the server returns when a request is refused, so the refusal responses above come from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs three separate sign-ins, one per permission level
 </t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14 + tech-plan §4 NFR-003 permissions)</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>API - Series past 8 weeks returns 409 until acknowledged; over 120 shifts 422</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed; an API session with Schedule: Edit exists.
 2. A schedulable work order line id and a technician staff id are known.</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>1. POST /api/schedule/shifts with a spread whose window exceeds 8 weeks (56 calendar days), WITHOUT acknowledgeLongSeries.
 2. Repeat the same POST with acknowledgeLongSeries=true.
@@ -9891,132 +9928,132 @@
 4. Check the board for leftovers after the refused calls.</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The over-8-week create is refused with HTTP 409 (a 'series too long' error) - nothing is created.
 2. With acknowledgeLongSeries=true the same request succeeds (HTTP 201) and returns the full materialized series under one series id.
 3. The over-120-shift request is refused with HTTP 422 even WITH the acknowledgement - the hard cap cannot be overridden.
 4. Refused calls leave no partial series behind.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§4.5), with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026, with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>SV-8691 (§4.5 + tech-plan D8 error cases)</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>API - No pricing fields in Schedule responses; WO details need Work Orders View</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed.
 2. A shift covering work order lines exists.
 3. Two API users: one with Schedule: View + Work Orders: View, one with Schedule: View but WITHOUT Work Orders: View.</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>1. As the full user, call GET /api/schedule/board, GET /api/schedule/shifts/{id}, and GET /api/schedule/work-orders and search the raw responses for money fields (price, cost, rate, total, $ amounts).
 2. As the user WITHOUT Work Orders: View, call GET /api/schedule/board and GET /api/schedule/shifts/{id} and read the work-order-derived fields (customer, unit, VIN, lines).</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. No Schedule response contains any pricing/money field for ANY caller - the schedule never returns labor, totals, or dollar amounts.
 2. For the caller without Work Orders: View, the work-order-derived details (customer, unit, VIN, line names) are absent/empty in the response itself - not just hidden on screen.
 3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.
 ---
-This is the expected behaviour as per epic SV-8685 and the Schedule specification version 27 (§14). The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14), read on 11 August 2026. The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (§14 + tech-plan D6/NFR-002 no pricing)</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>API - A shift from another location returns 404, not another shop's data</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>API — Schedule</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>1. The Schedule rewrite build is deployed.
 2. Two locations exist; a shift exists at location B; your API session is scoped to location A.
 3. The location-B shift's id is known (create it while switched to B, then switch back to A).</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>1. While scoped to location A, call GET /api/schedule/shifts/{id} with the location-B shift id.
 2. Also try PATCH /api/schedule/shifts/{id} on the same id.
 3. Call GET /api/schedule/board for location A's current week.</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The foreign-location GET is refused as not found (HTTP 404) - the response reveals nothing about the other location's shift.
 2. The PATCH on the foreign id is refused the same way (404) - no cross-location edit is possible.
 3. Location A's board contains only location A's shifts - nothing from location B leaks in.
 ---
-This is the expected behaviour as per epic SV-8685 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>SV-8685 [epic - cross-cutting,no single-story owner] (tech-plan NFR-001 location scoping)</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -1509,8 +1509,7 @@
         <is>
           <t xml:space="preserve">1. The Status group lists the work order statuses the app supports.
 2. Only work orders in the chosen status remain in the card list - no work order of any other status is shown.
-3. Choosing more than one status shows the work orders of all the chosen statuses together.
-4. The card left-border colours of the remaining cards are consistent with that status.
+3. The card left-border colours of the remaining cards are consistent with that status.
 Note for the tester: this shop's schedule list only holds work orders in two statuses, Approved and Review, so most of the other choices correctly come back empty. An empty list for a status no work order is in is the right answer, not a fault.
 ---
 This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
@@ -9381,7 +9380,7 @@
 3. Conflict and overtime cues remain distinguishable (they never rely on colour alone - text/icon still present).
 4. Switching back to light mode restores the normal look with nothing stuck in dark colours.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per story SV-8700 (dark theme), read on 11 August 2026, story SV-8698 (overtime and conflict cues are not colour-only), read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
 AUTOMATION: READY
 </t>
         </is>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -740,7 +740,7 @@
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. No such toggle exists - the department-grouped rows are the only grid grouping.
-2. Department visibility is controlled only through the department toggles in the 'Filter and Display' dropdown.
+2. Department visibility is controlled only through the department toggles in the 'Filter &amp; display' dropdown.
 ---
 This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
 AUTOMATION: READY
@@ -849,7 +849,7 @@
 2. Of the three buttons Day, Week and Month, the one that is switched on (highlighted) is Day.
 3. The grid shows the Day layout: a 24-hour timeline for each technician row, with shifts placed at their times.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the acceptance criterion of its story SV-8686, read on 11 August 2026, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 27 does not say which view the page opens on, so this expectation comes from the story rather than the specification. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the acceptance criterion of its story SV-8686, read on 11 August 2026, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 27 does not say which view the page opens on, so this expectation comes from the story rather than the specification. Last checked against build v3.5-65d6500 on 8/12/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2437,9 +2437,13 @@
         <is>
           <t xml:space="preserve">1. The item can be placed onto a cell without holding a drag - clicking arms it, and clicking a cell places it.
 2. The result is the same as the equivalent drag-and-drop (scope picker / spread step rules apply the same way).
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+What you should see today: there is no click alternative anywhere. The work order card in the left-hand panel carries no button that arms it for placing - not when the page loads, not when you rest the mouse on the card, and not inside the card's line list. The only way to place a job on the grid is to drag it. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8957. That ticket has been closed without the problem being fixed, so do not wait for a fix.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §11), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8957)
 </t>
         </is>
       </c>
@@ -4919,7 +4923,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The modal offers a Delete action (a trash icon in the header) and a close (x) icon - and no other actions.
+          <t xml:space="preserve">1. The modal offers a Delete action (a trash icon in the header) and a close (x) icon. It offers no way to move the shift to a different technician - no Reassign action, under that or any other name. Other editing controls may be present (for example notes, colour, or estimated hours); their presence is not what this test checks.
 2. There is no 'Reassign' action in the modal; reassignment is done by dragging a shift to another technician row (covered by its own case).
 3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).
 ---
@@ -5459,8 +5463,8 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The shift is flagged as a before-hours conflict, with a reason sentence in the spirit of 'Starts before working hours', measured against that technician's own configured working-day START time (not a fixed hour).
-2. The shift is flagged as an after-hours conflict, with a reason sentence in the spirit of 'Extends past working hours', measured against that technician's own configured working-day END time (not a fixed hour).
+          <t xml:space="preserve">1. The shift is flagged as a before-hours conflict, with a reason sentence in the spirit of 'Starts before business hours', measured against that technician's own configured working-day START time (not a fixed hour).
+2. The shift is flagged as an after-hours conflict, with a reason sentence in the spirit of 'Extends past business hours', measured against that technician's own configured working-day END time (not a fixed hour).
 3. Both the start and the end follow the hierarchy technician hours, then shop business hours, then the general default working day of 7:00 AM to 7:00 PM.
 4. Warning icon on the block in each case; the conflict appears in the toolbar dropdown.
 ---
@@ -6162,10 +6166,10 @@
 6. After you click it and the panel is hidden, the tooltip reads: Show panel
 7. The picture on the button is exactly the same in both states - only the tooltip changes.
 8. Clicking the button at step 4 hides the left panel, and clicking it again at step 7 shows it.
-Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 7 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse and §6 Grid toolbar), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: READY
+Run this test as written and mark it on what you actually find. When it was last checked, on 12 August 2026, the Schedule toolbar still had no panel button at all - the button furthest to the left above the grid was Today, and the only thing on the page that hides anything is the small arrow that folds away the month calendar inside the panel, which is a different control - so on that build steps 1 to 7 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse and §6 Grid toolbar), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -6221,10 +6225,10 @@
 2. The dividing line between the panel and the grid goes away with it, leaving no leftover line, seam or empty strip where the panel used to be.
 3. The grid grows into the space the panel gave up and lays itself out again in the wider area, so you can see more of the grid than you could before.
 4. Clicking the button a second time brings the panel back to its normal width, and the grid goes back to the size it was at step 1.
-Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 6 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse and §3.1 Left panel: work order sidebar), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: READY
+Run this test as written and mark it on what you actually find. When it was last checked, on 12 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 6 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 12 August 2026, its story SV-8686, read on 12 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse and §3.1 Left panel: work order sidebar), read on 12 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -6284,10 +6288,10 @@
 4. The list is still scrolled to roughly the position you left it at.
 5. The panel comes back showing that work order's lines, not the full list of work orders - it returns to whichever of the two views was open when you hid it.
 6. The work order you had opened is still the selected one.
-Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 7 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse and §3.1 Left panel: work order sidebar), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: READY
+Run this test as written and mark it on what you actually find. When it was last checked, on 12 August 2026, the Schedule toolbar still had no panel button at all - the button furthest to the left above the grid was Today, and the only thing on the page that hides anything is the small arrow that folds away the month calendar inside the panel, which is a different control - so on that build steps 1 to 7 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse and §3.1 Left panel: work order sidebar), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -6341,10 +6345,10 @@
           <t xml:space="preserve">1. With the panel hidden, the pop-up no longer keeps clear of the space the panel used to take up. It sits against the edge of the browser window with a normal margin instead.
 2. The whole pop-up is on screen: nothing is cut off at an edge, pushed outside the window, or left floating with a large empty gap beside it.
 3. The pop-up behaves normally otherwise - you can read it, use its buttons, and close it.
-Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 5 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse, Popovers and modals), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: READY
+Run this test as written and mark it on what you actually find. When it was last checked, on 12 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 5 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 12 August 2026, its story SV-8686, read on 12 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse, Popovers and modals), read on 12 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -6403,10 +6407,10 @@
 2. At step 6, after signing out and back in, the left panel is showing again. The choice is not carried over into a new sign-in: it is a working-mode preference for the session you are in, not a saved view setting.
 3. At step 7, the second person's left panel is showing as normal. Your choice applied only to you and did not change what anybody else sees.
 Still to be confirmed, and it affects the second point above. The product owner's description of 7 August says this choice lasts only for the current sign-in. Separately, the design review of 5 August asks for the Schedule's view settings to be stored per user so they survive signing out and back in. Those are two different promises. The question has been put to the product owner and has not been answered yet, so the second point follows the written specification for now. If the answer is that it should survive signing out, the second point will change.
-Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 7 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse, Persistence), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: READY
+Run this test as written and mark it on what you actually find. When it was last checked, on 12 August 2026, the Schedule toolbar still had no panel button at all - the button furthest to the left above the grid was Today, and the only thing on the page that hides anything is the small arrow that folds away the month calendar inside the panel, which is a different control - so on that build steps 1 to 7 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse, Persistence), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -6581,7 +6585,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>'Filter &amp; Display' dropdown combines department toggles, My Shifts, and VIN</t>
+          <t>'Filter &amp; display' dropdown: department toggles, 'My Shifts' and 'VIN Number'</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -6607,14 +6611,14 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>1. Open the 'Filter &amp; Display' dropdown in the grid toolbar.
+          <t>1. Open the 'Filter &amp; display' dropdown in the grid toolbar.
 2. Read its contents and default states.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The dropdown is checkbox style and contains: a toggle per department, 'My Shifts', and 'VIN'.
-2. Defaults: all department toggles ON, 'My Shifts' OFF, 'VIN' OFF.
+          <t xml:space="preserve">1. The dropdown is checkbox style and contains: a toggle per department, 'My Shifts', and 'VIN Number'.
+2. Defaults: all department toggles ON, 'My Shifts' OFF, 'VIN Number' OFF.
 3. There is no separate departments-only control - this dropdown replaces it.
 ---
 This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6, §9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
@@ -6660,7 +6664,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>1. In 'Filter and Display', turn OFF one department's toggle.
+          <t>1. In 'Filter &amp; display', turn OFF one department's toggle.
 2. Look at the grid.
 3. Turn it back ON.</t>
         </is>
@@ -6714,7 +6718,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>1. In 'Filter and Display', turn ON 'My Shifts'.
+          <t>1. In 'Filter &amp; display', turn ON 'My Shifts'.
 2. Look at the grid.
 3. Turn it OFF again.</t>
         </is>
@@ -6770,7 +6774,7 @@
       <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. With 'VIN Number' off: read the block in week view, hover for the tooltip, then open the detail modal.
-2. Turn 'VIN Number' ON in 'Filter and Display'.
+2. Turn 'VIN Number' ON in 'Filter &amp; display'.
 3. Read the block again in week view, then in day view, then in month view; hover for the tooltip and open the detail modal again.
 4. In day view, compare the height of the shift's lane with the toggle off and on.</t>
         </is>
@@ -6800,7 +6804,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>'View Options': six toggles with defaults; Capacity Bars and Events flip</t>
+          <t>'View options': six toggles with defaults; Capacity Planning and Events flip</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -6827,17 +6831,17 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'View Options' in the grid toolbar.
+          <t>1. Open 'View options' in the grid toolbar.
 2. Read each toggle and its state.
-3. Turn OFF Capacity Bars, look at the day column headers, then turn it back ON.
+3. Turn OFF Capacity Planning, look at the day column headers, then turn it back ON.
 4. Turn OFF Events, look at the grid, then turn it back ON.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Six toggles are offered: Business Hours, Capacity Bars, Events, Tech Hours, Saturday, Sunday.
-2. Defaults: Business Hours OFF, Capacity Bars ON, Events ON, Tech Hours OFF, Saturday ON, Sunday ON.
-3. Capacity Bars OFF: the capacity bars disappear from the column headers; ON: they reappear with the same values.
+          <t xml:space="preserve">1. Six toggles are offered: Business Hours, Capacity Planning, Events, Tech Hours, Show Saturday, Show Sunday.
+2. Defaults: Business Hours OFF, Capacity Planning ON, Events ON, Tech Hours OFF, Show Saturday ON, Show Sunday ON.
+3. Capacity Planning OFF: the capacity bars disappear from the column headers; ON: they reappear with the same values.
 4. Events OFF: event blocks disappear from the grid while shifts remain; ON: the events reappear unchanged.
 ---
 This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6, §9, §4.12), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
@@ -6884,7 +6888,7 @@
       <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Note the timeline background outside working hours.
-2. Turn ON Business Hours in 'View Options'.
+2. Turn ON Business Hours in 'View options'.
 3. Look at the timeline again.</t>
         </is>
       </c>
@@ -6937,7 +6941,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>1. Turn ON Tech Hours in 'View Options'.
+          <t>1. Turn ON Tech Hours in 'View options'.
 2. Look at the technician rows.</t>
         </is>
       </c>
@@ -6963,7 +6967,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Saturday and Sunday toggles include or exclude the weekend columns</t>
+          <t>'Show Saturday' and 'Show Sunday' include or exclude the weekend columns</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6989,15 +6993,15 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>1. Turn OFF Saturday in 'View Options'; look at the grid.
-2. Turn OFF Sunday too; look again.
+          <t>1. Turn OFF 'Show Saturday' in 'View options'; look at the grid.
+2. Turn OFF 'Show Sunday' too; look again.
 3. Turn both back ON.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Saturday off: the Saturday column is removed (6 columns remain).
-2. Sunday off too: 5 weekday columns remain (Monday to Friday).
+          <t xml:space="preserve">1. 'Show Saturday' off: the Saturday column is removed (6 columns remain).
+2. 'Show Sunday' off too: 5 weekday columns remain (Monday to Friday).
 3. Both back on: the full Monday-to-Sunday 7-column week returns.
 ---
 This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9, §3.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
@@ -8072,7 +8076,7 @@
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App with access to location settings.
-2. You are on the Edit Location screen for a shop.</t>
+2. You are on the Edit Location screen for a shop - Settings &gt; Locations, then the pencil on that shop's row.</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -8092,7 +8096,7 @@
 4. Each day has a From time and a To time you can set.
 5. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8108,7 +8112,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Edit Staff has a 'Set custom hours for this technician' toggle, off by default</t>
+          <t>Edit Staff has a 'Set working hours for this technician' toggle, off by default</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -8129,23 +8133,23 @@
       <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with access to staff settings.
-2. You open the Edit Staff Member screen for a technician.</t>
+2. You open the Edit Staff Member screen for a technician - Settings &gt; Staff, then the pencil on that technician's row.</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Open the Edit Staff Member screen for a technician.
 2. Find the custom-hours setting and read its default state.
-3. Turn the 'Set custom hours for this technician' toggle ON.</t>
+3. Turn the 'Set working hours for this technician' toggle ON.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Edit Staff Member shows a toggle labelled 'Set custom hours for this technician'.
+          <t xml:space="preserve">1. Edit Staff Member shows a toggle labelled 'Set working hours for this technician'.
 2. The toggle is OFF by default (no custom hours set).
 3. Turning it ON reveals a per-day working-hours editor for that technician.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8182,7 +8186,7 @@
       <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. The shop has business hours set for the shop.
-2. A technician has the 'Set custom hours for this technician' toggle OFF.</t>
+2. A technician has the 'Set working hours for this technician' toggle OFF.</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -8196,7 +8200,7 @@
           <t xml:space="preserve">1. With no custom hours, the technician's working hours fall back to the shop business hours.
 2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8212,7 +8216,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>'Add hours' appends a removable second range for split shifts, starting empty</t>
+          <t>'Add Hours' appends a removable second range for split shifts, starting empty</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -8232,23 +8236,23 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>1. You are in the per-day working-hours editor (location or technician) with a day's first range set.</t>
+          <t>1. You are in the per-day working-hours editor with a day's first range set. Reach it either from Settings &gt; Locations &gt; the pencil on a shop's row &gt; turn on 'Set business hours for this shop', or from Settings &gt; Staff &gt; the pencil on a technician's row &gt; turn on 'Set working hours for this technician'.</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>1. On one day, click 'Add hours'.
+          <t>1. On one day, click 'Add Hours'.
 2. Read the new range that appears.
 3. Set the second range, then remove it.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. 'Add hours' appends an additional From-To range to that day (to support split shifts).
+          <t xml:space="preserve">1. 'Add Hours' appends an additional From-To range to that day (to support split shifts).
 2. The added range starts empty (no From/To pre-filled).
 3. Each added range can be removed individually.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8783,7 +8787,7 @@
       <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Read the grid across all departments and technicians.
-2. Check 'My Shifts' in 'Filter and Display' is OFF (default).</t>
+2. Check 'My Shifts' in 'Filter &amp; display' is OFF (default).</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -8894,7 +8898,7 @@
           <t xml:space="preserve">1. The Time-Clock-ON staff member can clock in.
 2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.4), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.4), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
 AUTOMATION: HOLD - needs a second sign-in as each of the two staff members
 </t>
         </is>
@@ -8992,7 +8996,7 @@
       <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Open the roles screen where each role's permissions are listed.
-2. Take these roles one at a time - Technician, Parts Manager, Parts Tech, Office, Time Clock - use 'Reset To Template' so the role is back at its default, then read its Schedule permissions (View, Edit, Delete).
+2. Take these roles one at a time - Technician, Parts Manager, Parts Tech, Office, Time Clock. Open the role by clicking the pencil on its row, then click 'Reset to template' on the role's own screen so the role is back at its default, and read its Schedule permissions (View, Edit, Delete). Note: the three-dot menu on the roles list does NOT offer this - it only offers 'View Permissions'. The reset button is on the role's own screen.
 3. Do the same for these roles - Service Manager, Senior Service Advisor, Service Advisor, Foreman - and read their Schedule permissions.
 4. Sign in as a user with one of the roles from step 2 and try to drag a work order onto the grid.
 5. Sign in as a user with one of the roles from step 3 and try the same drag.
@@ -9006,7 +9010,7 @@
 3. The user from step 4 gets the read-only schedule - nothing can be dragged onto the grid and no shift can be created.
 4. The user from step 5 can drag a work order onto the grid and create a shift.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
+This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
 AUTOMATION: HOLD - needs a second sign-in as a holder of each permission level
 </t>
         </is>
@@ -9554,10 +9558,10 @@
           <t xml:space="preserve">1. The panel button still works on a narrow window: it is not hidden, greyed out or unresponsive below 960 pixels, and clicking it shows the left panel by hand even at that width.
 2. The panel stays as you set it while you keep working at that width - moving around the page does not undo your choice.
 3. Your choice only stops applying when the window is resized back across the 960 pixel mark; at that point the page goes back to deciding for itself whether the panel is shown.
-Run this test as written and mark it on what you actually find. When it was last checked, on 11 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 4 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8686, read on 11 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse, Narrow viewports), read on 11 August 2026. Last checked against build v3.5-af3a6e1 on 8/11/2026.
-AUTOMATION: READY
+Run this test as written and mark it on what you actually find. When it was last checked, on 12 August 2026, the Schedule toolbar had no panel button at all - the button furthest to the left above the grid was Today - so on that build steps 1 to 4 cannot be carried out and this test FAILS. Mark it failed if that is still what you see. If the button is there and behaves as described, mark it passed.
+---
+This is the expected behaviour as per epic SV-8685, read on 12 August 2026, its story SV-8686, read on 12 August 2026, and the Schedule specification version 27 (§5.3 Panel collapse, Narrow viewports), read on 12 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -528,8 +528,8 @@
 3. The left panel is the work order sidebar: a mini calendar at the top and a work order list beneath it.
 4. The main area is the schedule grid showing technician rows, with a toolbar above it.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3, §3.1, §3.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§3, §3.1, §3.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -585,8 +585,8 @@
 3. Month: the grid shows a compact calendar with per-day capacity bars and shift chips.
 4. The same shifts appear in all three views - each one drawn to suit that view: positioned on the hour line in Day, as a chip in the day column in Week, and as a compact chip in Month.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2, §6), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§3.2, §6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -638,8 +638,8 @@
 2. Each department's technicians are listed beneath that department's header.
 3. Every staff member assigned to a visible department appears as a row, regardless of their role.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2, §14.4), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§3.2, §14.4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -692,8 +692,8 @@
 2. Expanding shows the technician rows again, unchanged.
 3. Other department groups are unaffected.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§3.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -742,8 +742,8 @@
           <t xml:space="preserve">1. No such toggle exists - the department-grouped rows are the only grid grouping.
 2. Department visibility is controlled only through the department toggles in the 'Filter &amp; display' dropdown.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§3.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -849,8 +849,8 @@
 2. Of the three buttons Day, Week and Month, the one that is switched on (highlighted) is Day.
 3. The grid shows the Day layout: a 24-hour timeline for each technician row, with shifts placed at their times.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the acceptance criterion of its story SV-8686, read on 11 August 2026, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 27 does not say which view the page opens on, so this expectation comes from the story rather than the specification. Last checked against build v3.5-65d6500 on 8/12/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the acceptance criterion of its story SV-8686, read on 17 August 2026, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 30 does not say which view the page opens on, so this expectation comes from the story rather than the specification.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -901,8 +901,8 @@
 2. The toolbar date label updates to the new range.
 3. The clicked date is highlighted as the selected date in the mini calendar.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1, §5.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1, §5.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -956,8 +956,8 @@
 2. Choosing a month shows that month in the mini calendar.
 3. The main grid can then be navigated by clicking a date in the newly shown month.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1010,8 +1010,8 @@
           <t xml:space="preserve">1. The calendar grid collapses (hides), leaving more room for the work order list below.
 2. Clicking again expands the calendar grid back.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1, §5.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1, §5.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1065,8 +1065,8 @@
 2. Today's date has its own distinct indicator, different from the selection.
 3. Hovering a week row highlights that whole week row.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1119,8 +1119,8 @@
 2. The list scrolls when there are more cards than fit.
 3. There are no Assigned/Unassigned tabs - assignment is available only as a filter behind the 'Filter' button.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1, §5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1, §5.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1289,8 +1289,8 @@
 2. Deleting characters widens the results again.
 3. With very many work orders, the list may load further results in pages as you scroll - that is expected, not a fault.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1344,8 +1344,8 @@
 2. The app does not error; the sidebar remains usable.
 3. Clearing the search restores the full list.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1513,8 +1513,8 @@
 2. Applying a filter narrows the flat card list.
 3. The 'Filters' button shows a badge with the number of active filters.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1569,8 +1569,8 @@
 2. Assigned: only work orders with a technician assigned remain.
 3. There are no Assigned/Unassigned tabs - this filter is the only assignment split.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1, §3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1, §3.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1626,8 +1626,8 @@
 3. The card left-border colours of the remaining cards are consistent with that status.
 Note for the tester: this shop's schedule list only holds work orders in two statuses, Approved and Review, so most of the other choices correctly come back empty. An empty list for a status no work order is in is the right answer, not a fault.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1681,8 +1681,8 @@
           <t xml:space="preserve">1. The Priority group offers High, Medium, and Low.
 2. Only High-priority work orders remain in the list.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1725,7 +1725,7 @@
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Click 'Clear all'.
-2. Look at the list and the 'Filter' button.
+2. Look at the list and the 'Filters' button.
 </t>
         </is>
       </c>
@@ -1733,10 +1733,10 @@
         <is>
           <t xml:space="preserve">1. All applied filters are removed at once.
 2. The full work order list is shown again.
-3. The active-count badge on the 'Filter' button disappears (or shows zero).
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+3. The active-count badge on the 'Filters' button disappears (or shows zero).
+---
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1790,8 +1790,8 @@
           <t xml:space="preserve">1. The list shows only work orders that match BOTH the text search and the structured filter.
 2. Removing either the search text or the filter widens the list to the remaining condition.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1847,8 +1847,8 @@
 4. A back control is shown to return to the card list.
 5. Clicking back restores the work order card list.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1902,8 +1902,8 @@
 2. No line that has never been approved appears anywhere in the schedule sidebar - for example a line still sitting on an estimate, or one that was declined.
 3. The line count in the drill-down header matches the number of APPROVED lines on the work order - a line that was never approved is neither listed nor counted.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -1957,8 +1957,8 @@
 2. The current technician roster is shown as an avatar stack plus a count; there is no cap on how many technicians a line can have.
 3. Each line row has its own drag handle, so it can be dragged independently onto the grid.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1, §8.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1, §8.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2012,8 +2012,8 @@
 2. The line with a technician does not show the badge.
 3. After a technician is scheduled onto the badge-bearing line, the badge goes away.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2067,8 +2067,8 @@
           <t xml:space="preserve">1. Typing a line title narrows the list to matching lines.
 2. Typing the customer name returns no results - the line search matches line titles only (the list is already scoped to one work order, so customer/unit/WO fields are not searched).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2123,8 +2123,8 @@
 2. Unscheduled lists only the lines that have no shifts yet, and its count matches.
 3. All lists every approved line, and its count matches the drill-down header's line count.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§3.1, §5.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1, §5.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2231,8 +2231,8 @@
 2. It offers 'Schedule whole work order' at the top, the individual line rows beneath, and a 'Select multiple' control.
 3. No shift is created until a scope is chosen.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.1, §4.3), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.1, §4.3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2285,8 +2285,8 @@
 2. The block's last text line shows that line's name.
 3. The technician is added to that line's roster only (not to the order's other lines).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2391,8 +2391,8 @@
           <t xml:space="preserve">1. The shift is created straight away - the spread step does NOT appear.
 2. The shift sits on the dropped day only.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2444,8 +2444,8 @@
 2. A ghost block follows the drag showing the line name and its hours.
 3. Releasing outside any valid cell creates nothing.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2501,8 +2501,8 @@
 4. Dragging the same line onto a second technician adds that technician to the line's roster as well - the technician who was already there stays on it.
 5. Nothing asks you to swap or replace the technician who was already there, and no limit is reached on how many technicians a line can have.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§1.2, §4.3, §7), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§1.2, §4.3, §7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2552,13 +2552,9 @@
         <is>
           <t xml:space="preserve">1. The item can be placed onto a cell without holding a drag - clicking arms it, and clicking a cell places it.
 2. The result is the same as the equivalent drag-and-drop (scope picker / spread step rules apply the same way).
-What you should see today: there is no click alternative anywhere. The work order card in the left-hand panel carries no button that arms it for placing - not when the page loads, not when you rest the mouse on the card, and not inside the card's line list. The only way to place a job on the grid is to drag it. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8957. That ticket has been closed without the problem being fixed, so do not wait for a fix.
-- If you see exactly that, mark this test FAILED and do not raise anything new.
-- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §11), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8957)
+---
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§7, §11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2613,10 +2609,10 @@
           <t xml:space="preserve">1. While the card is held over a day box, that day box shows it is a drop target.
 2. Releasing on the day box books the work order onto that day, exactly as dropping it does in Week view: because this work order has more than one line, the scope picker opens so you can choose the whole order, one line, or several lines.
 3. After you confirm a scope, a shift appears in that day box, and its start time comes from the usual order of preference - the technician's own working hours first, otherwise the shop's business hours, otherwise 7:00 AM.
-Please read before running this test: what should happen in MONTH view specifically has not been settled yet. The Schedule specification version 27 says that a work order is dragged from the sidebar onto a cell in the grid without naming which view, and the acceptance criterion of story SV-8688 names only Week view. The question has been put to the product owner on SV-8870 (https://shopview.atlassian.net/browse/SV-8870), together with the point that Month view invites the user to drag ("Nothing is scheduled in this range. Drag a work order from the list to book it."). Until the product owner answers, treat a failure here as already reported under SV-8870 - mark it FAILED and link SV-8870; do not raise a new ticket.
+Please read before running this test: what should happen in MONTH view specifically has not been settled yet. The Schedule specification version 30 says that a work order is dragged from the sidebar onto a cell in the grid without naming which view, and the acceptance criterion of story SV-8688 names only Week view. The question has been put to the product owner on SV-8870 (https://shopview.atlassian.net/browse/SV-8870), together with the point that Month view invites the user to drag ("Nothing is scheduled in this range. Drag a work order from the list to book it."). Until the product owner answers, treat a failure here as already reported under SV-8870 - mark it FAILED and link SV-8870; do not raise a new ticket.
 What was seen on the build checked: the card lifts and follows the mouse, but no day box shows as a drop target and releasing does nothing at all - no scope picker, no shift, no message. The same drag of the same work order in Week view does open the scope picker, so the difference is Month view itself.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.1, §4.2), read on 11 August 2026, which describe dragging a work order from the sidebar onto a cell in the grid and the order of preference for the start time. Neither that specification nor story SV-8688 says whether Month view accepts the drop, so that point is an open product-owner question rather than a settled requirement. Last checked against build v3.5-d122eef on 8/5/2026.
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§4.1, §4.2), read on 17 August 2026, which describe dragging a work order from the sidebar onto a cell in the grid and the order of preference for the start time. Neither that specification nor story SV-8688 says whether Month view accepts the drop, so that point is an open product-owner question rather than a settled requirement.
 AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
 </t>
         </is>
@@ -2780,8 +2776,8 @@
 4. Each line row shows the line title and its estimated hours.
 5. Rows for lines that already have technicians show the current roster as an avatar stack plus count.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.3), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8689 and the Schedule specification version 30 (§4.3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2834,8 +2830,8 @@
 2. The block's last text line reads 'N Lines' (with N = the line count).
 3. The technician is added to the roster of every one of those lines.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.3, §4.4), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8689 and the Schedule specification version 30 (§4.3, §4.4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2887,8 +2883,8 @@
 2. The picker closes.
 3. The block's last text line shows the line's name.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.3), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8689 and the Schedule specification version 30 (§4.3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2946,8 +2942,8 @@
 4. A 'Cancel' control leaves tick-box mode and returns you to the ordinary single-tap line list, without creating anything and without closing the picker.
 5. Confirming creates ONE shift covering exactly the ticked lines, and the technician is added to those lines' rosters only - not to the other lines.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.3), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8689 and the Schedule specification version 30 (§4.3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -2999,8 +2995,8 @@
           <t xml:space="preserve">1. The shift starts at the technician's own configured start time (6:00 AM in the example), not the shop's business-hours start.
 Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -3051,8 +3047,8 @@
         <is>
           <t xml:space="preserve">1. The shift starts at the shop's business-hours start time.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -3157,8 +3153,8 @@
 2. The start time aligns to the timeline position (see the 15-minute snapping case).
 Note for the tester: every time on the Schedule is currently shown six hours later than the time it was booked for. That is already reported as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Read the position on the timeline rather than the printed time, and do not raise it again.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -3173,7 +3169,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Dropping onto the Unassigned row creates a shift with no technician</t>
+          <t>Dropping onto a department's unassigned lane creates a shift with no technician</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3200,24 +3196,24 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1. Drag the line from the sidebar and drop it onto the grid's Unassigned row on a working day.
+          <t>1. Drag the line from the sidebar and drop it onto a department's unassigned lane (the department group header row) on a working day.
 2. Look at the created block and the line's roster.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. An unassigned shift is created in the Unassigned row for that day.
-2. It has no technician (and no technician is added to the line's roster by this drop).
-3. The block uses the same anatomy as a regular shift (customer, unit, line name / 'N Lines').
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2, §3.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+          <t xml:space="preserve">1. An unassigned shift is created in that department's unassigned lane. The department group header row doubles as the lane - there is no separate 'Unassigned' row.
+2. It has no technician, and no technician is added to the line's roster by this drop.
+3. The block renders as a fixed-width chip carrying its hours - it is not scaled to a duration, because no technician's hours have been applied to it yet.
+---
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-9234 and the Schedule specification version 30 (§4.2, §3.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8688 (§4.2 (Unassigned shifts),§3.2)</t>
+          <t>SV-9234 (§3.2 §4.2 unassigned lane on the department header row)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3226,7 +3222,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Unassigned shift start time uses business hours or the default</t>
+          <t>Unassigned shift start time uses business hours or the app-level default</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3254,22 +3250,23 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1. Drop the line onto the Unassigned row.
+          <t>1. Drop the line onto a department's unassigned lane (the department group header row).
 2. Read the created shift's start time.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The unassigned shift starts at the shop's business-hours start (there is no technician whose hours could apply).
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+          <t xml:space="preserve">1. The unassigned shift takes its start time from the same rules as any shift, minus the technician level: the shop's business hours, or - if the shop has no business hours set - the app-level default of 7:00 AM.
+2. The day you dropped it on is recorded as the shift's target start date.
+---
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-9234 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8688 (§4.2)</t>
+          <t>SV-9234 (§4.2 unassigned shift start time)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3605,8 +3602,8 @@
 4. Clicking 'Change scope' takes the modal back to the scope picker (step 1) without creating anything.
 5. Choosing a new scope updates the spread step's header and hours accordingly.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -3819,8 +3816,8 @@
 2. It can be changed; technician B's series then starts after A's series ends (sequential, not parallel).
 3. B's series is created from the adjusted start date onward.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -3982,8 +3979,8 @@
 3. Each daily shift keeps its own day and hours.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5, §4.6, §8.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5, §4.6, §8.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4035,8 +4032,8 @@
 2. There is no shared 'remaining hours' counter across technicians and no splitting of a shift.
 3. Planned hours across technicians may now exceed the estimate - this is expected and produces no error (progress is driven by clocked-in time).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5, §12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5, §12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4091,8 +4088,8 @@
 3. A single spread that would create more than 120 daily shifts is refused outright - no confirmation can override it, and no shifts are created for that attempt.
 4. No half-created series is left behind after a refused attempt.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026, with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5), read on 17 August 2026, with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4374,8 +4371,8 @@
 2. It is labeled once at the start (including the technician); later weeks show a faded 'continues'-style label instead of repeating the full label.
 3. Weekend columns inside the series are empty (no bar) when no business hours are set for those weekend days.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.6), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§4.6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4428,8 +4425,8 @@
 2. Chevrons at the banner's edges indicate the series continues beyond the visible week (both sides, on a middle week).
 3. A 'week N of M' cue shows the position within the series.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.6), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§4.6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4480,8 +4477,8 @@
           <t xml:space="preserve">1. The day shows a single time-positioned block (no spanning bar - only one day is visible).
 2. The block carries a cue in the spirit of 'part of an M-week job' indicating it belongs to a longer series.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.6), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§4.6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4534,8 +4531,8 @@
 2. The overlapping day is flagged as a Double-booked conflict, exactly as it would be for standalone shifts.
 3. The detail modal shows that single day's shift (its own day and hours) while indicating it belongs to the series.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.6, §8.2), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§4.6, §8.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4587,8 +4584,8 @@
 3. Last line: the name of the scheduled line.
 4. No work order number appears on the block.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.4), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8690 and the Schedule specification version 30 (§4.4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4641,8 +4638,8 @@
 2. The subset block reads '2 Lines' - the block does not distinguish whole-order from subset beyond the count.
 3. Each detail modal lists exactly which lines the shift covers.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.4, §12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8690 and the Schedule specification version 30 (§4.4, §12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4694,8 +4691,8 @@
 2. The conflicted block shows the conflict (warning) icon on its first line - and that is the only icon that ever appears on a block.
 3. No scope icons distinguish whole-order from subset shifts.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.4), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8690 and the Schedule specification version 30 (§4.4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4749,8 +4746,8 @@
 3. The row stays at its normal height.
 4. No conflict is flagged for back-to-back (non-intersecting) shifts.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.7, §12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8693 and the Schedule specification version 30 (§4.7, §12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4801,8 +4798,8 @@
 2. The row grows in height to fit the lanes.
 3. The overlap is also flagged as a Double-booked conflict (stacking reads as 'resolve me').
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.7, §4.11), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8693 and the Schedule specification version 30 (§4.7, §4.11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4856,8 +4853,8 @@
 4. You can tell the '+2 more' is something to click without relying on its colour: it carries the count as words you can read, and it is drawn as its own distinct shape - a small chip, pill or button - not just a differently coloured patch of the lane.
 5. The hidden shifts can be opened from that popover.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.7 Overlap and lane stacking and §11 Accessibility - the overflow uses shape), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8693 and the Schedule specification version 30 (§4.7 Overlap and lane stacking and §11 Accessibility - the overflow uses shape), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -4910,8 +4907,8 @@
 2. Week and month views reach the '+N more' overflow sooner than day view (their cells are narrower), but the same cap-and-overflow model applies.
 3. The overflow affordance opens the hidden-shifts popover in each view.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8693 and the Schedule specification version 30 (§4.7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -5021,8 +5018,8 @@
           <t xml:space="preserve">1. In day view, the date/time header bar stays stuck to the top while the rows scroll beneath it - you always know which time column you are looking at.
 2. The same sticky-header behavior applies in week view.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.8), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8694 and the Schedule specification version 30 (§4.8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -5185,8 +5182,8 @@
 2. Its position matches the actual clock time.
 3. Hovering the now line while your pointer is over the grid shows a label (the current time).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.8), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8694 and the Schedule specification version 30 (§4.8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -5333,7 +5330,7 @@
       <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser.
-2. A shift exists for a unit that has a VIN; the VIN toggle in 'Filter and Display' is OFF.
+2. A shift exists for a unit that has a VIN; the VIN toggle in 'Filter &amp; display' is OFF.
 3. You are on the Schedule page.</t>
         </is>
       </c>
@@ -5349,8 +5346,8 @@
 2. It shows the customer name, unit number, the VIN (below unit and asset), and the work order id.
 3. The VIN is visible here even though the grid's VIN toggle is off - the modal always shows it.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9, §9), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9, §9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -5515,8 +5512,8 @@
 4. This is where whole-order vs subset scope is spelled out (the grid block only says 'N Lines').
 Note for the tester: the absence of any money figure is CORRECT and is what this test expects. The product owner ruled on 22 July 2026 that no total in dollars is shown anywhere on the Schedule. If you see no money figure, pass this test.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9, §4.4), read on 11 August 2026. Version 23 of that specification asked for the lines to carry 'labor/total figures'. Version 25, published on 6 August 2026, changed that to 'labor/status figures', so the specification and this test now agree that no money figure is shown; the specification still asks for a labor figure, which this test does not expect, and on that one point the behaviour above follows the product owner's later decision of 22 July 2026, recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9, §4.4), read on 17 August 2026. Version 23 of that specification asked for the lines to carry 'labor/total figures'. Version 25, published on 6 August 2026, changed that to 'labor/status figures', so the specification and this test now agree that no money figure is shown; the specification still asks for a labor figure, which this test does not expect, and on that one point the behaviour above follows the product owner's later decision of 22 July 2026, recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -5568,8 +5565,8 @@
 2. The new value persists after closing and re-opening.
 3. Dependent displays (progress vs estimate) reflect the new value.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -5584,7 +5581,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Notes can be added, edited, and deleted per work order from the modal</t>
+          <t>Notes can be added, edited, and deleted per shift from the modal</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5620,16 +5617,16 @@
           <t xml:space="preserve">1. The note is added and shown in the modal.
 2. The edit is saved and displayed.
 3. The delete removes the note.
-4. Notes are kept per work order (the same note is visible from another shift of the same work order).
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
+4. Notes are kept per shift - a note added to one shift is shown on that shift only, not on other shifts of the same work order.
+---
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>SV-8695 (§4.9 (Notes: add,edit,and delete per work order))</t>
+          <t>SV-8695 (§4.9 (Notes: add/edit/delete per shift))</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -5677,8 +5674,8 @@
 3. 'Adjust' leads to a way to resolve the conflict (for example changing the shift's time).
 4. An unconflicted shift's modal shows no such banner.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -5730,8 +5727,8 @@
 2. There is no 'Reassign' action in the modal; reassignment is done by dragging a shift to another technician row (covered by its own case).
 3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.9, §7), read on 11 August 2026. That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9, §7), read on 17 August 2026. That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -5893,8 +5890,8 @@
 3. Saving creates an event block on that technician's day.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10, §7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10, §7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -5946,8 +5943,8 @@
 2. A live preview block is shown while creating, and dragging resizes it.
 3. Completing creates the event at the previewed time/duration.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6002,8 +5999,8 @@
 4. With all-day ON, specific start/end times are not required (the time fields are disabled or hidden).
 5. The event is created as an all-day block for that technician and day.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10, §8.1), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10, §8.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6056,8 +6053,8 @@
 2. Dropping on another day moves it to that day.
 3. Each move produces a toast with Undo.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10, §7), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10, §7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6108,8 +6105,8 @@
 2. It has a small grey-filled rounded chip on the left containing a calendar icon, and two lines of text beside it: the event name, then the time range in secondary text.
 3. The shift reads as a tinted color-filled block with a colored left rail - the two types are separable at a glance, not by color alone.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6162,8 +6159,8 @@
 2. The color picker offers the same custom color palette as shifts (shared picker with editable labels).
 3. Choosing a color tints the card and the icon chip in matching tones, the same way a colored shift is tinted.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10, §10), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10, §10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6216,8 +6213,8 @@
 2. The event does NOT create a double-booked or overlap conflict with the shift, and the toolbar conflict count does not increase because of it.
 3. The two behave differently on purpose: an event uses up capacity, but it is never flagged as a conflict.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.10, §4.11, §4.12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10, §4.11, §4.12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6271,8 +6268,8 @@
 3. The toolbar conflict pill's count increases.
 4. The conflict is listed in the pill's dropdown.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.11), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8697 and the Schedule specification version 30 (§4.11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6437,8 +6434,8 @@
 3. The list covers all current conflicts (count matches the pill).
 4. Resolving a conflict (for example moving the shift) reduces the count - detection is continuous.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.11, §6), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8697 and the Schedule specification version 30 (§4.11, §6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6489,8 +6486,8 @@
           <t xml:space="preserve">1. The grid navigates to the relevant technician and day.
 2. The conflicted shift is brought into view.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.11), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8697 and the Schedule specification version 30 (§4.11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6541,8 +6538,8 @@
           <t xml:space="preserve">1. Overtime is signaled with the 'OT' text tag and amber tones - NOT red or alarming styling.
 2. Red/alarming styling appears only for conflicts and genuine errors.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.11, §4.12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8697 and the Schedule specification version 30 (§4.11, §4.12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6653,8 +6650,8 @@
 2. A more heavily booked day shows a longer blue fill; the fill never exceeds the track (clamped at 100%).
 3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8698 and the Schedule specification version 30 (§4.12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6704,8 +6701,8 @@
           <t xml:space="preserve">1. An amber segment extends past the right edge of the track, showing the excess.
 2. A tick marks the 100% line where the track ends.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.12), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8698 and the Schedule specification version 30 (§4.12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6756,8 +6753,8 @@
 2. The tag is text, not a color-only signal.
 3. Overtime (per-technician) and capacity (aggregate) are independent signals.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.12, §11), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8698 and the Schedule specification version 30 (§4.12, §11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6920,10 +6917,10 @@
           <t xml:space="preserve">1. The tooltip shows: the customer name; unit, vehicle, and VIN (the tooltip shows the VIN whenever the unit has one, regardless of the 'VIN Number' toggle); the date and time range; the technician; and a scope summary ('N lines · Xh' style).
 2. The individual line names appear as a short list capped at 3, with a '+N more lines' row for the rest (here '+2 more lines'); line statuses are NOT shown.
 3. A time-logged progress bar shows logged vs estimated hours ('X / Yh' style).
-Known issue on the build tested: The tooltip listed ALL FIVE line names on the 5-line series shift with no "+N more lines" row. Spec 4.13: "the individual line names as a short list capped at 3 with a '+N more lines' row". Everything else matched: customer, unit and VIN, date and time range, technician, scope summary "5 lines - 12h" and the progress bar. VIN appears with the toggle off, per Branko 2026-07-31. It has been reported to the QA lead but has no developer ticket yet. Mark this test FAILED and note it in your run comment; do not raise a new ticket without asking the QA lead.
----
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.13), read on 11 August 2026. The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+Known issue on the build tested: the tooltip shows the VIN only when the 'VIN Number' toggle inside 'Filter &amp; display' is switched ON. With that toggle OFF the tooltip shows the unit on its own (for example 'G30'); with it ON the same tooltip reads 'G30 - VIN 12-06696'. The expected behaviour above asks for the VIN whenever the unit has one, whichever way the toggle is set. It has been
+---
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.13), read on 17 August 2026. The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -6973,8 +6970,8 @@
           <t xml:space="preserve">1. The customer name line includes the conflict icon.
 2. The conflict reason is shown in amber.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.13), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.13), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7025,8 +7022,8 @@
 2. The date and time range are shown.
 3. The technician is shown.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.13), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.13), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7081,8 +7078,8 @@
 3. The tooltip is read-only (no buttons/actions inside it).
 4. Clicking the block opens the full detail modal as normal.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.13), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.13), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7134,8 +7131,8 @@
 2. Near a side edge, the tooltip shifts horizontally to stay fully within the viewport.
 3. No part of the tooltip is clipped off-screen.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.13), read on 11 August 2026. Last checked against build v3.5-d122eef on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.13), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7484,8 +7481,8 @@
           <t xml:space="preserve">1. The grid jumps to the range containing the current date (today's day, this week, or this month depending on the active view).
 2. The date label updates accordingly.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7538,8 +7535,8 @@
 3. Month view: each click moves one month; the label shows that month.
 4. The label always matches what the grid displays.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7591,10 +7588,9 @@
 2. All five of these are matched against, so searching any one of them finds the blocks it belongs to: customer name, work order number, unit number, technician name, and line name.
 3. Note for the tester: the specification does not say what happens to the blocks that do NOT match - whether they stay on the grid faded out, or disappear until you clear the search. Do not pass or fail this test on that. Check only that searching each of the five things above finds the right blocks. What happens to the non-matching blocks is an open question with the product owner.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6, Search), read on 11 August 2026, which describes the search as filtering the grid blocks by matching against customer name, WO number, unit number, technician name, and line name.
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§6, Search), read on 17 August 2026, which describes the search as filtering the grid blocks by matching against customer name, WO number, unit number, technician name, and line name.
 This case used to also expect matching blocks to highlight and non-matching blocks to fade. That sentence was in version 23 of the specification; version 24, published on 6 August 2026, deleted it, and it has not come back in versions 25, 26 or 27. Story SV-8686 does still ask for it, but that wording has not been touched since the story was created on 27 July 2026, so the specification's deletion is the newer decision and it is the one this case now follows.
-Last checked against build v3.5-7ec992f on 8/6/2026; the wording above was corrected on 11 August 2026 from the documents only, with no build opened.
-AUTOMATION: READY
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7645,8 +7641,8 @@
 2. Defaults: all department toggles ON, 'My Shifts' OFF, 'VIN Number' OFF.
 3. There is no separate departments-only control - this dropdown replaces it.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6, §9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§6, §9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7699,8 +7695,8 @@
 2. Other departments are unaffected.
 3. Turning it back on restores the group.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7754,8 +7750,8 @@
 3. This is a personal convenience filter only - it does not change what you are permitted to see (default is OFF, everyone's shifts visible).
 4. For a user who has no technician/staff record of their own, the 'My Shifts' option is not shown at all.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9, §14.3), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as a user with no staff record of their own
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§9, §14.3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7812,8 +7808,8 @@
 5. The 'VIN Number' toggle affects the block only - the tooltip and the modal always show the VIN when the unit has one.
 Note for the tester: the VIN staying visible in the hover summary and in the shift window while the VIN switch is off is CORRECT and is what this test expects. The product owner ruled on 31 July 2026 that the VIN is always visible on hover regardless of the switch. If you see it there, pass this test.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9, §4.4, §4.8), read on 11 August 2026. The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and stories SV-8700 and SV-8690 and SV-8694 and the Schedule specification version 30 (§9, §4.4, §4.8), read on 17 August 2026. The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7868,8 +7864,8 @@
 3. Capacity Planning OFF: the capacity bars disappear from the column headers; ON: they reappear with the same values.
 4. Events OFF: event blocks disappear from the grid while shifts remain; ON: the events reappear unchanged.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§6, §9, §4.12), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§6, §9, §4.12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7922,8 +7918,8 @@
 2. Working hours remain unshaded.
 3. Turning it off removes the shading.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9, §4.8), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§9, §4.8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -7975,8 +7971,8 @@
 2. The hours match the technicians' configured hours.
 3. Turning it off hides the hours again.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8028,8 +8024,8 @@
 2. 'Show Sunday' off too: 5 weekday columns remain (Monday to Friday).
 3. Both back on: the full Monday-to-Sunday 7-column week returns.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§9, §3.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§9, §3.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8083,8 +8079,8 @@
 3. Technician B is added to the affected line's roster and technician A is removed from it.
 4. A toast with Undo appears.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §12), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§7, §12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8189,8 +8185,8 @@
           <t xml:space="preserve">1. The menu offers a 'New Work Order' item.
 2. Choosing it directs the user to create a work order (a toast / prompt pointing to the Work Orders tab).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §4.10), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§7, §4.10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8247,8 +8243,8 @@
 3. After you confirm, the block sits in the new technician's row, that technician is added to the work order line's technician list, and the previous one is taken off it.
 Why this test covers Week view only: the specification describes reassignment as dragging a shift from one technician row to another, and Month view has no technician rows at all - it is a calendar of day boxes. Whether reassignment should be possible in Month view is therefore part of the open question on SV-8867 and is deliberately not asserted here.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §12), read on 11 August 2026: dragging a shift block from one technician row to another reassigns it and a confirmation handles cross-technician moves, and a series is a grouping over ordinary daily shifts rather than a different kind of thing, so an ordinary shift's behaviour applies to a series member too. Story SV-8692 covers series-aware deletion only and says nothing about reassignment. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8867 and the Schedule specification version 30 (§7, §12), read on 17 August 2026: dragging a shift block from one technician row to another reassigns it and a confirmation handles cross-technician moves, and a series is a grouping over ordinary daily shifts rather than a different kind of thing, so an ordinary shift's behaviour applies to a series member too. Story SV-8692 covers series-aware deletion only and says nothing about reassignment.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8354,11 +8350,11 @@
       <c r="G145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A scope prompt appears with three options: this shift only, this and everything after, and the whole series.
-2. Each option states its consequence in hours returned (spec's example format: 'returns 8h' / 'returns 56h').
+2. Each option states how many scheduled hours it removes.
 3. The prompt uses routine, lightweight styling - not alarming destructive styling.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8400,7 +8396,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>1. Delete a middle shift with the 'this shift only' scope.
+          <t>1. Delete a middle shift with the 'This shift only' scope.
 2. Look at the series on the grid.
 3. Check the scheduled hours.</t>
         </is>
@@ -8409,11 +8405,11 @@
         <is>
           <t xml:space="preserve">1. Only that day's shift is removed.
 2. The series keeps the gap - the remaining shifts do NOT shuffle to close it.
-3. The removed day's hours return to the estimate's remaining (scheduled hours drop by that day's hours).
+3. The scheduled hours drop by that day's hours (the estimate and any clocked hours are separate quantities and are not changed by the deletion).
 4. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8455,7 +8451,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>1. Delete the series' THIRD shift with the 'this and everything after' scope.
+          <t>1. Delete the series' THIRD shift with the 'This and all later shifts' scope.
 2. Look at the series on the grid.</t>
         </is>
       </c>
@@ -8465,8 +8461,8 @@
 2. The first two shifts remain untouched.
 3. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8518,8 +8514,8 @@
 2. Technician B's independent series is untouched (the scope is per technician's series).
 3. An undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8573,8 +8569,8 @@
 3. Middle shift: all three options.
 4. Cancelling leaves the series unchanged in every case.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8625,8 +8621,8 @@
           <t xml:space="preserve">1. No series-scope prompt appears (the scope question is only for shifts that belong to a series).
 2. The shift is deleted and an undo toast appears.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8641,7 +8637,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Toast lasts ~7s with Undo (about 4s without); stays on hover, goes on leave</t>
+          <t>Toast stays 4 to 7 seconds, stays while hovered, goes when the cursor leaves</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -8674,12 +8670,12 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Untouched, a toast that has an Undo action persists about 7 seconds; a toast without Undo persists about 4 seconds, before dismissing.
+          <t xml:space="preserve">1. Untouched, the toast stays on screen for between 4 and 7 seconds and then disappears on its own.
 2. While the cursor is over it, the toast stays (does not auto-dismiss).
 3. After the cursor leaves, it dismisses.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§7, §11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8736,8 +8732,8 @@
 4. Undo after reassign: the shift returns to the original technician, and the line's roster is restored (original tech back on, target tech off).
 5. Every destructive action is undoable within the toast's lifetime.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7, §11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§7, §11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8792,8 +8788,8 @@
 3. Clicking Undo within the toast's lifetime reverses the action (the deleted shift comes back).
 4. Note for the tester: Undo works by performing a reversing action, not by holding the change back - a change surviving a refresh before Undo is expected, not a bug.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026, which requires the toast and its Undo. That specification does not say how Undo works underneath, so the point above - that the action is already saved and Undo reverses it rather than holding it back - comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§7), read on 17 August 2026, which requires the toast and its Undo. That specification does not say how Undo works underneath, so the point above - that the action is already saved and Undo reverses it rather than holding it back - comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8848,8 +8844,8 @@
 4. With two layers open, the FIRST Escape closes only the topmost layer, and the SECOND Escape closes the next layer down.
 5. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8905,8 +8901,8 @@
 3. In the note editor, Enter inserts a new line in the note - it does NOT confirm or close the dialog.
 4. The multiline note can be completed and saved normally.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§7), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8958,8 +8954,8 @@
 2. Focus stays trapped inside the modal (wraps back to its first control) until the modal closes.
 3. On the page, toolbar and sidebar controls are reachable by keyboard.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9010,8 +9006,8 @@
           <t xml:space="preserve">1. Both the single shift and the multi-week series render in the default blue.
 2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§10), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9066,8 +9062,8 @@
 3. The color is per SHIFT, not per work order - the other shift from the same work order keeps its own (default blue) color and does not change.
 4. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§10, §4.9, §4.4), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and stories SV-8700 and SV-8690 and the Schedule specification version 30 (§10, §4.9, §4.4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9120,8 +9116,8 @@
 2. The renamed label shows for the whole shop - the same picker opened elsewhere shows 'ZZAUTOTEST Rush'.
 3. Shifts and events share the same custom palette with the same labels.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§10, §4.10), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§10, §4.10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9177,8 +9173,8 @@
 4. Each day has a From time and a To time you can set.
 5. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8699 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9230,8 +9226,8 @@
 2. The toggle is OFF by default (no custom hours set).
 3. Turning it ON reveals a per-day working-hours editor for that technician.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8699 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9281,8 +9277,8 @@
           <t xml:space="preserve">1. With no custom hours, the technician's working hours fall back to the shop business hours.
 2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8699 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9333,8 +9329,8 @@
 2. The added range starts empty (no From/To pre-filled).
 3. Each added range can be removed individually.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8699 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9388,8 +9384,8 @@
 4. The incomplete row (empty From/To) is ignored by the overlap check - it does not raise the overlap error.
 5. Save is not blocked by an incomplete row on its own (only genuine overlaps disable Save).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8699 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9444,8 +9440,8 @@
 3. ALL technicians' shifts and events are visible (not just the user's own).
 4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1, §14.3), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as a view-only user
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1, §14.3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9500,8 +9496,8 @@
 3. No creation menu opens at all - there is no 'Create Event' and no 'New Work Order' offered.
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as a view-only user
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9551,8 +9547,8 @@
           <t xml:space="preserve">1. The Schedule top-level nav item is not shown at all.
 2. The rest of the app works normally for the role.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as a user without the Schedule permission
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9608,8 +9604,8 @@
 4. Edge-resize and horizontal drag work in day view.
 5. Modal fields are editable and save.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as an edit-without-delete user
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9662,8 +9658,8 @@
 2. Events likewise offer no delete.
 3. No path exists to remove shifts or events - while creating and modifying still work.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as an edit-without-delete user
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9717,8 +9713,8 @@
 3. Events can be deleted too.
 4. Undo toasts appear (restore the items via Undo to clean up).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as a delete-capable user
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9770,8 +9766,8 @@
 2. Delete cannot be granted without Edit.
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9824,8 +9820,8 @@
 2. Shifts already on the grid can still be viewed and interacted with per the role's Schedule tier.
 3. New work orders cannot be dragged on - the WO list is simply not visible.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.2), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§14.2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9876,8 +9872,8 @@
           <t xml:space="preserve">1. The user sees ALL technicians' shifts and events, not only their own - there is no role-based 'own shifts only' restriction.
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.3), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as a view-only technician
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9928,8 +9924,8 @@
           <t xml:space="preserve">1. The department-assigned staff member appears as a technician row - row presence is controlled by the department on the staff record, NOT by role permission.
 2. The staff member without a department does not appear as a row.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.4), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§14.4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9979,8 +9975,8 @@
           <t xml:space="preserve">1. The Time-Clock-ON staff member can clock in.
 2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.4), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
-AUTOMATION: HOLD - needs a second sign-in as each of the two staff members
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§14.4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10033,8 +10029,8 @@
 2. The schedule structure itself (the shift's day, time, and technician) stays visible so the grid remains usable.
 3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.2), read on 11 August 2026. The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§14.2), read on 17 August 2026. The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10091,8 +10087,8 @@
 3. The user from step 4 gets the read-only schedule - nothing can be dragged onto the grid and no shift can be created.
 4. The user from step 5 can drag a work order onto the grid and create a shift.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14.1), read on 11 August 2026. Last checked against build v3.5-65d6500 on 8/12/2026.
-AUTOMATION: HOLD - needs a second sign-in as a holder of each permission level
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10145,8 +10141,8 @@
 3. On narrow viewports the sidebar collapses.
 4. No content becomes permanently unreachable and nothing errors.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and stories SV-8686 and SV-8687 and the Schedule specification version 30 (§11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10199,8 +10195,8 @@
 2. The drill-down behaves the same with many lines.
 3. Search stays responsive on the long list.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10253,8 +10249,8 @@
 2. View switches complete without long hangs.
 3. Tooltips and modals stay responsive.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10358,8 +10354,8 @@
           <t xml:space="preserve">1. All three quantities are shown/derivable and may differ from one another.
 2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5, §12), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5, §12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10410,8 +10406,8 @@
           <t xml:space="preserve">1. Every shift in the series starts at the SAME local wall-clock time (e.g. 8:00 AM) on both sides of the clock change.
 2. No shift in the series silently moves an hour earlier or later after the change date.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026, which covers spreading work across days. That specification says nothing about clock changes or daylight saving - those words do not appear in it at all - so the point above comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5), read on 17 August 2026, which covers spreading work across days. That specification says nothing about clock changes or daylight saving - those words do not appear in it at all - so the point above comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10465,8 +10461,8 @@
 3. Conflict and overtime cues remain distinguishable (they never rely on colour alone - text/icon still present).
 4. Switching back to light mode restores the normal look with nothing stuck in dark colours.
 ---
-This is the expected behaviour as per story SV-8700 (dark theme), read on 11 August 2026, story SV-8698 (overtime and conflict cues are not colour-only), read on 11 August 2026, and the Schedule specification version 27 (§11), read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per story SV-8700 (dark theme), read on 17 August 2026, story SV-8698 (overtime and conflict cues are not colour-only), read on 17 August 2026, and the Schedule specification version 30 (§11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10528,8 +10524,8 @@
 4. At step 8, on the other computer or in the private window, the Schedule is ALSO in dark mode. The choice is remembered against your account, not against the one browser you set it in.
 5. Switching back to light mode at step 9 works the same way and is remembered in the same way.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8700 (requirement 5), read on 11 August 2026, and the Schedule specification version 27 (§11 Dark theme), read on 11 August 2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, its story SV-8700 (requirement 5), read on 17 August 2026, and the Schedule specification version 30 (§11 Dark theme), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10585,8 +10581,8 @@
 3. None of the three blends into the page so that its edges cannot be made out, and none of them is missing that separation entirely while the light-mode version has it.
 4. Nothing you check is unreadable, and no text or icon disappears into the background.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, its story SV-8700 (requirement 5), read on 11 August 2026, and the Schedule specification version 27 (§11 Dark theme), read on 11 August 2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, its story SV-8700 (requirement 5), read on 17 August 2026, and the Schedule specification version 30 (§11 Dark theme), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10693,8 +10689,8 @@
 2. Events are still events and shifts are still shifts (nothing changed kind or vanished).
 3. Their details open normally and are editable/deletable like any other entry.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - cannot be run now - it needs shifts noted BEFORE the release, and the release is already deployed
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10746,8 +10742,8 @@
 2. Note for the tester: before this release the Dashboard duplicated such a work order once per scheduled day - showing one combined row now is the intended fix, do not report it as a missing-rows bug.
 3. Work orders with a single shift are unaffected.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - the Dashboard section this test needs does not exist in the build
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10799,8 +10795,8 @@
 2. It behaves like any other scheduled entry (opens, moves, deletes normally).
 3. It also appears in the Dashboard's schedule section for that day.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - work order creation offers no appointment in the build
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10853,8 +10849,8 @@
 2. The shift does NOT appear on location B's board, even though the technician is enrolled there too.
 3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10908,8 +10904,8 @@
 3. After saving, the Schedule sidebar reflects the chosen priority and the Priority filter finds the work order under High.
 4. A work order with no priority set simply shows none (it is not treated as an error).
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - the Priority field this test needs does not exist in the build
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -10963,8 +10959,8 @@
 3. View + Edit: the POST and PATCH succeed (HTTP 201/200); the DELETE is refused with HTTP 403 because the user lacks Schedule: Delete.
 4. Each refusal is a clean 403 response - never a server error.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14), read on 11 August 2026, which sets the three permission levels. That specification does not describe what the server returns when a request is refused, so the refusal responses above come from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs three separate sign-ins, one per permission level
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14), read on 17 August 2026, which sets the three permission levels. That specification does not describe what the server returns when a request is refused, so the refusal responses above come from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -11018,8 +11014,8 @@
 3. The over-120-shift request is refused with HTTP 422 even WITH the acknowledgement - the hard cap cannot be overridden.
 4. Refused calls leave no partial series behind.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§4.5), read on 11 August 2026, with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5), read on 17 August 2026, with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -11071,8 +11067,8 @@
 2. For the caller without Work Orders: View, the work-order-derived details (customer, unit, VIN, line names) are absent/empty in the response itself - not just hidden on screen.
 3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the Schedule specification version 27 (§14), read on 11 August 2026. The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 11 August 2026. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14), read on 17 August 2026. The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -11115,7 +11111,7 @@
       <c r="F196" s="2" t="inlineStr">
         <is>
           <t>1. While scoped to location A, call GET /api/schedule/shifts/{id} with the location-B shift id.
-2. Also try PATCH /api/schedule/shifts/{id} on the same id.
+2. Also try PATCH /api/schedule/shifts/{id} on the same id, changing a real field such as the colour. (A request that would change nothing is rejected on its own account before the location is even checked, so always send a real change here.)
 3. Call GET /api/schedule/board for location A's current week.</t>
         </is>
       </c>
@@ -11125,8 +11121,8 @@
 2. The PATCH on the foreign id is refused the same way (404) - no cross-location edit is possible.
 3. Location A's board contains only location A's shifts - nothing from location B leaks in.
 ---
-This is the expected behaviour as per epic SV-8685, read on 11 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 11 August 2026. No numbered requirement in the Schedule specification version 27 covers this point. Last checked against build v3.5-7ec992f on 8/6/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>

--- a/testrail-import/schedule-v1-testrail-import.xlsx
+++ b/testrail-import/schedule-v1-testrail-import.xlsx
@@ -529,7 +529,7 @@
 4. The main area is the schedule grid showing technician rows, with a toolbar above it.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§3, §3.1, §3.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -586,7 +586,7 @@
 4. The same shifts appear in all three views - each one drawn to suit that view: positioned on the hour line in Day, as a chip in the day column in Week, and as a compact chip in Month.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§3.2, §6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -639,7 +639,7 @@
 3. Every staff member assigned to a visible department appears as a row, regardless of their role.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§3.2, §14.4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -693,7 +693,7 @@
 3. Other department groups are unaffected.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§3.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -743,7 +743,7 @@
 2. Department visibility is controlled only through the department toggles in the 'Filter &amp; display' dropdown.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§3.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -850,7 +850,7 @@
 3. The grid shows the Day layout: a 24-hour timeline for each technician row, with shifts placed at their times.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the acceptance criterion of its story SV-8686, read on 17 August 2026, which states that when the schedule page loads the grid displays with day view as default. The Schedule specification version 30 does not say which view the page opens on, so this expectation comes from the story rather than the specification.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -902,7 +902,7 @@
 3. The clicked date is highlighted as the selected date in the mini calendar.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1, §5.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -957,7 +957,7 @@
 3. The main grid can then be navigated by clicking a date in the newly shown month.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1011,7 +1011,7 @@
 2. Clicking again expands the calendar grid back.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1, §5.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1066,7 +1066,7 @@
 3. Hovering a week row highlights that whole week row.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1120,7 +1120,7 @@
 3. There are no Assigned/Unassigned tabs - assignment is available only as a filter behind the 'Filter' button.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1, §5.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1290,7 +1290,7 @@
 3. With very many work orders, the list may load further results in pages as you scroll - that is expected, not a fault.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1345,7 +1345,7 @@
 3. Clearing the search restores the full list.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1514,7 +1514,7 @@
 3. The 'Filters' button shows a badge with the number of active filters.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1570,7 +1570,7 @@
 3. There are no Assigned/Unassigned tabs - this filter is the only assignment split.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1, §3.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1627,7 +1627,7 @@
 Note for the tester: this shop's schedule list only holds work orders in two statuses, Approved and Review, so most of the other choices correctly come back empty. An empty list for a status no work order is in is the right answer, not a fault.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1682,7 +1682,7 @@
 2. Only High-priority work orders remain in the list.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1791,7 +1791,7 @@
 2. Removing either the search text or the filter widens the list to the remaining condition.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§5.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1848,7 +1848,7 @@
 5. Clicking back restores the work order card list.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1903,7 +1903,7 @@
 3. The line count in the drill-down header matches the number of APPROVED lines on the work order - a line that was never approved is neither listed nor counted.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1958,7 +1958,7 @@
 3. Each line row has its own drag handle, so it can be dragged independently onto the grid.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1, §8.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2013,7 +2013,7 @@
 3. After a technician is scheduled onto the badge-bearing line, the badge goes away.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2068,7 +2068,7 @@
 2. Typing the customer name returns no results - the line search matches line titles only (the list is already scoped to one work order, so customer/unit/WO fields are not searched).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2124,7 +2124,7 @@
 3. All lists every approved line, and its count matches the drill-down header's line count.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§3.1, §5.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2232,7 +2232,7 @@
 3. No shift is created until a scope is chosen.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.1, §4.3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2286,7 +2286,7 @@
 3. The technician is added to that line's roster only (not to the order's other lines).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2392,7 +2392,7 @@
 2. The shift sits on the dropped day only.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2445,7 +2445,7 @@
 3. Releasing outside any valid cell creates nothing.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2502,7 +2502,7 @@
 5. Nothing asks you to swap or replace the technician who was already there, and no limit is reached on how many technicians a line can have.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§1.2, §4.3, §7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2554,7 +2554,7 @@
 2. The result is the same as the equivalent drag-and-drop (scope picker / spread step rules apply the same way).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§7, §11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY - EXPECT FAIL (SV-8957)
 </t>
         </is>
       </c>
@@ -2777,7 +2777,7 @@
 5. Rows for lines that already have technicians show the current roster as an avatar stack plus count.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8689 and the Schedule specification version 30 (§4.3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2831,7 +2831,7 @@
 3. The technician is added to the roster of every one of those lines.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8689 and the Schedule specification version 30 (§4.3, §4.4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2884,7 +2884,7 @@
 3. The block's last text line shows the line's name.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8689 and the Schedule specification version 30 (§4.3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2943,7 +2943,7 @@
 5. Confirming creates ONE shift covering exactly the ticked lines, and the technician is added to those lines' rosters only - not to the other lines.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8689 and the Schedule specification version 30 (§4.3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -2996,7 +2996,7 @@
 Known issue on the build tested: the time this test talks about is stored correctly but the Schedule SHOWS it six hours later than it should be, so a 7:00 AM start reads 1:00 PM on screen. That is already raised with the developers as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Check the value is right by the rule this test describes, and ignore the six-hour display shift - do not raise a new ticket for it.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3048,7 +3048,7 @@
           <t xml:space="preserve">1. The shift starts at the shop's business-hours start time.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3154,7 +3154,7 @@
 Note for the tester: every time on the Schedule is currently shown six hours later than the time it was booked for. That is already reported as SV-8848 (https://shopview.atlassian.net/browse/SV-8848). Read the position on the timeline rather than the printed time, and do not raise it again.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3603,7 +3603,7 @@
 5. Choosing a new scope updates the spread step's header and hours accordingly.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3817,7 +3817,7 @@
 3. B's series is created from the adjusted start date onward.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -3872,7 +3872,7 @@
 4. The end date is the result of the daily distribution (for 40h at 8h/day starting Monday, the series ends on the fifth working day).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and stories SV-8691 and SV-9238 (spread skips weekends only; nothing else skipped) and the Schedule specification version 30 (§4.5, §12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - waiting on the product owner's answer, and the question has not been sent yet
 </t>
         </is>
       </c>
@@ -3926,7 +3926,7 @@
 4. Confirming creates the series, and the confirm button carries the count, for example 'Create 13 shifts'.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and stories SV-8691 and SV-9237 (spread preview summary and confirm label) and the Schedule specification version 30 (§4.5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -3980,7 +3980,7 @@
 4. A toast with Undo appears.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5, §4.6, §8.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -4033,7 +4033,7 @@
 3. Planned hours across technicians may now exceed the estimate - this is expected and produces no error (progress is driven by clocked-in time).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5, §12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4089,7 +4089,7 @@
 4. No half-created series is left behind after a refused attempt.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5), read on 17 August 2026, with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4372,7 +4372,7 @@
 3. Weekend columns inside the series are empty (no bar) when no business hours are set for those weekend days.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§4.6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4426,7 +4426,7 @@
 3. A 'week N of M' cue shows the position within the series.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§4.6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4478,7 +4478,7 @@
 2. The block carries a cue in the spirit of 'part of an M-week job' indicating it belongs to a longer series.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§4.6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4532,7 +4532,7 @@
 3. The detail modal shows that single day's shift (its own day and hours) while indicating it belongs to the series.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§4.6, §8.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4585,7 +4585,7 @@
 4. No work order number appears on the block.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8690 and the Schedule specification version 30 (§4.4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4639,7 +4639,7 @@
 3. Each detail modal lists exactly which lines the shift covers.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8690 and the Schedule specification version 30 (§4.4, §12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4692,7 +4692,7 @@
 3. No scope icons distinguish whole-order from subset shifts.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8690 and the Schedule specification version 30 (§4.4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4747,7 +4747,7 @@
 4. No conflict is flagged for back-to-back (non-intersecting) shifts.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8693 and the Schedule specification version 30 (§4.7, §12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4799,7 +4799,7 @@
 3. The overlap is also flagged as a Double-booked conflict (stacking reads as 'resolve me').
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8693 and the Schedule specification version 30 (§4.7, §4.11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4854,7 +4854,7 @@
 5. The hidden shifts can be opened from that popover.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8693 and the Schedule specification version 30 (§4.7 Overlap and lane stacking and §11 Accessibility - the overflow uses shape), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4908,7 +4908,7 @@
 3. The overflow affordance opens the hidden-shifts popover in each view.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8693 and the Schedule specification version 30 (§4.7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5019,7 +5019,7 @@
 2. The same sticky-header behavior applies in week view.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8694 and the Schedule specification version 30 (§4.8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5075,7 +5075,7 @@
 5. A toast with Undo appears for the move.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and stories SV-8694 and SV-9244 (15-minute snap with a live time chip) and the Schedule specification version 30 (§4.8, §7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -5183,7 +5183,7 @@
 3. Hovering the now line while your pointer is over the grid shows a label (the current time).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8694 and the Schedule specification version 30 (§4.8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5513,7 +5513,7 @@
 Note for the tester: the absence of any money figure is CORRECT and is what this test expects. The product owner ruled on 22 July 2026 that no total in dollars is shown anywhere on the Schedule. If you see no money figure, pass this test.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9, §4.4), read on 17 August 2026. Version 23 of that specification asked for the lines to carry 'labor/total figures'. Version 25, published on 6 August 2026, changed that to 'labor/status figures', so the specification and this test now agree that no money figure is shown; the specification still asks for a labor figure, which this test does not expect, and on that one point the behaviour above follows the product owner's later decision of 22 July 2026, recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5566,7 +5566,7 @@
 3. Dependent displays (progress vs estimate) reflect the new value.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5620,7 +5620,7 @@
 4. Notes are kept per shift - a note added to one shift is shown on that shift only, not on other shifts of the same work order.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -5675,7 +5675,7 @@
 4. An unconflicted shift's modal shows no such banner.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5728,7 +5728,7 @@
 3. Delete on a series member asks for a deletion scope (the full scope behavior has its own cases).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.9, §7), read on 17 August 2026. That specification describes this point in two different ways, so the behaviour above follows its first-release wording and a product owner decision is still awaited; the open question is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5891,7 +5891,7 @@
 4. A toast with Undo appears.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10, §7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5944,7 +5944,7 @@
 3. Completing creates the event at the previewed time/duration.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6000,7 +6000,7 @@
 5. The event is created as an all-day block for that technician and day.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10, §8.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6054,7 +6054,7 @@
 3. Each move produces a toast with Undo.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10, §7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - not re-checked against the current build - it needs a drag that could not be completed
 </t>
         </is>
       </c>
@@ -6106,7 +6106,7 @@
 3. The shift reads as a tinted color-filled block with a colored left rail - the two types are separable at a glance, not by color alone.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6160,7 +6160,7 @@
 3. Choosing a color tints the card and the icon chip in matching tones, the same way a colored shift is tinted.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10, §10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6214,7 +6214,7 @@
 3. The two behave differently on purpose: an event uses up capacity, but it is never flagged as a conflict.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8696 and the Schedule specification version 30 (§4.10, §4.11, §4.12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6269,7 +6269,7 @@
 4. The conflict is listed in the pill's dropdown.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8697 and the Schedule specification version 30 (§4.11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6435,7 +6435,7 @@
 4. Resolving a conflict (for example moving the shift) reduces the count - detection is continuous.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8697 and the Schedule specification version 30 (§4.11, §6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6487,7 +6487,7 @@
 2. The conflicted shift is brought into view.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8697 and the Schedule specification version 30 (§4.11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6539,7 +6539,7 @@
 2. Red/alarming styling appears only for conflicts and genuine errors.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8697 and the Schedule specification version 30 (§4.11, §4.12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6651,7 +6651,7 @@
 3. The track width is identical across all days (capacity is not rescaled per day), so bars are comparable at a glance.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8698 and the Schedule specification version 30 (§4.12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6702,7 +6702,7 @@
 2. A tick marks the 100% line where the track ends.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8698 and the Schedule specification version 30 (§4.12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6754,7 +6754,7 @@
 3. Overtime (per-technician) and capacity (aggregate) are independent signals.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8698 and the Schedule specification version 30 (§4.12, §11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6971,7 +6971,7 @@
 2. The conflict reason is shown in amber.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.13), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7023,7 +7023,7 @@
 3. The technician is shown.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.13), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7079,7 +7079,7 @@
 4. Clicking the block opens the full detail modal as normal.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.13), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7132,7 +7132,7 @@
 3. No part of the tooltip is clipped off-screen.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§4.13), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7195,7 +7195,7 @@
 8. Clicking the button at step 4 hides the left panel, and clicking it again at step 7 shows it.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and its story SV-9243 (left-panel collapse toggle) and the Schedule specification version 30 (§5.3 Panel collapse and §6 Grid toolbar), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -7253,7 +7253,7 @@
 4. Clicking the button a second time brings the panel back to its normal width, and the grid goes back to the size it was at step 1.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and its story SV-9243 (left-panel collapse toggle) and the Schedule specification version 30 (§5.3 Panel collapse and §3.1 Left panel), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -7315,7 +7315,7 @@
 6. The work order you had opened is still the selected one.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and its story SV-9243 (left-panel collapse toggle) and the Schedule specification version 30 (§5.3 Panel collapse and §3.1 Left panel), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -7371,7 +7371,7 @@
 3. The pop-up behaves normally otherwise - you can read it, use its buttons, and close it.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and its story SV-9243 (left-panel collapse toggle) and the Schedule specification version 30 (§5.3 Panel collapse, Popovers and modals), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -7431,7 +7431,7 @@
 3. At step 7, the second person's left panel is showing as normal. Your choice applied only to you and did not change what anybody else sees.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and its story SV-9243 (left-panel collapse toggle) and the Schedule specification version 30 (§5.3 Panel collapse, Persistence), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -7482,7 +7482,7 @@
 2. The date label updates accordingly.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7536,7 +7536,7 @@
 4. The label always matches what the grid displays.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7590,7 +7590,7 @@
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§6, Search), read on 17 August 2026, which describes the search as filtering the grid blocks by matching against customer name, WO number, unit number, technician name, and line name.
 This case used to also expect matching blocks to highlight and non-matching blocks to fade. That sentence was in version 23 of the specification; version 24, published on 6 August 2026, deleted it, and it has not come back in versions 25, 26 or 27. Story SV-8686 does still ask for it, but that wording has not been touched since the story was created on 27 July 2026, so the specification's deletion is the newer decision and it is the one this case now follows.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7642,7 +7642,7 @@
 3. There is no separate departments-only control - this dropdown replaces it.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§6, §9), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7696,7 +7696,7 @@
 3. Turning it back on restores the group.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§9), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7751,7 +7751,7 @@
 4. For a user who has no technician/staff record of their own, the 'My Shifts' option is not shown at all.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§9, §14.3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as a user with no staff record of their own
 </t>
         </is>
       </c>
@@ -7809,7 +7809,7 @@
 Note for the tester: the VIN staying visible in the hover summary and in the shift window while the VIN switch is off is CORRECT and is what this test expects. The product owner ruled on 31 July 2026 that the VIN is always visible on hover regardless of the switch. If you see it there, pass this test.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and stories SV-8700 and SV-8690 and SV-8694 and the Schedule specification version 30 (§9, §4.4, §4.8), read on 17 August 2026. The behaviour above follows a later product owner decision dated 31 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7865,7 +7865,7 @@
 4. Events OFF: event blocks disappear from the grid while shifts remain; ON: the events reappear unchanged.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§6, §9, §4.12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7919,7 +7919,7 @@
 3. Turning it off removes the shading.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§9, §4.8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -7972,7 +7972,7 @@
 3. Turning it off hides the hours again.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§9), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8025,7 +8025,7 @@
 3. Both back on: the full Monday-to-Sunday 7-column week returns.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§9, §3.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8080,7 +8080,7 @@
 4. A toast with Undo appears.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8695 and the Schedule specification version 30 (§7, §12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8186,7 +8186,7 @@
 2. Choosing it directs the user to create a work order (a toast / prompt pointing to the Work Orders tab).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§7, §4.10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8244,7 +8244,7 @@
 Why this test covers Week view only: the specification describes reassignment as dragging a shift from one technician row to another, and Month view has no technician rows at all - it is a calendar of day boxes. Whether reassignment should be possible in Month view is therefore part of the open question on SV-8867 and is deliberately not asserted here.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8867 and the Schedule specification version 30 (§7, §12), read on 17 August 2026: dragging a shift block from one technician row to another reassigns it and a confirmation handles cross-technician moves, and a series is a grouping over ordinary daily shifts rather than a different kind of thing, so an ordinary shift's behaviour applies to a series member too. Story SV-8692 covers series-aware deletion only and says nothing about reassignment.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8301,7 +8301,6 @@
 This is the same capability as the old 'Add Existing Work Order' button (SV-8916), re-specified as a menu item.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-9242 and the Schedule specification version 30 (§7,§4.10,§14.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -8515,7 +8514,7 @@
 3. An undo toast appears.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8570,7 +8569,7 @@
 4. Cancelling leaves the series unchanged in every case.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8622,7 +8621,7 @@
 2. The shift is deleted and an undo toast appears.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8692 and the Schedule specification version 30 (§7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8733,7 +8732,7 @@
 5. Every destructive action is undoable within the toast's lifetime.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§7, §11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8789,7 +8788,7 @@
 4. Note for the tester: Undo works by performing a reversing action, not by holding the change back - a change surviving a refresh before Undo is expected, not a bug.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8688 and the Schedule specification version 30 (§7), read on 17 August 2026, which requires the toast and its Undo. That specification does not say how Undo works underneath, so the point above - that the action is already saved and Undo reverses it rather than holding it back - comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8845,7 +8844,7 @@
 5. Escape works anywhere on the schedule page as a global shortcut, following the defined stacking order (delete scope, reassign, spread, capacity, event modal, event view, line picker, shift detail, cell menu, calendar picker, customize, filters, search).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8902,7 +8901,7 @@
 4. The multiline note can be completed and saved normally.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -8955,7 +8954,7 @@
 3. On the page, toolbar and sidebar controls are reachable by keyboard.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9007,7 +9006,7 @@
 2. No special color is auto-applied to long jobs - blue is the default for ALL shifts.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9063,7 +9062,7 @@
 4. Colors carry no fixed meaning - they are free choice beyond the two defaults (blue shift / grey event).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and stories SV-8700 and SV-8690 and the Schedule specification version 30 (§10, §4.9, §4.4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9117,7 +9116,7 @@
 3. Shifts and events share the same custom palette with the same labels.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8700 and the Schedule specification version 30 (§10, §4.10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9174,7 +9173,6 @@
 5. The saved shop business hours are used by the Schedule (start-time hierarchy, before/after-hours conflicts, business-hours shading).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8699 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9227,7 +9225,6 @@
 3. Turning it ON reveals a per-day working-hours editor for that technician.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8699 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9278,7 +9275,6 @@
 2. Start-time defaults and before/after-hours conflict checks for that technician use the shop business hours.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8699 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9330,7 +9326,6 @@
 3. Each added range can be removed individually.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8699 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
 </t>
         </is>
       </c>
@@ -9385,7 +9380,7 @@
 5. Save is not blocked by an incomplete row on its own (only genuine overlaps disable Save).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8699 and the Schedule specification version 30 (§4.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9441,7 +9436,7 @@
 4. Tooltips show on hover, and the shift/event detail modals open in read-only mode.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1, §14.3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as a view-only user
 </t>
         </is>
       </c>
@@ -9497,7 +9492,7 @@
 4. In the modal, edit fields are hidden or disabled, and the reassign and delete actions are absent.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as a view-only user
 </t>
         </is>
       </c>
@@ -9548,7 +9543,7 @@
 2. The rest of the app works normally for the role.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as a user without the Schedule permission
 </t>
         </is>
       </c>
@@ -9605,7 +9600,7 @@
 5. Modal fields are editable and save.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as an edit-without-delete user
 </t>
         </is>
       </c>
@@ -9659,7 +9654,7 @@
 3. No path exists to remove shifts or events - while creating and modifying still work.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as an edit-without-delete user
 </t>
         </is>
       </c>
@@ -9714,7 +9709,7 @@
 4. Undo toasts appear (restore the items via Undo to clean up).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as a delete-capable user
 </t>
         </is>
       </c>
@@ -9767,7 +9762,7 @@
 3. The three tiers can be enabled in dependency order, so each higher level always includes the ones beneath it (Delete includes Edit, and Edit includes View).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9821,7 +9816,7 @@
 3. New work orders cannot be dragged on - the WO list is simply not visible.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§14.2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
       </c>
@@ -9873,7 +9868,7 @@
 2. 'My Shifts' exists only as an optional personal convenience filter (off by default), not a security boundary.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as a view-only technician
 </t>
         </is>
       </c>
@@ -9925,7 +9920,7 @@
 2. The staff member without a department does not appear as a row.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§14.4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -9976,7 +9971,7 @@
 2. The Time-Clock-OFF staff member cannot - the ability is controlled by the staff-record setting, not by the Schedule permission tier.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§14.4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as each of the two staff members
 </t>
         </is>
       </c>
@@ -10030,7 +10025,7 @@
 3. This extends the sidebar behavior (the work order list and drill-down are hidden) to the work-order data surfaced on the shifts themselves.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§14.2), read on 17 August 2026. The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
       </c>
@@ -10088,7 +10083,7 @@
 4. The user from step 5 can drag a work order onto the grid and create a shift.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14.1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as a holder of each permission level
 </t>
         </is>
       </c>
@@ -10142,7 +10137,7 @@
 4. No content becomes permanently unreachable and nothing errors.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and stories SV-8686 and SV-8687 and the Schedule specification version 30 (§11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -10196,7 +10191,7 @@
 3. Search stays responsive on the long list.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the Schedule specification version 30 (§11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -10250,7 +10245,7 @@
 3. Tooltips and modals stay responsive.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8686 and the Schedule specification version 30 (§11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -10304,7 +10299,7 @@
 3. The end date follows the normal daily distribution - no extra day is added for the closure.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and stories SV-8691 and SV-9238 (shop closures are not skipped by the spread; weekends only) and the Schedule specification version 30 (§12, §4.5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - waiting on the product owner's answer, and the shop-closure setting does not exist in the build
 </t>
         </is>
       </c>
@@ -10355,7 +10350,7 @@
 2. Nothing forces them to match - no error, no auto-correction (progress is driven by clocked-in time).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5, §12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -10407,7 +10402,7 @@
 2. No shift in the series silently moves an hour earlier or later after the change date.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5), read on 17 August 2026, which covers spreading work across days. That specification says nothing about clock changes or daylight saving - those words do not appear in it at all - so the point above comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -10462,7 +10457,7 @@
 4. Switching back to light mode restores the normal look with nothing stuck in dark colours.
 ---
 This is the expected behaviour as per story SV-8700 (dark theme), read on 17 August 2026, story SV-8698 (overtime and conflict cues are not colour-only), read on 17 August 2026, and the Schedule specification version 30 (§11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -10525,7 +10520,7 @@
 5. Switching back to light mode at step 9 works the same way and is remembered in the same way.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, its story SV-8700 (requirement 5), read on 17 August 2026, and the Schedule specification version 30 (§11 Dark theme), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -10582,7 +10577,7 @@
 4. Nothing you check is unreadable, and no text or icon disappears into the background.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, its story SV-8700 (requirement 5), read on 17 August 2026, and the Schedule specification version 30 (§11 Dark theme), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -10637,7 +10632,7 @@
 3. Your choice only stops applying when the window is resized back across the 960 pixel mark; at that point the page goes back to deciding for itself whether the panel is shown.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and its story SV-9243 (left-panel collapse toggle) and the Schedule specification version 30 (§5.3 Panel collapse, Narrow viewports), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - the panel button does not exist in this build
 </t>
         </is>
       </c>
@@ -10690,7 +10685,7 @@
 3. Their details open normally and are editable/deletable like any other entry.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - cannot be run now - it needs shifts noted BEFORE the release, and the release is already deployed
 </t>
         </is>
       </c>
@@ -10743,7 +10738,7 @@
 3. Work orders with a single shift are unaffected.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - the Dashboard section this test needs does not exist in the build
 </t>
         </is>
       </c>
@@ -10796,7 +10791,7 @@
 3. It also appears in the Dashboard's schedule section for that day.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - work order creation offers no appointment in the build
 </t>
         </is>
       </c>
@@ -10850,7 +10845,7 @@
 3. Note for the tester: before the rewrite such a shift showed on EVERY location the technician was enrolled at - showing it only on the work order's location is the intended new behaviour, do not report the disappearance from other locations as a bug.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -10905,7 +10900,7 @@
 4. A work order with no priority set simply shows none (it is not treated as an error).
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8687 and the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026. No numbered requirement in the Schedule specification version 30 covers this point.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - the Priority field this test needs does not exist in the build
 </t>
         </is>
       </c>
@@ -10960,7 +10955,7 @@
 4. Each refusal is a clean 403 response - never a server error.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14), read on 17 August 2026, which sets the three permission levels. That specification does not describe what the server returns when a request is refused, so the refusal responses above come from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs three separate sign-ins, one per permission level
 </t>
         </is>
       </c>
@@ -11015,7 +11010,7 @@
 4. Refused calls leave no partial series behind.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and story SV-8691 and the Schedule specification version 30 (§4.5), read on 17 August 2026, with the specific limits above taken from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/tech-plan-2026-07-29/TechPlan-Schedule-Module-Rewrite.md, read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -11068,7 +11063,7 @@
 3. Both calls still succeed (HTTP 200) - lacking Work Orders: View limits the content, it does not break the schedule read.
 ---
 This is the expected behaviour as per epic SV-8685, read on 17 August 2026, and the Schedule specification version 30 (§14), read on 17 August 2026. The behaviour above follows a later product owner decision dated 22 July 2026 rather than that specification's wording, and that decision is recorded in Branko's answers, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/schedule/branko-answers-2026-07-31/answers-ingested.md, read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+AUTOMATION: HOLD - needs a second sign-in as a user who cannot see work orders
 </t>
         </is>
       </c>
